--- a/backend/exports/master_export.xlsx
+++ b/backend/exports/master_export.xlsx
@@ -16,9 +16,9 @@
     <sheet name="Addon" sheetId="11" r:id="rId11"/>
     <sheet name="Occasion" sheetId="12" r:id="rId12"/>
     <sheet name="Order" sheetId="13" r:id="rId13"/>
-    <sheet name="Payment" sheetId="14" r:id="rId14"/>
-    <sheet name="Review" sheetId="15" r:id="rId15"/>
-    <sheet name="InShopOrder" sheetId="16" r:id="rId16"/>
+    <sheet name="InShopOrder" sheetId="14" r:id="rId14"/>
+    <sheet name="Payment" sheetId="15" r:id="rId15"/>
+    <sheet name="Review" sheetId="16" r:id="rId16"/>
     <sheet name="GoogleReview" sheetId="17" r:id="rId17"/>
   </sheets>
 </workbook>
@@ -521,13 +521,13 @@
         <v>true</v>
       </c>
       <c r="I2" t="str">
-        <v>2026-08-02T12:48:03.519Z</v>
+        <v>2026-08-02T18:25:21.980Z</v>
       </c>
       <c r="J2" t="str">
         <v>2026-04-23T06:52:27.990Z</v>
       </c>
       <c r="K2" t="str">
-        <v>2026-08-02T12:48:03.526Z</v>
+        <v>2026-08-02T18:25:21.983Z</v>
       </c>
       <c r="L2" t="str">
         <v>[]</v>
@@ -551,7 +551,7 @@
         <v>["6a63a983a800f3907b955c53"]</v>
       </c>
       <c r="S2" t="str">
-        <v>2026-08-02T17:46:49.010Z</v>
+        <v>2026-08-02T18:31:00.879Z</v>
       </c>
     </row>
     <row r="3">
@@ -604,7 +604,7 @@
         <v>[]</v>
       </c>
       <c r="S3" t="str">
-        <v>2026-08-02T17:46:49.010Z</v>
+        <v>2026-08-02T18:31:00.879Z</v>
       </c>
     </row>
     <row r="4">
@@ -657,7 +657,7 @@
         <v>[]</v>
       </c>
       <c r="S4" t="str">
-        <v>2026-08-02T17:46:49.010Z</v>
+        <v>2026-08-02T18:31:00.879Z</v>
       </c>
     </row>
   </sheetData>
@@ -761,7 +761,7 @@
         <v>2026-08-02T11:11:02.596Z</v>
       </c>
       <c r="K2" t="str">
-        <v>2026-08-02T17:46:51.167Z</v>
+        <v>2026-08-02T18:31:02.738Z</v>
       </c>
     </row>
     <row r="3">
@@ -796,7 +796,7 @@
         <v>2026-08-02T11:15:41.649Z</v>
       </c>
       <c r="K3" t="str">
-        <v>2026-08-02T17:46:51.167Z</v>
+        <v>2026-08-02T18:31:02.738Z</v>
       </c>
     </row>
     <row r="4">
@@ -831,7 +831,7 @@
         <v>2026-08-02T11:16:18.261Z</v>
       </c>
       <c r="K4" t="str">
-        <v>2026-08-02T17:46:51.167Z</v>
+        <v>2026-08-02T18:31:02.738Z</v>
       </c>
     </row>
   </sheetData>
@@ -911,7 +911,7 @@
         <v>2026-08-02T11:44:43.854Z</v>
       </c>
       <c r="I2" t="str">
-        <v>2026-08-02T17:46:51.233Z</v>
+        <v>2026-08-02T18:31:02.822Z</v>
       </c>
     </row>
     <row r="3">
@@ -940,7 +940,7 @@
         <v>2026-08-02T11:45:37.177Z</v>
       </c>
       <c r="I3" t="str">
-        <v>2026-08-02T17:46:51.233Z</v>
+        <v>2026-08-02T18:31:02.822Z</v>
       </c>
     </row>
     <row r="4">
@@ -969,7 +969,7 @@
         <v>2026-08-02T11:45:18.169Z</v>
       </c>
       <c r="I4" t="str">
-        <v>2026-08-02T17:46:51.233Z</v>
+        <v>2026-08-02T18:31:02.822Z</v>
       </c>
     </row>
     <row r="5">
@@ -998,7 +998,7 @@
         <v>2026-08-02T11:45:03.112Z</v>
       </c>
       <c r="I5" t="str">
-        <v>2026-08-02T17:46:51.233Z</v>
+        <v>2026-08-02T18:31:02.822Z</v>
       </c>
     </row>
     <row r="6">
@@ -1027,7 +1027,7 @@
         <v>2026-08-02T11:24:43.615Z</v>
       </c>
       <c r="I6" t="str">
-        <v>2026-08-02T17:46:51.233Z</v>
+        <v>2026-08-02T18:31:02.822Z</v>
       </c>
     </row>
   </sheetData>
@@ -1049,6 +1049,471 @@
 
 <file path=xl/worksheets/sheet14.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
+  <dimension ref="A1:AI4"/>
+  <cols>
+    <col min="1" max="1" width="26.83203125" customWidth="1"/>
+    <col min="2" max="2" width="10.83203125" customWidth="1"/>
+    <col min="3" max="3" width="26.83203125" customWidth="1"/>
+    <col min="4" max="4" width="15.83203125" customWidth="1"/>
+    <col min="5" max="5" width="26.83203125" customWidth="1"/>
+    <col min="6" max="6" width="26.83203125" customWidth="1"/>
+    <col min="7" max="7" width="16.83203125" customWidth="1"/>
+    <col min="8" max="8" width="7.83203125" customWidth="1"/>
+    <col min="9" max="9" width="12.83203125" customWidth="1"/>
+    <col min="10" max="10" width="17.83203125" customWidth="1"/>
+    <col min="11" max="11" width="13.83203125" customWidth="1"/>
+    <col min="12" max="12" width="52.83203125" customWidth="1"/>
+    <col min="13" max="13" width="10.83203125" customWidth="1"/>
+    <col min="14" max="14" width="10.83203125" customWidth="1"/>
+    <col min="15" max="15" width="16.83203125" customWidth="1"/>
+    <col min="16" max="16" width="16.83203125" customWidth="1"/>
+    <col min="17" max="17" width="5.83203125" customWidth="1"/>
+    <col min="18" max="18" width="7.83203125" customWidth="1"/>
+    <col min="19" max="19" width="15.83203125" customWidth="1"/>
+    <col min="20" max="20" width="15.83203125" customWidth="1"/>
+    <col min="21" max="21" width="13.83203125" customWidth="1"/>
+    <col min="22" max="22" width="15.83203125" customWidth="1"/>
+    <col min="23" max="23" width="18.83203125" customWidth="1"/>
+    <col min="24" max="24" width="15.83203125" customWidth="1"/>
+    <col min="25" max="25" width="17.83203125" customWidth="1"/>
+    <col min="26" max="26" width="20.83203125" customWidth="1"/>
+    <col min="27" max="27" width="14.83203125" customWidth="1"/>
+    <col min="28" max="28" width="17.83203125" customWidth="1"/>
+    <col min="29" max="29" width="26.83203125" customWidth="1"/>
+    <col min="30" max="30" width="26.83203125" customWidth="1"/>
+    <col min="31" max="31" width="18.83203125" customWidth="1"/>
+    <col min="32" max="32" width="18.83203125" customWidth="1"/>
+    <col min="33" max="33" width="26.83203125" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1">
+      <c r="A1" t="str">
+        <v>_id</v>
+      </c>
+      <c r="B1" t="str">
+        <v>reviewed</v>
+      </c>
+      <c r="C1" t="str">
+        <v>userId</v>
+      </c>
+      <c r="D1" t="str">
+        <v>isInShopOrder</v>
+      </c>
+      <c r="E1" t="str">
+        <v>createdByStaff</v>
+      </c>
+      <c r="F1" t="str">
+        <v>deliveryDate</v>
+      </c>
+      <c r="G1" t="str">
+        <v>deliverySlot</v>
+      </c>
+      <c r="H1" t="str">
+        <v>notes</v>
+      </c>
+      <c r="I1" t="str">
+        <v>kotPrinted</v>
+      </c>
+      <c r="J1" t="str">
+        <v>kotReprintCount</v>
+      </c>
+      <c r="K1" t="str">
+        <v>invoiceSent</v>
+      </c>
+      <c r="L1" t="str">
+        <v>items</v>
+      </c>
+      <c r="M1" t="str">
+        <v>subtotal</v>
+      </c>
+      <c r="N1" t="str">
+        <v>discount</v>
+      </c>
+      <c r="O1" t="str">
+        <v>deliveryCharge</v>
+      </c>
+      <c r="P1" t="str">
+        <v>convenienceFee</v>
+      </c>
+      <c r="Q1" t="str">
+        <v>gst</v>
+      </c>
+      <c r="R1" t="str">
+        <v>total</v>
+      </c>
+      <c r="S1" t="str">
+        <v>paymentMethod</v>
+      </c>
+      <c r="T1" t="str">
+        <v>paymentStatus</v>
+      </c>
+      <c r="U1" t="str">
+        <v>orderStatus</v>
+      </c>
+      <c r="V1" t="str">
+        <v>kitchenStatus</v>
+      </c>
+      <c r="W1" t="str">
+        <v>address_fullName</v>
+      </c>
+      <c r="X1" t="str">
+        <v>address_phone</v>
+      </c>
+      <c r="Y1" t="str">
+        <v>address_houseNo</v>
+      </c>
+      <c r="Z1" t="str">
+        <v>address_street</v>
+      </c>
+      <c r="AA1" t="str">
+        <v>address_city</v>
+      </c>
+      <c r="AB1" t="str">
+        <v>address_pincode</v>
+      </c>
+      <c r="AC1" t="str">
+        <v>createdAt</v>
+      </c>
+      <c r="AD1" t="str">
+        <v>updatedAt</v>
+      </c>
+      <c r="AE1" t="str">
+        <v>orderNumber</v>
+      </c>
+      <c r="AF1" t="str">
+        <v>trackingCode</v>
+      </c>
+      <c r="AG1" t="str">
+        <v>exportedAt</v>
+      </c>
+      <c r="AH1" t="str">
+        <v>kotPrintedAt</v>
+      </c>
+      <c r="AI1" t="str">
+        <v>invoiceNumber</v>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" t="str">
+        <v>6a6f8825bb09e37dbf7a0d64</v>
+      </c>
+      <c r="B2" t="str">
+        <v>false</v>
+      </c>
+      <c r="C2" t="str">
+        <v>6a6f79141549a52dedd88c3d</v>
+      </c>
+      <c r="D2" t="str">
+        <v>true</v>
+      </c>
+      <c r="E2" t="str">
+        <v>6a6f79141549a52dedd88c3d</v>
+      </c>
+      <c r="F2" t="str">
+        <v>2026-08-02T18:10:45.783Z</v>
+      </c>
+      <c r="G2" t="str">
+        <v>In-Shop Pickup</v>
+      </c>
+      <c r="H2" t="str">
+        <v/>
+      </c>
+      <c r="I2" t="str">
+        <v>false</v>
+      </c>
+      <c r="J2" t="str">
+        <v>0</v>
+      </c>
+      <c r="K2" t="str">
+        <v>false</v>
+      </c>
+      <c r="L2" t="str">
+        <v>[{"productId":"6a5f23fa0d6ff66fbbaceaae","name":"Choco chip cookies","qty":1,"price":150,"originalPrice":150,"discountAmount":0,"image":"https://res.cloudinary.com/djkfvoxpx/image/upload/v1784833569/desserts/xftlmv4pxfrjz4opepyd.png","selectedFlavor":null,"selectedWeight":null,"selectedColor":null,"category":"desserts","isCustomCake":false,"customDetails":{"lessSugar":false,"eggless":false},"_id":"6a6f8825bb09e37dbf7a0d65","addons":[],"sku":"CHO-CAK-ST-KG-260802-001"},{"productId":"6a5dbb4ece6fdf5b656f0722","name":"Brownie duo box","qty":1,"price":240,"originalPrice":240,"discountAmount":0,"image":"https://res.cloudinary.com/djkfvoxpx/image/upload/v1784527692/desserts/c18d4xpzw8ivjerkzkqj.png","selectedFlavor":null,"selectedWeight":null,"selectedColor":null,"category":"desserts","isCustomCake":false,"customDetails":{"lessSugar":false,"eggless":false},"_id":"6a6f8825bb09e37dbf7a0d66","addons":[],"sku":"BRO-CAK-ST-KG-260802-002"},{"productId":"6a5cd9216ef5380c1f6e3b7a","name":"Salted caramel","qty":1,"price":120,"originalPrice":120,"discountAmount":0,"image":"https://res.cloudinary.com/djkfvoxpx/image/upload/v1784469792/desserts/hnkkrj6r4rb2psu50ttp.png","selectedFlavor":null,"selectedWeight":null,"selectedColor":null,"category":"desserts","isCustomCake":false,"customDetails":{"lessSugar":false,"eggless":false},"_id":"6a6f8825bb09e37dbf7a0d67","addons":[],"sku":"SAL-CAK-ST-KG-260802-003"}]</v>
+      </c>
+      <c r="M2" t="str">
+        <v>510</v>
+      </c>
+      <c r="N2" t="str">
+        <v>0</v>
+      </c>
+      <c r="O2" t="str">
+        <v>0</v>
+      </c>
+      <c r="P2" t="str">
+        <v>0</v>
+      </c>
+      <c r="Q2" t="str">
+        <v>92</v>
+      </c>
+      <c r="R2" t="str">
+        <v>602</v>
+      </c>
+      <c r="S2" t="str">
+        <v>IN_SHOP</v>
+      </c>
+      <c r="T2" t="str">
+        <v>paid</v>
+      </c>
+      <c r="U2" t="str">
+        <v>delivered</v>
+      </c>
+      <c r="V2" t="str">
+        <v>pending</v>
+      </c>
+      <c r="W2" t="str">
+        <v>ffh</v>
+      </c>
+      <c r="X2" t="str">
+        <v>2728454454</v>
+      </c>
+      <c r="Y2" t="str">
+        <v>In-Shop</v>
+      </c>
+      <c r="Z2" t="str">
+        <v>The Chocolate Mine</v>
+      </c>
+      <c r="AA2" t="str">
+        <v>Coimbatore</v>
+      </c>
+      <c r="AB2" t="str">
+        <v>641001</v>
+      </c>
+      <c r="AC2" t="str">
+        <v>2026-08-02T18:10:45.820Z</v>
+      </c>
+      <c r="AD2" t="str">
+        <v>2026-08-02T18:10:45.820Z</v>
+      </c>
+      <c r="AE2" t="str">
+        <v>INSHOP-2026-0001</v>
+      </c>
+      <c r="AF2" t="str">
+        <v>INSHOP-2026-0001</v>
+      </c>
+      <c r="AG2" t="str">
+        <v>2026-08-02T18:31:03.031Z</v>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="str">
+        <v>6a6f88f9bb09e37dbf7a0d81</v>
+      </c>
+      <c r="B3" t="str">
+        <v>false</v>
+      </c>
+      <c r="C3" t="str">
+        <v>6a6f79141549a52dedd88c3d</v>
+      </c>
+      <c r="D3" t="str">
+        <v>true</v>
+      </c>
+      <c r="E3" t="str">
+        <v>6a6f79141549a52dedd88c3d</v>
+      </c>
+      <c r="F3" t="str">
+        <v>2026-08-02T18:14:17.262Z</v>
+      </c>
+      <c r="G3" t="str">
+        <v>In-Shop Pickup</v>
+      </c>
+      <c r="H3" t="str">
+        <v/>
+      </c>
+      <c r="I3" t="str">
+        <v>true</v>
+      </c>
+      <c r="J3" t="str">
+        <v>1</v>
+      </c>
+      <c r="K3" t="str">
+        <v>false</v>
+      </c>
+      <c r="L3" t="str">
+        <v>[{"productId":"6a5f9f8e7ffebf50deaafde3","name":"Cinderella","qty":1,"price":4370,"originalPrice":4370,"discountAmount":0,"image":"https://res.cloudinary.com/djkfvoxpx/image/upload/v1784651690/custom-cakes/s4d8hwfvwmtytxexqayd.png","selectedFlavor":"Choco Oreo","selectedWeight":"3 Kg","selectedColor":"Blue","category":"Custom Birthday Cakes","isCustomCake":true,"customDetails":{"lessSugar":false,"eggless":false},"_id":"6a6f88f9bb09e37dbf7a0d82","addons":[],"sku":"CIN-CAK-CH-3-260802-001"}]</v>
+      </c>
+      <c r="M3" t="str">
+        <v>4370</v>
+      </c>
+      <c r="N3" t="str">
+        <v>0</v>
+      </c>
+      <c r="O3" t="str">
+        <v>0</v>
+      </c>
+      <c r="P3" t="str">
+        <v>0</v>
+      </c>
+      <c r="Q3" t="str">
+        <v>787</v>
+      </c>
+      <c r="R3" t="str">
+        <v>5157</v>
+      </c>
+      <c r="S3" t="str">
+        <v>IN_SHOP</v>
+      </c>
+      <c r="T3" t="str">
+        <v>paid</v>
+      </c>
+      <c r="U3" t="str">
+        <v>delivered</v>
+      </c>
+      <c r="V3" t="str">
+        <v>pending</v>
+      </c>
+      <c r="W3" t="str">
+        <v>68</v>
+      </c>
+      <c r="X3" t="str">
+        <v>8796979669</v>
+      </c>
+      <c r="Y3" t="str">
+        <v>In-Shop</v>
+      </c>
+      <c r="Z3" t="str">
+        <v>The Chocolate Mine</v>
+      </c>
+      <c r="AA3" t="str">
+        <v>Coimbatore</v>
+      </c>
+      <c r="AB3" t="str">
+        <v>641001</v>
+      </c>
+      <c r="AC3" t="str">
+        <v>2026-08-02T18:14:17.272Z</v>
+      </c>
+      <c r="AD3" t="str">
+        <v>2026-08-02T18:21:57.650Z</v>
+      </c>
+      <c r="AE3" t="str">
+        <v>INSHOP-2026-0002</v>
+      </c>
+      <c r="AF3" t="str">
+        <v>INSHOP-2026-0002</v>
+      </c>
+      <c r="AG3" t="str">
+        <v>2026-08-02T18:31:03.031Z</v>
+      </c>
+      <c r="AH3" t="str">
+        <v>2026-08-02T18:21:57.647Z</v>
+      </c>
+      <c r="AI3" t="str">
+        <v>INV-1785694875565</v>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="str">
+        <v>6a6f8ca5888527fd1c2729d7</v>
+      </c>
+      <c r="B4" t="str">
+        <v>false</v>
+      </c>
+      <c r="C4" t="str">
+        <v>6a6f79141549a52dedd88c3d</v>
+      </c>
+      <c r="D4" t="str">
+        <v>true</v>
+      </c>
+      <c r="E4" t="str">
+        <v>6a6f79141549a52dedd88c3d</v>
+      </c>
+      <c r="F4" t="str">
+        <v>2026-08-02T18:29:57.614Z</v>
+      </c>
+      <c r="G4" t="str">
+        <v>In-Shop Pickup</v>
+      </c>
+      <c r="H4" t="str">
+        <v/>
+      </c>
+      <c r="I4" t="str">
+        <v>false</v>
+      </c>
+      <c r="J4" t="str">
+        <v>0</v>
+      </c>
+      <c r="K4" t="str">
+        <v>false</v>
+      </c>
+      <c r="L4" t="str">
+        <v>[{"productId":"6a68f96ea840ebab4394830f","name":"Boss Baby","qty":1,"price":3020,"originalPrice":3020,"discountAmount":0,"image":"https://res.cloudinary.com/djkfvoxpx/image/upload/v1785264508/custom-cakes/d23mblzbabyjokcp0b1x.png","selectedFlavor":"Choco Biscoff","selectedWeight":"1.5 Kg","selectedColor":"White","category":"Custom Birthday Cakes","isCustomCake":true,"customDetails":{"lessSugar":false,"eggless":false},"_id":"6a6f8ca5888527fd1c2729d8","addons":[],"sku":"BOS-CAK-CH-15-260802-001"}]</v>
+      </c>
+      <c r="M4" t="str">
+        <v>3020</v>
+      </c>
+      <c r="N4" t="str">
+        <v>0</v>
+      </c>
+      <c r="O4" t="str">
+        <v>0</v>
+      </c>
+      <c r="P4" t="str">
+        <v>76</v>
+      </c>
+      <c r="Q4" t="str">
+        <v>0</v>
+      </c>
+      <c r="R4" t="str">
+        <v>3096</v>
+      </c>
+      <c r="S4" t="str">
+        <v>IN_SHOP</v>
+      </c>
+      <c r="T4" t="str">
+        <v>paid</v>
+      </c>
+      <c r="U4" t="str">
+        <v>delivered</v>
+      </c>
+      <c r="V4" t="str">
+        <v>pending</v>
+      </c>
+      <c r="W4" t="str">
+        <v>eee</v>
+      </c>
+      <c r="X4" t="str">
+        <v>3432344355</v>
+      </c>
+      <c r="Y4" t="str">
+        <v>In-Shop</v>
+      </c>
+      <c r="Z4" t="str">
+        <v>The Chocolate Mine</v>
+      </c>
+      <c r="AA4" t="str">
+        <v>Coimbatore</v>
+      </c>
+      <c r="AB4" t="str">
+        <v>641001</v>
+      </c>
+      <c r="AC4" t="str">
+        <v>2026-08-02T18:29:57.642Z</v>
+      </c>
+      <c r="AD4" t="str">
+        <v>2026-08-02T18:30:08.965Z</v>
+      </c>
+      <c r="AE4" t="str">
+        <v>INSHOP-2026-0003</v>
+      </c>
+      <c r="AF4" t="str">
+        <v>INSHOP-2026-0003</v>
+      </c>
+      <c r="AG4" t="str">
+        <v>2026-08-02T18:31:03.031Z</v>
+      </c>
+      <c r="AI4" t="str">
+        <v>INV-1785695408962</v>
+      </c>
+    </row>
+  </sheetData>
+  <ignoredErrors>
+    <ignoredError numberStoredAsText="1" sqref="A1:AI4"/>
+  </ignoredErrors>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet15.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
   <dimension ref="A1:A2"/>
   <sheetData/>
   <ignoredErrors>
@@ -1057,7 +1522,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet15.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet16.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
   <dimension ref="A1:L10"/>
   <cols>
@@ -1148,7 +1613,7 @@
         <v>2026-04-25T05:16:45.245Z</v>
       </c>
       <c r="L2" t="str">
-        <v>2026-08-02T17:46:51.577Z</v>
+        <v>2026-08-02T18:31:03.204Z</v>
       </c>
     </row>
     <row r="3">
@@ -1186,7 +1651,7 @@
         <v>2026-04-26T13:01:08.188Z</v>
       </c>
       <c r="L3" t="str">
-        <v>2026-08-02T17:46:51.577Z</v>
+        <v>2026-08-02T18:31:03.204Z</v>
       </c>
     </row>
     <row r="4">
@@ -1224,7 +1689,7 @@
         <v>2026-04-26T15:36:57.443Z</v>
       </c>
       <c r="L4" t="str">
-        <v>2026-08-02T17:46:51.577Z</v>
+        <v>2026-08-02T18:31:03.204Z</v>
       </c>
     </row>
     <row r="5">
@@ -1262,7 +1727,7 @@
         <v>2026-04-28T15:26:52.023Z</v>
       </c>
       <c r="L5" t="str">
-        <v>2026-08-02T17:46:51.577Z</v>
+        <v>2026-08-02T18:31:03.204Z</v>
       </c>
     </row>
     <row r="6">
@@ -1300,7 +1765,7 @@
         <v>2026-06-07T14:24:10.694Z</v>
       </c>
       <c r="L6" t="str">
-        <v>2026-08-02T17:46:51.577Z</v>
+        <v>2026-08-02T18:31:03.204Z</v>
       </c>
     </row>
     <row r="7">
@@ -1338,7 +1803,7 @@
         <v>2026-06-10T17:55:28.556Z</v>
       </c>
       <c r="L7" t="str">
-        <v>2026-08-02T17:46:51.577Z</v>
+        <v>2026-08-02T18:31:03.204Z</v>
       </c>
     </row>
     <row r="8">
@@ -1376,7 +1841,7 @@
         <v>2026-06-13T16:20:41.698Z</v>
       </c>
       <c r="L8" t="str">
-        <v>2026-08-02T17:46:51.577Z</v>
+        <v>2026-08-02T18:31:03.204Z</v>
       </c>
     </row>
     <row r="9">
@@ -1414,7 +1879,7 @@
         <v>2026-06-13T16:25:47.423Z</v>
       </c>
       <c r="L9" t="str">
-        <v>2026-08-02T17:46:51.577Z</v>
+        <v>2026-08-02T18:31:03.204Z</v>
       </c>
     </row>
     <row r="10">
@@ -1452,22 +1917,12 @@
         <v>2026-07-11T10:23:53.937Z</v>
       </c>
       <c r="L10" t="str">
-        <v>2026-08-02T17:46:51.577Z</v>
+        <v>2026-08-02T18:31:03.204Z</v>
       </c>
     </row>
   </sheetData>
   <ignoredErrors>
     <ignoredError numberStoredAsText="1" sqref="A1:L10"/>
-  </ignoredErrors>
-</worksheet>
-</file>
-
-<file path=xl/worksheets/sheet16.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:A2"/>
-  <sheetData/>
-  <ignoredErrors>
-    <ignoredError numberStoredAsText="1" sqref="A1:A2"/>
   </ignoredErrors>
 </worksheet>
 </file>
@@ -1619,7 +2074,7 @@
         <v>2026-03-05T10:51:19.227Z</v>
       </c>
       <c r="T2" t="str">
-        <v>2026-08-02T17:46:51.883Z</v>
+        <v>2026-08-02T18:31:03.338Z</v>
       </c>
     </row>
     <row r="3" xml:space="preserve">
@@ -1683,7 +2138,7 @@
         <v>2026-01-31T07:51:47.756Z</v>
       </c>
       <c r="T3" t="str">
-        <v>2026-08-02T17:46:51.883Z</v>
+        <v>2026-08-02T18:31:03.339Z</v>
       </c>
     </row>
     <row r="4">
@@ -1745,7 +2200,7 @@
         <v>2026-01-16T16:33:33.279Z</v>
       </c>
       <c r="T4" t="str">
-        <v>2026-08-02T17:46:51.883Z</v>
+        <v>2026-08-02T18:31:03.339Z</v>
       </c>
     </row>
     <row r="5">
@@ -1801,7 +2256,7 @@
         <v>2026-06-12T17:08:32.112Z</v>
       </c>
       <c r="T5" t="str">
-        <v>2026-08-02T17:46:51.884Z</v>
+        <v>2026-08-02T18:31:03.339Z</v>
       </c>
     </row>
     <row r="6">
@@ -1863,7 +2318,7 @@
         <v>2026-02-25T11:00:52.464Z</v>
       </c>
       <c r="T6" t="str">
-        <v>2026-08-02T17:46:51.884Z</v>
+        <v>2026-08-02T18:31:03.339Z</v>
       </c>
     </row>
     <row r="7">
@@ -1904,7 +2359,7 @@
         <v>apify</v>
       </c>
       <c r="M7" t="str">
-        <v>2026-08-02T17:46:41.553Z</v>
+        <v>2026-08-02T18:30:53.311Z</v>
       </c>
       <c r="N7" t="str">
         <v>[]</v>
@@ -1913,19 +2368,19 @@
         <v>I ordered fresh mango cake and the cake was delicious and subtle making me want to eat more and I needed the cake in a very short span and they delivered it soon and made the moment memorable</v>
       </c>
       <c r="P7" t="str">
-        <v>2026-08-02T17:46:41.553Z</v>
+        <v>2026-08-02T18:30:53.311Z</v>
       </c>
       <c r="Q7" t="str">
-        <v>2026-08-02T17:46:47.273Z</v>
+        <v>2026-08-02T18:30:59.138Z</v>
       </c>
       <c r="R7" t="str">
         <v>["https://lh3.googleusercontent.com/grass-cs/ACvplmO_pqUM6Inbd4_tYNoXGkmjVXuMvqW1k6_n3WKo5GFjIU-jy6NJXw54DGSD41LE-vcpvHH45HW9eD-aeGFYOmHWhIvTyxBBuqd6GwDjK2xkDrER4qts8deU47gt4tI5Du1u0drm0TLOEtN-=w600-h450-p-k-no"]</v>
       </c>
       <c r="S7" t="str">
-        <v>2026-05-04T17:46:31.926Z</v>
+        <v>2026-05-04T18:30:42.833Z</v>
       </c>
       <c r="T7" t="str">
-        <v>2026-08-02T17:46:51.884Z</v>
+        <v>2026-08-02T18:31:03.339Z</v>
       </c>
     </row>
     <row r="8">
@@ -1987,7 +2442,7 @@
         <v>2026-02-04T08:34:24.383Z</v>
       </c>
       <c r="T8" t="str">
-        <v>2026-08-02T17:46:51.884Z</v>
+        <v>2026-08-02T18:31:03.339Z</v>
       </c>
     </row>
     <row r="9">
@@ -2049,7 +2504,7 @@
         <v>2026-03-05T11:17:24.179Z</v>
       </c>
       <c r="T9" t="str">
-        <v>2026-08-02T17:46:51.884Z</v>
+        <v>2026-08-02T18:31:03.339Z</v>
       </c>
     </row>
     <row r="10">
@@ -2105,7 +2560,7 @@
         <v>2026-06-12T17:08:32.573Z</v>
       </c>
       <c r="T10" t="str">
-        <v>2026-08-02T17:46:51.884Z</v>
+        <v>2026-08-02T18:31:03.339Z</v>
       </c>
     </row>
     <row r="11">
@@ -2167,7 +2622,7 @@
         <v>2026-01-28T12:33:53.732Z</v>
       </c>
       <c r="T11" t="str">
-        <v>2026-08-02T17:46:51.884Z</v>
+        <v>2026-08-02T18:31:03.339Z</v>
       </c>
     </row>
     <row r="12">
@@ -2208,7 +2663,7 @@
         <v>apify</v>
       </c>
       <c r="M12" t="str">
-        <v>2026-08-02T17:46:41.553Z</v>
+        <v>2026-08-02T18:30:53.311Z</v>
       </c>
       <c r="N12" t="str">
         <v>[]</v>
@@ -2217,19 +2672,19 @@
         <v>Cake serious ah romba super ah irrunthuchu and really worth for Money and more over I really cannot forget how it was so perfectly baked and the softness is it was top norch and thanks for making my birthday so special with your wonderful cakes</v>
       </c>
       <c r="P12" t="str">
-        <v>2026-08-02T17:46:41.553Z</v>
+        <v>2026-08-02T18:30:53.311Z</v>
       </c>
       <c r="Q12" t="str">
-        <v>2026-08-02T17:46:44.815Z</v>
+        <v>2026-08-02T18:30:56.574Z</v>
       </c>
       <c r="R12" t="str">
         <v>["https://lh3.googleusercontent.com/grass-cs/ACvplmNZM8KFdpuGqaUu50FgOBu6H6AhkveDzw9G98Qnxq9ZePYgdpngx2-5qTiqwBOpbWY7II_QN2p2lB-Ja9KLC6YEC_EqkQ6UfIpB6KwY6A-cCs2quV9lfvWgy55NXDgG1jsUcCr9BsDxGKf2=w600-h450-p-k-no"]</v>
       </c>
       <c r="S12" t="str">
-        <v>2026-07-03T17:46:22.868Z</v>
+        <v>2026-07-03T18:30:33.189Z</v>
       </c>
       <c r="T12" t="str">
-        <v>2026-08-02T17:46:51.884Z</v>
+        <v>2026-08-02T18:31:03.339Z</v>
       </c>
     </row>
     <row r="13">
@@ -2270,7 +2725,7 @@
         <v>apify</v>
       </c>
       <c r="M13" t="str">
-        <v>2026-08-02T17:46:41.553Z</v>
+        <v>2026-08-02T18:30:53.311Z</v>
       </c>
       <c r="N13" t="str">
         <v>[]</v>
@@ -2279,19 +2734,19 @@
         <v>Thank you for making our special day even more special with your wonderful cake. It was absolutely fabulous, and everyone in my family loved it. The birthday girl especially loved it a lot We truly enjoyed it!</v>
       </c>
       <c r="P13" t="str">
-        <v>2026-08-02T17:46:41.553Z</v>
+        <v>2026-08-02T18:30:53.311Z</v>
       </c>
       <c r="Q13" t="str">
-        <v>2026-08-02T17:46:44.917Z</v>
+        <v>2026-08-02T18:30:56.677Z</v>
       </c>
       <c r="R13" t="str">
         <v>["https://lh3.googleusercontent.com/grass-cs/ACvplmMulUa3xPhcvcWL9C2ZnjqVk3cm3fH6dvtIGWEA5ehkU7hw6DVpeNKZU9MEzz2gk2EFkRuJhbbmc3RtKB_cPs05ROPsIHTpkmMFvA4lISBmkO5-fYepMwk7ucK8ydnw7e_D3-3LSMDxWiRn=w600-h450-p-k-no"]</v>
       </c>
       <c r="S13" t="str">
-        <v>2026-07-03T17:46:25.380Z</v>
+        <v>2026-07-03T18:30:35.419Z</v>
       </c>
       <c r="T13" t="str">
-        <v>2026-08-02T17:46:51.884Z</v>
+        <v>2026-08-02T18:31:03.339Z</v>
       </c>
     </row>
     <row r="14">
@@ -2332,7 +2787,7 @@
         <v>apify</v>
       </c>
       <c r="M14" t="str">
-        <v>2026-08-02T17:46:41.553Z</v>
+        <v>2026-08-02T18:30:53.311Z</v>
       </c>
       <c r="N14" t="str">
         <v>[]</v>
@@ -2341,19 +2796,19 @@
         <v>Good</v>
       </c>
       <c r="P14" t="str">
-        <v>2026-08-02T17:46:41.553Z</v>
+        <v>2026-08-02T18:30:53.311Z</v>
       </c>
       <c r="Q14" t="str">
-        <v>2026-08-02T17:46:45.020Z</v>
+        <v>2026-08-02T18:30:56.783Z</v>
       </c>
       <c r="R14" t="str">
         <v>[]</v>
       </c>
       <c r="S14" t="str">
-        <v>2026-07-03T17:46:25.380Z</v>
+        <v>2026-07-03T18:30:35.419Z</v>
       </c>
       <c r="T14" t="str">
-        <v>2026-08-02T17:46:51.884Z</v>
+        <v>2026-08-02T18:31:03.339Z</v>
       </c>
     </row>
     <row r="15">
@@ -2394,7 +2849,7 @@
         <v>apify</v>
       </c>
       <c r="M15" t="str">
-        <v>2026-08-02T17:46:41.553Z</v>
+        <v>2026-08-02T18:30:53.311Z</v>
       </c>
       <c r="N15" t="str">
         <v>[]</v>
@@ -2403,19 +2858,19 @@
         <v>Ordered a chocolate truffle cake which was delicious &amp; loved by all and customised designed was too cute as expected!</v>
       </c>
       <c r="P15" t="str">
-        <v>2026-08-02T17:46:41.553Z</v>
+        <v>2026-08-02T18:30:53.311Z</v>
       </c>
       <c r="Q15" t="str">
-        <v>2026-08-02T17:46:45.100Z</v>
+        <v>2026-08-02T18:30:56.885Z</v>
       </c>
       <c r="R15" t="str">
         <v>[]</v>
       </c>
       <c r="S15" t="str">
-        <v>2026-07-03T17:46:25.380Z</v>
+        <v>2026-07-03T18:30:35.419Z</v>
       </c>
       <c r="T15" t="str">
-        <v>2026-08-02T17:46:51.884Z</v>
+        <v>2026-08-02T18:31:03.339Z</v>
       </c>
     </row>
     <row r="16" xml:space="preserve">
@@ -2456,7 +2911,7 @@
         <v>apify</v>
       </c>
       <c r="M16" t="str">
-        <v>2026-08-02T17:46:41.553Z</v>
+        <v>2026-08-02T18:30:53.311Z</v>
       </c>
       <c r="N16" t="str">
         <v>[]</v>
@@ -2466,10 +2921,10 @@
 Super tasty without egg.</v>
       </c>
       <c r="P16" t="str">
-        <v>2026-08-02T17:46:41.553Z</v>
+        <v>2026-08-02T18:30:53.311Z</v>
       </c>
       <c r="Q16" t="str">
-        <v>2026-08-02T17:46:45.186Z</v>
+        <v>2026-08-02T18:30:56.988Z</v>
       </c>
       <c r="R16" t="str">
         <v>["https://lh3.googleusercontent.com/grass-cs/ACvplmNh-xicME2ofiwmQH1k9DJDa4nXvzeG7LhMGPnnmlAoMMrsbWdZ1Q11GL9IEWIgvgoJX3UqlW1c49ihHN4UhCT6yT9HCDJr-OQzfTZGOfYwHAmfBf0iXEt0iCCcky5nxz2eEzI45wxHa_yq=w600-h450-p-k-no"]</v>
@@ -2478,7 +2933,7 @@
         <v/>
       </c>
       <c r="T16" t="str">
-        <v>2026-08-02T17:46:51.884Z</v>
+        <v>2026-08-02T18:31:03.339Z</v>
       </c>
     </row>
     <row r="17">
@@ -2519,7 +2974,7 @@
         <v>apify</v>
       </c>
       <c r="M17" t="str">
-        <v>2026-08-02T17:46:41.553Z</v>
+        <v>2026-08-02T18:30:53.311Z</v>
       </c>
       <c r="N17" t="str">
         <v>[]</v>
@@ -2528,19 +2983,19 @@
         <v>Such a good ambience....and taste is too good</v>
       </c>
       <c r="P17" t="str">
-        <v>2026-08-02T17:46:41.553Z</v>
+        <v>2026-08-02T18:30:53.311Z</v>
       </c>
       <c r="Q17" t="str">
-        <v>2026-08-02T17:46:45.236Z</v>
+        <v>2026-08-02T18:30:57.089Z</v>
       </c>
       <c r="R17" t="str">
         <v>["https://lh3.googleusercontent.com/grass-cs/ACvplmP4BFSL8OnHyysD92QO_8srpC0hUvwOd6WmTGT3V1rCZn8dfEWQeMi73l-C1IPBJ50MPjszaxQ-D4wFWoQtEMMxS0CLNZcmeJM7E8YaP5E5Ea-VefkPKZr2Dg6zonQksa7Fhvs7Czdqw8I=w600-h450-p-k-no"]</v>
       </c>
       <c r="S17" t="str">
-        <v>2026-07-03T17:46:25.380Z</v>
+        <v>2026-07-03T18:30:35.419Z</v>
       </c>
       <c r="T17" t="str">
-        <v>2026-08-02T17:46:51.884Z</v>
+        <v>2026-08-02T18:31:03.339Z</v>
       </c>
     </row>
     <row r="18">
@@ -2581,7 +3036,7 @@
         <v>apify</v>
       </c>
       <c r="M18" t="str">
-        <v>2026-08-02T17:46:41.553Z</v>
+        <v>2026-08-02T18:30:53.311Z</v>
       </c>
       <c r="N18" t="str">
         <v>[]</v>
@@ -2590,19 +3045,19 @@
         <v>a month agoRecommended dishesTiramisu, Sizzling Brownie, Black Forest Cake 500 G, Tres Leches RosemilkLike</v>
       </c>
       <c r="P18" t="str">
-        <v>2026-08-02T17:46:41.553Z</v>
+        <v>2026-08-02T18:30:53.311Z</v>
       </c>
       <c r="Q18" t="str">
-        <v>2026-08-02T17:46:45.297Z</v>
+        <v>2026-08-02T18:30:57.192Z</v>
       </c>
       <c r="R18" t="str">
         <v>[]</v>
       </c>
       <c r="S18" t="str">
-        <v>2026-07-03T17:46:25.380Z</v>
+        <v>2026-07-03T18:30:35.419Z</v>
       </c>
       <c r="T18" t="str">
-        <v>2026-08-02T17:46:51.884Z</v>
+        <v>2026-08-02T18:31:03.339Z</v>
       </c>
     </row>
     <row r="19">
@@ -2643,7 +3098,7 @@
         <v>apify</v>
       </c>
       <c r="M19" t="str">
-        <v>2026-08-02T17:46:41.553Z</v>
+        <v>2026-08-02T18:30:53.311Z</v>
       </c>
       <c r="N19" t="str">
         <v>[]</v>
@@ -2652,19 +3107,19 @@
         <v>Taste was very good...</v>
       </c>
       <c r="P19" t="str">
-        <v>2026-08-02T17:46:41.553Z</v>
+        <v>2026-08-02T18:30:53.311Z</v>
       </c>
       <c r="Q19" t="str">
-        <v>2026-08-02T17:46:45.431Z</v>
+        <v>2026-08-02T18:30:57.295Z</v>
       </c>
       <c r="R19" t="str">
         <v>["https://lh3.googleusercontent.com/grass-cs/ACvplmOgtR4VUkuepj9Tp2Lmn6DXdVIFdRY9WHSKLlAh7UVDZSdd68nHtZqEkGDNbU474br7znLKGIZRHMb9BCsFK0FhlR-WRXjfKjI9f4IytETKQZBn77rp0CntQzUBphkowfJoDAvNoza61pT3=w600-h450-p-k-no"]</v>
       </c>
       <c r="S19" t="str">
-        <v>2026-06-03T17:46:25.380Z</v>
+        <v>2026-06-03T18:30:35.419Z</v>
       </c>
       <c r="T19" t="str">
-        <v>2026-08-02T17:46:51.884Z</v>
+        <v>2026-08-02T18:31:03.339Z</v>
       </c>
     </row>
     <row r="20">
@@ -2705,7 +3160,7 @@
         <v>apify</v>
       </c>
       <c r="M20" t="str">
-        <v>2026-08-02T17:46:41.553Z</v>
+        <v>2026-08-02T18:30:53.311Z</v>
       </c>
       <c r="N20" t="str">
         <v>[]</v>
@@ -2714,19 +3169,19 @@
         <v>The hot chocolate was superb, the milkshake and chocolate brownie was so comforting. Love it</v>
       </c>
       <c r="P20" t="str">
-        <v>2026-08-02T17:46:41.553Z</v>
+        <v>2026-08-02T18:30:53.311Z</v>
       </c>
       <c r="Q20" t="str">
-        <v>2026-08-02T17:46:45.532Z</v>
+        <v>2026-08-02T18:30:57.397Z</v>
       </c>
       <c r="R20" t="str">
         <v>[]</v>
       </c>
       <c r="S20" t="str">
-        <v>2026-06-03T17:46:27.751Z</v>
+        <v>2026-06-03T18:30:37.823Z</v>
       </c>
       <c r="T20" t="str">
-        <v>2026-08-02T17:46:51.884Z</v>
+        <v>2026-08-02T18:31:03.339Z</v>
       </c>
     </row>
     <row r="21">
@@ -2767,7 +3222,7 @@
         <v>apify</v>
       </c>
       <c r="M21" t="str">
-        <v>2026-08-02T17:46:41.553Z</v>
+        <v>2026-08-02T18:30:53.311Z</v>
       </c>
       <c r="N21" t="str">
         <v>[]</v>
@@ -2776,19 +3231,19 @@
         <v>Comforting pastry, rich hot chocolate, and the perfect cozy combo. 🤎 Belgium hot chocolate was awesome. …</v>
       </c>
       <c r="P21" t="str">
-        <v>2026-08-02T17:46:41.553Z</v>
+        <v>2026-08-02T18:30:53.311Z</v>
       </c>
       <c r="Q21" t="str">
-        <v>2026-08-02T17:46:45.596Z</v>
+        <v>2026-08-02T18:30:57.462Z</v>
       </c>
       <c r="R21" t="str">
         <v>[]</v>
       </c>
       <c r="S21" t="str">
-        <v>2026-06-03T17:46:27.751Z</v>
+        <v>2026-06-03T18:30:37.823Z</v>
       </c>
       <c r="T21" t="str">
-        <v>2026-08-02T17:46:51.884Z</v>
+        <v>2026-08-02T18:31:03.339Z</v>
       </c>
     </row>
     <row r="22" xml:space="preserve">
@@ -2829,7 +3284,7 @@
         <v>apify</v>
       </c>
       <c r="M22" t="str">
-        <v>2026-08-02T17:46:41.553Z</v>
+        <v>2026-08-02T18:30:53.311Z</v>
       </c>
       <c r="N22" t="str">
         <v>[]</v>
@@ -2839,19 +3294,19 @@
 This place is worth its price 💯</v>
       </c>
       <c r="P22" t="str">
-        <v>2026-08-02T17:46:41.553Z</v>
+        <v>2026-08-02T18:30:53.311Z</v>
       </c>
       <c r="Q22" t="str">
-        <v>2026-08-02T17:46:45.737Z</v>
+        <v>2026-08-02T18:30:57.603Z</v>
       </c>
       <c r="R22" t="str">
         <v>[]</v>
       </c>
       <c r="S22" t="str">
-        <v>2026-06-03T17:46:27.751Z</v>
+        <v>2026-06-03T18:30:37.823Z</v>
       </c>
       <c r="T22" t="str">
-        <v>2026-08-02T17:46:51.884Z</v>
+        <v>2026-08-02T18:31:03.339Z</v>
       </c>
     </row>
     <row r="23">
@@ -2892,7 +3347,7 @@
         <v>apify</v>
       </c>
       <c r="M23" t="str">
-        <v>2026-08-02T17:46:41.553Z</v>
+        <v>2026-08-02T18:30:53.311Z</v>
       </c>
       <c r="N23" t="str">
         <v>[]</v>
@@ -2901,19 +3356,19 @@
         <v>Absolutely loved their Belgium hot chocolate and hazel nut hot chocolate. Also enjoyed their sandwich and burger..... Beautiful ambience and host ❤️</v>
       </c>
       <c r="P23" t="str">
-        <v>2026-08-02T17:46:41.553Z</v>
+        <v>2026-08-02T18:30:53.311Z</v>
       </c>
       <c r="Q23" t="str">
-        <v>2026-08-02T17:46:45.840Z</v>
+        <v>2026-08-02T18:30:57.704Z</v>
       </c>
       <c r="R23" t="str">
         <v>["https://lh3.googleusercontent.com/grass-cs/ACvplmPS1SB7POkSiZDsNmQAQxUX-uXw8DfgIbcaHm9QtC3Mi30H7S5v9mDaVlT8jSLXwUuhDEynK3jp8Stp4360Sqp7drESl3uoA_4-8rMONNQvEEn13XWQpVs9v8PwpL0CdS5Yi_B3SfcYQTw=w600-h450-p-k-no"]</v>
       </c>
       <c r="S23" t="str">
-        <v>2026-06-03T17:46:27.751Z</v>
+        <v>2026-06-03T18:30:37.823Z</v>
       </c>
       <c r="T23" t="str">
-        <v>2026-08-02T17:46:51.884Z</v>
+        <v>2026-08-02T18:31:03.339Z</v>
       </c>
     </row>
     <row r="24" xml:space="preserve">
@@ -2954,7 +3409,7 @@
         <v>apify</v>
       </c>
       <c r="M24" t="str">
-        <v>2026-08-02T17:46:41.553Z</v>
+        <v>2026-08-02T18:30:53.311Z</v>
       </c>
       <c r="N24" t="str">
         <v>[]</v>
@@ -2964,19 +3419,19 @@
 I would defenitely reach back here once again</v>
       </c>
       <c r="P24" t="str">
-        <v>2026-08-02T17:46:41.553Z</v>
+        <v>2026-08-02T18:30:53.311Z</v>
       </c>
       <c r="Q24" t="str">
-        <v>2026-08-02T17:46:45.942Z</v>
+        <v>2026-08-02T18:30:57.769Z</v>
       </c>
       <c r="R24" t="str">
         <v>[]</v>
       </c>
       <c r="S24" t="str">
-        <v>2026-06-03T17:46:27.751Z</v>
+        <v>2026-06-03T18:30:37.823Z</v>
       </c>
       <c r="T24" t="str">
-        <v>2026-08-02T17:46:51.884Z</v>
+        <v>2026-08-02T18:31:03.339Z</v>
       </c>
     </row>
     <row r="25">
@@ -3017,7 +3472,7 @@
         <v>apify</v>
       </c>
       <c r="M25" t="str">
-        <v>2026-08-02T17:46:41.553Z</v>
+        <v>2026-08-02T18:30:53.311Z</v>
       </c>
       <c r="N25" t="str">
         <v>[]</v>
@@ -3026,19 +3481,19 @@
         <v>Good</v>
       </c>
       <c r="P25" t="str">
-        <v>2026-08-02T17:46:41.553Z</v>
+        <v>2026-08-02T18:30:53.311Z</v>
       </c>
       <c r="Q25" t="str">
-        <v>2026-08-02T17:46:46.043Z</v>
+        <v>2026-08-02T18:30:57.909Z</v>
       </c>
       <c r="R25" t="str">
         <v>[]</v>
       </c>
       <c r="S25" t="str">
-        <v>2026-06-03T17:46:27.751Z</v>
+        <v>2026-06-03T18:30:37.823Z</v>
       </c>
       <c r="T25" t="str">
-        <v>2026-08-02T17:46:51.884Z</v>
+        <v>2026-08-02T18:31:03.339Z</v>
       </c>
     </row>
     <row r="26">
@@ -3079,7 +3534,7 @@
         <v>apify</v>
       </c>
       <c r="M26" t="str">
-        <v>2026-08-02T17:46:41.553Z</v>
+        <v>2026-08-02T18:30:53.311Z</v>
       </c>
       <c r="N26" t="str">
         <v>[]</v>
@@ -3088,19 +3543,19 @@
         <v>Ordered customized cake. Taste was really good and they customized the cake based on my preference.</v>
       </c>
       <c r="P26" t="str">
-        <v>2026-08-02T17:46:41.553Z</v>
+        <v>2026-08-02T18:30:53.311Z</v>
       </c>
       <c r="Q26" t="str">
-        <v>2026-08-02T17:46:46.147Z</v>
+        <v>2026-08-02T18:30:58.011Z</v>
       </c>
       <c r="R26" t="str">
         <v>[]</v>
       </c>
       <c r="S26" t="str">
-        <v>2026-06-03T17:46:27.751Z</v>
+        <v>2026-06-03T18:30:37.823Z</v>
       </c>
       <c r="T26" t="str">
-        <v>2026-08-02T17:46:51.884Z</v>
+        <v>2026-08-02T18:31:03.339Z</v>
       </c>
     </row>
     <row r="27">
@@ -3141,7 +3596,7 @@
         <v>apify</v>
       </c>
       <c r="M27" t="str">
-        <v>2026-08-02T17:46:41.553Z</v>
+        <v>2026-08-02T18:30:53.311Z</v>
       </c>
       <c r="N27" t="str">
         <v>[]</v>
@@ -3150,19 +3605,19 @@
         <v>Delicious cakes 😋 and great service and one of my favorite cake shop !!</v>
       </c>
       <c r="P27" t="str">
-        <v>2026-08-02T17:46:41.553Z</v>
+        <v>2026-08-02T18:30:53.311Z</v>
       </c>
       <c r="Q27" t="str">
-        <v>2026-08-02T17:46:46.249Z</v>
+        <v>2026-08-02T18:30:58.113Z</v>
       </c>
       <c r="R27" t="str">
         <v>["https://lh3.googleusercontent.com/grass-cs/ACvplmOEAdAP3uUCNZ9DBvVjsfn-syPBXegPJ008NKTREB0XlHxeBTQUAxRhTkWJq4mxsXtIcdDzV-CAtVZ4RJOqmtKjKVCXXQNZG9yeGBTmA0EtTkT9iQO8pDTSz21QSdC1sT89AXMBv5lVRrsJ=w600-h450-p-k-no"]</v>
       </c>
       <c r="S27" t="str">
-        <v>2026-06-03T17:46:27.751Z</v>
+        <v>2026-06-03T18:30:37.823Z</v>
       </c>
       <c r="T27" t="str">
-        <v>2026-08-02T17:46:51.884Z</v>
+        <v>2026-08-02T18:31:03.339Z</v>
       </c>
     </row>
     <row r="28">
@@ -3203,7 +3658,7 @@
         <v>apify</v>
       </c>
       <c r="M28" t="str">
-        <v>2026-08-02T17:46:41.553Z</v>
+        <v>2026-08-02T18:30:53.311Z</v>
       </c>
       <c r="N28" t="str">
         <v>[]</v>
@@ -3212,19 +3667,19 @@
         <v>Tried chocolate truffle cake here and it was really awesome</v>
       </c>
       <c r="P28" t="str">
-        <v>2026-08-02T17:46:41.553Z</v>
+        <v>2026-08-02T18:30:53.311Z</v>
       </c>
       <c r="Q28" t="str">
-        <v>2026-08-02T17:46:46.352Z</v>
+        <v>2026-08-02T18:30:58.188Z</v>
       </c>
       <c r="R28" t="str">
         <v>[]</v>
       </c>
       <c r="S28" t="str">
-        <v>2026-06-03T17:46:29.662Z</v>
+        <v>2026-06-03T18:30:40.360Z</v>
       </c>
       <c r="T28" t="str">
-        <v>2026-08-02T17:46:51.884Z</v>
+        <v>2026-08-02T18:31:03.339Z</v>
       </c>
     </row>
     <row r="29" xml:space="preserve">
@@ -3265,7 +3720,7 @@
         <v>apify</v>
       </c>
       <c r="M29" t="str">
-        <v>2026-08-02T17:46:41.553Z</v>
+        <v>2026-08-02T18:30:53.311Z</v>
       </c>
       <c r="N29" t="str">
         <v>[]</v>
@@ -3276,19 +3731,19 @@
 Done exactly like the reference picture</v>
       </c>
       <c r="P29" t="str">
-        <v>2026-08-02T17:46:41.553Z</v>
+        <v>2026-08-02T18:30:53.311Z</v>
       </c>
       <c r="Q29" t="str">
-        <v>2026-08-02T17:46:46.462Z</v>
+        <v>2026-08-02T18:30:58.293Z</v>
       </c>
       <c r="R29" t="str">
         <v>[]</v>
       </c>
       <c r="S29" t="str">
-        <v>2026-06-03T17:46:29.662Z</v>
+        <v>2026-06-03T18:30:40.360Z</v>
       </c>
       <c r="T29" t="str">
-        <v>2026-08-02T17:46:51.884Z</v>
+        <v>2026-08-02T18:31:03.339Z</v>
       </c>
     </row>
     <row r="30">
@@ -3329,7 +3784,7 @@
         <v>apify</v>
       </c>
       <c r="M30" t="str">
-        <v>2026-08-02T17:46:41.553Z</v>
+        <v>2026-08-02T18:30:53.311Z</v>
       </c>
       <c r="N30" t="str">
         <v>[]</v>
@@ -3338,19 +3793,19 @@
         <v>We ordered Vannila flavour theme cake for our daughter birthday. It was upto the expected level both in taste and theme quality</v>
       </c>
       <c r="P30" t="str">
-        <v>2026-08-02T17:46:41.553Z</v>
+        <v>2026-08-02T18:30:53.311Z</v>
       </c>
       <c r="Q30" t="str">
-        <v>2026-08-02T17:46:46.517Z</v>
+        <v>2026-08-02T18:30:58.388Z</v>
       </c>
       <c r="R30" t="str">
         <v>["https://lh3.googleusercontent.com/grass-cs/ACvplmODoeuEHqYZHHUsHgjYdIAQEW_uY5Aplk0_6550J5iNyqJcsFt6mM1axejcsC_qjq99AkeYYLEnH4esRbYqXvo1G01dcHablNwQ8cKmbAIkijCLnDzKXmj45JtVigIEG-ItkYRiMdMaiGRA=w600-h450-p-k-no"]</v>
       </c>
       <c r="S30" t="str">
-        <v>2026-06-03T17:46:29.662Z</v>
+        <v>2026-06-03T18:30:40.360Z</v>
       </c>
       <c r="T30" t="str">
-        <v>2026-08-02T17:46:51.884Z</v>
+        <v>2026-08-02T18:31:03.339Z</v>
       </c>
     </row>
     <row r="31">
@@ -3391,7 +3846,7 @@
         <v>apify</v>
       </c>
       <c r="M31" t="str">
-        <v>2026-08-02T17:46:41.553Z</v>
+        <v>2026-08-02T18:30:53.311Z</v>
       </c>
       <c r="N31" t="str">
         <v>[]</v>
@@ -3400,19 +3855,19 @@
         <v>So delicious</v>
       </c>
       <c r="P31" t="str">
-        <v>2026-08-02T17:46:41.553Z</v>
+        <v>2026-08-02T18:30:53.311Z</v>
       </c>
       <c r="Q31" t="str">
-        <v>2026-08-02T17:46:46.568Z</v>
+        <v>2026-08-02T18:30:58.451Z</v>
       </c>
       <c r="R31" t="str">
         <v>[]</v>
       </c>
       <c r="S31" t="str">
-        <v>2026-06-03T17:46:29.662Z</v>
+        <v>2026-06-03T18:30:40.360Z</v>
       </c>
       <c r="T31" t="str">
-        <v>2026-08-02T17:46:51.884Z</v>
+        <v>2026-08-02T18:31:03.339Z</v>
       </c>
     </row>
     <row r="32">
@@ -3453,7 +3908,7 @@
         <v>apify</v>
       </c>
       <c r="M32" t="str">
-        <v>2026-08-02T17:46:41.553Z</v>
+        <v>2026-08-02T18:30:53.311Z</v>
       </c>
       <c r="N32" t="str">
         <v>[]</v>
@@ -3462,19 +3917,19 @@
         <v>Best place for fresh cakes and muffins</v>
       </c>
       <c r="P32" t="str">
-        <v>2026-08-02T17:46:41.553Z</v>
+        <v>2026-08-02T18:30:53.311Z</v>
       </c>
       <c r="Q32" t="str">
-        <v>2026-08-02T17:46:46.658Z</v>
+        <v>2026-08-02T18:30:58.526Z</v>
       </c>
       <c r="R32" t="str">
         <v>[]</v>
       </c>
       <c r="S32" t="str">
-        <v>2026-06-03T17:46:29.662Z</v>
+        <v>2026-06-03T18:30:40.360Z</v>
       </c>
       <c r="T32" t="str">
-        <v>2026-08-02T17:46:51.884Z</v>
+        <v>2026-08-02T18:31:03.339Z</v>
       </c>
     </row>
     <row r="33">
@@ -3515,7 +3970,7 @@
         <v>apify</v>
       </c>
       <c r="M33" t="str">
-        <v>2026-08-02T17:46:41.553Z</v>
+        <v>2026-08-02T18:30:53.311Z</v>
       </c>
       <c r="N33" t="str">
         <v>[]</v>
@@ -3524,19 +3979,19 @@
         <v>The veggie sandwich was delicious! So was the brownie milkshake which is a must try. The atmosphere is really good here and it's def an underrated café.</v>
       </c>
       <c r="P33" t="str">
-        <v>2026-08-02T17:46:41.553Z</v>
+        <v>2026-08-02T18:30:53.311Z</v>
       </c>
       <c r="Q33" t="str">
-        <v>2026-08-02T17:46:46.761Z</v>
+        <v>2026-08-02T18:30:58.603Z</v>
       </c>
       <c r="R33" t="str">
         <v>[]</v>
       </c>
       <c r="S33" t="str">
-        <v>2026-06-03T17:46:31.926Z</v>
+        <v>2026-06-03T18:30:42.833Z</v>
       </c>
       <c r="T33" t="str">
-        <v>2026-08-02T17:46:51.884Z</v>
+        <v>2026-08-02T18:31:03.339Z</v>
       </c>
     </row>
     <row r="34">
@@ -3577,7 +4032,7 @@
         <v>apify</v>
       </c>
       <c r="M34" t="str">
-        <v>2026-08-02T17:46:41.553Z</v>
+        <v>2026-08-02T18:30:53.311Z</v>
       </c>
       <c r="N34" t="str">
         <v>[]</v>
@@ -3586,10 +4041,10 @@
         <v>Excellent taste. Had fun. Excellent customer service. Tres lechues Cherry chocolate is mind blowing.</v>
       </c>
       <c r="P34" t="str">
-        <v>2026-08-02T17:46:41.553Z</v>
+        <v>2026-08-02T18:30:53.311Z</v>
       </c>
       <c r="Q34" t="str">
-        <v>2026-08-02T17:46:46.863Z</v>
+        <v>2026-08-02T18:30:58.731Z</v>
       </c>
       <c r="R34" t="str">
         <v>[]</v>
@@ -3598,7 +4053,7 @@
         <v/>
       </c>
       <c r="T34" t="str">
-        <v>2026-08-02T17:46:51.884Z</v>
+        <v>2026-08-02T18:31:03.339Z</v>
       </c>
     </row>
     <row r="35">
@@ -3639,7 +4094,7 @@
         <v>apify</v>
       </c>
       <c r="M35" t="str">
-        <v>2026-08-02T17:46:41.553Z</v>
+        <v>2026-08-02T18:30:53.311Z</v>
       </c>
       <c r="N35" t="str">
         <v>[]</v>
@@ -3648,10 +4103,10 @@
         <v>I ordered a birthday cake as I specified about cake with animals theme 🎂...I felt so good to taste and it's so good Thank you</v>
       </c>
       <c r="P35" t="str">
-        <v>2026-08-02T17:46:41.553Z</v>
+        <v>2026-08-02T18:30:53.311Z</v>
       </c>
       <c r="Q35" t="str">
-        <v>2026-08-02T17:46:46.966Z</v>
+        <v>2026-08-02T18:30:58.831Z</v>
       </c>
       <c r="R35" t="str">
         <v>[]</v>
@@ -3660,7 +4115,7 @@
         <v/>
       </c>
       <c r="T35" t="str">
-        <v>2026-08-02T17:46:51.884Z</v>
+        <v>2026-08-02T18:31:03.339Z</v>
       </c>
     </row>
     <row r="36">
@@ -3701,7 +4156,7 @@
         <v>apify</v>
       </c>
       <c r="M36" t="str">
-        <v>2026-08-02T17:46:41.553Z</v>
+        <v>2026-08-02T18:30:53.311Z</v>
       </c>
       <c r="N36" t="str">
         <v>[]</v>
@@ -3710,19 +4165,19 @@
         <v>Cake was very very tasty and look wise very beautiful and i really enjoy a lot and my family members thank you so much for your beautiful cake🥰🥰</v>
       </c>
       <c r="P36" t="str">
-        <v>2026-08-02T17:46:41.553Z</v>
+        <v>2026-08-02T18:30:53.311Z</v>
       </c>
       <c r="Q36" t="str">
-        <v>2026-08-02T17:46:47.070Z</v>
+        <v>2026-08-02T18:30:58.935Z</v>
       </c>
       <c r="R36" t="str">
         <v>["https://lh3.googleusercontent.com/grass-cs/ACvplmPChtL6XGhJ0T0zLfRXppsYurx-hiXimk1pnloXnAfHRWILetziSB8VF_KZNWLv_ltMV2a0zY-Zv8Pse9lHzz4khIQ1ePYzEUgCqa52NeUMn8R8OrkQVjeAQ-bR90bHkTeok3Yd-H6auW4j=w300-h450-p-k-no","https://lh3.googleusercontent.com/grass-cs/ACvplmNQshi_oKTrEyCeIRUredk0eAVgCLpUjnUFc-mQUFapgheM4gYQXeA3m3vU367aeoHtiZGiwPKk-aug9AOo1Es-gRpYBu_v7gVmX-jnITBRmyl9iZpisOSshL5RYEEdrLjCMykDjoQvUwMv=w300-h450-p-k-no"]</v>
       </c>
       <c r="S36" t="str">
-        <v>2026-05-04T17:46:31.926Z</v>
+        <v>2026-05-04T18:30:42.833Z</v>
       </c>
       <c r="T36" t="str">
-        <v>2026-08-02T17:46:51.884Z</v>
+        <v>2026-08-02T18:31:03.339Z</v>
       </c>
     </row>
     <row r="37">
@@ -3763,7 +4218,7 @@
         <v>apify</v>
       </c>
       <c r="M37" t="str">
-        <v>2026-08-02T17:46:41.553Z</v>
+        <v>2026-08-02T18:30:53.311Z</v>
       </c>
       <c r="N37" t="str">
         <v>[]</v>
@@ -3772,10 +4227,10 @@
         <v>Very nice</v>
       </c>
       <c r="P37" t="str">
-        <v>2026-08-02T17:46:41.553Z</v>
+        <v>2026-08-02T18:30:53.311Z</v>
       </c>
       <c r="Q37" t="str">
-        <v>2026-08-02T17:46:47.171Z</v>
+        <v>2026-08-02T18:30:59.035Z</v>
       </c>
       <c r="R37" t="str">
         <v>["https://lh3.googleusercontent.com/grass-cs/ACvplmPaK6IAJqFroL-Q3eCe1oY9R0jG9-WtqOMA7gc0Ui6H3F7VYJnet34e52FOD8o_mIOS8RVfOQoZs9DGhv1WdPfAx5WmDB8370r9Wrvhunzs_dtm0wlI0_v2YxJ6T4wmX7Ajb6IikdgTXCQ3=w300-h450-p-k-no","https://lh3.googleusercontent.com/grass-cs/ACvplmNhrHmxhhmHRD-QplXBACjz2vblYTPVIsrE1tD-FQdZKhzrPWDsLercN8dXWffZPDEhC3Fng7DVQzYRMkRg5TKM7Qz6kMUJl6QoawkWlBlqummwpC4URga4hVKOD3CLOtB3fXQatOG4tds=w300-h450-p-k-no"]</v>
@@ -3784,7 +4239,7 @@
         <v/>
       </c>
       <c r="T37" t="str">
-        <v>2026-08-02T17:46:51.884Z</v>
+        <v>2026-08-02T18:31:03.339Z</v>
       </c>
     </row>
     <row r="38">
@@ -3825,7 +4280,7 @@
         <v>apify</v>
       </c>
       <c r="M38" t="str">
-        <v>2026-08-02T17:46:41.553Z</v>
+        <v>2026-08-02T18:30:53.311Z</v>
       </c>
       <c r="N38" t="str">
         <v>[]</v>
@@ -3834,19 +4289,19 @@
         <v>3 months agoOrder typeTake outMeal typeBrunchLike</v>
       </c>
       <c r="P38" t="str">
-        <v>2026-08-02T17:46:41.553Z</v>
+        <v>2026-08-02T18:30:53.311Z</v>
       </c>
       <c r="Q38" t="str">
-        <v>2026-08-02T17:46:47.377Z</v>
+        <v>2026-08-02T18:30:59.210Z</v>
       </c>
       <c r="R38" t="str">
         <v>[]</v>
       </c>
       <c r="S38" t="str">
-        <v>2026-05-04T17:46:34.254Z</v>
+        <v>2026-05-04T18:30:45.242Z</v>
       </c>
       <c r="T38" t="str">
-        <v>2026-08-02T17:46:51.884Z</v>
+        <v>2026-08-02T18:31:03.339Z</v>
       </c>
     </row>
     <row r="39">
@@ -3887,7 +4342,7 @@
         <v>apify</v>
       </c>
       <c r="M39" t="str">
-        <v>2026-08-02T17:46:41.553Z</v>
+        <v>2026-08-02T18:30:53.311Z</v>
       </c>
       <c r="N39" t="str">
         <v>[]</v>
@@ -3896,19 +4351,19 @@
         <v>Had ordered for a Rose Milk Birthday Cake few months before and it exceeded the expectation of everyone in taste. The order and Delicery experience was also very professional and able to feel the passion of the promoter. Today ordered their Mango Stick Melt Box, which again was yummy and felt very light. One of the must try dessert this summer</v>
       </c>
       <c r="P39" t="str">
-        <v>2026-08-02T17:46:41.553Z</v>
+        <v>2026-08-02T18:30:53.311Z</v>
       </c>
       <c r="Q39" t="str">
-        <v>2026-08-02T17:46:47.479Z</v>
+        <v>2026-08-02T18:30:59.343Z</v>
       </c>
       <c r="R39" t="str">
         <v>["https://lh3.googleusercontent.com/grass-cs/ACvplmOj6ImrxKOz6WxmFbQ9h5d15Ff8B5wrbMC86uLyoCh5XFujplz--OwZWIfR_M1tIiS9yf-HuPFAMIs4UHgWBTS4tT_QIILL_eiBQiOcSO1naxY9BYmaYFo39WJHFZwQVvIm1rVOhTlUCW8=w300-h450-p-k-no","https://lh3.googleusercontent.com/grass-cs/ACvplmO-0GzWLqvrpb7tOp3qI8jtfk3fwsnUsUA10rG4a4GL4moYeolLxjyI81nOM5KUNSSMysTTa6iAv6pjZzKChSPhonfCcLmKs7sa8B5Py6dQSTyTGv3wQtbd7bCug0OVz_VCnjqDa9S4tK4=w300-h450-p-k-no"]</v>
       </c>
       <c r="S39" t="str">
-        <v>2026-05-04T17:46:34.254Z</v>
+        <v>2026-05-04T18:30:45.242Z</v>
       </c>
       <c r="T39" t="str">
-        <v>2026-08-02T17:46:51.884Z</v>
+        <v>2026-08-02T18:31:03.339Z</v>
       </c>
     </row>
     <row r="40" xml:space="preserve">
@@ -3949,7 +4404,7 @@
         <v>apify</v>
       </c>
       <c r="M40" t="str">
-        <v>2026-08-02T17:46:41.553Z</v>
+        <v>2026-08-02T18:30:53.311Z</v>
       </c>
       <c r="N40" t="str">
         <v>[]</v>
@@ -3959,10 +4414,10 @@
 More than we expected.. 💜</v>
       </c>
       <c r="P40" t="str">
-        <v>2026-08-02T17:46:41.553Z</v>
+        <v>2026-08-02T18:30:53.311Z</v>
       </c>
       <c r="Q40" t="str">
-        <v>2026-08-02T17:46:47.581Z</v>
+        <v>2026-08-02T18:30:59.407Z</v>
       </c>
       <c r="R40" t="str">
         <v>["https://lh3.googleusercontent.com/grass-cs/ACvplmN8esRE8BLAeC1xIDFb6CE6g5KxnHQT0Xgqu5wC-Z6lElKuNEF8nGWHgyjOCzeHV6bXHmT89PoJpWgEWhf5RuHwCWQIvHRwTtlxVj7s6jpUyhpVDONytNnPMJ6Z0fnW2vLk9_Lav3uGadem=w300-h450-p-k-no","https://lh3.googleusercontent.com/grass-cs/ACvplmMFy5gdRcKFcVFsSEj7WFcptjf87kxwiJaSwmu2F79is-rQvyEBWoCRRMtpEod-6j0Ck31M7907DHQDgIm_t7i0UJKKspyAZjWAV4i4TCgjoVqNIgUGLr9ysGHMlSG5PrphNT4pUdJYX0A=w300-h225-p-k-no","https://lh3.googleusercontent.com/grass-cs/ACvplmPEQUn0A14Ns2vj18iEN-fU1fK1dWMALFKr15Z96Y_iLZT1AvG4eB5jgS76IXkwNJKwyHDS8hfe5uBaELLAqOGV657qpNBCW9nc4kmNtZgYaaJeRYBYKQlSNOis9GhYxHm2AHhHLwAcgslM=w300-h225-p-k-no"]</v>
@@ -3971,7 +4426,7 @@
         <v/>
       </c>
       <c r="T40" t="str">
-        <v>2026-08-02T17:46:51.885Z</v>
+        <v>2026-08-02T18:31:03.339Z</v>
       </c>
     </row>
     <row r="41">
@@ -4012,7 +4467,7 @@
         <v>apify</v>
       </c>
       <c r="M41" t="str">
-        <v>2026-08-02T17:46:41.553Z</v>
+        <v>2026-08-02T18:30:53.311Z</v>
       </c>
       <c r="N41" t="str">
         <v>[]</v>
@@ -4021,19 +4476,19 @@
         <v>That cake was for my daughter’s 11th birthday, she loved the vancho flavor and the cake was better than she expected! Thank you so much.</v>
       </c>
       <c r="P41" t="str">
-        <v>2026-08-02T17:46:41.553Z</v>
+        <v>2026-08-02T18:30:53.311Z</v>
       </c>
       <c r="Q41" t="str">
-        <v>2026-08-02T17:46:47.683Z</v>
+        <v>2026-08-02T18:30:59.548Z</v>
       </c>
       <c r="R41" t="str">
         <v>["https://lh3.googleusercontent.com/grass-cs/ACvplmMOJMdqXOm3OBhv20MqC7Hxa1HXV6b7TPqZFHrnXMKCWRDfQxnOFlnnH2SGj1iw3E-CuMOZmjEISP-L6UlEkpWvuY7tfBCAdAHJ4uKLeHqhbt9vUUmLTcVx844ZEXx5pU1WOIV8qbh7SaVW=w600-h450-p-k-no"]</v>
       </c>
       <c r="S41" t="str">
-        <v>2026-05-04T17:46:34.254Z</v>
+        <v>2026-05-04T18:30:45.242Z</v>
       </c>
       <c r="T41" t="str">
-        <v>2026-08-02T17:46:51.885Z</v>
+        <v>2026-08-02T18:31:03.339Z</v>
       </c>
     </row>
     <row r="42">
@@ -4074,7 +4529,7 @@
         <v>apify</v>
       </c>
       <c r="M42" t="str">
-        <v>2026-08-02T17:46:41.553Z</v>
+        <v>2026-08-02T18:30:53.311Z</v>
       </c>
       <c r="N42" t="str">
         <v>[]</v>
@@ -4083,19 +4538,19 @@
         <v>We ordered rose milk cake from chocolate mine. The cake was absolutely delicious and flavorful and very well customized as per our wish...Everyone loved it.. thank you for the wonderful cake</v>
       </c>
       <c r="P42" t="str">
-        <v>2026-08-02T17:46:41.553Z</v>
+        <v>2026-08-02T18:30:53.311Z</v>
       </c>
       <c r="Q42" t="str">
-        <v>2026-08-02T17:46:47.785Z</v>
+        <v>2026-08-02T18:30:59.651Z</v>
       </c>
       <c r="R42" t="str">
         <v>[]</v>
       </c>
       <c r="S42" t="str">
-        <v>2026-05-04T17:46:34.254Z</v>
+        <v>2026-05-04T18:30:45.242Z</v>
       </c>
       <c r="T42" t="str">
-        <v>2026-08-02T17:46:51.885Z</v>
+        <v>2026-08-02T18:31:03.339Z</v>
       </c>
     </row>
     <row r="43">
@@ -4136,7 +4591,7 @@
         <v>apify</v>
       </c>
       <c r="M43" t="str">
-        <v>2026-08-02T17:46:41.553Z</v>
+        <v>2026-08-02T18:30:53.311Z</v>
       </c>
       <c r="N43" t="str">
         <v>[]</v>
@@ -4145,19 +4600,19 @@
         <v>Choco Lava Cake and Cheese Cake must try😌😋</v>
       </c>
       <c r="P43" t="str">
-        <v>2026-08-02T17:46:41.553Z</v>
+        <v>2026-08-02T18:30:53.311Z</v>
       </c>
       <c r="Q43" t="str">
-        <v>2026-08-02T17:46:47.887Z</v>
+        <v>2026-08-02T18:30:59.752Z</v>
       </c>
       <c r="R43" t="str">
         <v>[]</v>
       </c>
       <c r="S43" t="str">
-        <v>2026-05-04T17:46:34.254Z</v>
+        <v>2026-05-04T18:30:45.242Z</v>
       </c>
       <c r="T43" t="str">
-        <v>2026-08-02T17:46:51.885Z</v>
+        <v>2026-08-02T18:31:03.339Z</v>
       </c>
     </row>
     <row r="44">
@@ -4198,7 +4653,7 @@
         <v>apify</v>
       </c>
       <c r="M44" t="str">
-        <v>2026-08-02T17:46:41.553Z</v>
+        <v>2026-08-02T18:30:53.311Z</v>
       </c>
       <c r="N44" t="str">
         <v>[]</v>
@@ -4207,19 +4662,19 @@
         <v>Thank you so much mam...it was a delicious cake for my daughter...all the children loved the cake and decoration was superb</v>
       </c>
       <c r="P44" t="str">
-        <v>2026-08-02T17:46:41.553Z</v>
+        <v>2026-08-02T18:30:53.311Z</v>
       </c>
       <c r="Q44" t="str">
-        <v>2026-08-02T17:46:47.990Z</v>
+        <v>2026-08-02T18:30:59.854Z</v>
       </c>
       <c r="R44" t="str">
         <v>["https://lh3.googleusercontent.com/grass-cs/ACvplmPA3y_aD66omtRox5jRa9j6deraN4g_Zl8hgzlp_W4viyqhRVtOFyZcsQkQ7sLel_luWGoGcKwwazGIa0HEUK_1w7MWiurNLcTLonU-zCnlzUbczjLnbVwz9UpwUMyEsTXcuyq3bjUPEByK=w600-h450-p-k-no"]</v>
       </c>
       <c r="S44" t="str">
-        <v>2026-04-04T17:46:34.254Z</v>
+        <v>2026-04-04T18:30:45.242Z</v>
       </c>
       <c r="T44" t="str">
-        <v>2026-08-02T17:46:51.885Z</v>
+        <v>2026-08-02T18:31:03.339Z</v>
       </c>
     </row>
     <row r="45">
@@ -4260,7 +4715,7 @@
         <v>apify</v>
       </c>
       <c r="M45" t="str">
-        <v>2026-08-02T17:46:41.553Z</v>
+        <v>2026-08-02T18:30:53.311Z</v>
       </c>
       <c r="N45" t="str">
         <v>[]</v>
@@ -4269,19 +4724,19 @@
         <v>We recently celebrated our lil ones bday at this cafe which turned out to be a full satisfied event for us! Throughout all the details and requests they were polite and served us the best. Spl mention- their hazelnut hot choc is a must try🥤🥰</v>
       </c>
       <c r="P45" t="str">
-        <v>2026-08-02T17:46:41.553Z</v>
+        <v>2026-08-02T18:30:53.311Z</v>
       </c>
       <c r="Q45" t="str">
-        <v>2026-08-02T17:46:48.092Z</v>
+        <v>2026-08-02T18:30:59.958Z</v>
       </c>
       <c r="R45" t="str">
         <v>["https://lh3.googleusercontent.com/grass-cs/ACvplmOFTwvXMaET5XUZMNctQyhyQXXBJwZxj2kRpaecUE8afDcRwUAlEBZhxBk--YhOg0joBMrXhu0PJRKxObRCqjSTYvI9-76bI7KCOlAyGDAukk4MmU-eGRC0t7DmdGzeQpbBH2pSfApcnmhM=w300-h450-p-k-no","https://lh3.googleusercontent.com/grass-cs/ACvplmM1rjl5OAXts1YhjTtQx2zi-Bzw86UqPifCGW9Hvq4Uq9d-s0MY7Y12-JMNqRXSoYC4dywqr3NNBhIQtEiMwsgyPg9TqMVzfCiztV8ouOM4WgoXLC1-oc72s9fz05t_U5weiZeRpfakTAOh=w300-h450-p-k-no"]</v>
       </c>
       <c r="S45" t="str">
-        <v>2026-04-04T17:46:36.220Z</v>
+        <v>2026-04-04T18:30:47.750Z</v>
       </c>
       <c r="T45" t="str">
-        <v>2026-08-02T17:46:51.885Z</v>
+        <v>2026-08-02T18:31:03.339Z</v>
       </c>
     </row>
     <row r="46">
@@ -4322,7 +4777,7 @@
         <v>apify</v>
       </c>
       <c r="M46" t="str">
-        <v>2026-08-02T17:46:41.553Z</v>
+        <v>2026-08-02T18:30:53.311Z</v>
       </c>
       <c r="N46" t="str">
         <v>[]</v>
@@ -4331,19 +4786,19 @@
         <v>I ordered B'day bento cake for my loved one.......it takes good and also we are tres leches it tadte like topnotch......really enjoyed</v>
       </c>
       <c r="P46" t="str">
-        <v>2026-08-02T17:46:41.553Z</v>
+        <v>2026-08-02T18:30:53.311Z</v>
       </c>
       <c r="Q46" t="str">
-        <v>2026-08-02T17:46:48.195Z</v>
+        <v>2026-08-02T18:31:00.059Z</v>
       </c>
       <c r="R46" t="str">
         <v>[]</v>
       </c>
       <c r="S46" t="str">
-        <v>2026-04-04T17:46:36.220Z</v>
+        <v>2026-04-04T18:30:47.750Z</v>
       </c>
       <c r="T46" t="str">
-        <v>2026-08-02T17:46:51.885Z</v>
+        <v>2026-08-02T18:31:03.339Z</v>
       </c>
     </row>
     <row r="47">
@@ -4384,7 +4839,7 @@
         <v>apify</v>
       </c>
       <c r="M47" t="str">
-        <v>2026-08-02T17:46:41.553Z</v>
+        <v>2026-08-02T18:30:53.311Z</v>
       </c>
       <c r="N47" t="str">
         <v>[]</v>
@@ -4393,19 +4848,19 @@
         <v>The food was good, so was the coffee. It took a long time for the food to arrive once the order was placed</v>
       </c>
       <c r="P47" t="str">
-        <v>2026-08-02T17:46:41.553Z</v>
+        <v>2026-08-02T18:30:53.311Z</v>
       </c>
       <c r="Q47" t="str">
-        <v>2026-08-02T17:46:48.297Z</v>
+        <v>2026-08-02T18:31:00.131Z</v>
       </c>
       <c r="R47" t="str">
         <v>[]</v>
       </c>
       <c r="S47" t="str">
-        <v>2026-04-04T17:46:36.220Z</v>
+        <v>2026-04-04T18:30:47.750Z</v>
       </c>
       <c r="T47" t="str">
-        <v>2026-08-02T17:46:51.885Z</v>
+        <v>2026-08-02T18:31:03.339Z</v>
       </c>
     </row>
     <row r="48">
@@ -4446,7 +4901,7 @@
         <v>apify</v>
       </c>
       <c r="M48" t="str">
-        <v>2026-08-02T17:46:41.553Z</v>
+        <v>2026-08-02T18:30:53.311Z</v>
       </c>
       <c r="N48" t="str">
         <v>[]</v>
@@ -4455,19 +4910,19 @@
         <v>Very good service</v>
       </c>
       <c r="P48" t="str">
-        <v>2026-08-02T17:46:41.553Z</v>
+        <v>2026-08-02T18:30:53.311Z</v>
       </c>
       <c r="Q48" t="str">
-        <v>2026-08-02T17:46:48.400Z</v>
+        <v>2026-08-02T18:31:00.266Z</v>
       </c>
       <c r="R48" t="str">
         <v>[]</v>
       </c>
       <c r="S48" t="str">
-        <v>2026-04-04T17:46:36.220Z</v>
+        <v>2026-04-04T18:30:47.750Z</v>
       </c>
       <c r="T48" t="str">
-        <v>2026-08-02T17:46:51.885Z</v>
+        <v>2026-08-02T18:31:03.339Z</v>
       </c>
     </row>
     <row r="49">
@@ -4508,7 +4963,7 @@
         <v>apify</v>
       </c>
       <c r="M49" t="str">
-        <v>2026-08-02T17:46:41.553Z</v>
+        <v>2026-08-02T18:30:53.311Z</v>
       </c>
       <c r="N49" t="str">
         <v>[]</v>
@@ -4517,19 +4972,19 @@
         <v>Pleasant ambience and the taste was extraordinary ❤️</v>
       </c>
       <c r="P49" t="str">
-        <v>2026-08-02T17:46:41.553Z</v>
+        <v>2026-08-02T18:30:53.311Z</v>
       </c>
       <c r="Q49" t="str">
-        <v>2026-08-02T17:46:48.459Z</v>
+        <v>2026-08-02T18:31:00.367Z</v>
       </c>
       <c r="R49" t="str">
         <v>[]</v>
       </c>
       <c r="S49" t="str">
-        <v>2026-04-04T17:46:36.220Z</v>
+        <v>2026-04-04T18:30:47.750Z</v>
       </c>
       <c r="T49" t="str">
-        <v>2026-08-02T17:46:51.885Z</v>
+        <v>2026-08-02T18:31:03.339Z</v>
       </c>
     </row>
     <row r="50">
@@ -4570,7 +5025,7 @@
         <v>apify</v>
       </c>
       <c r="M50" t="str">
-        <v>2026-08-02T17:46:41.553Z</v>
+        <v>2026-08-02T18:30:53.311Z</v>
       </c>
       <c r="N50" t="str">
         <v>[]</v>
@@ -4579,19 +5034,19 @@
         <v>Chocolate coffee was top notch🤌🤌</v>
       </c>
       <c r="P50" t="str">
-        <v>2026-08-02T17:46:41.553Z</v>
+        <v>2026-08-02T18:30:53.311Z</v>
       </c>
       <c r="Q50" t="str">
-        <v>2026-08-02T17:46:48.558Z</v>
+        <v>2026-08-02T18:31:00.469Z</v>
       </c>
       <c r="R50" t="str">
         <v>[]</v>
       </c>
       <c r="S50" t="str">
-        <v>2026-04-04T17:46:36.220Z</v>
+        <v>2026-04-04T18:30:47.750Z</v>
       </c>
       <c r="T50" t="str">
-        <v>2026-08-02T17:46:51.885Z</v>
+        <v>2026-08-02T18:31:03.339Z</v>
       </c>
     </row>
     <row r="51">
@@ -4632,7 +5087,7 @@
         <v>apify</v>
       </c>
       <c r="M51" t="str">
-        <v>2026-08-02T17:46:41.553Z</v>
+        <v>2026-08-02T18:30:53.311Z</v>
       </c>
       <c r="N51" t="str">
         <v>[]</v>
@@ -4641,19 +5096,19 @@
         <v>Good</v>
       </c>
       <c r="P51" t="str">
-        <v>2026-08-02T17:46:41.553Z</v>
+        <v>2026-08-02T18:30:53.311Z</v>
       </c>
       <c r="Q51" t="str">
-        <v>2026-08-02T17:46:48.707Z</v>
+        <v>2026-08-02T18:31:00.572Z</v>
       </c>
       <c r="R51" t="str">
         <v>["https://lh3.googleusercontent.com/grass-cs/ACvplmMyfCkNzIiywCFwVg5mvXmZYywEK4pYCOkWEDOEQHNboewjOX_qoxwPuxJnLmjJ0vaVbdlP4Fpp71WP4CizLeTup0mbKhtfeyl0IiW4NAD7xfOPtE58faQdN3Zpi5fn1MXyY1fS1Re1YKw=w600-h450-p-k-no"]</v>
       </c>
       <c r="S51" t="str">
-        <v>2026-03-05T17:46:36.220Z</v>
+        <v>2026-03-05T18:30:47.750Z</v>
       </c>
       <c r="T51" t="str">
-        <v>2026-08-02T17:46:51.885Z</v>
+        <v>2026-08-02T18:31:03.339Z</v>
       </c>
     </row>
     <row r="52">
@@ -4694,7 +5149,7 @@
         <v>apify</v>
       </c>
       <c r="M52" t="str">
-        <v>2026-08-02T17:46:41.553Z</v>
+        <v>2026-08-02T18:30:53.311Z</v>
       </c>
       <c r="N52" t="str">
         <v>[]</v>
@@ -4703,19 +5158,19 @@
         <v>Response from the owner 5 months agoHello Mam, Sorry we couldn’t track your purchase in our customer database. Kindly please share your grievances, we will try to address the same. Thank you!</v>
       </c>
       <c r="P52" t="str">
-        <v>2026-08-02T17:46:41.553Z</v>
+        <v>2026-08-02T18:30:53.311Z</v>
       </c>
       <c r="Q52" t="str">
-        <v>2026-08-02T17:46:48.808Z</v>
+        <v>2026-08-02T18:31:00.647Z</v>
       </c>
       <c r="R52" t="str">
         <v>[]</v>
       </c>
       <c r="S52" t="str">
-        <v>2026-03-05T17:46:36.220Z</v>
+        <v>2026-03-05T18:30:47.750Z</v>
       </c>
       <c r="T52" t="str">
-        <v>2026-08-02T17:46:51.885Z</v>
+        <v>2026-08-02T18:31:03.339Z</v>
       </c>
     </row>
     <row r="53">
@@ -4777,7 +5232,7 @@
         <v>2026-03-01T06:45:44.320Z</v>
       </c>
       <c r="T53" t="str">
-        <v>2026-08-02T17:46:51.885Z</v>
+        <v>2026-08-02T18:31:03.339Z</v>
       </c>
     </row>
     <row r="54">
@@ -4839,7 +5294,7 @@
         <v>2026-02-27T10:19:29.898Z</v>
       </c>
       <c r="T54" t="str">
-        <v>2026-08-02T17:46:51.885Z</v>
+        <v>2026-08-02T18:31:03.340Z</v>
       </c>
     </row>
     <row r="55">
@@ -4901,7 +5356,7 @@
         <v>2026-02-26T13:13:36.195Z</v>
       </c>
       <c r="T55" t="str">
-        <v>2026-08-02T17:46:51.885Z</v>
+        <v>2026-08-02T18:31:03.340Z</v>
       </c>
     </row>
     <row r="56">
@@ -4963,7 +5418,7 @@
         <v>2026-02-24T18:31:20.668Z</v>
       </c>
       <c r="T56" t="str">
-        <v>2026-08-02T17:46:51.885Z</v>
+        <v>2026-08-02T18:31:03.340Z</v>
       </c>
     </row>
     <row r="57">
@@ -5025,7 +5480,7 @@
         <v>2026-02-11T10:33:29.369Z</v>
       </c>
       <c r="T57" t="str">
-        <v>2026-08-02T17:46:51.885Z</v>
+        <v>2026-08-02T18:31:03.340Z</v>
       </c>
     </row>
     <row r="58" xml:space="preserve">
@@ -5088,7 +5543,7 @@
         <v>2026-03-06T08:34:24.383Z</v>
       </c>
       <c r="T58" t="str">
-        <v>2026-08-02T17:46:51.885Z</v>
+        <v>2026-08-02T18:31:03.340Z</v>
       </c>
     </row>
     <row r="59">
@@ -5150,7 +5605,7 @@
         <v>2026-03-06T08:34:24.383Z</v>
       </c>
       <c r="T59" t="str">
-        <v>2026-08-02T17:46:51.885Z</v>
+        <v>2026-08-02T18:31:03.340Z</v>
       </c>
     </row>
     <row r="60">
@@ -5212,7 +5667,7 @@
         <v>2026-03-06T08:34:24.383Z</v>
       </c>
       <c r="T60" t="str">
-        <v>2026-08-02T17:46:51.885Z</v>
+        <v>2026-08-02T18:31:03.340Z</v>
       </c>
     </row>
     <row r="61">
@@ -5274,7 +5729,7 @@
         <v>2026-03-06T08:34:24.383Z</v>
       </c>
       <c r="T61" t="str">
-        <v>2026-08-02T17:46:51.885Z</v>
+        <v>2026-08-02T18:31:03.340Z</v>
       </c>
     </row>
     <row r="62">
@@ -5336,7 +5791,7 @@
         <v>2026-03-06T08:34:24.383Z</v>
       </c>
       <c r="T62" t="str">
-        <v>2026-08-02T17:46:51.885Z</v>
+        <v>2026-08-02T18:31:03.340Z</v>
       </c>
     </row>
     <row r="63">
@@ -5398,7 +5853,7 @@
         <v>2026-02-04T08:34:24.383Z</v>
       </c>
       <c r="T63" t="str">
-        <v>2026-08-02T17:46:51.885Z</v>
+        <v>2026-08-02T18:31:03.340Z</v>
       </c>
     </row>
     <row r="64" xml:space="preserve">
@@ -5461,7 +5916,7 @@
         <v>2026-02-01T13:59:29.989Z</v>
       </c>
       <c r="T64" t="str">
-        <v>2026-08-02T17:46:51.885Z</v>
+        <v>2026-08-02T18:31:03.340Z</v>
       </c>
     </row>
     <row r="65">
@@ -5523,7 +5978,7 @@
         <v>2026-02-24T17:08:34.231Z</v>
       </c>
       <c r="T65" t="str">
-        <v>2026-08-02T17:46:51.885Z</v>
+        <v>2026-08-02T18:31:03.340Z</v>
       </c>
     </row>
     <row r="66">
@@ -5585,7 +6040,7 @@
         <v>2026-02-13T15:37:15.383Z</v>
       </c>
       <c r="T66" t="str">
-        <v>2026-08-02T17:46:51.885Z</v>
+        <v>2026-08-02T18:31:03.340Z</v>
       </c>
     </row>
     <row r="67" xml:space="preserve">
@@ -5651,7 +6106,7 @@
         <v>2026-02-13T15:37:15.383Z</v>
       </c>
       <c r="T67" t="str">
-        <v>2026-08-02T17:46:51.885Z</v>
+        <v>2026-08-02T18:31:03.340Z</v>
       </c>
     </row>
     <row r="68">
@@ -5713,7 +6168,7 @@
         <v>2026-02-13T15:37:17.562Z</v>
       </c>
       <c r="T68" t="str">
-        <v>2026-08-02T17:46:51.885Z</v>
+        <v>2026-08-02T18:31:03.340Z</v>
       </c>
     </row>
     <row r="69">
@@ -5775,7 +6230,7 @@
         <v>2026-02-13T15:37:17.562Z</v>
       </c>
       <c r="T69" t="str">
-        <v>2026-08-02T17:46:51.885Z</v>
+        <v>2026-08-02T18:31:03.340Z</v>
       </c>
     </row>
     <row r="70">
@@ -5837,7 +6292,7 @@
         <v>2026-02-13T15:37:17.562Z</v>
       </c>
       <c r="T70" t="str">
-        <v>2026-08-02T17:46:51.885Z</v>
+        <v>2026-08-02T18:31:03.340Z</v>
       </c>
     </row>
     <row r="71">
@@ -5899,7 +6354,7 @@
         <v>2026-01-14T15:37:17.562Z</v>
       </c>
       <c r="T71" t="str">
-        <v>2026-08-02T17:46:51.885Z</v>
+        <v>2026-08-02T18:31:03.340Z</v>
       </c>
     </row>
     <row r="72">
@@ -5961,7 +6416,7 @@
         <v>2026-01-14T15:26:08.566Z</v>
       </c>
       <c r="T72" t="str">
-        <v>2026-08-02T17:46:51.885Z</v>
+        <v>2026-08-02T18:31:03.340Z</v>
       </c>
     </row>
     <row r="73">
@@ -6020,7 +6475,7 @@
         <v>["https://lh3.googleusercontent.com/a-/ALV-UjX1CoTz92K_REISpy2kSrmfkUl8O2_fiev-hVBoxR0mWvdo3xi9hg=w36-h36-p-rp-mo-br100"]</v>
       </c>
       <c r="T73" t="str">
-        <v>2026-08-02T17:46:51.886Z</v>
+        <v>2026-08-02T18:31:03.340Z</v>
       </c>
     </row>
     <row r="74">
@@ -6082,7 +6537,7 @@
         <v>2026-06-15T13:04:41.344Z</v>
       </c>
       <c r="T74" t="str">
-        <v>2026-08-02T17:46:51.886Z</v>
+        <v>2026-08-02T18:31:03.340Z</v>
       </c>
     </row>
     <row r="75">
@@ -6144,7 +6599,7 @@
         <v>2026-05-25T17:13:36.799Z</v>
       </c>
       <c r="T75" t="str">
-        <v>2026-08-02T17:46:51.886Z</v>
+        <v>2026-08-02T18:31:03.340Z</v>
       </c>
     </row>
     <row r="76">
@@ -6206,7 +6661,7 @@
         <v>2026-06-03T16:50:09.620Z</v>
       </c>
       <c r="T76" t="str">
-        <v>2026-08-02T17:46:51.886Z</v>
+        <v>2026-08-02T18:31:03.340Z</v>
       </c>
     </row>
     <row r="77">
@@ -6268,7 +6723,7 @@
         <v>2026-04-21T05:25:07.829Z</v>
       </c>
       <c r="T77" t="str">
-        <v>2026-08-02T17:46:51.886Z</v>
+        <v>2026-08-02T18:31:03.340Z</v>
       </c>
     </row>
     <row r="78">
@@ -6330,7 +6785,7 @@
         <v>2026-02-27T10:36:46.583Z</v>
       </c>
       <c r="T78" t="str">
-        <v>2026-08-02T17:46:51.886Z</v>
+        <v>2026-08-02T18:31:03.340Z</v>
       </c>
     </row>
     <row r="79">
@@ -6392,7 +6847,7 @@
         <v>2026-01-28T10:36:46.583Z</v>
       </c>
       <c r="T79" t="str">
-        <v>2026-08-02T17:46:51.886Z</v>
+        <v>2026-08-02T18:31:03.340Z</v>
       </c>
     </row>
     <row r="80">
@@ -6433,7 +6888,7 @@
         <v>apify</v>
       </c>
       <c r="M80" t="str">
-        <v>2026-08-02T17:46:41.553Z</v>
+        <v>2026-08-02T18:30:53.311Z</v>
       </c>
       <c r="N80" t="str">
         <v>[]</v>
@@ -6442,19 +6897,19 @@
         <v>Good desserts 🤤🤤🤤🤤🤤🤤</v>
       </c>
       <c r="P80" t="str">
-        <v>2026-08-02T17:46:41.553Z</v>
+        <v>2026-08-02T18:30:53.311Z</v>
       </c>
       <c r="Q80" t="str">
-        <v>2026-08-02T17:46:44.505Z</v>
+        <v>2026-08-02T18:30:56.271Z</v>
       </c>
       <c r="R80" t="str">
         <v>[]</v>
       </c>
       <c r="S80" t="str">
-        <v>2026-07-03T17:46:22.868Z</v>
+        <v>2026-07-03T18:30:33.189Z</v>
       </c>
       <c r="T80" t="str">
-        <v>2026-08-02T17:46:51.886Z</v>
+        <v>2026-08-02T18:31:03.340Z</v>
       </c>
     </row>
     <row r="81">
@@ -6495,7 +6950,7 @@
         <v>apify</v>
       </c>
       <c r="M81" t="str">
-        <v>2026-08-02T17:46:41.553Z</v>
+        <v>2026-08-02T18:30:53.311Z</v>
       </c>
       <c r="N81" t="str">
         <v>[]</v>
@@ -6504,19 +6959,19 @@
         <v>Good service</v>
       </c>
       <c r="P81" t="str">
-        <v>2026-08-02T17:46:41.553Z</v>
+        <v>2026-08-02T18:30:53.311Z</v>
       </c>
       <c r="Q81" t="str">
-        <v>2026-08-02T17:46:44.607Z</v>
+        <v>2026-08-02T18:30:56.373Z</v>
       </c>
       <c r="R81" t="str">
         <v>[]</v>
       </c>
       <c r="S81" t="str">
-        <v>2026-07-03T17:46:22.868Z</v>
+        <v>2026-07-03T18:30:33.189Z</v>
       </c>
       <c r="T81" t="str">
-        <v>2026-08-02T17:46:51.886Z</v>
+        <v>2026-08-02T18:31:03.340Z</v>
       </c>
     </row>
     <row r="82">
@@ -6557,7 +7012,7 @@
         <v>apify</v>
       </c>
       <c r="M82" t="str">
-        <v>2026-08-02T17:46:41.553Z</v>
+        <v>2026-08-02T18:30:53.311Z</v>
       </c>
       <c r="N82" t="str">
         <v>[]</v>
@@ -6566,19 +7021,19 @@
         <v>Brownie was super appetising!!!</v>
       </c>
       <c r="P82" t="str">
-        <v>2026-08-02T17:46:41.553Z</v>
+        <v>2026-08-02T18:30:53.311Z</v>
       </c>
       <c r="Q82" t="str">
-        <v>2026-08-02T17:46:43.483Z</v>
+        <v>2026-08-02T18:30:55.251Z</v>
       </c>
       <c r="R82" t="str">
         <v>[]</v>
       </c>
       <c r="S82" t="str">
-        <v>2026-07-03T17:46:20.629Z</v>
+        <v>2026-07-03T18:30:30.935Z</v>
       </c>
       <c r="T82" t="str">
-        <v>2026-08-02T17:46:51.886Z</v>
+        <v>2026-08-02T18:31:03.340Z</v>
       </c>
     </row>
     <row r="83">
@@ -6619,7 +7074,7 @@
         <v>apify</v>
       </c>
       <c r="M83" t="str">
-        <v>2026-08-02T17:46:41.553Z</v>
+        <v>2026-08-02T18:30:53.311Z</v>
       </c>
       <c r="N83" t="str">
         <v>[]</v>
@@ -6628,19 +7083,19 @@
         <v>Always good 👍 …</v>
       </c>
       <c r="P83" t="str">
-        <v>2026-08-02T17:46:41.553Z</v>
+        <v>2026-08-02T18:30:53.311Z</v>
       </c>
       <c r="Q83" t="str">
-        <v>2026-08-02T17:46:43.586Z</v>
+        <v>2026-08-02T18:30:55.359Z</v>
       </c>
       <c r="R83" t="str">
         <v>[]</v>
       </c>
       <c r="S83" t="str">
-        <v>2026-07-03T17:46:20.629Z</v>
+        <v>2026-07-03T18:30:30.935Z</v>
       </c>
       <c r="T83" t="str">
-        <v>2026-08-02T17:46:51.886Z</v>
+        <v>2026-08-02T18:31:03.340Z</v>
       </c>
     </row>
     <row r="84">
@@ -6681,7 +7136,7 @@
         <v>apify</v>
       </c>
       <c r="M84" t="str">
-        <v>2026-08-02T17:46:41.553Z</v>
+        <v>2026-08-02T18:30:53.311Z</v>
       </c>
       <c r="N84" t="str">
         <v>[]</v>
@@ -6690,19 +7145,19 @@
         <v>I ordered a two-tier customized cake for my daughter's birthday, and it was absolutely amazing! The cake tasted delicious, and the customization was done beautifully, exactly as requested. The team was very responsive throughout the process, and the delivery was right on time. Thank you, Chocolate Mine, for making our special day even more memorable!</v>
       </c>
       <c r="P84" t="str">
-        <v>2026-08-02T17:46:41.553Z</v>
+        <v>2026-08-02T18:30:53.311Z</v>
       </c>
       <c r="Q84" t="str">
-        <v>2026-08-02T17:46:43.689Z</v>
+        <v>2026-08-02T18:30:55.456Z</v>
       </c>
       <c r="R84" t="str">
         <v>["https://lh3.googleusercontent.com/grass-cs/ACvplmMaK-dnXvNR14M9LIGkk7FN2aRHM30FBsYTJOik5O9rNIXKSo9B1R1iKHSoxcz9UER6O3l8xWUF7qTA1OqCkFXPs_mte6lXcD4A9rB7366E47WJLb1MxrfLJShTtSomBdDiyUKdXAotmRvm=w300-h225-p-k-no","https://lh3.googleusercontent.com/grass-cs/ACvplmOYZR9CLhI8X2bpM9zsIE6IYWaqqZna4v1o1wZOkmFlEqswyPWzwT4pjKBkffu5vCQLRBUzTMhxP-e84z9NtB7h0xFYFuWiX_sf6JLz3RqnUm5EE3-vKLHAAPjvOqBOgGlARPf0FIB9V1M=w300-h225-p-k-no","https://lh3.googleusercontent.com/grass-cs/ACvplmM6QUO1EhMXTbezTHTGWWMftekKXqyM2EAs5dK5mRy-5hEQ9q3yYgntI1BmJ7pMKRc6qg5vhLHDKZtP-2TdcKxfPb_PFnWPTXx9agk3jkZ064qVYmgjb4SCneKInNIrebtv0geIxh7dJQvF=w300-h225-p-k-no","https://lh3.googleusercontent.com/grass-cs/ACvplmPMS4RF9rvmkCDRobFjyuSLHevCNSiXaQBsA0MXtmVvlstkeC-D7oJfztd25qX_i1sXaxvMz_xoameV67sonH4tavZPo81V3r5NGOOzvpl_72vCB-6ljaY3dSURFLV6qPc7jttItQOE0gQY=w300-h225-p-k-no"]</v>
       </c>
       <c r="S84" t="str">
-        <v>2026-07-03T17:46:20.629Z</v>
+        <v>2026-07-03T18:30:30.935Z</v>
       </c>
       <c r="T84" t="str">
-        <v>2026-08-02T17:46:51.886Z</v>
+        <v>2026-08-02T18:31:03.340Z</v>
       </c>
     </row>
     <row r="85">
@@ -6743,7 +7198,7 @@
         <v>apify</v>
       </c>
       <c r="M85" t="str">
-        <v>2026-08-02T17:46:41.553Z</v>
+        <v>2026-08-02T18:30:53.311Z</v>
       </c>
       <c r="N85" t="str">
         <v>[]</v>
@@ -6752,19 +7207,19 @@
         <v>Good desserts with calm atmosphere</v>
       </c>
       <c r="P85" t="str">
-        <v>2026-08-02T17:46:41.553Z</v>
+        <v>2026-08-02T18:30:53.311Z</v>
       </c>
       <c r="Q85" t="str">
-        <v>2026-08-02T17:46:43.768Z</v>
+        <v>2026-08-02T18:30:55.559Z</v>
       </c>
       <c r="R85" t="str">
         <v>[]</v>
       </c>
       <c r="S85" t="str">
-        <v>2026-07-03T17:46:20.629Z</v>
+        <v>2026-07-03T18:30:30.935Z</v>
       </c>
       <c r="T85" t="str">
-        <v>2026-08-02T17:46:51.886Z</v>
+        <v>2026-08-02T18:31:03.340Z</v>
       </c>
     </row>
     <row r="86">
@@ -6805,7 +7260,7 @@
         <v>apify</v>
       </c>
       <c r="M86" t="str">
-        <v>2026-08-02T17:46:41.553Z</v>
+        <v>2026-08-02T18:30:53.311Z</v>
       </c>
       <c r="N86" t="str">
         <v>[]</v>
@@ -6814,19 +7269,19 @@
         <v>Extraordinary ambience and wonderful service</v>
       </c>
       <c r="P86" t="str">
-        <v>2026-08-02T17:46:41.553Z</v>
+        <v>2026-08-02T18:30:53.311Z</v>
       </c>
       <c r="Q86" t="str">
-        <v>2026-08-02T17:46:43.895Z</v>
+        <v>2026-08-02T18:30:55.720Z</v>
       </c>
       <c r="R86" t="str">
         <v>[]</v>
       </c>
       <c r="S86" t="str">
-        <v>2026-07-03T17:46:20.629Z</v>
+        <v>2026-07-03T18:30:30.935Z</v>
       </c>
       <c r="T86" t="str">
-        <v>2026-08-02T17:46:51.886Z</v>
+        <v>2026-08-02T18:31:03.340Z</v>
       </c>
     </row>
     <row r="87">
@@ -6867,7 +7322,7 @@
         <v>apify</v>
       </c>
       <c r="M87" t="str">
-        <v>2026-08-02T17:46:41.553Z</v>
+        <v>2026-08-02T18:30:53.311Z</v>
       </c>
       <c r="N87" t="str">
         <v>[]</v>
@@ -6876,19 +7331,19 @@
         <v>Nice food.Thank you chocolate mine for your wonderful service.</v>
       </c>
       <c r="P87" t="str">
-        <v>2026-08-02T17:46:41.553Z</v>
+        <v>2026-08-02T18:30:53.311Z</v>
       </c>
       <c r="Q87" t="str">
-        <v>2026-08-02T17:46:43.960Z</v>
+        <v>2026-08-02T18:30:55.786Z</v>
       </c>
       <c r="R87" t="str">
         <v>[]</v>
       </c>
       <c r="S87" t="str">
-        <v>2026-07-03T17:46:22.868Z</v>
+        <v>2026-07-03T18:30:33.189Z</v>
       </c>
       <c r="T87" t="str">
-        <v>2026-08-02T17:46:51.886Z</v>
+        <v>2026-08-02T18:31:03.340Z</v>
       </c>
     </row>
     <row r="88">
@@ -6929,7 +7384,7 @@
         <v>apify</v>
       </c>
       <c r="M88" t="str">
-        <v>2026-08-02T17:46:41.553Z</v>
+        <v>2026-08-02T18:30:53.311Z</v>
       </c>
       <c r="N88" t="str">
         <v>[]</v>
@@ -6938,19 +7393,19 @@
         <v>Tried the Tres Leches Lotus Biscoff….which was very yummy. A good ambience with eggless cake ,waffles , shakes ,sandwiches , sundaes etc.</v>
       </c>
       <c r="P88" t="str">
-        <v>2026-08-02T17:46:41.553Z</v>
+        <v>2026-08-02T18:30:53.311Z</v>
       </c>
       <c r="Q88" t="str">
-        <v>2026-08-02T17:46:44.099Z</v>
+        <v>2026-08-02T18:30:55.838Z</v>
       </c>
       <c r="R88" t="str">
         <v>[]</v>
       </c>
       <c r="S88" t="str">
-        <v>2026-07-03T17:46:22.868Z</v>
+        <v>2026-07-03T18:30:33.189Z</v>
       </c>
       <c r="T88" t="str">
-        <v>2026-08-02T17:46:51.886Z</v>
+        <v>2026-08-02T18:31:03.340Z</v>
       </c>
     </row>
     <row r="89">
@@ -6991,7 +7446,7 @@
         <v>apify</v>
       </c>
       <c r="M89" t="str">
-        <v>2026-08-02T17:46:41.553Z</v>
+        <v>2026-08-02T18:30:53.311Z</v>
       </c>
       <c r="N89" t="str">
         <v>[]</v>
@@ -7000,19 +7455,19 @@
         <v>Peak milk cake…. Would come again fosho</v>
       </c>
       <c r="P89" t="str">
-        <v>2026-08-02T17:46:41.553Z</v>
+        <v>2026-08-02T18:30:53.311Z</v>
       </c>
       <c r="Q89" t="str">
-        <v>2026-08-02T17:46:44.202Z</v>
+        <v>2026-08-02T18:30:55.963Z</v>
       </c>
       <c r="R89" t="str">
         <v>[]</v>
       </c>
       <c r="S89" t="str">
-        <v>2026-07-03T17:46:22.868Z</v>
+        <v>2026-07-03T18:30:33.189Z</v>
       </c>
       <c r="T89" t="str">
-        <v>2026-08-02T17:46:51.886Z</v>
+        <v>2026-08-02T18:31:03.340Z</v>
       </c>
     </row>
     <row r="90">
@@ -7053,7 +7508,7 @@
         <v>apify</v>
       </c>
       <c r="M90" t="str">
-        <v>2026-08-02T17:46:41.553Z</v>
+        <v>2026-08-02T18:30:53.311Z</v>
       </c>
       <c r="N90" t="str">
         <v>[]</v>
@@ -7062,19 +7517,19 @@
         <v>Tres leches is very tasty....</v>
       </c>
       <c r="P90" t="str">
-        <v>2026-08-02T17:46:41.553Z</v>
+        <v>2026-08-02T18:30:53.311Z</v>
       </c>
       <c r="Q90" t="str">
-        <v>2026-08-02T17:46:44.303Z</v>
+        <v>2026-08-02T18:30:56.066Z</v>
       </c>
       <c r="R90" t="str">
         <v>[]</v>
       </c>
       <c r="S90" t="str">
-        <v>2026-07-03T17:46:22.868Z</v>
+        <v>2026-07-03T18:30:33.189Z</v>
       </c>
       <c r="T90" t="str">
-        <v>2026-08-02T17:46:51.886Z</v>
+        <v>2026-08-02T18:31:03.340Z</v>
       </c>
     </row>
     <row r="91">
@@ -7115,7 +7570,7 @@
         <v>apify</v>
       </c>
       <c r="M91" t="str">
-        <v>2026-08-02T17:46:41.553Z</v>
+        <v>2026-08-02T18:30:53.311Z</v>
       </c>
       <c r="N91" t="str">
         <v>[]</v>
@@ -7124,19 +7579,19 @@
         <v>a month agoOrder typeDine inMeal typeOtherPrice per person₹400–600Wait timeNo waitRecommendation for vegetariansHighly recommendVegetarian offeringsMenu is all vegetarianLike</v>
       </c>
       <c r="P91" t="str">
-        <v>2026-08-02T17:46:41.553Z</v>
+        <v>2026-08-02T18:30:53.311Z</v>
       </c>
       <c r="Q91" t="str">
-        <v>2026-08-02T17:46:44.406Z</v>
+        <v>2026-08-02T18:30:56.168Z</v>
       </c>
       <c r="R91" t="str">
         <v>["https://lh3.googleusercontent.com/grass-cs/ACvplmMwSUyxZuDC8KDV3xkUrKB3x96ltdl531HnYFsx9iVC6HwrOMg4Ntv6Caii22JKbl0uRb9ZhO3ZIC8bHqFenbLXwGHgkV4jKwlNm9lTBTwN0cbkK46VA45ldkp2p61t1V3yKYvotkaTA1c=w600-h450-p-k-no"]</v>
       </c>
       <c r="S91" t="str">
-        <v>2026-07-03T17:46:22.868Z</v>
+        <v>2026-07-03T18:30:33.189Z</v>
       </c>
       <c r="T91" t="str">
-        <v>2026-08-02T17:46:51.886Z</v>
+        <v>2026-08-02T18:31:03.340Z</v>
       </c>
     </row>
     <row r="92">
@@ -7177,7 +7632,7 @@
         <v>apify</v>
       </c>
       <c r="M92" t="str">
-        <v>2026-08-02T17:46:41.553Z</v>
+        <v>2026-08-02T18:30:53.311Z</v>
       </c>
       <c r="N92" t="str">
         <v>[]</v>
@@ -7186,19 +7641,19 @@
         <v>Good</v>
       </c>
       <c r="P92" t="str">
-        <v>2026-08-02T17:46:41.553Z</v>
+        <v>2026-08-02T18:30:53.311Z</v>
       </c>
       <c r="Q92" t="str">
-        <v>2026-08-02T17:46:43.342Z</v>
+        <v>2026-08-02T18:30:55.144Z</v>
       </c>
       <c r="R92" t="str">
         <v>[]</v>
       </c>
       <c r="S92" t="str">
-        <v>2026-07-03T17:46:20.629Z</v>
+        <v>2026-07-03T18:30:30.935Z</v>
       </c>
       <c r="T92" t="str">
-        <v>2026-08-02T17:46:51.886Z</v>
+        <v>2026-08-02T18:31:03.340Z</v>
       </c>
     </row>
     <row r="93">
@@ -7260,7 +7715,7 @@
         <v>2026-06-20T06:58:37.945Z</v>
       </c>
       <c r="T93" t="str">
-        <v>2026-08-02T17:46:51.886Z</v>
+        <v>2026-08-02T18:31:03.340Z</v>
       </c>
     </row>
     <row r="94">
@@ -7322,7 +7777,7 @@
         <v>2026-06-06T13:17:22.024Z</v>
       </c>
       <c r="T94" t="str">
-        <v>2026-08-02T17:46:51.886Z</v>
+        <v>2026-08-02T18:31:03.340Z</v>
       </c>
     </row>
     <row r="95">
@@ -7363,7 +7818,7 @@
         <v>apify</v>
       </c>
       <c r="M95" t="str">
-        <v>2026-08-02T17:46:41.553Z</v>
+        <v>2026-08-02T18:30:53.311Z</v>
       </c>
       <c r="N95" t="str">
         <v>[]</v>
@@ -7372,19 +7827,19 @@
         <v>Cake mine is good. Kids love the cakes here</v>
       </c>
       <c r="P95" t="str">
-        <v>2026-08-02T17:46:41.553Z</v>
+        <v>2026-08-02T18:30:53.311Z</v>
       </c>
       <c r="Q95" t="str">
-        <v>2026-08-02T17:46:43.279Z</v>
+        <v>2026-08-02T18:30:55.041Z</v>
       </c>
       <c r="R95" t="str">
         <v>[]</v>
       </c>
       <c r="S95" t="str">
-        <v>2026-07-03T17:46:20.629Z</v>
+        <v>2026-07-03T18:30:30.935Z</v>
       </c>
       <c r="T95" t="str">
-        <v>2026-08-02T17:46:51.886Z</v>
+        <v>2026-08-02T18:31:03.341Z</v>
       </c>
     </row>
     <row r="96">
@@ -7446,7 +7901,7 @@
         <v>2026-07-01T16:29:51.259Z</v>
       </c>
       <c r="T96" t="str">
-        <v>2026-08-02T17:46:51.886Z</v>
+        <v>2026-08-02T18:31:03.341Z</v>
       </c>
     </row>
     <row r="97">
@@ -7487,7 +7942,7 @@
         <v>apify</v>
       </c>
       <c r="M97" t="str">
-        <v>2026-08-02T17:46:41.553Z</v>
+        <v>2026-08-02T18:30:53.311Z</v>
       </c>
       <c r="N97" t="str">
         <v>[]</v>
@@ -7496,19 +7951,19 @@
         <v>Belgian chocolate is a must try ❤️</v>
       </c>
       <c r="P97" t="str">
-        <v>2026-08-02T17:46:41.553Z</v>
+        <v>2026-08-02T18:30:53.311Z</v>
       </c>
       <c r="Q97" t="str">
-        <v>2026-08-02T17:46:43.177Z</v>
+        <v>2026-08-02T18:30:54.941Z</v>
       </c>
       <c r="R97" t="str">
         <v>["https://lh3.googleusercontent.com/grass-cs/ACvplmOkgPjySRE7wIakNrMXViE1gpuY08R20tW4cBcCe1IT98sFt-1aTq4VEFmAE7vF4B330YNgsIVszRznxTWeCc0VcGtUf9smDPj5ZjISa9xfEqmMetE9MNe-ZcmYvjsfW3WopiP-jwluBV5v=w600-h450-p-k-no"]</v>
       </c>
       <c r="S97" t="str">
-        <v>2026-07-03T17:46:20.629Z</v>
+        <v>2026-07-03T18:30:30.935Z</v>
       </c>
       <c r="T97" t="str">
-        <v>2026-08-02T17:46:51.886Z</v>
+        <v>2026-08-02T18:31:03.341Z</v>
       </c>
     </row>
     <row r="98">
@@ -7549,7 +8004,7 @@
         <v>apify</v>
       </c>
       <c r="M98" t="str">
-        <v>2026-08-02T17:46:41.553Z</v>
+        <v>2026-08-02T18:30:53.311Z</v>
       </c>
       <c r="N98" t="str">
         <v>[]</v>
@@ -7558,19 +8013,19 @@
         <v>Veryyy good and tasty!!!!</v>
       </c>
       <c r="P98" t="str">
-        <v>2026-08-02T17:46:41.553Z</v>
+        <v>2026-08-02T18:30:53.311Z</v>
       </c>
       <c r="Q98" t="str">
-        <v>2026-08-02T17:46:42.973Z</v>
+        <v>2026-08-02T18:30:54.731Z</v>
       </c>
       <c r="R98" t="str">
         <v>["https://lh3.googleusercontent.com/grass-cs/ACvplmNbEkU69ERfyprZOnd3ce4a8jikXMVgNW1mdz4D69wljnvina7fNCC0UmN_5GsX4teH8aQncXdkZa6CqKu9R2Irr1DCH2lRhU2QW_0CjmGV4hESKUqE8H9mdwEhN2i0PD7KntHVCjfDPKRr=w600-h450-p-k-no"]</v>
       </c>
       <c r="S98" t="str">
-        <v>2026-07-05T17:46:18.717Z</v>
+        <v>2026-07-05T18:30:28.538Z</v>
       </c>
       <c r="T98" t="str">
-        <v>2026-08-02T17:46:51.887Z</v>
+        <v>2026-08-02T18:31:03.341Z</v>
       </c>
     </row>
     <row r="99">
@@ -7611,7 +8066,7 @@
         <v>apify</v>
       </c>
       <c r="M99" t="str">
-        <v>2026-08-02T17:46:41.553Z</v>
+        <v>2026-08-02T18:30:53.311Z</v>
       </c>
       <c r="N99" t="str">
         <v>[]</v>
@@ -7620,10 +8075,10 @@
         <v>Premium quality and taste</v>
       </c>
       <c r="P99" t="str">
-        <v>2026-08-02T17:46:41.553Z</v>
+        <v>2026-08-02T18:30:53.311Z</v>
       </c>
       <c r="Q99" t="str">
-        <v>2026-08-02T17:46:43.075Z</v>
+        <v>2026-08-02T18:30:54.837Z</v>
       </c>
       <c r="R99" t="str">
         <v>["https://lh3.googleusercontent.com/grass-cs/ACvplmN5ouJ7eQ0jDV3rqAledmzeWOv_REbYTFSnqVAIJ7XY7Ynw6qL-JBZaxTFqpxwIcjj24_xkuh0zXfcs5NR2bc6seJsCkeUmrvmHxr8OilQjq6OzCxSjBaAY9I3MMZ-mRPAasiFf79WQlKef=w600-h450-p-k-no"]</v>
@@ -7632,7 +8087,7 @@
         <v/>
       </c>
       <c r="T99" t="str">
-        <v>2026-08-02T17:46:51.887Z</v>
+        <v>2026-08-02T18:31:03.341Z</v>
       </c>
     </row>
     <row r="100">
@@ -7673,7 +8128,7 @@
         <v>apify</v>
       </c>
       <c r="M100" t="str">
-        <v>2026-08-02T17:46:41.553Z</v>
+        <v>2026-08-02T18:30:53.311Z</v>
       </c>
       <c r="N100" t="str">
         <v>[]</v>
@@ -7682,19 +8137,19 @@
         <v>Everything was perfect! The packaging was neat and secure, and the cake was fresh and looked beautiful. The taste was absolutely amazing-soft, rich, and so delicious. Everyone loved it. Thank you so much for this wonderful cake! Will definitely order again ma'am. ❤️Highly recommended</v>
       </c>
       <c r="P100" t="str">
-        <v>2026-08-02T17:46:41.553Z</v>
+        <v>2026-08-02T18:30:53.311Z</v>
       </c>
       <c r="Q100" t="str">
-        <v>2026-08-02T17:46:42.358Z</v>
+        <v>2026-08-02T18:30:54.018Z</v>
       </c>
       <c r="R100" t="str">
         <v>["https://lh3.googleusercontent.com/grass-cs/ACvplmP2YkBSVGgI3pHvwSFM3gYJ9Ec7QucpLRuXOqeMut6eXk_P38NBQSF9VaEXopebIcFeQ722fg5x8xEsWZdCqx8zSsindkbeURPzvY5smW1Mxahwy6Q6TTORRNxdRDlXCDNj1syWBFZ9c7yx=w300-h450-p-k-no","https://lh3.googleusercontent.com/grass-cs/ACvplmMdWn3xvNVvUP0XvziW-DjXGp-7ECFCPJR_9Rha9G9xISw-yGJPPp_4exu8bi0JxGsGxP0Q_Lq4WIsRhD689-jg64ynSSeMtGth0lcRH91JQ56ChFu9fqDmvbqh_E4p2N1Hja5Atto1x1s7=w300-h450-p-k-no"]</v>
       </c>
       <c r="S100" t="str">
-        <v>2026-07-12T17:46:18.717Z</v>
+        <v>2026-07-12T18:30:28.538Z</v>
       </c>
       <c r="T100" t="str">
-        <v>2026-08-02T17:46:51.887Z</v>
+        <v>2026-08-02T18:31:03.341Z</v>
       </c>
     </row>
     <row r="101">
@@ -7735,7 +8190,7 @@
         <v>apify</v>
       </c>
       <c r="M101" t="str">
-        <v>2026-08-02T17:46:41.553Z</v>
+        <v>2026-08-02T18:30:53.311Z</v>
       </c>
       <c r="N101" t="str">
         <v>[]</v>
@@ -7744,19 +8199,19 @@
         <v>We have ordered the cake, for my daughter's 1st birthday celebration.. The cake tastes too good and their service was speechless.. once again thank you so much..</v>
       </c>
       <c r="P101" t="str">
-        <v>2026-08-02T17:46:41.553Z</v>
+        <v>2026-08-02T18:30:53.311Z</v>
       </c>
       <c r="Q101" t="str">
-        <v>2026-08-02T17:46:42.424Z</v>
+        <v>2026-08-02T18:30:54.121Z</v>
       </c>
       <c r="R101" t="str">
         <v>[]</v>
       </c>
       <c r="S101" t="str">
-        <v>2026-07-12T17:46:18.717Z</v>
+        <v>2026-07-12T18:30:28.538Z</v>
       </c>
       <c r="T101" t="str">
-        <v>2026-08-02T17:46:51.887Z</v>
+        <v>2026-08-02T18:31:03.341Z</v>
       </c>
     </row>
     <row r="102">
@@ -7797,7 +8252,7 @@
         <v>apify</v>
       </c>
       <c r="M102" t="str">
-        <v>2026-08-02T17:46:41.553Z</v>
+        <v>2026-08-02T18:30:53.311Z</v>
       </c>
       <c r="N102" t="str">
         <v>[]</v>
@@ -7806,19 +8261,19 @@
         <v>Super happy with the cake! I ordered it last night, and it was delivered today exactly as I requested. Great quality and service! 🤸🏽🤠✌🏽:)) …</v>
       </c>
       <c r="P102" t="str">
-        <v>2026-08-02T17:46:41.553Z</v>
+        <v>2026-08-02T18:30:53.311Z</v>
       </c>
       <c r="Q102" t="str">
-        <v>2026-08-02T17:46:42.499Z</v>
+        <v>2026-08-02T18:30:54.223Z</v>
       </c>
       <c r="R102" t="str">
         <v>["https://lh3.googleusercontent.com/grass-cs/ACvplmN-fZ4ZbA56LmNiHVlExrbqgANFAZMy8bqKwQL2NZQoPLvsH32nLMA8NdeOB0u3oUSm80MLB3LqUA_CilitL9CMi_-quzFH8w85r3M8mAkOZ81DYaLY87FPXWd43Jpk0USLvFk1dmP2f3Iv=w300-h450-p-k-no","https://lh3.googleusercontent.com/grass-cs/ACvplmOvlC9uxrUItjnZMY3rJESOjaRKkYAWwWKCD5Cx_8PbUpHfm0q2au8j8QH8TmXiFVemOKjjz4UKPb0CG0nANcdYulKJZbQTDPeV4QEL1L-8YwJGJxz8TJoTL3A-fjs3_5LB9er8fXo6qrsf=w300-h450-p-k-no"]</v>
       </c>
       <c r="S102" t="str">
-        <v>2026-07-12T17:46:18.717Z</v>
+        <v>2026-07-12T18:30:28.538Z</v>
       </c>
       <c r="T102" t="str">
-        <v>2026-08-02T17:46:51.887Z</v>
+        <v>2026-08-02T18:31:03.341Z</v>
       </c>
     </row>
     <row r="103">
@@ -7859,7 +8314,7 @@
         <v>apify</v>
       </c>
       <c r="M103" t="str">
-        <v>2026-08-02T17:46:41.553Z</v>
+        <v>2026-08-02T18:30:53.311Z</v>
       </c>
       <c r="N103" t="str">
         <v>[]</v>
@@ -7868,19 +8323,19 @@
         <v>The cake was absolutely delicious! It tasted fresh, had the perfect level of sweetness, and everyone loved it. Thank you for making my son's birthday extra special. Highly recommended!</v>
       </c>
       <c r="P103" t="str">
-        <v>2026-08-02T17:46:41.553Z</v>
+        <v>2026-08-02T18:30:53.311Z</v>
       </c>
       <c r="Q103" t="str">
-        <v>2026-08-02T17:46:42.579Z</v>
+        <v>2026-08-02T18:30:54.326Z</v>
       </c>
       <c r="R103" t="str">
         <v>["https://lh3.googleusercontent.com/grass-cs/ACvplmMeRXm0SSD5mteNu-lgaN_YaRFYN91719zu6BfGSwoZYP6sa-TJye-lHTw4H4s7BM_O4TkhfXuZt-FL3CdqPgZsCYXS4xTdJIWn3q_vLQBKYOuHopXOxlxxl7V0q11KKMDMpYeS2rwxqE57=w600-h450-p-k-no"]</v>
       </c>
       <c r="S103" t="str">
-        <v>2026-07-12T17:46:18.717Z</v>
+        <v>2026-07-12T18:30:28.538Z</v>
       </c>
       <c r="T103" t="str">
-        <v>2026-08-02T17:46:51.887Z</v>
+        <v>2026-08-02T18:31:03.341Z</v>
       </c>
     </row>
     <row r="104">
@@ -7921,7 +8376,7 @@
         <v>apify</v>
       </c>
       <c r="M104" t="str">
-        <v>2026-08-02T17:46:41.553Z</v>
+        <v>2026-08-02T18:30:53.311Z</v>
       </c>
       <c r="N104" t="str">
         <v>[]</v>
@@ -7930,19 +8385,19 @@
         <v>Absolutely love this place! Ordered a chocolate truffle cake on very short notice and they came through beautifully. The taste was fantastic and the design was lovely too. Highly recommend to anyone looking for a truly special cake!</v>
       </c>
       <c r="P104" t="str">
-        <v>2026-08-02T17:46:41.553Z</v>
+        <v>2026-08-02T18:30:53.311Z</v>
       </c>
       <c r="Q104" t="str">
-        <v>2026-08-02T17:46:42.666Z</v>
+        <v>2026-08-02T18:30:54.429Z</v>
       </c>
       <c r="R104" t="str">
         <v>[]</v>
       </c>
       <c r="S104" t="str">
-        <v>2026-07-12T17:46:18.717Z</v>
+        <v>2026-07-12T18:30:28.538Z</v>
       </c>
       <c r="T104" t="str">
-        <v>2026-08-02T17:46:51.887Z</v>
+        <v>2026-08-02T18:31:03.341Z</v>
       </c>
     </row>
     <row r="105">
@@ -7983,7 +8438,7 @@
         <v>apify</v>
       </c>
       <c r="M105" t="str">
-        <v>2026-08-02T17:46:41.553Z</v>
+        <v>2026-08-02T18:30:53.311Z</v>
       </c>
       <c r="N105" t="str">
         <v>[]</v>
@@ -7992,19 +8447,19 @@
         <v>The taste was top-notch, the communication and delivery is hassle free. I would definitely order further. Thank you Chocolate mine</v>
       </c>
       <c r="P105" t="str">
-        <v>2026-08-02T17:46:41.553Z</v>
+        <v>2026-08-02T18:30:53.311Z</v>
       </c>
       <c r="Q105" t="str">
-        <v>2026-08-02T17:46:42.768Z</v>
+        <v>2026-08-02T18:30:54.530Z</v>
       </c>
       <c r="R105" t="str">
         <v>["https://lh3.googleusercontent.com/grass-cs/ACvplmMYbf3lUetX9-BmZqKHSU1S1c6HZqIdYH_S-_WQC1eER29Hc3vH0R68Tt7W8Cmi6gRgUpLcb3_kCKobYOnLMCJky9YYBtVjE1oPSoQVxJzwGJBXI4r85UJvKjk49rf7GtnmaXYWCL5yrJo=w300-h450-p-k-no","https://lh3.googleusercontent.com/grass-cs/ACvplmMfT5aWOXYVMky5tDsUIf1jZcEqaHrdzejhuI1RzxOLjpRSE4Pv8YFFlWxcLHOL3KQZj_KQpSp7-kro1W7bLmmVRWWEYMbeEvN4Tvg73FUKsvuG_RkYgYz3ATf9ElcG6HVnawHw8Eu2-RA=w300-h450-p-k-no"]</v>
       </c>
       <c r="S105" t="str">
-        <v>2026-07-12T17:46:18.717Z</v>
+        <v>2026-07-12T18:30:28.538Z</v>
       </c>
       <c r="T105" t="str">
-        <v>2026-08-02T17:46:51.887Z</v>
+        <v>2026-08-02T18:31:03.341Z</v>
       </c>
     </row>
     <row r="106">
@@ -8066,7 +8521,7 @@
         <v>2026-07-10T16:29:46.315Z</v>
       </c>
       <c r="T106" t="str">
-        <v>2026-08-02T17:46:51.887Z</v>
+        <v>2026-08-02T18:31:03.341Z</v>
       </c>
     </row>
     <row r="107">
@@ -8107,7 +8562,7 @@
         <v>apify</v>
       </c>
       <c r="M107" t="str">
-        <v>2026-08-02T17:46:41.553Z</v>
+        <v>2026-08-02T18:30:53.311Z</v>
       </c>
       <c r="N107" t="str">
         <v>[]</v>
@@ -8116,19 +8571,19 @@
         <v>I like the ambience of the shop and the food are tasty, personally highly recommend this shop</v>
       </c>
       <c r="P107" t="str">
-        <v>2026-08-02T17:46:41.552Z</v>
+        <v>2026-08-02T18:30:53.311Z</v>
       </c>
       <c r="Q107" t="str">
-        <v>2026-08-02T17:46:42.255Z</v>
+        <v>2026-08-02T18:30:53.916Z</v>
       </c>
       <c r="R107" t="str">
         <v>[]</v>
       </c>
       <c r="S107" t="str">
-        <v>2026-07-12T17:46:16.290Z</v>
+        <v>2026-07-12T18:30:26.343Z</v>
       </c>
       <c r="T107" t="str">
-        <v>2026-08-02T17:46:51.887Z</v>
+        <v>2026-08-02T18:31:03.341Z</v>
       </c>
     </row>
     <row r="108">
@@ -8169,7 +8624,7 @@
         <v>apify</v>
       </c>
       <c r="M108" t="str">
-        <v>2026-08-02T17:46:41.552Z</v>
+        <v>2026-08-02T18:30:53.311Z</v>
       </c>
       <c r="N108" t="str">
         <v>[]</v>
@@ -8178,19 +8633,19 @@
         <v>café. Great coffee. Amazing atmosphere. 🤍☕</v>
       </c>
       <c r="P108" t="str">
-        <v>2026-08-02T17:46:41.552Z</v>
+        <v>2026-08-02T18:30:53.311Z</v>
       </c>
       <c r="Q108" t="str">
-        <v>2026-08-02T17:46:42.152Z</v>
+        <v>2026-08-02T18:30:53.812Z</v>
       </c>
       <c r="R108" t="str">
         <v>["https://lh3.googleusercontent.com/grass-cs/ACvplmMMC3yG9rrCB5KYzYoQFN9qW3Yq--_BLFSY9kvW6uX86JRM-rM12lrFY_EOuOQoR_d5kRTn7TKHxSjwEEidH2ybV-b7yCoARYVhTLQZCfcmgJyuyYwl4AnyYK2g6fOchlrQf_8-6QnZ0OEZ=w600-h450-p-k-no"]</v>
       </c>
       <c r="S108" t="str">
-        <v>2026-07-19T17:46:16.290Z</v>
+        <v>2026-07-19T18:30:26.343Z</v>
       </c>
       <c r="T108" t="str">
-        <v>2026-08-02T17:46:51.887Z</v>
+        <v>2026-08-02T18:31:03.341Z</v>
       </c>
     </row>
     <row r="109">
@@ -8231,7 +8686,7 @@
         <v>apify</v>
       </c>
       <c r="M109" t="str">
-        <v>2026-08-02T17:46:41.552Z</v>
+        <v>2026-08-02T18:30:53.311Z</v>
       </c>
       <c r="N109" t="str">
         <v>[]</v>
@@ -8240,19 +8695,19 @@
         <v>Very good... service Approach nice...food and packing delivery timeing also fine.</v>
       </c>
       <c r="P109" t="str">
-        <v>2026-08-02T17:46:41.552Z</v>
+        <v>2026-08-02T18:30:53.311Z</v>
       </c>
       <c r="Q109" t="str">
-        <v>2026-08-02T17:46:42.054Z</v>
+        <v>2026-08-02T18:30:53.711Z</v>
       </c>
       <c r="R109" t="str">
         <v>["https://lh3.googleusercontent.com/grass-cs/ACvplmMMdeI6wHhLMi9cHH0U71XGCOTjTsKmA1ubH89peQ9NTwJCzJOZwcqpGtIBOcnXFH2fFK3j0mDPgF5ZCPnFSfONb1OVF0f6ORDCppErezerC1_vPexGxIz0GOkuDBRjQq0aajoItELXleg=w600-h450-p-k-no"]</v>
       </c>
       <c r="S109" t="str">
-        <v>2026-07-19T17:46:16.290Z</v>
+        <v>2026-07-19T18:30:26.343Z</v>
       </c>
       <c r="T109" t="str">
-        <v>2026-08-02T17:46:51.887Z</v>
+        <v>2026-08-02T18:31:03.341Z</v>
       </c>
     </row>
     <row r="110">
@@ -8314,7 +8769,7 @@
         <v>2026-03-30T18:20:59.728Z</v>
       </c>
       <c r="T110" t="str">
-        <v>2026-08-02T17:46:51.887Z</v>
+        <v>2026-08-02T18:31:03.341Z</v>
       </c>
     </row>
     <row r="111">
@@ -8355,7 +8810,7 @@
         <v>apify</v>
       </c>
       <c r="M111" t="str">
-        <v>2026-08-02T17:46:41.552Z</v>
+        <v>2026-08-02T18:30:53.311Z</v>
       </c>
       <c r="N111" t="str">
         <v>[]</v>
@@ -8364,19 +8819,19 @@
         <v>Hi! We have ordered cake from you for the 3rd time. So satisfied with your cake flavours, the taste is very rich and everlasting thinking about ordering from you next time too😊</v>
       </c>
       <c r="P111" t="str">
-        <v>2026-08-02T17:46:41.552Z</v>
+        <v>2026-08-02T18:30:53.311Z</v>
       </c>
       <c r="Q111" t="str">
-        <v>2026-08-02T17:46:41.950Z</v>
+        <v>2026-08-02T18:30:53.609Z</v>
       </c>
       <c r="R111" t="str">
         <v>["https://lh3.googleusercontent.com/grass-cs/ACvplmM6kT-Te8Zrdt6j12pc0F6CvQJP0d-F4Ydo0WymjwTEPuEDYDaUfUwenrZjT2O_R1CCBHPeZx7Gege1ki_i-IkwLpXB6TGN6nbUl45E_3Uk0MRrw3_UbPXNyDptH1e_1HGK9_4El7RhbNo=w600-h450-p-k-no"]</v>
       </c>
       <c r="S111" t="str">
-        <v>2026-07-26T17:46:16.290Z</v>
+        <v>2026-07-26T18:30:26.343Z</v>
       </c>
       <c r="T111" t="str">
-        <v>2026-08-02T17:46:51.887Z</v>
+        <v>2026-08-02T18:31:03.341Z</v>
       </c>
     </row>
     <row r="112">
@@ -8417,7 +8872,7 @@
         <v>apify</v>
       </c>
       <c r="M112" t="str">
-        <v>2026-08-02T17:46:41.552Z</v>
+        <v>2026-08-02T18:30:53.311Z</v>
       </c>
       <c r="N112" t="str">
         <v>[]</v>
@@ -8426,19 +8881,19 @@
         <v>The cake was awesome and i got it delivered at time</v>
       </c>
       <c r="P112" t="str">
-        <v>2026-08-02T17:46:41.552Z</v>
+        <v>2026-08-02T18:30:53.311Z</v>
       </c>
       <c r="Q112" t="str">
-        <v>2026-08-02T17:46:41.824Z</v>
+        <v>2026-08-02T18:30:53.506Z</v>
       </c>
       <c r="R112" t="str">
         <v>["https://lh3.googleusercontent.com/grass-cs/ACvplmOJ1SE90YCjDxsi9u_Afy2IxrgFsm5_GnHNSa2GpnP_ZhUw12zOUql5dOikgXd5uX9Aee5YbU_37lLczekjr3bQEVQa1Jo4Grll6lP9rK-Xu0_MJ3LsTYTyI1-cZoG7JL_waeabyMlXZugH=w600-h450-p-k-no"]</v>
       </c>
       <c r="S112" t="str">
-        <v>2026-07-27T17:46:16.290Z</v>
+        <v>2026-07-27T18:30:26.343Z</v>
       </c>
       <c r="T112" t="str">
-        <v>2026-08-02T17:46:51.887Z</v>
+        <v>2026-08-02T18:31:03.341Z</v>
       </c>
     </row>
     <row r="113">
@@ -8500,7 +8955,7 @@
         <v>2026-07-27T16:49:55.429Z</v>
       </c>
       <c r="T113" t="str">
-        <v>2026-08-02T17:46:51.887Z</v>
+        <v>2026-08-02T18:31:03.341Z</v>
       </c>
     </row>
     <row r="114">
@@ -8562,7 +9017,7 @@
         <v>2026-07-26T16:49:55.429Z</v>
       </c>
       <c r="T114" t="str">
-        <v>2026-08-02T17:46:51.887Z</v>
+        <v>2026-08-02T18:31:03.341Z</v>
       </c>
     </row>
     <row r="115">
@@ -8624,7 +9079,7 @@
         <v>2026-07-29T10:10:17.865Z</v>
       </c>
       <c r="T115" t="str">
-        <v>2026-08-02T17:46:51.887Z</v>
+        <v>2026-08-02T18:31:03.341Z</v>
       </c>
     </row>
     <row r="116">
@@ -8665,7 +9120,7 @@
         <v>apify</v>
       </c>
       <c r="M116" t="str">
-        <v>2026-08-02T17:46:41.553Z</v>
+        <v>2026-08-02T18:30:53.311Z</v>
       </c>
       <c r="N116" t="str">
         <v>[]</v>
@@ -8674,19 +9129,19 @@
         <v>Good Food and Good Ambience 🫠</v>
       </c>
       <c r="P116" t="str">
-        <v>2026-08-02T17:46:41.553Z</v>
+        <v>2026-08-02T18:30:53.311Z</v>
       </c>
       <c r="Q116" t="str">
-        <v>2026-08-02T17:46:42.871Z</v>
+        <v>2026-08-02T18:30:54.587Z</v>
       </c>
       <c r="R116" t="str">
         <v>["https://lh3.googleusercontent.com/grass-cs/ACvplmN401sNmtP83XsqQt6BKbK_P4Oy4udD5hjyoq2D6w8Vnz1_1JzvdCZcxofDtYNVr7KgNMGUffs-YE6lrAJdLwozvgqrBmXGA8Pe0DsAa7kvBtgT_GcrxPHbkVdFKwvOE85kGl73K8vq68IW=w300-h225-p-k-no","https://lh3.googleusercontent.com/grass-cs/ACvplmOF2lQFaJzIT7zBkceNBVbmHErEYuG0i-5NBiLtrdYq3vh7zZI0yGMHPrlYvcEH3I1O-i2Q2F1ioVrhXxSdt6AhShylrmdhk6gORkXSj8zA_p-HQ7gMNxZ2fwd1xoEZwqR-vhQt3zWKVRQv=w300-h225-p-k-no","https://lh3.googleusercontent.com/grass-cs/ACvplmP-O01jDu1yIZg3Tp7Wr8SaYhm5rPrpnv6WSHPO69y0EBP1XAC0a-MwoZyTtvCcGGIsu19-yYNTSMPZgBW5lx315eewd5GYs40UDOgdBUgmP29co1Tg8rgDYMQ2ELeNl_O0FW1SqJKz8k7c=w300-h225-p-k-no","https://lh3.googleusercontent.com/grass-cs/ACvplmO55VnSL8zaOT_uzqG6WWdTAWq_otM7wzdBYfJaJtg5ida5fVo9SVL7bqXFJAyxs9rcZpdlSzzkPE9HtMW7N8x2DKo2GOQmQH5icUO729pXLLwSLFBOkN0PSnPfFot1h_-nhtFIT_QZqdpq=w300-h225-p-k-no"]</v>
       </c>
       <c r="S116" t="str">
-        <v>2026-07-05T17:46:18.717Z</v>
+        <v>2026-07-05T18:30:28.538Z</v>
       </c>
       <c r="T116" t="str">
-        <v>2026-08-02T17:46:51.887Z</v>
+        <v>2026-08-02T18:31:03.341Z</v>
       </c>
     </row>
     <row r="117">
@@ -8727,7 +9182,7 @@
         <v>apify</v>
       </c>
       <c r="M117" t="str">
-        <v>2026-08-02T17:46:41.553Z</v>
+        <v>2026-08-02T18:30:53.311Z</v>
       </c>
       <c r="N117" t="str">
         <v>[]</v>
@@ -8736,19 +9191,19 @@
         <v>Must try paneer tikka sandwich..... Served fresh and hot... Soooo good!!!.</v>
       </c>
       <c r="P117" t="str">
-        <v>2026-08-02T17:46:41.553Z</v>
+        <v>2026-08-02T18:30:53.311Z</v>
       </c>
       <c r="Q117" t="str">
-        <v>2026-08-02T17:46:44.717Z</v>
+        <v>2026-08-02T18:30:56.476Z</v>
       </c>
       <c r="R117" t="str">
         <v>[]</v>
       </c>
       <c r="S117" t="str">
-        <v>2026-07-03T17:46:22.868Z</v>
+        <v>2026-07-03T18:30:33.189Z</v>
       </c>
       <c r="T117" t="str">
-        <v>2026-08-02T17:46:51.887Z</v>
+        <v>2026-08-02T18:31:03.341Z</v>
       </c>
     </row>
     <row r="118">
@@ -8789,7 +9244,7 @@
         <v>apify</v>
       </c>
       <c r="M118" t="str">
-        <v>2026-08-02T17:46:41.552Z</v>
+        <v>2026-08-02T18:30:53.310Z</v>
       </c>
       <c r="N118" t="str">
         <v>[]</v>
@@ -8798,19 +9253,19 @@
         <v>The cake was absolutely delicious! It was fresh, soft, and perfectly moist.It looked beautiful and tasted even better.</v>
       </c>
       <c r="P118" t="str">
-        <v>2026-08-02T17:46:41.550Z</v>
+        <v>2026-08-02T18:30:53.310Z</v>
       </c>
       <c r="Q118" t="str">
-        <v>2026-08-02T17:46:41.557Z</v>
+        <v>2026-08-02T18:30:53.312Z</v>
       </c>
       <c r="R118" t="str">
         <v>["https://lh3.googleusercontent.com/grass-cs/ACvplmOLQ-GteCh5CnyR5daudxRpT1k36KzeceTsP9np2FBDQ9kFZxAZUlgPbbDaJ3CH26d-OShDsoxAXCNWNIHzWxz-kK7BNfNz5EHluow3fMPb3J0wl_K5lR2Y93v_vvcUO--NE6YFXd5z0iK5=w600-h450-p-k-no"]</v>
       </c>
       <c r="S118" t="str">
-        <v>2026-08-02T13:46:16.290Z</v>
+        <v>2026-08-02T13:30:26.343Z</v>
       </c>
       <c r="T118" t="str">
-        <v>2026-08-02T17:46:51.887Z</v>
+        <v>2026-08-02T18:31:03.341Z</v>
       </c>
     </row>
     <row r="119">
@@ -8851,7 +9306,7 @@
         <v>apify</v>
       </c>
       <c r="M119" t="str">
-        <v>2026-08-02T17:46:41.552Z</v>
+        <v>2026-08-02T18:30:53.310Z</v>
       </c>
       <c r="N119" t="str">
         <v>[]</v>
@@ -8860,19 +9315,19 @@
         <v>Quick and delicious service... What a wow Biscoff tres leches ...</v>
       </c>
       <c r="P119" t="str">
-        <v>2026-08-02T17:46:41.552Z</v>
+        <v>2026-08-02T18:30:53.310Z</v>
       </c>
       <c r="Q119" t="str">
-        <v>2026-08-02T17:46:41.745Z</v>
+        <v>2026-08-02T18:30:53.403Z</v>
       </c>
       <c r="R119" t="str">
         <v>[]</v>
       </c>
       <c r="S119" t="str">
-        <v>2026-08-02T11:46:16.290Z</v>
+        <v>2026-08-02T12:30:26.343Z</v>
       </c>
       <c r="T119" t="str">
-        <v>2026-08-02T17:46:51.887Z</v>
+        <v>2026-08-02T18:31:03.341Z</v>
       </c>
     </row>
   </sheetData>
@@ -9139,7 +9594,7 @@
         <v>false</v>
       </c>
       <c r="AH2" t="str">
-        <v>2026-08-02T17:46:49.527Z</v>
+        <v>2026-08-02T18:31:01.269Z</v>
       </c>
     </row>
     <row r="3">
@@ -9243,7 +9698,7 @@
         <v>true</v>
       </c>
       <c r="AH3" t="str">
-        <v>2026-08-02T17:46:49.527Z</v>
+        <v>2026-08-02T18:31:01.270Z</v>
       </c>
     </row>
     <row r="4">
@@ -9338,7 +9793,7 @@
         <v>false</v>
       </c>
       <c r="AH4" t="str">
-        <v>2026-08-02T17:46:49.527Z</v>
+        <v>2026-08-02T18:31:01.270Z</v>
       </c>
     </row>
     <row r="5">
@@ -9442,7 +9897,7 @@
         <v>false</v>
       </c>
       <c r="AH5" t="str">
-        <v>2026-08-02T17:46:49.527Z</v>
+        <v>2026-08-02T18:31:01.270Z</v>
       </c>
     </row>
     <row r="6">
@@ -9546,7 +10001,7 @@
         <v>false</v>
       </c>
       <c r="AH6" t="str">
-        <v>2026-08-02T17:46:49.527Z</v>
+        <v>2026-08-02T18:31:01.270Z</v>
       </c>
     </row>
     <row r="7">
@@ -9650,7 +10105,7 @@
         <v>false</v>
       </c>
       <c r="AH7" t="str">
-        <v>2026-08-02T17:46:49.527Z</v>
+        <v>2026-08-02T18:31:01.270Z</v>
       </c>
     </row>
     <row r="8">
@@ -9745,7 +10200,7 @@
         <v>false</v>
       </c>
       <c r="AH8" t="str">
-        <v>2026-08-02T17:46:49.527Z</v>
+        <v>2026-08-02T18:31:01.270Z</v>
       </c>
     </row>
     <row r="9">
@@ -9849,7 +10304,7 @@
         <v>false</v>
       </c>
       <c r="AH9" t="str">
-        <v>2026-08-02T17:46:49.527Z</v>
+        <v>2026-08-02T18:31:01.270Z</v>
       </c>
     </row>
     <row r="10">
@@ -9953,7 +10408,7 @@
         <v>false</v>
       </c>
       <c r="AH10" t="str">
-        <v>2026-08-02T17:46:49.527Z</v>
+        <v>2026-08-02T18:31:01.270Z</v>
       </c>
     </row>
     <row r="11">
@@ -10057,7 +10512,7 @@
         <v>false</v>
       </c>
       <c r="AH11" t="str">
-        <v>2026-08-02T17:46:49.527Z</v>
+        <v>2026-08-02T18:31:01.270Z</v>
       </c>
     </row>
     <row r="12">
@@ -10161,7 +10616,7 @@
         <v>false</v>
       </c>
       <c r="AH12" t="str">
-        <v>2026-08-02T17:46:49.527Z</v>
+        <v>2026-08-02T18:31:01.270Z</v>
       </c>
     </row>
     <row r="13">
@@ -10256,7 +10711,7 @@
         <v>false</v>
       </c>
       <c r="AH13" t="str">
-        <v>2026-08-02T17:46:49.527Z</v>
+        <v>2026-08-02T18:31:01.270Z</v>
       </c>
     </row>
     <row r="14">
@@ -10360,7 +10815,7 @@
         <v>false</v>
       </c>
       <c r="AH14" t="str">
-        <v>2026-08-02T17:46:49.527Z</v>
+        <v>2026-08-02T18:31:01.270Z</v>
       </c>
     </row>
     <row r="15">
@@ -10464,7 +10919,7 @@
         <v>true</v>
       </c>
       <c r="AH15" t="str">
-        <v>2026-08-02T17:46:49.527Z</v>
+        <v>2026-08-02T18:31:01.270Z</v>
       </c>
     </row>
     <row r="16">
@@ -10568,7 +11023,7 @@
         <v>true</v>
       </c>
       <c r="AH16" t="str">
-        <v>2026-08-02T17:46:49.527Z</v>
+        <v>2026-08-02T18:31:01.270Z</v>
       </c>
     </row>
     <row r="17">
@@ -10672,7 +11127,7 @@
         <v>false</v>
       </c>
       <c r="AH17" t="str">
-        <v>2026-08-02T17:46:49.527Z</v>
+        <v>2026-08-02T18:31:01.270Z</v>
       </c>
     </row>
     <row r="18">
@@ -10776,7 +11231,7 @@
         <v>true</v>
       </c>
       <c r="AH18" t="str">
-        <v>2026-08-02T17:46:49.527Z</v>
+        <v>2026-08-02T18:31:01.270Z</v>
       </c>
     </row>
     <row r="19">
@@ -10880,7 +11335,7 @@
         <v>false</v>
       </c>
       <c r="AH19" t="str">
-        <v>2026-08-02T17:46:49.527Z</v>
+        <v>2026-08-02T18:31:01.270Z</v>
       </c>
     </row>
     <row r="20">
@@ -10975,7 +11430,7 @@
         <v>false</v>
       </c>
       <c r="AH20" t="str">
-        <v>2026-08-02T17:46:49.527Z</v>
+        <v>2026-08-02T18:31:01.270Z</v>
       </c>
     </row>
     <row r="21">
@@ -11070,7 +11525,7 @@
         <v>false</v>
       </c>
       <c r="AH21" t="str">
-        <v>2026-08-02T17:46:49.527Z</v>
+        <v>2026-08-02T18:31:01.270Z</v>
       </c>
     </row>
     <row r="22">
@@ -11174,7 +11629,7 @@
         <v>false</v>
       </c>
       <c r="AH22" t="str">
-        <v>2026-08-02T17:46:49.527Z</v>
+        <v>2026-08-02T18:31:01.271Z</v>
       </c>
     </row>
     <row r="23">
@@ -11278,7 +11733,7 @@
         <v>false</v>
       </c>
       <c r="AH23" t="str">
-        <v>2026-08-02T17:46:49.527Z</v>
+        <v>2026-08-02T18:31:01.271Z</v>
       </c>
     </row>
     <row r="24">
@@ -11373,7 +11828,7 @@
         <v>false</v>
       </c>
       <c r="AH24" t="str">
-        <v>2026-08-02T17:46:49.527Z</v>
+        <v>2026-08-02T18:31:01.271Z</v>
       </c>
     </row>
     <row r="25">
@@ -11477,7 +11932,7 @@
         <v>false</v>
       </c>
       <c r="AH25" t="str">
-        <v>2026-08-02T17:46:49.527Z</v>
+        <v>2026-08-02T18:31:01.271Z</v>
       </c>
     </row>
     <row r="26">
@@ -11581,7 +12036,7 @@
         <v>true</v>
       </c>
       <c r="AH26" t="str">
-        <v>2026-08-02T17:46:49.528Z</v>
+        <v>2026-08-02T18:31:01.271Z</v>
       </c>
     </row>
     <row r="27">
@@ -11685,7 +12140,7 @@
         <v>true</v>
       </c>
       <c r="AH27" t="str">
-        <v>2026-08-02T17:46:49.528Z</v>
+        <v>2026-08-02T18:31:01.271Z</v>
       </c>
     </row>
     <row r="28">
@@ -11789,7 +12244,7 @@
         <v>false</v>
       </c>
       <c r="AH28" t="str">
-        <v>2026-08-02T17:46:49.528Z</v>
+        <v>2026-08-02T18:31:01.271Z</v>
       </c>
     </row>
     <row r="29">
@@ -11893,7 +12348,7 @@
         <v>false</v>
       </c>
       <c r="AH29" t="str">
-        <v>2026-08-02T17:46:49.528Z</v>
+        <v>2026-08-02T18:31:01.271Z</v>
       </c>
     </row>
     <row r="30">
@@ -11997,7 +12452,7 @@
         <v>false</v>
       </c>
       <c r="AH30" t="str">
-        <v>2026-08-02T17:46:49.528Z</v>
+        <v>2026-08-02T18:31:01.271Z</v>
       </c>
     </row>
     <row r="31">
@@ -12101,7 +12556,7 @@
         <v>false</v>
       </c>
       <c r="AH31" t="str">
-        <v>2026-08-02T17:46:49.528Z</v>
+        <v>2026-08-02T18:31:01.271Z</v>
       </c>
     </row>
     <row r="32">
@@ -12196,7 +12651,7 @@
         <v>false</v>
       </c>
       <c r="AH32" t="str">
-        <v>2026-08-02T17:46:49.528Z</v>
+        <v>2026-08-02T18:31:01.271Z</v>
       </c>
     </row>
     <row r="33">
@@ -12300,7 +12755,7 @@
         <v>false</v>
       </c>
       <c r="AH33" t="str">
-        <v>2026-08-02T17:46:49.528Z</v>
+        <v>2026-08-02T18:31:01.271Z</v>
       </c>
     </row>
     <row r="34">
@@ -12404,7 +12859,7 @@
         <v>true</v>
       </c>
       <c r="AH34" t="str">
-        <v>2026-08-02T17:46:49.528Z</v>
+        <v>2026-08-02T18:31:01.271Z</v>
       </c>
     </row>
     <row r="35">
@@ -12508,7 +12963,7 @@
         <v>true</v>
       </c>
       <c r="AH35" t="str">
-        <v>2026-08-02T17:46:49.528Z</v>
+        <v>2026-08-02T18:31:01.271Z</v>
       </c>
     </row>
     <row r="36">
@@ -12612,7 +13067,7 @@
         <v>true</v>
       </c>
       <c r="AH36" t="str">
-        <v>2026-08-02T17:46:49.528Z</v>
+        <v>2026-08-02T18:31:01.271Z</v>
       </c>
     </row>
     <row r="37">
@@ -12707,7 +13162,7 @@
         <v>false</v>
       </c>
       <c r="AH37" t="str">
-        <v>2026-08-02T17:46:49.528Z</v>
+        <v>2026-08-02T18:31:01.271Z</v>
       </c>
     </row>
     <row r="38">
@@ -12811,7 +13266,7 @@
         <v>false</v>
       </c>
       <c r="AH38" t="str">
-        <v>2026-08-02T17:46:49.528Z</v>
+        <v>2026-08-02T18:31:01.271Z</v>
       </c>
     </row>
     <row r="39">
@@ -12915,7 +13370,7 @@
         <v>false</v>
       </c>
       <c r="AH39" t="str">
-        <v>2026-08-02T17:46:49.528Z</v>
+        <v>2026-08-02T18:31:01.271Z</v>
       </c>
     </row>
     <row r="40">
@@ -13010,7 +13465,7 @@
         <v>false</v>
       </c>
       <c r="AH40" t="str">
-        <v>2026-08-02T17:46:49.528Z</v>
+        <v>2026-08-02T18:31:01.272Z</v>
       </c>
     </row>
     <row r="41">
@@ -13114,7 +13569,7 @@
         <v>false</v>
       </c>
       <c r="AH41" t="str">
-        <v>2026-08-02T17:46:49.528Z</v>
+        <v>2026-08-02T18:31:01.272Z</v>
       </c>
     </row>
     <row r="42">
@@ -13218,7 +13673,7 @@
         <v>false</v>
       </c>
       <c r="AH42" t="str">
-        <v>2026-08-02T17:46:49.528Z</v>
+        <v>2026-08-02T18:31:01.272Z</v>
       </c>
     </row>
     <row r="43">
@@ -13322,7 +13777,7 @@
         <v>false</v>
       </c>
       <c r="AH43" t="str">
-        <v>2026-08-02T17:46:49.528Z</v>
+        <v>2026-08-02T18:31:01.272Z</v>
       </c>
     </row>
     <row r="44">
@@ -13426,7 +13881,7 @@
         <v>false</v>
       </c>
       <c r="AH44" t="str">
-        <v>2026-08-02T17:46:49.528Z</v>
+        <v>2026-08-02T18:31:01.272Z</v>
       </c>
     </row>
     <row r="45">
@@ -13530,7 +13985,7 @@
         <v>false</v>
       </c>
       <c r="AH45" t="str">
-        <v>2026-08-02T17:46:49.528Z</v>
+        <v>2026-08-02T18:31:01.272Z</v>
       </c>
     </row>
     <row r="46">
@@ -13634,7 +14089,7 @@
         <v>false</v>
       </c>
       <c r="AH46" t="str">
-        <v>2026-08-02T17:46:49.528Z</v>
+        <v>2026-08-02T18:31:01.272Z</v>
       </c>
     </row>
     <row r="47">
@@ -13738,7 +14193,7 @@
         <v>true</v>
       </c>
       <c r="AH47" t="str">
-        <v>2026-08-02T17:46:49.528Z</v>
+        <v>2026-08-02T18:31:01.272Z</v>
       </c>
       <c r="AI47" t="str">
         <v/>
@@ -13851,7 +14306,7 @@
         <v>true</v>
       </c>
       <c r="AH48" t="str">
-        <v>2026-08-02T17:46:49.528Z</v>
+        <v>2026-08-02T18:31:01.272Z</v>
       </c>
       <c r="AI48" t="str">
         <v/>
@@ -13964,7 +14419,7 @@
         <v>true</v>
       </c>
       <c r="AH49" t="str">
-        <v>2026-08-02T17:46:49.528Z</v>
+        <v>2026-08-02T18:31:01.272Z</v>
       </c>
       <c r="AI49" t="str">
         <v/>
@@ -14077,7 +14532,7 @@
         <v>true</v>
       </c>
       <c r="AH50" t="str">
-        <v>2026-08-02T17:46:49.528Z</v>
+        <v>2026-08-02T18:31:01.272Z</v>
       </c>
       <c r="AI50" t="str">
         <v/>
@@ -14190,7 +14645,7 @@
         <v>true</v>
       </c>
       <c r="AH51" t="str">
-        <v>2026-08-02T17:46:49.528Z</v>
+        <v>2026-08-02T18:31:01.272Z</v>
       </c>
       <c r="AI51" t="str">
         <v/>
@@ -14294,7 +14749,7 @@
         <v>false</v>
       </c>
       <c r="AH52" t="str">
-        <v>2026-08-02T17:46:49.529Z</v>
+        <v>2026-08-02T18:31:01.272Z</v>
       </c>
       <c r="AI52" t="str">
         <v/>
@@ -14398,7 +14853,7 @@
         <v>false</v>
       </c>
       <c r="AH53" t="str">
-        <v>2026-08-02T17:46:49.529Z</v>
+        <v>2026-08-02T18:31:01.272Z</v>
       </c>
       <c r="AI53" t="str">
         <v/>
@@ -14502,7 +14957,7 @@
         <v>false</v>
       </c>
       <c r="AH54" t="str">
-        <v>2026-08-02T17:46:49.529Z</v>
+        <v>2026-08-02T18:31:01.272Z</v>
       </c>
       <c r="AI54" t="str">
         <v/>
@@ -14606,7 +15061,7 @@
         <v>false</v>
       </c>
       <c r="AH55" t="str">
-        <v>2026-08-02T17:46:49.529Z</v>
+        <v>2026-08-02T18:31:01.272Z</v>
       </c>
       <c r="AI55" t="str">
         <v/>
@@ -14710,7 +15165,7 @@
         <v>false</v>
       </c>
       <c r="AH56" t="str">
-        <v>2026-08-02T17:46:49.529Z</v>
+        <v>2026-08-02T18:31:01.272Z</v>
       </c>
       <c r="AI56" t="str">
         <v/>
@@ -14814,7 +15269,7 @@
         <v>false</v>
       </c>
       <c r="AH57" t="str">
-        <v>2026-08-02T17:46:49.529Z</v>
+        <v>2026-08-02T18:31:01.272Z</v>
       </c>
       <c r="AI57" t="str">
         <v/>
@@ -14918,7 +15373,7 @@
         <v>false</v>
       </c>
       <c r="AH58" t="str">
-        <v>2026-08-02T17:46:49.529Z</v>
+        <v>2026-08-02T18:31:01.272Z</v>
       </c>
       <c r="AI58" t="str">
         <v/>
@@ -15022,7 +15477,7 @@
         <v>false</v>
       </c>
       <c r="AH59" t="str">
-        <v>2026-08-02T17:46:49.529Z</v>
+        <v>2026-08-02T18:31:01.272Z</v>
       </c>
       <c r="AI59" t="str">
         <v/>
@@ -15126,7 +15581,7 @@
         <v>false</v>
       </c>
       <c r="AH60" t="str">
-        <v>2026-08-02T17:46:49.529Z</v>
+        <v>2026-08-02T18:31:01.272Z</v>
       </c>
       <c r="AI60" t="str">
         <v/>
@@ -15230,7 +15685,7 @@
         <v>false</v>
       </c>
       <c r="AH61" t="str">
-        <v>2026-08-02T17:46:49.529Z</v>
+        <v>2026-08-02T18:31:01.272Z</v>
       </c>
       <c r="AI61" t="str">
         <v/>
@@ -15334,7 +15789,7 @@
         <v>general/wcywpveuxadvnoh7xtrz</v>
       </c>
       <c r="AH62" t="str">
-        <v>2026-08-02T17:46:49.529Z</v>
+        <v>2026-08-02T18:31:01.272Z</v>
       </c>
       <c r="AI62" t="str">
         <v/>
@@ -15441,7 +15896,7 @@
         <v>false</v>
       </c>
       <c r="AH63" t="str">
-        <v>2026-08-02T17:46:49.529Z</v>
+        <v>2026-08-02T18:31:01.272Z</v>
       </c>
       <c r="AI63" t="str">
         <v/>
@@ -15545,7 +16000,7 @@
         <v>false</v>
       </c>
       <c r="AH64" t="str">
-        <v>2026-08-02T17:46:49.529Z</v>
+        <v>2026-08-02T18:31:01.272Z</v>
       </c>
       <c r="AI64" t="str">
         <v/>
@@ -15649,7 +16104,7 @@
         <v>false</v>
       </c>
       <c r="AH65" t="str">
-        <v>2026-08-02T17:46:49.529Z</v>
+        <v>2026-08-02T18:31:01.272Z</v>
       </c>
       <c r="AI65" t="str">
         <v/>
@@ -15744,7 +16199,7 @@
         <v>chocolates/wwosfnmcbprgc1pawgbe</v>
       </c>
       <c r="AH66" t="str">
-        <v>2026-08-02T17:46:49.529Z</v>
+        <v>2026-08-02T18:31:01.272Z</v>
       </c>
       <c r="AI66" t="str">
         <v/>
@@ -15848,7 +16303,7 @@
         <v>chocolates/xpe7ug2cdorh6wrn1ipm</v>
       </c>
       <c r="AH67" t="str">
-        <v>2026-08-02T17:46:49.529Z</v>
+        <v>2026-08-02T18:31:01.272Z</v>
       </c>
       <c r="AI67" t="str">
         <v/>
@@ -15955,7 +16410,7 @@
         <v>chocolates/tbokikjrhqddueyxp051</v>
       </c>
       <c r="AH68" t="str">
-        <v>2026-08-02T17:46:49.530Z</v>
+        <v>2026-08-02T18:31:01.272Z</v>
       </c>
       <c r="AI68" t="str">
         <v/>
@@ -16062,7 +16517,7 @@
         <v>chocolates/jser4gem9bty2zqikzk9</v>
       </c>
       <c r="AH69" t="str">
-        <v>2026-08-02T17:46:49.530Z</v>
+        <v>2026-08-02T18:31:01.272Z</v>
       </c>
       <c r="AI69" t="str">
         <v/>
@@ -16169,7 +16624,7 @@
         <v>false</v>
       </c>
       <c r="AH70" t="str">
-        <v>2026-08-02T17:46:49.530Z</v>
+        <v>2026-08-02T18:31:01.273Z</v>
       </c>
       <c r="AI70" t="str">
         <v/>
@@ -16267,7 +16722,7 @@
         <v>false</v>
       </c>
       <c r="AH71" t="str">
-        <v>2026-08-02T17:46:49.530Z</v>
+        <v>2026-08-02T18:31:01.273Z</v>
       </c>
       <c r="AI71" t="str">
         <v/>
@@ -16365,7 +16820,7 @@
         <v>false</v>
       </c>
       <c r="AH72" t="str">
-        <v>2026-08-02T17:46:49.530Z</v>
+        <v>2026-08-02T18:31:01.273Z</v>
       </c>
       <c r="AI72" t="str">
         <v/>
@@ -16463,7 +16918,7 @@
         <v>false</v>
       </c>
       <c r="AH73" t="str">
-        <v>2026-08-02T17:46:49.530Z</v>
+        <v>2026-08-02T18:31:01.273Z</v>
       </c>
       <c r="AI73" t="str">
         <v/>
@@ -16561,7 +17016,7 @@
         <v>false</v>
       </c>
       <c r="AH74" t="str">
-        <v>2026-08-02T17:46:49.530Z</v>
+        <v>2026-08-02T18:31:01.273Z</v>
       </c>
       <c r="AI74" t="str">
         <v/>
@@ -16659,7 +17114,7 @@
         <v>false</v>
       </c>
       <c r="AH75" t="str">
-        <v>2026-08-02T17:46:49.530Z</v>
+        <v>2026-08-02T18:31:01.273Z</v>
       </c>
       <c r="AI75" t="str">
         <v/>
@@ -16757,7 +17212,7 @@
         <v>false</v>
       </c>
       <c r="AH76" t="str">
-        <v>2026-08-02T17:46:49.530Z</v>
+        <v>2026-08-02T18:31:01.273Z</v>
       </c>
       <c r="AI76" t="str">
         <v/>
@@ -16855,7 +17310,7 @@
         <v>false</v>
       </c>
       <c r="AH77" t="str">
-        <v>2026-08-02T17:46:49.530Z</v>
+        <v>2026-08-02T18:31:01.273Z</v>
       </c>
       <c r="AI77" t="str">
         <v/>
@@ -16953,7 +17408,7 @@
         <v>false</v>
       </c>
       <c r="AH78" t="str">
-        <v>2026-08-02T17:46:49.530Z</v>
+        <v>2026-08-02T18:31:01.273Z</v>
       </c>
       <c r="AI78" t="str">
         <v/>
@@ -17066,7 +17521,7 @@
         <v>true</v>
       </c>
       <c r="AH79" t="str">
-        <v>2026-08-02T17:46:49.530Z</v>
+        <v>2026-08-02T18:31:01.273Z</v>
       </c>
       <c r="AI79" t="str">
         <v/>
@@ -17179,7 +17634,7 @@
         <v>true</v>
       </c>
       <c r="AH80" t="str">
-        <v>2026-08-02T17:46:49.530Z</v>
+        <v>2026-08-02T18:31:01.273Z</v>
       </c>
       <c r="AI80" t="str">
         <v/>
@@ -17292,7 +17747,7 @@
         <v>false</v>
       </c>
       <c r="AH81" t="str">
-        <v>2026-08-02T17:46:49.530Z</v>
+        <v>2026-08-02T18:31:01.273Z</v>
       </c>
       <c r="AI81" t="str">
         <v/>
@@ -17405,7 +17860,7 @@
         <v>true</v>
       </c>
       <c r="AH82" t="str">
-        <v>2026-08-02T17:46:49.530Z</v>
+        <v>2026-08-02T18:31:01.273Z</v>
       </c>
       <c r="AI82" t="str">
         <v/>
@@ -17518,7 +17973,7 @@
         <v>true</v>
       </c>
       <c r="AH83" t="str">
-        <v>2026-08-02T17:46:49.530Z</v>
+        <v>2026-08-02T18:31:01.273Z</v>
       </c>
       <c r="AI83" t="str">
         <v/>
@@ -17622,7 +18077,7 @@
         <v>true</v>
       </c>
       <c r="AH84" t="str">
-        <v>2026-08-02T17:46:49.530Z</v>
+        <v>2026-08-02T18:31:01.273Z</v>
       </c>
       <c r="AI84" t="str">
         <v/>
@@ -17726,7 +18181,7 @@
         <v>true</v>
       </c>
       <c r="AH85" t="str">
-        <v>2026-08-02T17:46:49.531Z</v>
+        <v>2026-08-02T18:31:01.274Z</v>
       </c>
       <c r="AI85" t="str">
         <v/>
@@ -17830,7 +18285,7 @@
         <v>true</v>
       </c>
       <c r="AH86" t="str">
-        <v>2026-08-02T17:46:49.531Z</v>
+        <v>2026-08-02T18:31:01.274Z</v>
       </c>
       <c r="AI86" t="str">
         <v/>
@@ -17943,7 +18398,7 @@
         <v>false</v>
       </c>
       <c r="AH87" t="str">
-        <v>2026-08-02T17:46:49.531Z</v>
+        <v>2026-08-02T18:31:01.274Z</v>
       </c>
       <c r="AI87" t="str">
         <v/>
@@ -18047,7 +18502,7 @@
         <v>true</v>
       </c>
       <c r="AH88" t="str">
-        <v>2026-08-02T17:46:49.531Z</v>
+        <v>2026-08-02T18:31:01.274Z</v>
       </c>
       <c r="AI88" t="str">
         <v/>
@@ -18160,7 +18615,7 @@
         <v>true</v>
       </c>
       <c r="AH89" t="str">
-        <v>2026-08-02T17:46:49.531Z</v>
+        <v>2026-08-02T18:31:01.274Z</v>
       </c>
       <c r="AI89" t="str">
         <v/>
@@ -18273,7 +18728,7 @@
         <v>true</v>
       </c>
       <c r="AH90" t="str">
-        <v>2026-08-02T17:46:49.531Z</v>
+        <v>2026-08-02T18:31:01.274Z</v>
       </c>
       <c r="AI90" t="str">
         <v/>
@@ -18386,7 +18841,7 @@
         <v>true</v>
       </c>
       <c r="AH91" t="str">
-        <v>2026-08-02T17:46:49.531Z</v>
+        <v>2026-08-02T18:31:01.274Z</v>
       </c>
       <c r="AI91" t="str">
         <v/>
@@ -18490,7 +18945,7 @@
         <v>false</v>
       </c>
       <c r="AH92" t="str">
-        <v>2026-08-02T17:46:49.531Z</v>
+        <v>2026-08-02T18:31:01.274Z</v>
       </c>
       <c r="AI92" t="str">
         <v/>
@@ -18594,7 +19049,7 @@
         <v>false</v>
       </c>
       <c r="AH93" t="str">
-        <v>2026-08-02T17:46:49.531Z</v>
+        <v>2026-08-02T18:31:01.274Z</v>
       </c>
       <c r="AI93" t="str">
         <v/>
@@ -18698,7 +19153,7 @@
         <v>false</v>
       </c>
       <c r="AH94" t="str">
-        <v>2026-08-02T17:46:49.531Z</v>
+        <v>2026-08-02T18:31:01.274Z</v>
       </c>
       <c r="AI94" t="str">
         <v/>
@@ -18802,7 +19257,7 @@
         <v>false</v>
       </c>
       <c r="AH95" t="str">
-        <v>2026-08-02T17:46:49.531Z</v>
+        <v>2026-08-02T18:31:01.274Z</v>
       </c>
       <c r="AI95" t="str">
         <v/>
@@ -18906,7 +19361,7 @@
         <v>false</v>
       </c>
       <c r="AH96" t="str">
-        <v>2026-08-02T17:46:49.531Z</v>
+        <v>2026-08-02T18:31:01.274Z</v>
       </c>
       <c r="AI96" t="str">
         <v/>
@@ -19010,7 +19465,7 @@
         <v>false</v>
       </c>
       <c r="AH97" t="str">
-        <v>2026-08-02T17:46:49.531Z</v>
+        <v>2026-08-02T18:31:01.274Z</v>
       </c>
       <c r="AI97" t="str">
         <v/>
@@ -19114,7 +19569,7 @@
         <v>false</v>
       </c>
       <c r="AH98" t="str">
-        <v>2026-08-02T17:46:49.531Z</v>
+        <v>2026-08-02T18:31:01.274Z</v>
       </c>
       <c r="AI98" t="str">
         <v/>
@@ -19218,7 +19673,7 @@
         <v>false</v>
       </c>
       <c r="AH99" t="str">
-        <v>2026-08-02T17:46:49.531Z</v>
+        <v>2026-08-02T18:31:01.274Z</v>
       </c>
       <c r="AI99" t="str">
         <v/>
@@ -19322,7 +19777,7 @@
         <v>false</v>
       </c>
       <c r="AH100" t="str">
-        <v>2026-08-02T17:46:49.531Z</v>
+        <v>2026-08-02T18:31:01.274Z</v>
       </c>
       <c r="AI100" t="str">
         <v/>
@@ -19435,7 +19890,7 @@
         <v>false</v>
       </c>
       <c r="AH101" t="str">
-        <v>2026-08-02T17:46:49.531Z</v>
+        <v>2026-08-02T18:31:01.274Z</v>
       </c>
       <c r="AI101" t="str">
         <v/>
@@ -19539,7 +19994,7 @@
         <v>false</v>
       </c>
       <c r="AH102" t="str">
-        <v>2026-08-02T17:46:49.531Z</v>
+        <v>2026-08-02T18:31:01.274Z</v>
       </c>
       <c r="AI102" t="str">
         <v/>
@@ -19652,7 +20107,7 @@
         <v>true</v>
       </c>
       <c r="AH103" t="str">
-        <v>2026-08-02T17:46:49.531Z</v>
+        <v>2026-08-02T18:31:01.274Z</v>
       </c>
       <c r="AI103" t="str">
         <v/>
@@ -19765,7 +20220,7 @@
         <v>false</v>
       </c>
       <c r="AH104" t="str">
-        <v>2026-08-02T17:46:49.531Z</v>
+        <v>2026-08-02T18:31:01.275Z</v>
       </c>
       <c r="AI104" t="str">
         <v/>
@@ -19878,7 +20333,7 @@
         <v>false</v>
       </c>
       <c r="AH105" t="str">
-        <v>2026-08-02T17:46:49.532Z</v>
+        <v>2026-08-02T18:31:01.275Z</v>
       </c>
       <c r="AI105" t="str">
         <v/>
@@ -19994,7 +20449,7 @@
         <v>true</v>
       </c>
       <c r="AH106" t="str">
-        <v>2026-08-02T17:46:49.532Z</v>
+        <v>2026-08-02T18:31:01.275Z</v>
       </c>
       <c r="AI106" t="str">
         <v/>
@@ -20168,7 +20623,7 @@
         <v>2026-07-24T16:56:36.026Z</v>
       </c>
       <c r="R2" t="str">
-        <v>2026-08-02T17:46:50.289Z</v>
+        <v>2026-08-02T18:31:02.035Z</v>
       </c>
     </row>
     <row r="3">
@@ -20224,7 +20679,7 @@
         <v>2026-07-28T17:39:40.124Z</v>
       </c>
       <c r="R3" t="str">
-        <v>2026-08-02T17:46:50.291Z</v>
+        <v>2026-08-02T18:31:02.035Z</v>
       </c>
       <c r="S3" t="str">
         <v>[]</v>
@@ -20292,7 +20747,7 @@
         <v>2026-07-28T17:42:45.014Z</v>
       </c>
       <c r="R4" t="str">
-        <v>2026-08-02T17:46:50.293Z</v>
+        <v>2026-08-02T18:31:02.036Z</v>
       </c>
       <c r="S4" t="str">
         <v>[]</v>
@@ -20360,7 +20815,7 @@
         <v>2026-07-28T17:35:21.654Z</v>
       </c>
       <c r="R5" t="str">
-        <v>2026-08-02T17:46:50.294Z</v>
+        <v>2026-08-02T18:31:02.037Z</v>
       </c>
       <c r="S5" t="str">
         <v>[]</v>
@@ -20428,7 +20883,7 @@
         <v>2026-07-28T17:30:16.981Z</v>
       </c>
       <c r="R6" t="str">
-        <v>2026-08-02T17:46:50.296Z</v>
+        <v>2026-08-02T18:31:02.038Z</v>
       </c>
       <c r="S6" t="str">
         <v>[]</v>
@@ -20496,7 +20951,7 @@
         <v>2026-08-02T10:49:00.973Z</v>
       </c>
       <c r="R7" t="str">
-        <v>2026-08-02T17:46:50.297Z</v>
+        <v>2026-08-02T18:31:02.038Z</v>
       </c>
       <c r="S7" t="str">
         <v>[]</v>
@@ -20564,7 +21019,7 @@
         <v>2026-07-26T18:00:06.903Z</v>
       </c>
       <c r="R8" t="str">
-        <v>2026-08-02T17:46:50.298Z</v>
+        <v>2026-08-02T18:31:02.039Z</v>
       </c>
     </row>
     <row r="9">
@@ -20620,7 +21075,7 @@
         <v>2026-07-28T17:37:46.453Z</v>
       </c>
       <c r="R9" t="str">
-        <v>2026-08-02T17:46:50.299Z</v>
+        <v>2026-08-02T18:31:02.039Z</v>
       </c>
       <c r="S9" t="str">
         <v>[]</v>
@@ -20688,7 +21143,7 @@
         <v>2026-07-28T15:52:28.248Z</v>
       </c>
       <c r="R10" t="str">
-        <v>2026-08-02T17:46:50.300Z</v>
+        <v>2026-08-02T18:31:02.040Z</v>
       </c>
       <c r="S10" t="str">
         <v>[]</v>
@@ -20756,7 +21211,7 @@
         <v>2026-07-28T17:48:40.457Z</v>
       </c>
       <c r="R11" t="str">
-        <v>2026-08-02T17:46:50.301Z</v>
+        <v>2026-08-02T18:31:02.041Z</v>
       </c>
       <c r="S11" t="str">
         <v>[]</v>
@@ -20824,7 +21279,7 @@
         <v>2026-07-28T17:49:54.713Z</v>
       </c>
       <c r="R12" t="str">
-        <v>2026-08-02T17:46:50.303Z</v>
+        <v>2026-08-02T18:31:02.043Z</v>
       </c>
       <c r="S12" t="str">
         <v>[]</v>
@@ -20892,7 +21347,7 @@
         <v>2026-07-28T17:34:40.195Z</v>
       </c>
       <c r="R13" t="str">
-        <v>2026-08-02T17:46:50.305Z</v>
+        <v>2026-08-02T18:31:02.044Z</v>
       </c>
       <c r="S13" t="str">
         <v>[]</v>
@@ -20960,7 +21415,7 @@
         <v>2026-07-28T16:31:18.393Z</v>
       </c>
       <c r="R14" t="str">
-        <v>2026-08-02T17:46:50.306Z</v>
+        <v>2026-08-02T18:31:02.045Z</v>
       </c>
       <c r="S14" t="str">
         <v>[]</v>
@@ -21028,7 +21483,7 @@
         <v>2026-07-28T17:43:02.299Z</v>
       </c>
       <c r="R15" t="str">
-        <v>2026-08-02T17:46:50.307Z</v>
+        <v>2026-08-02T18:31:02.046Z</v>
       </c>
       <c r="S15" t="str">
         <v>[]</v>
@@ -21096,7 +21551,7 @@
         <v>2026-07-28T16:20:47.688Z</v>
       </c>
       <c r="R16" t="str">
-        <v>2026-08-02T17:46:50.309Z</v>
+        <v>2026-08-02T18:31:02.046Z</v>
       </c>
       <c r="S16" t="str">
         <v>[]</v>
@@ -21164,7 +21619,7 @@
         <v>2026-07-24T17:04:18.204Z</v>
       </c>
       <c r="R17" t="str">
-        <v>2026-08-02T17:46:50.310Z</v>
+        <v>2026-08-02T18:31:02.046Z</v>
       </c>
     </row>
     <row r="18">
@@ -21220,7 +21675,7 @@
         <v>2026-07-24T17:04:57.812Z</v>
       </c>
       <c r="R18" t="str">
-        <v>2026-08-02T17:46:50.311Z</v>
+        <v>2026-08-02T18:31:02.047Z</v>
       </c>
     </row>
     <row r="19">
@@ -21276,7 +21731,7 @@
         <v>2026-07-28T15:06:55.169Z</v>
       </c>
       <c r="R19" t="str">
-        <v>2026-08-02T17:46:50.312Z</v>
+        <v>2026-08-02T18:31:02.047Z</v>
       </c>
       <c r="S19" t="str">
         <v>[]</v>
@@ -21344,7 +21799,7 @@
         <v>2026-08-02T10:48:10.527Z</v>
       </c>
       <c r="R20" t="str">
-        <v>2026-08-02T17:46:50.313Z</v>
+        <v>2026-08-02T18:31:02.047Z</v>
       </c>
       <c r="S20" t="str">
         <v>[]</v>
@@ -21412,7 +21867,7 @@
         <v>2026-07-24T17:12:35.802Z</v>
       </c>
       <c r="R21" t="str">
-        <v>2026-08-02T17:46:50.314Z</v>
+        <v>2026-08-02T18:31:02.047Z</v>
       </c>
     </row>
     <row r="22">
@@ -21468,7 +21923,7 @@
         <v>2026-07-28T17:26:06.217Z</v>
       </c>
       <c r="R22" t="str">
-        <v>2026-08-02T17:46:50.316Z</v>
+        <v>2026-08-02T18:31:02.048Z</v>
       </c>
       <c r="S22" t="str">
         <v>[]</v>
@@ -21543,7 +21998,7 @@
         <v>2026-07-28T17:46:53.114Z</v>
       </c>
       <c r="R23" t="str">
-        <v>2026-08-02T17:46:50.318Z</v>
+        <v>2026-08-02T18:31:02.048Z</v>
       </c>
       <c r="S23" t="str">
         <v>[]</v>
@@ -21611,7 +22066,7 @@
         <v>2026-07-24T17:18:21.488Z</v>
       </c>
       <c r="R24" t="str">
-        <v>2026-08-02T17:46:50.319Z</v>
+        <v>2026-08-02T18:31:02.048Z</v>
       </c>
     </row>
     <row r="25">
@@ -21667,7 +22122,7 @@
         <v>2026-07-28T17:36:56.657Z</v>
       </c>
       <c r="R25" t="str">
-        <v>2026-08-02T17:46:50.321Z</v>
+        <v>2026-08-02T18:31:02.049Z</v>
       </c>
       <c r="S25" t="str">
         <v>[]</v>
@@ -21735,7 +22190,7 @@
         <v>2026-07-28T17:41:34.056Z</v>
       </c>
       <c r="R26" t="str">
-        <v>2026-08-02T17:46:50.322Z</v>
+        <v>2026-08-02T18:31:02.049Z</v>
       </c>
       <c r="S26" t="str">
         <v>[]</v>
@@ -21803,7 +22258,7 @@
         <v>2026-07-28T17:45:36.923Z</v>
       </c>
       <c r="R27" t="str">
-        <v>2026-08-02T17:46:50.324Z</v>
+        <v>2026-08-02T18:31:02.050Z</v>
       </c>
       <c r="S27" t="str">
         <v>[]</v>
@@ -21871,7 +22326,7 @@
         <v>2026-07-28T16:21:56.496Z</v>
       </c>
       <c r="R28" t="str">
-        <v>2026-08-02T17:46:50.326Z</v>
+        <v>2026-08-02T18:31:02.050Z</v>
       </c>
       <c r="S28" t="str">
         <v>[]</v>
@@ -21939,7 +22394,7 @@
         <v>2026-07-28T17:55:18.892Z</v>
       </c>
       <c r="R29" t="str">
-        <v>2026-08-02T17:46:50.326Z</v>
+        <v>2026-08-02T18:31:02.050Z</v>
       </c>
       <c r="S29" t="str">
         <v>[]</v>
@@ -22007,7 +22462,7 @@
         <v>2026-07-28T17:38:24.726Z</v>
       </c>
       <c r="R30" t="str">
-        <v>2026-08-02T17:46:50.327Z</v>
+        <v>2026-08-02T18:31:02.051Z</v>
       </c>
       <c r="S30" t="str">
         <v>[]</v>
@@ -22075,7 +22530,7 @@
         <v>2026-07-24T17:26:49.450Z</v>
       </c>
       <c r="R31" t="str">
-        <v>2026-08-02T17:46:50.327Z</v>
+        <v>2026-08-02T18:31:02.052Z</v>
       </c>
     </row>
     <row r="32">
@@ -22131,7 +22586,7 @@
         <v>2026-07-24T17:27:41.339Z</v>
       </c>
       <c r="R32" t="str">
-        <v>2026-08-02T17:46:50.328Z</v>
+        <v>2026-08-02T18:31:02.052Z</v>
       </c>
     </row>
     <row r="33">
@@ -22187,7 +22642,7 @@
         <v>2026-07-28T17:39:19.058Z</v>
       </c>
       <c r="R33" t="str">
-        <v>2026-08-02T17:46:50.329Z</v>
+        <v>2026-08-02T18:31:02.053Z</v>
       </c>
       <c r="S33" t="str">
         <v>[]</v>
@@ -22255,7 +22710,7 @@
         <v>2026-07-24T17:30:20.928Z</v>
       </c>
       <c r="R34" t="str">
-        <v>2026-08-02T17:46:50.330Z</v>
+        <v>2026-08-02T18:31:02.053Z</v>
       </c>
     </row>
     <row r="35">
@@ -22311,7 +22766,7 @@
         <v>2026-07-28T17:36:25.555Z</v>
       </c>
       <c r="R35" t="str">
-        <v>2026-08-02T17:46:50.331Z</v>
+        <v>2026-08-02T18:31:02.054Z</v>
       </c>
       <c r="S35" t="str">
         <v>[]</v>
@@ -22379,7 +22834,7 @@
         <v>2026-07-28T17:28:41.534Z</v>
       </c>
       <c r="R36" t="str">
-        <v>2026-08-02T17:46:50.332Z</v>
+        <v>2026-08-02T18:31:02.054Z</v>
       </c>
       <c r="S36" t="str">
         <v>[]</v>
@@ -22447,7 +22902,7 @@
         <v>2026-07-28T16:23:07.254Z</v>
       </c>
       <c r="R37" t="str">
-        <v>2026-08-02T17:46:50.333Z</v>
+        <v>2026-08-02T18:31:02.054Z</v>
       </c>
       <c r="S37" t="str">
         <v>[]</v>
@@ -22515,7 +22970,7 @@
         <v>2026-07-28T17:22:37.075Z</v>
       </c>
       <c r="R38" t="str">
-        <v>2026-08-02T17:46:50.334Z</v>
+        <v>2026-08-02T18:31:02.055Z</v>
       </c>
       <c r="S38" t="str">
         <v>[]</v>
@@ -22583,7 +23038,7 @@
         <v>2026-07-24T17:34:48.053Z</v>
       </c>
       <c r="R39" t="str">
-        <v>2026-08-02T17:46:50.336Z</v>
+        <v>2026-08-02T18:31:02.055Z</v>
       </c>
     </row>
     <row r="40">
@@ -22639,7 +23094,7 @@
         <v>2026-07-28T17:28:07.567Z</v>
       </c>
       <c r="R40" t="str">
-        <v>2026-08-02T17:46:50.337Z</v>
+        <v>2026-08-02T18:31:02.056Z</v>
       </c>
       <c r="S40" t="str">
         <v>[]</v>
@@ -22707,7 +23162,7 @@
         <v>2026-08-02T10:15:51.491Z</v>
       </c>
       <c r="R41" t="str">
-        <v>2026-08-02T17:46:50.337Z</v>
+        <v>2026-08-02T18:31:02.056Z</v>
       </c>
       <c r="S41" t="str">
         <v>[]</v>
@@ -22775,7 +23230,7 @@
         <v>2026-07-24T17:37:33.123Z</v>
       </c>
       <c r="R42" t="str">
-        <v>2026-08-02T17:46:50.338Z</v>
+        <v>2026-08-02T18:31:02.056Z</v>
       </c>
     </row>
     <row r="43">
@@ -22831,7 +23286,7 @@
         <v>2026-07-24T17:38:22.625Z</v>
       </c>
       <c r="R43" t="str">
-        <v>2026-08-02T17:46:50.339Z</v>
+        <v>2026-08-02T18:31:02.056Z</v>
       </c>
     </row>
     <row r="44">
@@ -22887,7 +23342,7 @@
         <v>2026-07-28T17:29:28.255Z</v>
       </c>
       <c r="R44" t="str">
-        <v>2026-08-02T17:46:50.341Z</v>
+        <v>2026-08-02T18:31:02.057Z</v>
       </c>
       <c r="S44" t="str">
         <v>[]</v>
@@ -22955,7 +23410,7 @@
         <v>2026-07-24T17:40:00.365Z</v>
       </c>
       <c r="R45" t="str">
-        <v>2026-08-02T17:46:50.343Z</v>
+        <v>2026-08-02T18:31:02.057Z</v>
       </c>
     </row>
     <row r="46">
@@ -23011,7 +23466,7 @@
         <v>2026-07-28T16:16:46.824Z</v>
       </c>
       <c r="R46" t="str">
-        <v>2026-08-02T17:46:50.344Z</v>
+        <v>2026-08-02T18:31:02.058Z</v>
       </c>
       <c r="S46" t="str">
         <v>[]</v>
@@ -23079,7 +23534,7 @@
         <v>2026-07-24T17:41:27.886Z</v>
       </c>
       <c r="R47" t="str">
-        <v>2026-08-02T17:46:50.344Z</v>
+        <v>2026-08-02T18:31:02.058Z</v>
       </c>
     </row>
     <row r="48">
@@ -23135,7 +23590,7 @@
         <v>2026-07-24T17:42:36.169Z</v>
       </c>
       <c r="R48" t="str">
-        <v>2026-08-02T17:46:50.345Z</v>
+        <v>2026-08-02T18:31:02.059Z</v>
       </c>
     </row>
     <row r="49">
@@ -23191,7 +23646,7 @@
         <v>2026-07-28T17:45:07.109Z</v>
       </c>
       <c r="R49" t="str">
-        <v>2026-08-02T17:46:50.346Z</v>
+        <v>2026-08-02T18:31:02.060Z</v>
       </c>
       <c r="S49" t="str">
         <v>[]</v>
@@ -23259,7 +23714,7 @@
         <v>2026-07-28T16:27:55.642Z</v>
       </c>
       <c r="R50" t="str">
-        <v>2026-08-02T17:46:50.348Z</v>
+        <v>2026-08-02T18:31:02.060Z</v>
       </c>
       <c r="S50" t="str">
         <v>[]</v>
@@ -23327,7 +23782,7 @@
         <v>2026-07-28T16:36:51.938Z</v>
       </c>
       <c r="R51" t="str">
-        <v>2026-08-02T17:46:50.348Z</v>
+        <v>2026-08-02T18:31:02.060Z</v>
       </c>
       <c r="S51" t="str">
         <v>[]</v>
@@ -23395,7 +23850,7 @@
         <v>2026-07-24T17:45:28.097Z</v>
       </c>
       <c r="R52" t="str">
-        <v>2026-08-02T17:46:50.349Z</v>
+        <v>2026-08-02T18:31:02.061Z</v>
       </c>
     </row>
     <row r="53">
@@ -23451,7 +23906,7 @@
         <v>2026-07-28T17:27:31.311Z</v>
       </c>
       <c r="R53" t="str">
-        <v>2026-08-02T17:46:50.350Z</v>
+        <v>2026-08-02T18:31:02.061Z</v>
       </c>
       <c r="S53" t="str">
         <v>[]</v>
@@ -23519,7 +23974,7 @@
         <v>2026-07-28T17:26:46.941Z</v>
       </c>
       <c r="R54" t="str">
-        <v>2026-08-02T17:46:50.351Z</v>
+        <v>2026-08-02T18:31:02.062Z</v>
       </c>
       <c r="S54" t="str">
         <v>[]</v>
@@ -23587,7 +24042,7 @@
         <v>2026-07-24T17:48:00.294Z</v>
       </c>
       <c r="R55" t="str">
-        <v>2026-08-02T17:46:50.352Z</v>
+        <v>2026-08-02T18:31:02.062Z</v>
       </c>
     </row>
     <row r="56">
@@ -23643,7 +24098,7 @@
         <v>2026-07-28T17:40:11.014Z</v>
       </c>
       <c r="R56" t="str">
-        <v>2026-08-02T17:46:50.353Z</v>
+        <v>2026-08-02T18:31:02.063Z</v>
       </c>
       <c r="S56" t="str">
         <v>[]</v>
@@ -23711,7 +24166,7 @@
         <v>2026-07-24T17:54:52.356Z</v>
       </c>
       <c r="R57" t="str">
-        <v>2026-08-02T17:46:50.354Z</v>
+        <v>2026-08-02T18:31:02.063Z</v>
       </c>
     </row>
     <row r="58">
@@ -23767,7 +24222,7 @@
         <v>2026-07-24T17:56:05.755Z</v>
       </c>
       <c r="R58" t="str">
-        <v>2026-08-02T17:46:50.355Z</v>
+        <v>2026-08-02T18:31:02.063Z</v>
       </c>
     </row>
     <row r="59">
@@ -23823,7 +24278,7 @@
         <v>2026-07-28T17:47:53.747Z</v>
       </c>
       <c r="R59" t="str">
-        <v>2026-08-02T17:46:50.356Z</v>
+        <v>2026-08-02T18:31:02.064Z</v>
       </c>
       <c r="S59" t="str">
         <v>[]</v>
@@ -23891,7 +24346,7 @@
         <v>2026-07-28T16:12:36.281Z</v>
       </c>
       <c r="R60" t="str">
-        <v>2026-08-02T17:46:50.357Z</v>
+        <v>2026-08-02T18:31:02.064Z</v>
       </c>
       <c r="S60" t="str">
         <v>[{"weight":"0.5kg","price":560,"_id":"6a68d4f432f685de96f72a57"}]</v>
@@ -23959,7 +24414,7 @@
         <v>2026-07-24T18:00:08.054Z</v>
       </c>
       <c r="R61" t="str">
-        <v>2026-08-02T17:46:50.358Z</v>
+        <v>2026-08-02T18:31:02.065Z</v>
       </c>
     </row>
     <row r="62">
@@ -24015,7 +24470,7 @@
         <v>2026-07-28T17:41:55.851Z</v>
       </c>
       <c r="R62" t="str">
-        <v>2026-08-02T17:46:50.359Z</v>
+        <v>2026-08-02T18:31:02.065Z</v>
       </c>
       <c r="S62" t="str">
         <v>[]</v>
@@ -24083,7 +24538,7 @@
         <v>2026-07-24T18:06:05.196Z</v>
       </c>
       <c r="R63" t="str">
-        <v>2026-08-02T17:46:50.361Z</v>
+        <v>2026-08-02T18:31:02.066Z</v>
       </c>
     </row>
     <row r="64">
@@ -24139,7 +24594,7 @@
         <v>2026-07-28T17:40:57.835Z</v>
       </c>
       <c r="R64" t="str">
-        <v>2026-08-02T17:46:50.361Z</v>
+        <v>2026-08-02T18:31:02.066Z</v>
       </c>
       <c r="S64" t="str">
         <v>[]</v>
@@ -24207,7 +24662,7 @@
         <v>2026-07-28T17:48:30.756Z</v>
       </c>
       <c r="R65" t="str">
-        <v>2026-08-02T17:46:50.363Z</v>
+        <v>2026-08-02T18:31:02.067Z</v>
       </c>
       <c r="S65" t="str">
         <v>[]</v>
@@ -24275,7 +24730,7 @@
         <v>2026-07-28T17:22:03.434Z</v>
       </c>
       <c r="R66" t="str">
-        <v>2026-08-02T17:46:50.365Z</v>
+        <v>2026-08-02T18:31:02.067Z</v>
       </c>
       <c r="S66" t="str">
         <v>[]</v>
@@ -24343,7 +24798,7 @@
         <v>2026-07-28T17:24:37.742Z</v>
       </c>
       <c r="R67" t="str">
-        <v>2026-08-02T17:46:50.366Z</v>
+        <v>2026-08-02T18:31:02.068Z</v>
       </c>
       <c r="S67" t="str">
         <v>[]</v>
@@ -24411,7 +24866,7 @@
         <v>2026-07-26T12:39:12.538Z</v>
       </c>
       <c r="R68" t="str">
-        <v>2026-08-02T17:46:50.367Z</v>
+        <v>2026-08-02T18:31:02.068Z</v>
       </c>
     </row>
     <row r="69">
@@ -24467,7 +24922,7 @@
         <v>2026-07-28T17:25:18.284Z</v>
       </c>
       <c r="R69" t="str">
-        <v>2026-08-02T17:46:50.368Z</v>
+        <v>2026-08-02T18:31:02.069Z</v>
       </c>
       <c r="S69" t="str">
         <v>[]</v>
@@ -24535,7 +24990,7 @@
         <v>2026-07-24T18:20:53.747Z</v>
       </c>
       <c r="R70" t="str">
-        <v>2026-08-02T17:46:50.369Z</v>
+        <v>2026-08-02T18:31:02.069Z</v>
       </c>
     </row>
     <row r="71">
@@ -24591,7 +25046,7 @@
         <v>2026-07-24T18:22:21.034Z</v>
       </c>
       <c r="R71" t="str">
-        <v>2026-08-02T17:46:50.369Z</v>
+        <v>2026-08-02T18:31:02.070Z</v>
       </c>
     </row>
     <row r="72">
@@ -24647,7 +25102,7 @@
         <v>2026-07-24T18:25:36.466Z</v>
       </c>
       <c r="R72" t="str">
-        <v>2026-08-02T17:46:50.371Z</v>
+        <v>2026-08-02T18:31:02.070Z</v>
       </c>
     </row>
     <row r="73">
@@ -24703,7 +25158,7 @@
         <v>2026-07-24T18:26:40.938Z</v>
       </c>
       <c r="R73" t="str">
-        <v>2026-08-02T17:46:50.373Z</v>
+        <v>2026-08-02T18:31:02.071Z</v>
       </c>
     </row>
     <row r="74">
@@ -24759,7 +25214,7 @@
         <v>2026-07-26T12:47:01.249Z</v>
       </c>
       <c r="R74" t="str">
-        <v>2026-08-02T17:46:50.376Z</v>
+        <v>2026-08-02T18:31:02.071Z</v>
       </c>
     </row>
     <row r="75">
@@ -24815,7 +25270,7 @@
         <v>2026-07-26T12:37:09.891Z</v>
       </c>
       <c r="R75" t="str">
-        <v>2026-08-02T17:46:50.377Z</v>
+        <v>2026-08-02T18:31:02.072Z</v>
       </c>
     </row>
     <row r="76">
@@ -24871,7 +25326,7 @@
         <v>2026-07-26T13:20:31.760Z</v>
       </c>
       <c r="R76" t="str">
-        <v>2026-08-02T17:46:50.379Z</v>
+        <v>2026-08-02T18:31:02.072Z</v>
       </c>
     </row>
     <row r="77">
@@ -24927,7 +25382,7 @@
         <v>2026-07-28T16:03:01.985Z</v>
       </c>
       <c r="R77" t="str">
-        <v>2026-08-02T17:46:50.380Z</v>
+        <v>2026-08-02T18:31:02.072Z</v>
       </c>
       <c r="S77" t="str">
         <v>[]</v>
@@ -24995,7 +25450,7 @@
         <v>2026-07-28T17:42:26.187Z</v>
       </c>
       <c r="R78" t="str">
-        <v>2026-08-02T17:46:50.382Z</v>
+        <v>2026-08-02T18:31:02.073Z</v>
       </c>
       <c r="S78" t="str">
         <v>[]</v>
@@ -25063,7 +25518,7 @@
         <v>2026-07-28T17:47:34.157Z</v>
       </c>
       <c r="R79" t="str">
-        <v>2026-08-02T17:46:50.385Z</v>
+        <v>2026-08-02T18:31:02.074Z</v>
       </c>
       <c r="S79" t="str">
         <v>[]</v>
@@ -25131,7 +25586,7 @@
         <v>2026-07-28T17:47:12.892Z</v>
       </c>
       <c r="R80" t="str">
-        <v>2026-08-02T17:46:50.386Z</v>
+        <v>2026-08-02T18:31:02.074Z</v>
       </c>
       <c r="S80" t="str">
         <v>[]</v>
@@ -25199,7 +25654,7 @@
         <v>2026-07-27T17:12:53.242Z</v>
       </c>
       <c r="R81" t="str">
-        <v>2026-08-02T17:46:50.388Z</v>
+        <v>2026-08-02T18:31:02.075Z</v>
       </c>
     </row>
     <row r="82">
@@ -25255,7 +25710,7 @@
         <v>2026-07-27T17:14:28.622Z</v>
       </c>
       <c r="R82" t="str">
-        <v>2026-08-02T17:46:50.390Z</v>
+        <v>2026-08-02T18:31:02.075Z</v>
       </c>
     </row>
     <row r="83">
@@ -25311,7 +25766,7 @@
         <v>2026-07-28T17:40:34.872Z</v>
       </c>
       <c r="R83" t="str">
-        <v>2026-08-02T17:46:50.392Z</v>
+        <v>2026-08-02T18:31:02.076Z</v>
       </c>
       <c r="S83" t="str">
         <v>[]</v>
@@ -25379,7 +25834,7 @@
         <v>2026-07-28T17:30:47.490Z</v>
       </c>
       <c r="R84" t="str">
-        <v>2026-08-02T17:46:50.394Z</v>
+        <v>2026-08-02T18:31:02.077Z</v>
       </c>
       <c r="S84" t="str">
         <v>[]</v>
@@ -25447,7 +25902,7 @@
         <v>2026-07-28T17:23:22.756Z</v>
       </c>
       <c r="R85" t="str">
-        <v>2026-08-02T17:46:50.397Z</v>
+        <v>2026-08-02T18:31:02.077Z</v>
       </c>
       <c r="S85" t="str">
         <v>[]</v>
@@ -25515,7 +25970,7 @@
         <v>2026-07-27T17:23:24.773Z</v>
       </c>
       <c r="R86" t="str">
-        <v>2026-08-02T17:46:50.401Z</v>
+        <v>2026-08-02T18:31:02.078Z</v>
       </c>
     </row>
     <row r="87">
@@ -25571,7 +26026,7 @@
         <v>2026-07-28T17:59:21.885Z</v>
       </c>
       <c r="R87" t="str">
-        <v>2026-08-02T17:46:50.403Z</v>
+        <v>2026-08-02T18:31:02.078Z</v>
       </c>
       <c r="S87" t="str">
         <v>[]</v>
@@ -25639,7 +26094,7 @@
         <v>2026-07-28T18:44:44.782Z</v>
       </c>
       <c r="R88" t="str">
-        <v>2026-08-02T17:46:50.406Z</v>
+        <v>2026-08-02T18:31:02.079Z</v>
       </c>
       <c r="S88" t="str">
         <v>[]</v>
@@ -25707,7 +26162,7 @@
         <v>2026-07-28T18:48:28.617Z</v>
       </c>
       <c r="R89" t="str">
-        <v>2026-08-02T17:46:50.407Z</v>
+        <v>2026-08-02T18:31:02.080Z</v>
       </c>
       <c r="S89" t="str">
         <v>[]</v>
@@ -25775,7 +26230,7 @@
         <v>2026-08-02T06:43:12.026Z</v>
       </c>
       <c r="R90" t="str">
-        <v>2026-08-02T17:46:50.409Z</v>
+        <v>2026-08-02T18:31:02.081Z</v>
       </c>
       <c r="S90" t="str">
         <v>[]</v>
@@ -25843,7 +26298,7 @@
         <v>2026-08-02T10:30:24.114Z</v>
       </c>
       <c r="R91" t="str">
-        <v>2026-08-02T17:46:50.410Z</v>
+        <v>2026-08-02T18:31:02.081Z</v>
       </c>
       <c r="S91" t="str">
         <v>[]</v>
@@ -25921,7 +26376,7 @@
         <v>2026-07-21T13:19:06.517Z</v>
       </c>
       <c r="G2" t="str">
-        <v>2026-08-02T17:46:50.568Z</v>
+        <v>2026-08-02T18:31:02.210Z</v>
       </c>
     </row>
     <row r="3">
@@ -25944,7 +26399,7 @@
         <v>2026-07-21T13:19:28.352Z</v>
       </c>
       <c r="G3" t="str">
-        <v>2026-08-02T17:46:50.568Z</v>
+        <v>2026-08-02T18:31:02.210Z</v>
       </c>
     </row>
     <row r="4">
@@ -25967,7 +26422,7 @@
         <v>2026-07-21T13:19:53.589Z</v>
       </c>
       <c r="G4" t="str">
-        <v>2026-08-02T17:46:50.568Z</v>
+        <v>2026-08-02T18:31:02.210Z</v>
       </c>
     </row>
     <row r="5">
@@ -25990,7 +26445,7 @@
         <v>2026-07-21T13:20:07.470Z</v>
       </c>
       <c r="G5" t="str">
-        <v>2026-08-02T17:46:50.570Z</v>
+        <v>2026-08-02T18:31:02.210Z</v>
       </c>
     </row>
     <row r="6">
@@ -26013,7 +26468,7 @@
         <v>2026-07-21T14:33:48.138Z</v>
       </c>
       <c r="G6" t="str">
-        <v>2026-08-02T17:46:50.570Z</v>
+        <v>2026-08-02T18:31:02.210Z</v>
       </c>
     </row>
     <row r="7">
@@ -26036,7 +26491,7 @@
         <v>2026-07-21T16:49:35.554Z</v>
       </c>
       <c r="G7" t="str">
-        <v>2026-08-02T17:46:50.570Z</v>
+        <v>2026-08-02T18:31:02.210Z</v>
       </c>
     </row>
     <row r="8">
@@ -26059,7 +26514,7 @@
         <v>2026-07-21T18:31:41.689Z</v>
       </c>
       <c r="G8" t="str">
-        <v>2026-08-02T17:46:50.570Z</v>
+        <v>2026-08-02T18:31:02.210Z</v>
       </c>
     </row>
     <row r="9">
@@ -26082,7 +26537,7 @@
         <v>2026-07-21T18:34:21.514Z</v>
       </c>
       <c r="G9" t="str">
-        <v>2026-08-02T17:46:50.570Z</v>
+        <v>2026-08-02T18:31:02.210Z</v>
       </c>
     </row>
   </sheetData>
@@ -26172,7 +26627,7 @@
         <v>2026-06-05T13:08:47.084Z</v>
       </c>
       <c r="I2" t="str">
-        <v>2026-08-02T17:46:50.759Z</v>
+        <v>2026-08-02T18:31:02.417Z</v>
       </c>
     </row>
     <row r="3">
@@ -26201,7 +26656,7 @@
         <v>2026-06-05T13:08:47.087Z</v>
       </c>
       <c r="I3" t="str">
-        <v>2026-08-02T17:46:50.759Z</v>
+        <v>2026-08-02T18:31:02.417Z</v>
       </c>
     </row>
     <row r="4">
@@ -26230,7 +26685,7 @@
         <v>2026-06-27T07:29:40.036Z</v>
       </c>
       <c r="I4" t="str">
-        <v>2026-08-02T17:46:50.759Z</v>
+        <v>2026-08-02T18:31:02.417Z</v>
       </c>
     </row>
     <row r="5">
@@ -26259,7 +26714,7 @@
         <v>2026-06-05T13:08:47.087Z</v>
       </c>
       <c r="I5" t="str">
-        <v>2026-08-02T17:46:50.759Z</v>
+        <v>2026-08-02T18:31:02.417Z</v>
       </c>
     </row>
     <row r="6">
@@ -26288,7 +26743,7 @@
         <v>2026-06-05T13:08:47.088Z</v>
       </c>
       <c r="I6" t="str">
-        <v>2026-08-02T17:46:50.759Z</v>
+        <v>2026-08-02T18:31:02.417Z</v>
       </c>
     </row>
     <row r="7">
@@ -26317,7 +26772,7 @@
         <v>2026-06-05T13:08:47.088Z</v>
       </c>
       <c r="I7" t="str">
-        <v>2026-08-02T17:46:50.759Z</v>
+        <v>2026-08-02T18:31:02.417Z</v>
       </c>
     </row>
     <row r="8">
@@ -26346,7 +26801,7 @@
         <v>2026-06-05T13:08:47.088Z</v>
       </c>
       <c r="I8" t="str">
-        <v>2026-08-02T17:46:50.759Z</v>
+        <v>2026-08-02T18:31:02.417Z</v>
       </c>
     </row>
     <row r="9">
@@ -26375,7 +26830,7 @@
         <v>2026-06-05T13:08:47.088Z</v>
       </c>
       <c r="I9" t="str">
-        <v>2026-08-02T17:46:50.759Z</v>
+        <v>2026-08-02T18:31:02.417Z</v>
       </c>
     </row>
     <row r="10">
@@ -26404,7 +26859,7 @@
         <v>2026-06-05T13:08:47.088Z</v>
       </c>
       <c r="I10" t="str">
-        <v>2026-08-02T17:46:50.760Z</v>
+        <v>2026-08-02T18:31:02.417Z</v>
       </c>
     </row>
     <row r="11">
@@ -26433,7 +26888,7 @@
         <v>2026-06-05T13:08:47.089Z</v>
       </c>
       <c r="I11" t="str">
-        <v>2026-08-02T17:46:50.760Z</v>
+        <v>2026-08-02T18:31:02.417Z</v>
       </c>
     </row>
     <row r="12">
@@ -26462,7 +26917,7 @@
         <v>2026-06-05T13:08:47.089Z</v>
       </c>
       <c r="I12" t="str">
-        <v>2026-08-02T17:46:50.760Z</v>
+        <v>2026-08-02T18:31:02.417Z</v>
       </c>
     </row>
     <row r="13">
@@ -26491,7 +26946,7 @@
         <v>2026-06-05T13:08:47.089Z</v>
       </c>
       <c r="I13" t="str">
-        <v>2026-08-02T17:46:50.760Z</v>
+        <v>2026-08-02T18:31:02.417Z</v>
       </c>
     </row>
     <row r="14">
@@ -26520,7 +26975,7 @@
         <v>2026-06-05T13:08:47.089Z</v>
       </c>
       <c r="I14" t="str">
-        <v>2026-08-02T17:46:50.760Z</v>
+        <v>2026-08-02T18:31:02.417Z</v>
       </c>
     </row>
     <row r="15">
@@ -26549,7 +27004,7 @@
         <v>2026-06-05T13:08:47.089Z</v>
       </c>
       <c r="I15" t="str">
-        <v>2026-08-02T17:46:50.761Z</v>
+        <v>2026-08-02T18:31:02.417Z</v>
       </c>
     </row>
     <row r="16">
@@ -26578,7 +27033,7 @@
         <v>2026-06-05T13:08:47.089Z</v>
       </c>
       <c r="I16" t="str">
-        <v>2026-08-02T17:46:50.761Z</v>
+        <v>2026-08-02T18:31:02.417Z</v>
       </c>
     </row>
     <row r="17">
@@ -26607,7 +27062,7 @@
         <v>2026-06-05T13:08:47.089Z</v>
       </c>
       <c r="I17" t="str">
-        <v>2026-08-02T17:46:50.761Z</v>
+        <v>2026-08-02T18:31:02.418Z</v>
       </c>
     </row>
     <row r="18">
@@ -26636,7 +27091,7 @@
         <v>2026-06-05T13:08:47.089Z</v>
       </c>
       <c r="I18" t="str">
-        <v>2026-08-02T17:46:50.761Z</v>
+        <v>2026-08-02T18:31:02.418Z</v>
       </c>
     </row>
     <row r="19">
@@ -26665,7 +27120,7 @@
         <v>2026-06-05T13:08:47.089Z</v>
       </c>
       <c r="I19" t="str">
-        <v>2026-08-02T17:46:50.761Z</v>
+        <v>2026-08-02T18:31:02.418Z</v>
       </c>
     </row>
     <row r="20">
@@ -26694,7 +27149,7 @@
         <v>2026-06-05T13:08:47.089Z</v>
       </c>
       <c r="I20" t="str">
-        <v>2026-08-02T17:46:50.761Z</v>
+        <v>2026-08-02T18:31:02.418Z</v>
       </c>
     </row>
     <row r="21">
@@ -26723,7 +27178,7 @@
         <v>2026-06-05T13:08:47.089Z</v>
       </c>
       <c r="I21" t="str">
-        <v>2026-08-02T17:46:50.761Z</v>
+        <v>2026-08-02T18:31:02.418Z</v>
       </c>
     </row>
     <row r="22">
@@ -26752,7 +27207,7 @@
         <v>2026-06-05T13:08:47.089Z</v>
       </c>
       <c r="I22" t="str">
-        <v>2026-08-02T17:46:50.761Z</v>
+        <v>2026-08-02T18:31:02.418Z</v>
       </c>
     </row>
     <row r="23">
@@ -26781,7 +27236,7 @@
         <v>2026-06-05T13:08:47.090Z</v>
       </c>
       <c r="I23" t="str">
-        <v>2026-08-02T17:46:50.762Z</v>
+        <v>2026-08-02T18:31:02.418Z</v>
       </c>
     </row>
     <row r="24">
@@ -26810,7 +27265,7 @@
         <v>2026-06-05T13:08:47.090Z</v>
       </c>
       <c r="I24" t="str">
-        <v>2026-08-02T17:46:50.762Z</v>
+        <v>2026-08-02T18:31:02.418Z</v>
       </c>
     </row>
     <row r="25">
@@ -26839,7 +27294,7 @@
         <v>2026-06-05T13:08:47.090Z</v>
       </c>
       <c r="I25" t="str">
-        <v>2026-08-02T17:46:50.762Z</v>
+        <v>2026-08-02T18:31:02.418Z</v>
       </c>
     </row>
     <row r="26">
@@ -26868,7 +27323,7 @@
         <v>2026-06-05T13:08:47.090Z</v>
       </c>
       <c r="I26" t="str">
-        <v>2026-08-02T17:46:50.762Z</v>
+        <v>2026-08-02T18:31:02.418Z</v>
       </c>
     </row>
     <row r="27">
@@ -26897,7 +27352,7 @@
         <v>2026-06-05T13:08:47.090Z</v>
       </c>
       <c r="I27" t="str">
-        <v>2026-08-02T17:46:50.762Z</v>
+        <v>2026-08-02T18:31:02.418Z</v>
       </c>
     </row>
     <row r="28">
@@ -26926,7 +27381,7 @@
         <v>2026-06-05T13:08:47.090Z</v>
       </c>
       <c r="I28" t="str">
-        <v>2026-08-02T17:46:50.762Z</v>
+        <v>2026-08-02T18:31:02.418Z</v>
       </c>
     </row>
     <row r="29">
@@ -26955,7 +27410,7 @@
         <v>2026-06-05T13:08:47.090Z</v>
       </c>
       <c r="I29" t="str">
-        <v>2026-08-02T17:46:50.762Z</v>
+        <v>2026-08-02T18:31:02.418Z</v>
       </c>
     </row>
     <row r="30">
@@ -26984,7 +27439,7 @@
         <v>2026-06-05T13:08:47.090Z</v>
       </c>
       <c r="I30" t="str">
-        <v>2026-08-02T17:46:50.762Z</v>
+        <v>2026-08-02T18:31:02.418Z</v>
       </c>
     </row>
     <row r="31">
@@ -27013,7 +27468,7 @@
         <v>2026-06-05T13:08:47.090Z</v>
       </c>
       <c r="I31" t="str">
-        <v>2026-08-02T17:46:50.762Z</v>
+        <v>2026-08-02T18:31:02.418Z</v>
       </c>
     </row>
     <row r="32">
@@ -27042,7 +27497,7 @@
         <v>2026-06-05T13:08:47.090Z</v>
       </c>
       <c r="I32" t="str">
-        <v>2026-08-02T17:46:50.762Z</v>
+        <v>2026-08-02T18:31:02.418Z</v>
       </c>
     </row>
     <row r="33">
@@ -27071,7 +27526,7 @@
         <v>2026-06-05T13:08:47.090Z</v>
       </c>
       <c r="I33" t="str">
-        <v>2026-08-02T17:46:50.762Z</v>
+        <v>2026-08-02T18:31:02.418Z</v>
       </c>
     </row>
     <row r="34">
@@ -27100,7 +27555,7 @@
         <v>2026-06-05T13:08:47.090Z</v>
       </c>
       <c r="I34" t="str">
-        <v>2026-08-02T17:46:50.762Z</v>
+        <v>2026-08-02T18:31:02.418Z</v>
       </c>
     </row>
     <row r="35">
@@ -27129,7 +27584,7 @@
         <v>2026-06-05T13:08:47.090Z</v>
       </c>
       <c r="I35" t="str">
-        <v>2026-08-02T17:46:50.763Z</v>
+        <v>2026-08-02T18:31:02.418Z</v>
       </c>
     </row>
     <row r="36">
@@ -27158,7 +27613,7 @@
         <v>2026-06-05T13:08:47.090Z</v>
       </c>
       <c r="I36" t="str">
-        <v>2026-08-02T17:46:50.763Z</v>
+        <v>2026-08-02T18:31:02.418Z</v>
       </c>
     </row>
     <row r="37">
@@ -27187,7 +27642,7 @@
         <v>2026-06-05T13:08:47.091Z</v>
       </c>
       <c r="I37" t="str">
-        <v>2026-08-02T17:46:50.763Z</v>
+        <v>2026-08-02T18:31:02.418Z</v>
       </c>
     </row>
     <row r="38">
@@ -27216,7 +27671,7 @@
         <v>2026-06-05T13:08:47.091Z</v>
       </c>
       <c r="I38" t="str">
-        <v>2026-08-02T17:46:50.763Z</v>
+        <v>2026-08-02T18:31:02.418Z</v>
       </c>
     </row>
   </sheetData>
@@ -27324,7 +27779,7 @@
         <v>ordinary</v>
       </c>
       <c r="M2" t="str">
-        <v>2026-08-02T17:46:50.858Z</v>
+        <v>2026-08-02T18:31:02.518Z</v>
       </c>
     </row>
     <row r="3">
@@ -27365,7 +27820,7 @@
         <v>custom</v>
       </c>
       <c r="M3" t="str">
-        <v>2026-08-02T17:46:50.858Z</v>
+        <v>2026-08-02T18:31:02.518Z</v>
       </c>
     </row>
     <row r="4">
@@ -27406,7 +27861,7 @@
         <v>ordinary</v>
       </c>
       <c r="M4" t="str">
-        <v>2026-08-02T17:46:50.858Z</v>
+        <v>2026-08-02T18:31:02.518Z</v>
       </c>
     </row>
     <row r="5">
@@ -27441,7 +27896,7 @@
         <v>ordinary</v>
       </c>
       <c r="M5" t="str">
-        <v>2026-08-02T17:46:50.858Z</v>
+        <v>2026-08-02T18:31:02.518Z</v>
       </c>
     </row>
     <row r="6">
@@ -27476,7 +27931,7 @@
         <v>ordinary</v>
       </c>
       <c r="M6" t="str">
-        <v>2026-08-02T17:46:50.858Z</v>
+        <v>2026-08-02T18:31:02.518Z</v>
       </c>
     </row>
     <row r="7">
@@ -27511,7 +27966,7 @@
         <v>ordinary</v>
       </c>
       <c r="M7" t="str">
-        <v>2026-08-02T17:46:50.858Z</v>
+        <v>2026-08-02T18:31:02.518Z</v>
       </c>
     </row>
     <row r="8">
@@ -27546,7 +28001,7 @@
         <v>custom</v>
       </c>
       <c r="M8" t="str">
-        <v>2026-08-02T17:46:50.858Z</v>
+        <v>2026-08-02T18:31:02.518Z</v>
       </c>
     </row>
     <row r="9">
@@ -27581,7 +28036,7 @@
         <v>ordinary</v>
       </c>
       <c r="M9" t="str">
-        <v>2026-08-02T17:46:50.858Z</v>
+        <v>2026-08-02T18:31:02.518Z</v>
       </c>
     </row>
   </sheetData>
@@ -27675,7 +28130,7 @@
         <v>2026-07-28T18:42:43.600Z</v>
       </c>
       <c r="K2" t="str">
-        <v>2026-08-02T17:46:50.962Z</v>
+        <v>2026-08-02T18:31:02.621Z</v>
       </c>
     </row>
     <row r="3">
@@ -27710,7 +28165,7 @@
         <v>2026-07-28T14:48:54.403Z</v>
       </c>
       <c r="K3" t="str">
-        <v>2026-08-02T17:46:50.962Z</v>
+        <v>2026-08-02T18:31:02.621Z</v>
       </c>
     </row>
     <row r="4">
@@ -27745,7 +28200,7 @@
         <v>2026-07-28T18:14:52.960Z</v>
       </c>
       <c r="K4" t="str">
-        <v>2026-08-02T17:46:50.962Z</v>
+        <v>2026-08-02T18:31:02.621Z</v>
       </c>
     </row>
   </sheetData>

--- a/backend/exports/master_export.xlsx
+++ b/backend/exports/master_export.xlsx
@@ -20,6 +20,7 @@
     <sheet name="Payment" sheetId="15" r:id="rId15"/>
     <sheet name="Review" sheetId="16" r:id="rId16"/>
     <sheet name="GoogleReview" sheetId="17" r:id="rId17"/>
+    <sheet name="AdminFcmToken" sheetId="18" r:id="rId18"/>
   </sheets>
 </workbook>
 </file>
@@ -413,10 +414,10 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:S12"/>
+  <dimension ref="A1:S9"/>
   <cols>
     <col min="1" max="1" width="26.83203125" customWidth="1"/>
-    <col min="2" max="2" width="27.83203125" customWidth="1"/>
+    <col min="2" max="2" width="26.83203125" customWidth="1"/>
     <col min="3" max="3" width="34.83203125" customWidth="1"/>
     <col min="4" max="4" width="10.83203125" customWidth="1"/>
     <col min="5" max="5" width="12.83203125" customWidth="1"/>
@@ -521,13 +522,13 @@
         <v>true</v>
       </c>
       <c r="I2" t="str">
-        <v>2026-08-03T13:24:34.727Z</v>
+        <v>2026-08-04T06:28:41.872Z</v>
       </c>
       <c r="J2" t="str">
         <v>2026-04-23T06:52:27.990Z</v>
       </c>
       <c r="K2" t="str">
-        <v>2026-08-03T13:24:34.728Z</v>
+        <v>2026-08-04T06:28:41.875Z</v>
       </c>
       <c r="L2" t="str">
         <v>[]</v>
@@ -551,7 +552,7 @@
         <v>["6a63a983a800f3907b955c53"]</v>
       </c>
       <c r="S2" t="str">
-        <v>2026-08-04T05:27:19.859Z</v>
+        <v>2026-08-04T08:17:41.274Z</v>
       </c>
     </row>
     <row r="3">
@@ -604,7 +605,7 @@
         <v>[]</v>
       </c>
       <c r="S3" t="str">
-        <v>2026-08-04T05:27:19.859Z</v>
+        <v>2026-08-04T08:17:41.274Z</v>
       </c>
     </row>
     <row r="4">
@@ -639,7 +640,7 @@
         <v>2026-08-02T17:06:28.042Z</v>
       </c>
       <c r="K4" t="str">
-        <v>2026-08-03T13:24:38.246Z</v>
+        <v>2026-08-04T07:09:07.947Z</v>
       </c>
       <c r="L4" t="str">
         <v>[]</v>
@@ -648,7 +649,7 @@
         <v>[]</v>
       </c>
       <c r="P4" t="str">
-        <v>[{"token":"fkS05Gk4TUiBWtUJwKFzHR:APA91bEbe3GKehQ4saJspl41KySjD8GUthqYpR2f7-3euQagWyA2yibbNj-CeYtGWWfYrYE7nIuQKPktxtvn8zQzGItn2pGtgLqBSXmxpPsgnUwye56DXQA","deviceName":"Windows Desktop","createdAt":"2026-08-03T04:34:54.543Z","_id":"6a701a6e1aed5008c4d24d7b"}]</v>
+        <v>[{"token":"fkS05Gk4TUiBWtUJwKFzHR:APA91bEbe3GKehQ4saJspl41KySjD8GUthqYpR2f7-3euQagWyA2yibbNj-CeYtGWWfYrYE7nIuQKPktxtvn8zQzGItn2pGtgLqBSXmxpPsgnUwye56DXQA","deviceName":"Windows Desktop","createdAt":"2026-08-04T07:09:07.947Z","_id":"6a701a6e1aed5008c4d24d7b"}]</v>
       </c>
       <c r="Q4" t="str">
         <v>true</v>
@@ -657,21 +658,24 @@
         <v>[]</v>
       </c>
       <c r="S4" t="str">
-        <v>2026-08-04T05:27:19.859Z</v>
+        <v>2026-08-04T08:17:41.275Z</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="str">
-        <v>6a7052141aed5008c4d25059</v>
+        <v>6a7078161aed5008c4d25733</v>
       </c>
       <c r="B5" t="str">
-        <v>Mithulasree Senthil</v>
+        <v>Mithula Sree</v>
       </c>
       <c r="C5" t="str">
-        <v>mithulasrees123@gmail.com</v>
+        <v>mithulasreesenthil@gmail.com</v>
       </c>
       <c r="D5" t="str">
-        <v>google</v>
+        <v>local</v>
+      </c>
+      <c r="E5" t="str">
+        <v>9597290061</v>
       </c>
       <c r="F5" t="str">
         <v>user</v>
@@ -683,13 +687,13 @@
         <v>true</v>
       </c>
       <c r="I5" t="str">
-        <v>2026-08-03T08:32:20.139Z</v>
+        <v>2026-08-03T11:14:30.390Z</v>
       </c>
       <c r="J5" t="str">
-        <v>2026-08-03T08:32:20.142Z</v>
+        <v>2026-08-03T11:14:30.391Z</v>
       </c>
       <c r="K5" t="str">
-        <v>2026-08-03T08:32:20.142Z</v>
+        <v>2026-08-04T02:51:12.069Z</v>
       </c>
       <c r="L5" t="str">
         <v>[]</v>
@@ -707,24 +711,24 @@
         <v>[]</v>
       </c>
       <c r="S5" t="str">
-        <v>2026-08-04T05:27:19.859Z</v>
+        <v>2026-08-04T08:17:41.275Z</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="str">
-        <v>6a7078161aed5008c4d25733</v>
+        <v>6a707bbeaab7ba55ee1ffdb7</v>
       </c>
       <c r="B6" t="str">
-        <v>Mithula Sree</v>
+        <v>VictoX Gaming</v>
       </c>
       <c r="C6" t="str">
-        <v>mithulasreesenthil@gmail.com</v>
+        <v>victoxgaming23@gmail.com</v>
       </c>
       <c r="D6" t="str">
         <v>local</v>
       </c>
       <c r="E6" t="str">
-        <v>9597290061</v>
+        <v>9087656435</v>
       </c>
       <c r="F6" t="str">
         <v>user</v>
@@ -736,13 +740,13 @@
         <v>true</v>
       </c>
       <c r="I6" t="str">
-        <v>2026-08-03T11:14:30.390Z</v>
+        <v>2026-08-03T11:37:22.245Z</v>
       </c>
       <c r="J6" t="str">
-        <v>2026-08-03T11:14:30.391Z</v>
+        <v>2026-08-03T11:30:06.667Z</v>
       </c>
       <c r="K6" t="str">
-        <v>2026-08-04T02:51:12.069Z</v>
+        <v>2026-08-03T11:37:32.755Z</v>
       </c>
       <c r="L6" t="str">
         <v>[]</v>
@@ -751,7 +755,7 @@
         <v>[]</v>
       </c>
       <c r="P6" t="str">
-        <v>[]</v>
+        <v>[{"token":"fGb7DBm3GT6XegrFEszd1o:APA91bG6GPnkbvqXNXeWTNQ-U0yxSNEh0mrvQXnut8HemUAdRQc3W1FSdA0Zb0krim6MkIwpRqiFss_qP1aAk8ftIhcPBEccQYBYvIw5CdCzQfpOqvCpka4","deviceName":"Windows Desktop","createdAt":"2026-08-03T11:37:32.753Z","_id":"6a707d7caab7ba55ee1ffdbb"}]</v>
       </c>
       <c r="Q6" t="str">
         <v>true</v>
@@ -760,24 +764,24 @@
         <v>[]</v>
       </c>
       <c r="S6" t="str">
-        <v>2026-08-04T05:27:19.859Z</v>
+        <v>2026-08-04T08:17:41.275Z</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="str">
-        <v>6a707bbeaab7ba55ee1ffdb7</v>
+        <v>6a707e784aac857cdce1455f</v>
       </c>
       <c r="B7" t="str">
-        <v>VictoX Gaming</v>
+        <v>Ak webflair technologies</v>
       </c>
       <c r="C7" t="str">
-        <v>victoxgaming23@gmail.com</v>
+        <v>akwebflairtechnologies@gmail.com</v>
       </c>
       <c r="D7" t="str">
         <v>local</v>
       </c>
       <c r="E7" t="str">
-        <v>9087656435</v>
+        <v>9600732162</v>
       </c>
       <c r="F7" t="str">
         <v>user</v>
@@ -789,13 +793,13 @@
         <v>true</v>
       </c>
       <c r="I7" t="str">
-        <v>2026-08-03T11:37:22.245Z</v>
+        <v>2026-08-04T06:53:57.675Z</v>
       </c>
       <c r="J7" t="str">
-        <v>2026-08-03T11:30:06.667Z</v>
+        <v>2026-08-03T11:41:44.423Z</v>
       </c>
       <c r="K7" t="str">
-        <v>2026-08-03T11:37:32.755Z</v>
+        <v>2026-08-04T06:55:30.127Z</v>
       </c>
       <c r="L7" t="str">
         <v>[]</v>
@@ -804,7 +808,7 @@
         <v>[]</v>
       </c>
       <c r="P7" t="str">
-        <v>[{"token":"fGb7DBm3GT6XegrFEszd1o:APA91bG6GPnkbvqXNXeWTNQ-U0yxSNEh0mrvQXnut8HemUAdRQc3W1FSdA0Zb0krim6MkIwpRqiFss_qP1aAk8ftIhcPBEccQYBYvIw5CdCzQfpOqvCpka4","deviceName":"Windows Desktop","createdAt":"2026-08-03T11:37:32.753Z","_id":"6a707d7caab7ba55ee1ffdbb"}]</v>
+        <v>[]</v>
       </c>
       <c r="Q7" t="str">
         <v>true</v>
@@ -813,24 +817,24 @@
         <v>[]</v>
       </c>
       <c r="S7" t="str">
-        <v>2026-08-04T05:27:19.859Z</v>
+        <v>2026-08-04T08:17:41.275Z</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="str">
-        <v>6a707e784aac857cdce1455f</v>
+        <v>6a7154b74aac857cdce15cbd</v>
       </c>
       <c r="B8" t="str">
-        <v>Ak webflair technologies</v>
+        <v>Sarvathan C</v>
       </c>
       <c r="C8" t="str">
-        <v>akwebflairtechnologies@gmail.com</v>
+        <v>sarvathan7235@gmail.com</v>
       </c>
       <c r="D8" t="str">
         <v>local</v>
       </c>
       <c r="E8" t="str">
-        <v>9600732162</v>
+        <v>9363265477</v>
       </c>
       <c r="F8" t="str">
         <v>user</v>
@@ -842,13 +846,13 @@
         <v>true</v>
       </c>
       <c r="I8" t="str">
-        <v>2026-08-03T11:51:04.436Z</v>
+        <v>2026-08-04T02:55:51.439Z</v>
       </c>
       <c r="J8" t="str">
-        <v>2026-08-03T11:41:44.423Z</v>
+        <v>2026-08-04T02:55:51.440Z</v>
       </c>
       <c r="K8" t="str">
-        <v>2026-08-03T11:51:08.881Z</v>
+        <v>2026-08-04T02:56:56.559Z</v>
       </c>
       <c r="L8" t="str">
         <v>[]</v>
@@ -857,7 +861,7 @@
         <v>[]</v>
       </c>
       <c r="P8" t="str">
-        <v>[{"token":"drKAwVZ0kl41gNb1BjK41y:APA91bFMlM8UMSclPnTu7O8Lo_rt65cw5VZZT12kIerGKg3GfGB2WrF5UkmXm2mwKXeU58NkxGS0b_0nbFNcXwtua4qtlIHaFHKHa3LVP6mbLg-rlQ8aFzs","deviceName":"Windows Desktop","createdAt":"2026-08-03T11:51:08.879Z","_id":"6a7080ac4aac857cdce147f0"}]</v>
+        <v>[]</v>
       </c>
       <c r="Q8" t="str">
         <v>true</v>
@@ -866,21 +870,24 @@
         <v>[]</v>
       </c>
       <c r="S8" t="str">
-        <v>2026-08-04T05:27:19.859Z</v>
+        <v>2026-08-04T08:17:41.275Z</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="str">
-        <v>6a71547a4aac857cdce15cba</v>
+        <v>6a7154f14aac857cdce15cc0</v>
       </c>
       <c r="B9" t="str">
-        <v>Sarvathan C</v>
+        <v>Prem Neesanth</v>
       </c>
       <c r="C9" t="str">
-        <v>sarvathan9363@gmail.com</v>
+        <v>neesanth.1309@gmail.com</v>
       </c>
       <c r="D9" t="str">
-        <v>google</v>
+        <v>local</v>
+      </c>
+      <c r="E9" t="str">
+        <v>7339536677</v>
       </c>
       <c r="F9" t="str">
         <v>user</v>
@@ -892,13 +899,13 @@
         <v>true</v>
       </c>
       <c r="I9" t="str">
-        <v>2026-08-04T02:54:50.797Z</v>
+        <v>2026-08-04T02:56:49.325Z</v>
       </c>
       <c r="J9" t="str">
-        <v>2026-08-04T02:54:50.797Z</v>
+        <v>2026-08-04T02:56:49.325Z</v>
       </c>
       <c r="K9" t="str">
-        <v>2026-08-04T02:54:50.797Z</v>
+        <v>2026-08-04T02:58:17.168Z</v>
       </c>
       <c r="L9" t="str">
         <v>[]</v>
@@ -916,168 +923,12 @@
         <v>[]</v>
       </c>
       <c r="S9" t="str">
-        <v>2026-08-04T05:27:19.859Z</v>
-      </c>
-    </row>
-    <row r="10">
-      <c r="A10" t="str">
-        <v>6a7154b74aac857cdce15cbd</v>
-      </c>
-      <c r="B10" t="str">
-        <v>Sarvathan C</v>
-      </c>
-      <c r="C10" t="str">
-        <v>sarvathan7235@gmail.com</v>
-      </c>
-      <c r="D10" t="str">
-        <v>local</v>
-      </c>
-      <c r="E10" t="str">
-        <v>9363265477</v>
-      </c>
-      <c r="F10" t="str">
-        <v>user</v>
-      </c>
-      <c r="G10" t="str">
-        <v>true</v>
-      </c>
-      <c r="H10" t="str">
-        <v>true</v>
-      </c>
-      <c r="I10" t="str">
-        <v>2026-08-04T02:55:51.439Z</v>
-      </c>
-      <c r="J10" t="str">
-        <v>2026-08-04T02:55:51.440Z</v>
-      </c>
-      <c r="K10" t="str">
-        <v>2026-08-04T02:56:56.559Z</v>
-      </c>
-      <c r="L10" t="str">
-        <v>[]</v>
-      </c>
-      <c r="M10" t="str">
-        <v>[]</v>
-      </c>
-      <c r="P10" t="str">
-        <v>[]</v>
-      </c>
-      <c r="Q10" t="str">
-        <v>true</v>
-      </c>
-      <c r="R10" t="str">
-        <v>[]</v>
-      </c>
-      <c r="S10" t="str">
-        <v>2026-08-04T05:27:19.859Z</v>
-      </c>
-    </row>
-    <row r="11">
-      <c r="A11" t="str">
-        <v>6a7154f14aac857cdce15cc0</v>
-      </c>
-      <c r="B11" t="str">
-        <v>Prem Neesanth</v>
-      </c>
-      <c r="C11" t="str">
-        <v>neesanth.1309@gmail.com</v>
-      </c>
-      <c r="D11" t="str">
-        <v>local</v>
-      </c>
-      <c r="E11" t="str">
-        <v>7339536677</v>
-      </c>
-      <c r="F11" t="str">
-        <v>user</v>
-      </c>
-      <c r="G11" t="str">
-        <v>true</v>
-      </c>
-      <c r="H11" t="str">
-        <v>true</v>
-      </c>
-      <c r="I11" t="str">
-        <v>2026-08-04T02:56:49.325Z</v>
-      </c>
-      <c r="J11" t="str">
-        <v>2026-08-04T02:56:49.325Z</v>
-      </c>
-      <c r="K11" t="str">
-        <v>2026-08-04T02:58:17.168Z</v>
-      </c>
-      <c r="L11" t="str">
-        <v>[]</v>
-      </c>
-      <c r="M11" t="str">
-        <v>[]</v>
-      </c>
-      <c r="P11" t="str">
-        <v>[]</v>
-      </c>
-      <c r="Q11" t="str">
-        <v>true</v>
-      </c>
-      <c r="R11" t="str">
-        <v>[]</v>
-      </c>
-      <c r="S11" t="str">
-        <v>2026-08-04T05:27:19.859Z</v>
-      </c>
-    </row>
-    <row r="12">
-      <c r="A12" t="str">
-        <v>6a71677c4aac857cdce15f62</v>
-      </c>
-      <c r="B12" t="str">
-        <v>HARIS KUMAR SIVASHANMUGAM</v>
-      </c>
-      <c r="C12" t="str">
-        <v>gsh2798@gmail.com</v>
-      </c>
-      <c r="D12" t="str">
-        <v>google</v>
-      </c>
-      <c r="F12" t="str">
-        <v>user</v>
-      </c>
-      <c r="G12" t="str">
-        <v>true</v>
-      </c>
-      <c r="H12" t="str">
-        <v>true</v>
-      </c>
-      <c r="I12" t="str">
-        <v>2026-08-04T04:15:56.708Z</v>
-      </c>
-      <c r="J12" t="str">
-        <v>2026-08-04T04:15:56.709Z</v>
-      </c>
-      <c r="K12" t="str">
-        <v>2026-08-04T04:15:56.709Z</v>
-      </c>
-      <c r="L12" t="str">
-        <v>[]</v>
-      </c>
-      <c r="M12" t="str">
-        <v>[]</v>
-      </c>
-      <c r="P12" t="str">
-        <v>[]</v>
-      </c>
-      <c r="Q12" t="str">
-        <v>true</v>
-      </c>
-      <c r="R12" t="str">
-        <v>[]</v>
-      </c>
-      <c r="S12" t="str">
-        <v>2026-08-04T05:27:19.859Z</v>
+        <v>2026-08-04T08:17:41.275Z</v>
       </c>
     </row>
   </sheetData>
   <ignoredErrors>
-    <ignoredError numberStoredAsText="1" sqref="A1:S12"/>
+    <ignoredError numberStoredAsText="1" sqref="A1:S9"/>
   </ignoredErrors>
 </worksheet>
 </file>
@@ -1176,7 +1027,7 @@
         <v>2026-08-03T13:43:50.194Z</v>
       </c>
       <c r="K2" t="str">
-        <v>2026-08-04T05:27:22.021Z</v>
+        <v>2026-08-04T08:17:44.718Z</v>
       </c>
     </row>
     <row r="3">
@@ -1211,7 +1062,7 @@
         <v>2026-08-02T11:15:41.649Z</v>
       </c>
       <c r="K3" t="str">
-        <v>2026-08-04T05:27:22.022Z</v>
+        <v>2026-08-04T08:17:44.718Z</v>
       </c>
     </row>
     <row r="4">
@@ -1246,7 +1097,7 @@
         <v>2026-08-03T13:43:35.459Z</v>
       </c>
       <c r="K4" t="str">
-        <v>2026-08-04T05:27:22.022Z</v>
+        <v>2026-08-04T08:17:44.718Z</v>
       </c>
     </row>
   </sheetData>
@@ -1326,7 +1177,7 @@
         <v>2026-08-02T11:44:43.854Z</v>
       </c>
       <c r="I2" t="str">
-        <v>2026-08-04T05:27:22.133Z</v>
+        <v>2026-08-04T08:17:44.841Z</v>
       </c>
     </row>
     <row r="3">
@@ -1355,7 +1206,7 @@
         <v>2026-08-02T11:45:37.177Z</v>
       </c>
       <c r="I3" t="str">
-        <v>2026-08-04T05:27:22.133Z</v>
+        <v>2026-08-04T08:17:44.841Z</v>
       </c>
     </row>
     <row r="4">
@@ -1384,7 +1235,7 @@
         <v>2026-08-02T11:45:18.169Z</v>
       </c>
       <c r="I4" t="str">
-        <v>2026-08-04T05:27:22.133Z</v>
+        <v>2026-08-04T08:17:44.841Z</v>
       </c>
     </row>
     <row r="5">
@@ -1413,7 +1264,7 @@
         <v>2026-08-02T11:45:03.112Z</v>
       </c>
       <c r="I5" t="str">
-        <v>2026-08-04T05:27:22.133Z</v>
+        <v>2026-08-04T08:17:44.841Z</v>
       </c>
     </row>
     <row r="6">
@@ -1442,7 +1293,7 @@
         <v>2026-08-02T11:24:43.615Z</v>
       </c>
       <c r="I6" t="str">
-        <v>2026-08-04T05:27:22.133Z</v>
+        <v>2026-08-04T08:17:44.841Z</v>
       </c>
     </row>
   </sheetData>
@@ -1454,7 +1305,7 @@
 
 <file path=xl/worksheets/sheet13.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:AM4"/>
+  <dimension ref="A1:AM5"/>
   <cols>
     <col min="1" max="1" width="26.83203125" customWidth="1"/>
     <col min="2" max="2" width="10.83203125" customWidth="1"/>
@@ -1476,7 +1327,7 @@
     <col min="18" max="18" width="15.83203125" customWidth="1"/>
     <col min="19" max="19" width="13.83203125" customWidth="1"/>
     <col min="20" max="20" width="15.83203125" customWidth="1"/>
-    <col min="21" max="21" width="18.83203125" customWidth="1"/>
+    <col min="21" max="21" width="26.83203125" customWidth="1"/>
     <col min="22" max="22" width="15.83203125" customWidth="1"/>
     <col min="23" max="23" width="32.83203125" customWidth="1"/>
     <col min="24" max="24" width="49.83203125" customWidth="1"/>
@@ -1728,7 +1579,7 @@
         <v>TCM-2026-0001</v>
       </c>
       <c r="AL2" t="str">
-        <v>2026-08-04T05:27:22.243Z</v>
+        <v>2026-08-04T08:17:45.092Z</v>
       </c>
     </row>
     <row r="3">
@@ -1844,7 +1695,7 @@
         <v>TCM-2026-0002</v>
       </c>
       <c r="AL3" t="str">
-        <v>2026-08-04T05:27:22.243Z</v>
+        <v>2026-08-04T08:17:45.092Z</v>
       </c>
       <c r="AM3" t="str">
         <v>User closed payment window before completion.</v>
@@ -1963,12 +1814,131 @@
         <v>TCM-2026-0003</v>
       </c>
       <c r="AL4" t="str">
-        <v>2026-08-04T05:27:22.244Z</v>
+        <v>2026-08-04T08:17:45.092Z</v>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="str">
+        <v>6a718cc0f0f91c3459f15086</v>
+      </c>
+      <c r="B5" t="str">
+        <v>false</v>
+      </c>
+      <c r="C5" t="str">
+        <v>6a707e784aac857cdce1455f</v>
+      </c>
+      <c r="D5" t="str">
+        <v>false</v>
+      </c>
+      <c r="E5" t="str">
+        <v>2026-08-03T18:30:00.000Z</v>
+      </c>
+      <c r="F5" t="str">
+        <v>4:00 PM – 6:00 PM</v>
+      </c>
+      <c r="G5" t="str">
+        <v>false</v>
+      </c>
+      <c r="H5" t="str">
+        <v>0</v>
+      </c>
+      <c r="I5" t="str">
+        <v>false</v>
+      </c>
+      <c r="J5" t="str">
+        <v>[{"productId":"6a299407c4fc5fbd6d56cfff","name":"Honey &amp; Almond","qty":1,"price":690,"originalPrice":690,"couponCode":null,"discountAmount":0,"image":"https://res.cloudinary.com/djkfvoxpx/image/upload/v1782736956/birthday%20cakes/lastgccevxmig4sxduwq.png","selectedFlavor":null,"selectedWeight":"500g","category":"birthday cakes","isCustomCake":false,"customDetails":null,"addons":[],"_id":"6a718cc0f0f91c3459f15087","sku":"HON-CAK-ST-50-260804-001"}]</v>
+      </c>
+      <c r="K5" t="str">
+        <v>690</v>
+      </c>
+      <c r="L5" t="str">
+        <v>0</v>
+      </c>
+      <c r="M5" t="str">
+        <v>33</v>
+      </c>
+      <c r="N5" t="str">
+        <v>17</v>
+      </c>
+      <c r="O5" t="str">
+        <v>33</v>
+      </c>
+      <c r="P5" t="str">
+        <v>740</v>
+      </c>
+      <c r="Q5" t="str">
+        <v>ONLINE</v>
+      </c>
+      <c r="R5" t="str">
+        <v>failed</v>
+      </c>
+      <c r="S5" t="str">
+        <v>confirmed</v>
+      </c>
+      <c r="T5" t="str">
+        <v>pending</v>
+      </c>
+      <c r="U5" t="str">
+        <v>Ak webflair technologies</v>
+      </c>
+      <c r="V5" t="str">
+        <v>9600732162</v>
+      </c>
+      <c r="W5" t="str">
+        <v>saasa</v>
+      </c>
+      <c r="X5" t="str">
+        <v>Vadakovai, Tamil Nadu, 641002</v>
+      </c>
+      <c r="Y5" t="str">
+        <v>as</v>
+      </c>
+      <c r="Z5" t="str">
+        <v>Coimbatore</v>
+      </c>
+      <c r="AA5" t="str">
+        <v>641002</v>
+      </c>
+      <c r="AB5" t="str">
+        <v>11.014139755391808</v>
+      </c>
+      <c r="AC5" t="str">
+        <v>76.94631442149254</v>
+      </c>
+      <c r="AD5" t="str">
+        <v>order_TLbK97205cPXNs</v>
+      </c>
+      <c r="AE5" t="str">
+        <v>2026-08-04T06:54:56.284Z</v>
+      </c>
+      <c r="AF5" t="str">
+        <v>false</v>
+      </c>
+      <c r="AG5" t="str">
+        <v>0</v>
+      </c>
+      <c r="AH5" t="str">
+        <v>2026-08-04T06:54:56.290Z</v>
+      </c>
+      <c r="AI5" t="str">
+        <v>2026-08-04T06:55:12.899Z</v>
+      </c>
+      <c r="AJ5" t="str">
+        <v>TCM-2026-0004</v>
+      </c>
+      <c r="AK5" t="str">
+        <v>TCM-2026-0004</v>
+      </c>
+      <c r="AL5" t="str">
+        <v>2026-08-04T08:17:45.092Z</v>
+      </c>
+      <c r="AM5" t="str">
+        <v>User closed payment window before completion.</v>
       </c>
     </row>
   </sheetData>
   <ignoredErrors>
-    <ignoredError numberStoredAsText="1" sqref="A1:AM4"/>
+    <ignoredError numberStoredAsText="1" sqref="A1:AM5"/>
   </ignoredErrors>
 </worksheet>
 </file>
@@ -1985,7 +1955,7 @@
 
 <file path=xl/worksheets/sheet15.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:M4"/>
+  <dimension ref="A1:M5"/>
   <cols>
     <col min="1" max="1" width="26.83203125" customWidth="1"/>
     <col min="2" max="2" width="26.83203125" customWidth="1"/>
@@ -2081,7 +2051,7 @@
         <v>2026-08-04T03:02:01.248Z</v>
       </c>
       <c r="M2" t="str">
-        <v>2026-08-04T05:27:22.433Z</v>
+        <v>2026-08-04T08:17:45.296Z</v>
       </c>
     </row>
     <row r="3">
@@ -2122,7 +2092,7 @@
         <v>2026-08-04T03:07:35.154Z</v>
       </c>
       <c r="M3" t="str">
-        <v>2026-08-04T05:27:22.433Z</v>
+        <v>2026-08-04T08:17:45.296Z</v>
       </c>
     </row>
     <row r="4">
@@ -2163,12 +2133,53 @@
         <v>2026-08-04T03:13:26.310Z</v>
       </c>
       <c r="M4" t="str">
-        <v>2026-08-04T05:27:22.433Z</v>
+        <v>2026-08-04T08:17:45.296Z</v>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="str">
+        <v>6a718cc1f0f91c3459f15089</v>
+      </c>
+      <c r="B5" t="str">
+        <v>6a718cc0f0f91c3459f15086</v>
+      </c>
+      <c r="C5" t="str">
+        <v>order_TLbK97205cPXNs</v>
+      </c>
+      <c r="D5" t="str">
+        <v/>
+      </c>
+      <c r="E5" t="str">
+        <v/>
+      </c>
+      <c r="F5" t="str">
+        <v>740</v>
+      </c>
+      <c r="G5" t="str">
+        <v>INR</v>
+      </c>
+      <c r="H5" t="str">
+        <v>failed</v>
+      </c>
+      <c r="I5" t="str">
+        <v>razorpay</v>
+      </c>
+      <c r="J5" t="str">
+        <v>User closed payment window before completion.</v>
+      </c>
+      <c r="K5" t="str">
+        <v>2026-08-04T06:54:57.002Z</v>
+      </c>
+      <c r="L5" t="str">
+        <v>2026-08-04T06:55:13.137Z</v>
+      </c>
+      <c r="M5" t="str">
+        <v>2026-08-04T08:17:45.296Z</v>
       </c>
     </row>
   </sheetData>
   <ignoredErrors>
-    <ignoredError numberStoredAsText="1" sqref="A1:M4"/>
+    <ignoredError numberStoredAsText="1" sqref="A1:M5"/>
   </ignoredErrors>
 </worksheet>
 </file>
@@ -2264,7 +2275,7 @@
         <v>2026-04-25T05:16:45.245Z</v>
       </c>
       <c r="L2" t="str">
-        <v>2026-08-04T05:27:22.561Z</v>
+        <v>2026-08-04T08:17:45.418Z</v>
       </c>
     </row>
     <row r="3">
@@ -2302,7 +2313,7 @@
         <v>2026-04-26T13:01:08.188Z</v>
       </c>
       <c r="L3" t="str">
-        <v>2026-08-04T05:27:22.561Z</v>
+        <v>2026-08-04T08:17:45.418Z</v>
       </c>
     </row>
     <row r="4">
@@ -2340,7 +2351,7 @@
         <v>2026-04-26T15:36:57.443Z</v>
       </c>
       <c r="L4" t="str">
-        <v>2026-08-04T05:27:22.561Z</v>
+        <v>2026-08-04T08:17:45.418Z</v>
       </c>
     </row>
     <row r="5">
@@ -2378,7 +2389,7 @@
         <v>2026-04-28T15:26:52.023Z</v>
       </c>
       <c r="L5" t="str">
-        <v>2026-08-04T05:27:22.561Z</v>
+        <v>2026-08-04T08:17:45.418Z</v>
       </c>
     </row>
     <row r="6">
@@ -2416,7 +2427,7 @@
         <v>2026-06-07T14:24:10.694Z</v>
       </c>
       <c r="L6" t="str">
-        <v>2026-08-04T05:27:22.561Z</v>
+        <v>2026-08-04T08:17:45.418Z</v>
       </c>
     </row>
     <row r="7">
@@ -2454,7 +2465,7 @@
         <v>2026-06-10T17:55:28.556Z</v>
       </c>
       <c r="L7" t="str">
-        <v>2026-08-04T05:27:22.561Z</v>
+        <v>2026-08-04T08:17:45.418Z</v>
       </c>
     </row>
     <row r="8">
@@ -2492,7 +2503,7 @@
         <v>2026-06-13T16:20:41.698Z</v>
       </c>
       <c r="L8" t="str">
-        <v>2026-08-04T05:27:22.561Z</v>
+        <v>2026-08-04T08:17:45.418Z</v>
       </c>
     </row>
     <row r="9">
@@ -2530,7 +2541,7 @@
         <v>2026-06-13T16:25:47.423Z</v>
       </c>
       <c r="L9" t="str">
-        <v>2026-08-04T05:27:22.561Z</v>
+        <v>2026-08-04T08:17:45.418Z</v>
       </c>
     </row>
     <row r="10">
@@ -2568,7 +2579,7 @@
         <v>2026-07-11T10:23:53.937Z</v>
       </c>
       <c r="L10" t="str">
-        <v>2026-08-04T05:27:22.561Z</v>
+        <v>2026-08-04T08:17:45.418Z</v>
       </c>
     </row>
   </sheetData>
@@ -2725,7 +2736,7 @@
         <v>2026-03-05T10:51:19.227Z</v>
       </c>
       <c r="T2" t="str">
-        <v>2026-08-04T05:27:22.785Z</v>
+        <v>2026-08-04T08:17:45.657Z</v>
       </c>
     </row>
     <row r="3" xml:space="preserve">
@@ -2789,7 +2800,7 @@
         <v>2026-01-31T07:51:47.756Z</v>
       </c>
       <c r="T3" t="str">
-        <v>2026-08-04T05:27:22.785Z</v>
+        <v>2026-08-04T08:17:45.657Z</v>
       </c>
     </row>
     <row r="4">
@@ -2851,7 +2862,7 @@
         <v>2026-01-16T16:33:33.279Z</v>
       </c>
       <c r="T4" t="str">
-        <v>2026-08-04T05:27:22.785Z</v>
+        <v>2026-08-04T08:17:45.657Z</v>
       </c>
     </row>
     <row r="5">
@@ -2907,7 +2918,7 @@
         <v>2026-06-12T17:08:32.112Z</v>
       </c>
       <c r="T5" t="str">
-        <v>2026-08-04T05:27:22.785Z</v>
+        <v>2026-08-04T08:17:45.657Z</v>
       </c>
     </row>
     <row r="6">
@@ -2969,7 +2980,7 @@
         <v>2026-02-25T11:00:52.464Z</v>
       </c>
       <c r="T6" t="str">
-        <v>2026-08-04T05:27:22.785Z</v>
+        <v>2026-08-04T08:17:45.657Z</v>
       </c>
     </row>
     <row r="7">
@@ -3010,7 +3021,7 @@
         <v>apify</v>
       </c>
       <c r="M7" t="str">
-        <v>2026-08-04T05:27:10.795Z</v>
+        <v>2026-08-04T08:17:31.120Z</v>
       </c>
       <c r="N7" t="str">
         <v>[]</v>
@@ -3019,19 +3030,19 @@
         <v>I ordered fresh mango cake and the cake was delicious and subtle making me want to eat more and I needed the cake in a very short span and they delivered it soon and made the moment memorable</v>
       </c>
       <c r="P7" t="str">
-        <v>2026-08-04T05:27:10.795Z</v>
+        <v>2026-08-04T08:17:31.120Z</v>
       </c>
       <c r="Q7" t="str">
-        <v>2026-08-04T05:27:18.046Z</v>
+        <v>2026-08-04T08:17:39.004Z</v>
       </c>
       <c r="R7" t="str">
         <v>["https://lh3.googleusercontent.com/grass-cs/ACvplmO_pqUM6Inbd4_tYNoXGkmjVXuMvqW1k6_n3WKo5GFjIU-jy6NJXw54DGSD41LE-vcpvHH45HW9eD-aeGFYOmHWhIvTyxBBuqd6GwDjK2xkDrER4qts8deU47gt4tI5Du1u0drm0TLOEtN-=w600-h450-p-k-no"]</v>
       </c>
       <c r="S7" t="str">
-        <v>2026-05-06T05:27:15.509Z</v>
+        <v>2026-05-06T08:17:37.228Z</v>
       </c>
       <c r="T7" t="str">
-        <v>2026-08-04T05:27:22.785Z</v>
+        <v>2026-08-04T08:17:45.657Z</v>
       </c>
     </row>
     <row r="8">
@@ -3093,7 +3104,7 @@
         <v>2026-02-04T08:34:24.383Z</v>
       </c>
       <c r="T8" t="str">
-        <v>2026-08-04T05:27:22.785Z</v>
+        <v>2026-08-04T08:17:45.657Z</v>
       </c>
     </row>
     <row r="9">
@@ -3155,7 +3166,7 @@
         <v>2026-03-05T11:17:24.179Z</v>
       </c>
       <c r="T9" t="str">
-        <v>2026-08-04T05:27:22.785Z</v>
+        <v>2026-08-04T08:17:45.657Z</v>
       </c>
     </row>
     <row r="10">
@@ -3211,7 +3222,7 @@
         <v>2026-06-12T17:08:32.573Z</v>
       </c>
       <c r="T10" t="str">
-        <v>2026-08-04T05:27:22.785Z</v>
+        <v>2026-08-04T08:17:45.657Z</v>
       </c>
     </row>
     <row r="11">
@@ -3273,7 +3284,7 @@
         <v>2026-01-28T12:33:53.732Z</v>
       </c>
       <c r="T11" t="str">
-        <v>2026-08-04T05:27:22.785Z</v>
+        <v>2026-08-04T08:17:45.657Z</v>
       </c>
     </row>
     <row r="12">
@@ -3314,7 +3325,7 @@
         <v>apify</v>
       </c>
       <c r="M12" t="str">
-        <v>2026-08-04T05:27:10.794Z</v>
+        <v>2026-08-04T08:17:31.119Z</v>
       </c>
       <c r="N12" t="str">
         <v>[]</v>
@@ -3323,19 +3334,19 @@
         <v>Cake serious ah romba super ah irrunthuchu and really worth for Money and more over I really cannot forget how it was so perfectly baked and the softness is it was top norch and thanks for making my birthday so special with your wonderful cakes</v>
       </c>
       <c r="P12" t="str">
-        <v>2026-08-04T05:27:10.794Z</v>
+        <v>2026-08-04T08:17:31.119Z</v>
       </c>
       <c r="Q12" t="str">
-        <v>2026-08-04T05:27:14.922Z</v>
+        <v>2026-08-04T08:17:35.658Z</v>
       </c>
       <c r="R12" t="str">
         <v>["https://lh3.googleusercontent.com/grass-cs/ACvplmOG5juTOg0n2Beu1G4Z36P75AAYFcngApbdEIQ8bWX_kgVMQYhGX700QZt9X6SnFtaNFrjSkpsNLwwBdKw478tehnEh5yXt4pkMBvEOLUcvS7MXI7846rYwqVXbXXfdy_Ogx3Qhpql9SQ_n=w600-h450-p-k-no"]</v>
       </c>
       <c r="S12" t="str">
-        <v>2026-07-05T05:27:09.522Z</v>
+        <v>2026-07-05T08:17:29.399Z</v>
       </c>
       <c r="T12" t="str">
-        <v>2026-08-04T05:27:22.785Z</v>
+        <v>2026-08-04T08:17:45.657Z</v>
       </c>
     </row>
     <row r="13">
@@ -3376,7 +3387,7 @@
         <v>apify</v>
       </c>
       <c r="M13" t="str">
-        <v>2026-08-04T05:27:10.794Z</v>
+        <v>2026-08-04T08:17:31.119Z</v>
       </c>
       <c r="N13" t="str">
         <v>[]</v>
@@ -3385,19 +3396,19 @@
         <v>Thank you for making our special day even more special with your wonderful cake. It was absolutely fabulous, and everyone in my family loved it. The birthday girl especially loved it a lot We truly enjoyed it!</v>
       </c>
       <c r="P13" t="str">
-        <v>2026-08-04T05:27:10.794Z</v>
+        <v>2026-08-04T08:17:31.119Z</v>
       </c>
       <c r="Q13" t="str">
-        <v>2026-08-04T05:27:15.078Z</v>
+        <v>2026-08-04T08:17:35.782Z</v>
       </c>
       <c r="R13" t="str">
-        <v>["https://lh3.googleusercontent.com/grass-cs/ACvplmMulUa3xPhcvcWL9C2ZnjqVk3cm3fH6dvtIGWEA5ehkU7hw6DVpeNKZU9MEzz2gk2EFkRuJhbbmc3RtKB_cPs05ROPsIHTpkmMFvA4lISBmkO5-fYepMwk7ucK8ydnw7e_D3-3LSMDxWiRn=w600-h450-p-k-no"]</v>
+        <v>["https://lh3.googleusercontent.com/grass-cs/ACvplmO0A6fdSyS7vmWIkbQK4rcTInFQpzKUTtFRzho5FfZbx-wsVCA9CcTx_eSpgfwQC2ljTWZu0yS5FepZ1imnGZNTWgnEr_KRmzBB70noiCZos4L_R3pPU8Q6cGyz2qd76STVZm7Nf0p9AbFh=w600-h450-p-k-no"]</v>
       </c>
       <c r="S13" t="str">
-        <v>2026-07-05T05:27:09.522Z</v>
+        <v>2026-07-05T08:17:29.399Z</v>
       </c>
       <c r="T13" t="str">
-        <v>2026-08-04T05:27:22.785Z</v>
+        <v>2026-08-04T08:17:45.657Z</v>
       </c>
     </row>
     <row r="14">
@@ -3438,7 +3449,7 @@
         <v>apify</v>
       </c>
       <c r="M14" t="str">
-        <v>2026-08-04T05:27:10.794Z</v>
+        <v>2026-08-04T08:17:31.119Z</v>
       </c>
       <c r="N14" t="str">
         <v>[]</v>
@@ -3447,19 +3458,19 @@
         <v>Good</v>
       </c>
       <c r="P14" t="str">
-        <v>2026-08-04T05:27:10.794Z</v>
+        <v>2026-08-04T08:17:31.119Z</v>
       </c>
       <c r="Q14" t="str">
-        <v>2026-08-04T05:27:15.188Z</v>
+        <v>2026-08-04T08:17:35.909Z</v>
       </c>
       <c r="R14" t="str">
         <v>[]</v>
       </c>
       <c r="S14" t="str">
-        <v>2026-07-05T05:27:09.522Z</v>
+        <v>2026-07-05T08:17:29.399Z</v>
       </c>
       <c r="T14" t="str">
-        <v>2026-08-04T05:27:22.785Z</v>
+        <v>2026-08-04T08:17:45.657Z</v>
       </c>
     </row>
     <row r="15">
@@ -3500,7 +3511,7 @@
         <v>apify</v>
       </c>
       <c r="M15" t="str">
-        <v>2026-08-04T05:27:10.794Z</v>
+        <v>2026-08-04T08:17:31.119Z</v>
       </c>
       <c r="N15" t="str">
         <v>[]</v>
@@ -3509,19 +3520,19 @@
         <v>Ordered a chocolate truffle cake which was delicious &amp; loved by all and customised designed was too cute as expected!</v>
       </c>
       <c r="P15" t="str">
-        <v>2026-08-04T05:27:10.794Z</v>
+        <v>2026-08-04T08:17:31.119Z</v>
       </c>
       <c r="Q15" t="str">
-        <v>2026-08-04T05:27:15.311Z</v>
+        <v>2026-08-04T08:17:36.065Z</v>
       </c>
       <c r="R15" t="str">
         <v>[]</v>
       </c>
       <c r="S15" t="str">
-        <v>2026-07-05T05:27:09.522Z</v>
+        <v>2026-07-05T08:17:29.399Z</v>
       </c>
       <c r="T15" t="str">
-        <v>2026-08-04T05:27:22.785Z</v>
+        <v>2026-08-04T08:17:45.657Z</v>
       </c>
     </row>
     <row r="16" xml:space="preserve">
@@ -3562,7 +3573,7 @@
         <v>apify</v>
       </c>
       <c r="M16" t="str">
-        <v>2026-08-04T05:27:10.794Z</v>
+        <v>2026-08-04T08:17:31.119Z</v>
       </c>
       <c r="N16" t="str">
         <v>[]</v>
@@ -3572,10 +3583,10 @@
 Super tasty without egg.</v>
       </c>
       <c r="P16" t="str">
-        <v>2026-08-04T05:27:10.794Z</v>
+        <v>2026-08-04T08:17:31.119Z</v>
       </c>
       <c r="Q16" t="str">
-        <v>2026-08-04T05:27:15.438Z</v>
+        <v>2026-08-04T08:17:36.191Z</v>
       </c>
       <c r="R16" t="str">
         <v>["https://lh3.googleusercontent.com/grass-cs/ACvplmONtSSbB4uGez6qp_Oo8LiQdedj1qwfFuDdIJXVqvkKvZyR_cObSIrJJTDlYeKkfu1doLjLCI-wKgky_rYcMlkNyHQgmPX6FAqLSJhw39Sk2BGr1EmZiU4De_RNF8CN5uSsJ7FaqHSDAZqV=w600-h450-p-k-no"]</v>
@@ -3584,7 +3595,7 @@
         <v/>
       </c>
       <c r="T16" t="str">
-        <v>2026-08-04T05:27:22.785Z</v>
+        <v>2026-08-04T08:17:45.657Z</v>
       </c>
     </row>
     <row r="17">
@@ -3625,7 +3636,7 @@
         <v>apify</v>
       </c>
       <c r="M17" t="str">
-        <v>2026-08-04T05:27:10.794Z</v>
+        <v>2026-08-04T08:17:31.119Z</v>
       </c>
       <c r="N17" t="str">
         <v>[]</v>
@@ -3634,19 +3645,19 @@
         <v>Such a good ambience....and taste is too good</v>
       </c>
       <c r="P17" t="str">
-        <v>2026-08-04T05:27:10.794Z</v>
+        <v>2026-08-04T08:17:31.119Z</v>
       </c>
       <c r="Q17" t="str">
-        <v>2026-08-04T05:27:15.562Z</v>
+        <v>2026-08-04T08:17:36.315Z</v>
       </c>
       <c r="R17" t="str">
         <v>["https://lh3.googleusercontent.com/grass-cs/ACvplmO0kf3mosn0MhTEpsOSZW09MccHmzeA8TZsdRO-p3IGf3RxaIl4y6SPd1_0ef9GnSku92QtmySFuZfjG8vZOOx0oaU8KVlLu5q_qEap9rdGaHi608Mdw_slZC-my59ygMAPUb9sEZlnQQc=w600-h450-p-k-no"]</v>
       </c>
       <c r="S17" t="str">
-        <v>2026-07-05T05:27:09.522Z</v>
+        <v>2026-07-05T08:17:29.399Z</v>
       </c>
       <c r="T17" t="str">
-        <v>2026-08-04T05:27:22.785Z</v>
+        <v>2026-08-04T08:17:45.657Z</v>
       </c>
     </row>
     <row r="18">
@@ -3687,7 +3698,7 @@
         <v>apify</v>
       </c>
       <c r="M18" t="str">
-        <v>2026-08-04T05:27:10.794Z</v>
+        <v>2026-08-04T08:17:31.119Z</v>
       </c>
       <c r="N18" t="str">
         <v>[]</v>
@@ -3696,19 +3707,19 @@
         <v>a month agoRecommended dishesTiramisu, Sizzling Brownie, Black Forest Cake 500 G, Tres Leches RosemilkLike</v>
       </c>
       <c r="P18" t="str">
-        <v>2026-08-04T05:27:10.794Z</v>
+        <v>2026-08-04T08:17:31.119Z</v>
       </c>
       <c r="Q18" t="str">
-        <v>2026-08-04T05:27:15.655Z</v>
+        <v>2026-08-04T08:17:36.456Z</v>
       </c>
       <c r="R18" t="str">
         <v>[]</v>
       </c>
       <c r="S18" t="str">
-        <v>2026-07-05T05:27:09.522Z</v>
+        <v>2026-07-05T08:17:29.399Z</v>
       </c>
       <c r="T18" t="str">
-        <v>2026-08-04T05:27:22.785Z</v>
+        <v>2026-08-04T08:17:45.657Z</v>
       </c>
     </row>
     <row r="19">
@@ -3749,7 +3760,7 @@
         <v>apify</v>
       </c>
       <c r="M19" t="str">
-        <v>2026-08-04T05:27:10.794Z</v>
+        <v>2026-08-04T08:17:31.119Z</v>
       </c>
       <c r="N19" t="str">
         <v>[]</v>
@@ -3758,19 +3769,19 @@
         <v>Taste was very good...</v>
       </c>
       <c r="P19" t="str">
-        <v>2026-08-04T05:27:10.794Z</v>
+        <v>2026-08-04T08:17:31.119Z</v>
       </c>
       <c r="Q19" t="str">
-        <v>2026-08-04T05:27:15.796Z</v>
+        <v>2026-08-04T08:17:36.596Z</v>
       </c>
       <c r="R19" t="str">
-        <v>["https://lh3.googleusercontent.com/grass-cs/ACvplmOgtR4VUkuepj9Tp2Lmn6DXdVIFdRY9WHSKLlAh7UVDZSdd68nHtZqEkGDNbU474br7znLKGIZRHMb9BCsFK0FhlR-WRXjfKjI9f4IytETKQZBn77rp0CntQzUBphkowfJoDAvNoza61pT3=w600-h450-p-k-no"]</v>
+        <v>["https://lh3.googleusercontent.com/grass-cs/ACvplmMQhLM__tf-fQLYIKdtORSGqBUtG5S298WNziQA0YLBa0qcmqlGp1pmBKP7Xufta2V6R_ZgJGv4QeX88I4JE3KFrMDsieR1Vota59d7i2OwAN4tNlHejKJUC3ppgv1lsBKPztomFcKY1cI3=w600-h450-p-k-no"]</v>
       </c>
       <c r="S19" t="str">
-        <v>2026-06-05T05:27:11.319Z</v>
+        <v>2026-06-05T08:17:31.361Z</v>
       </c>
       <c r="T19" t="str">
-        <v>2026-08-04T05:27:22.785Z</v>
+        <v>2026-08-04T08:17:45.657Z</v>
       </c>
     </row>
     <row r="20">
@@ -3811,7 +3822,7 @@
         <v>apify</v>
       </c>
       <c r="M20" t="str">
-        <v>2026-08-04T05:27:10.794Z</v>
+        <v>2026-08-04T08:17:31.119Z</v>
       </c>
       <c r="N20" t="str">
         <v>[]</v>
@@ -3820,19 +3831,19 @@
         <v>The hot chocolate was superb, the milkshake and chocolate brownie was so comforting. Love it</v>
       </c>
       <c r="P20" t="str">
-        <v>2026-08-04T05:27:10.794Z</v>
+        <v>2026-08-04T08:17:31.119Z</v>
       </c>
       <c r="Q20" t="str">
-        <v>2026-08-04T05:27:15.906Z</v>
+        <v>2026-08-04T08:17:36.723Z</v>
       </c>
       <c r="R20" t="str">
         <v>[]</v>
       </c>
       <c r="S20" t="str">
-        <v>2026-06-05T05:27:11.319Z</v>
+        <v>2026-06-05T08:17:31.361Z</v>
       </c>
       <c r="T20" t="str">
-        <v>2026-08-04T05:27:22.785Z</v>
+        <v>2026-08-04T08:17:45.657Z</v>
       </c>
     </row>
     <row r="21">
@@ -3873,7 +3884,7 @@
         <v>apify</v>
       </c>
       <c r="M21" t="str">
-        <v>2026-08-04T05:27:10.794Z</v>
+        <v>2026-08-04T08:17:31.119Z</v>
       </c>
       <c r="N21" t="str">
         <v>[]</v>
@@ -3882,19 +3893,19 @@
         <v>Comforting pastry, rich hot chocolate, and the perfect cozy combo. 🤎 Belgium hot chocolate was awesome. …</v>
       </c>
       <c r="P21" t="str">
-        <v>2026-08-04T05:27:10.794Z</v>
+        <v>2026-08-04T08:17:31.119Z</v>
       </c>
       <c r="Q21" t="str">
-        <v>2026-08-04T05:27:16.062Z</v>
+        <v>2026-08-04T08:17:36.846Z</v>
       </c>
       <c r="R21" t="str">
         <v>[]</v>
       </c>
       <c r="S21" t="str">
-        <v>2026-06-05T05:27:11.319Z</v>
+        <v>2026-06-05T08:17:31.361Z</v>
       </c>
       <c r="T21" t="str">
-        <v>2026-08-04T05:27:22.785Z</v>
+        <v>2026-08-04T08:17:45.657Z</v>
       </c>
     </row>
     <row r="22" xml:space="preserve">
@@ -3935,7 +3946,7 @@
         <v>apify</v>
       </c>
       <c r="M22" t="str">
-        <v>2026-08-04T05:27:10.794Z</v>
+        <v>2026-08-04T08:17:31.119Z</v>
       </c>
       <c r="N22" t="str">
         <v>[]</v>
@@ -3945,19 +3956,19 @@
 This place is worth its price 💯</v>
       </c>
       <c r="P22" t="str">
-        <v>2026-08-04T05:27:10.794Z</v>
+        <v>2026-08-04T08:17:31.119Z</v>
       </c>
       <c r="Q22" t="str">
-        <v>2026-08-04T05:27:16.172Z</v>
+        <v>2026-08-04T08:17:36.956Z</v>
       </c>
       <c r="R22" t="str">
         <v>[]</v>
       </c>
       <c r="S22" t="str">
-        <v>2026-06-05T05:27:11.319Z</v>
+        <v>2026-06-05T08:17:31.361Z</v>
       </c>
       <c r="T22" t="str">
-        <v>2026-08-04T05:27:22.785Z</v>
+        <v>2026-08-04T08:17:45.657Z</v>
       </c>
     </row>
     <row r="23">
@@ -3998,7 +4009,7 @@
         <v>apify</v>
       </c>
       <c r="M23" t="str">
-        <v>2026-08-04T05:27:10.794Z</v>
+        <v>2026-08-04T08:17:31.119Z</v>
       </c>
       <c r="N23" t="str">
         <v>[]</v>
@@ -4007,19 +4018,19 @@
         <v>Absolutely loved their Belgium hot chocolate and hazel nut hot chocolate. Also enjoyed their sandwich and burger..... Beautiful ambience and host ❤️</v>
       </c>
       <c r="P23" t="str">
-        <v>2026-08-04T05:27:10.794Z</v>
+        <v>2026-08-04T08:17:31.119Z</v>
       </c>
       <c r="Q23" t="str">
-        <v>2026-08-04T05:27:16.296Z</v>
+        <v>2026-08-04T08:17:37.080Z</v>
       </c>
       <c r="R23" t="str">
         <v>["https://lh3.googleusercontent.com/grass-cs/ACvplmOXAZUZBxNTEwmcNAOXzyMJILSZKCGgRdx_SRzeZcQgg2_2KoLfuNVhZbfhshPOOgJASJ3O_fM_Q9pVms4Um_jwyX3NwEE9oW8nI4vlm6jsmCPPE04Wpo-0HAeErO0yeZNUKXFsbaf87G0=w600-h450-p-k-no"]</v>
       </c>
       <c r="S23" t="str">
-        <v>2026-06-05T05:27:11.319Z</v>
+        <v>2026-06-05T08:17:31.361Z</v>
       </c>
       <c r="T23" t="str">
-        <v>2026-08-04T05:27:22.786Z</v>
+        <v>2026-08-04T08:17:45.657Z</v>
       </c>
     </row>
     <row r="24" xml:space="preserve">
@@ -4060,7 +4071,7 @@
         <v>apify</v>
       </c>
       <c r="M24" t="str">
-        <v>2026-08-04T05:27:10.794Z</v>
+        <v>2026-08-04T08:17:31.120Z</v>
       </c>
       <c r="N24" t="str">
         <v>[]</v>
@@ -4070,19 +4081,19 @@
 I would defenitely reach back here once again</v>
       </c>
       <c r="P24" t="str">
-        <v>2026-08-04T05:27:10.794Z</v>
+        <v>2026-08-04T08:17:31.119Z</v>
       </c>
       <c r="Q24" t="str">
-        <v>2026-08-04T05:27:16.438Z</v>
+        <v>2026-08-04T08:17:37.316Z</v>
       </c>
       <c r="R24" t="str">
         <v>[]</v>
       </c>
       <c r="S24" t="str">
-        <v>2026-06-05T05:27:11.319Z</v>
+        <v>2026-06-05T08:17:31.361Z</v>
       </c>
       <c r="T24" t="str">
-        <v>2026-08-04T05:27:22.786Z</v>
+        <v>2026-08-04T08:17:45.657Z</v>
       </c>
     </row>
     <row r="25">
@@ -4123,7 +4134,7 @@
         <v>apify</v>
       </c>
       <c r="M25" t="str">
-        <v>2026-08-04T05:27:10.794Z</v>
+        <v>2026-08-04T08:17:31.120Z</v>
       </c>
       <c r="N25" t="str">
         <v>[]</v>
@@ -4132,19 +4143,19 @@
         <v>Good</v>
       </c>
       <c r="P25" t="str">
-        <v>2026-08-04T05:27:10.794Z</v>
+        <v>2026-08-04T08:17:31.120Z</v>
       </c>
       <c r="Q25" t="str">
-        <v>2026-08-04T05:27:16.561Z</v>
+        <v>2026-08-04T08:17:37.472Z</v>
       </c>
       <c r="R25" t="str">
         <v>[]</v>
       </c>
       <c r="S25" t="str">
-        <v>2026-06-05T05:27:11.319Z</v>
+        <v>2026-06-05T08:17:31.361Z</v>
       </c>
       <c r="T25" t="str">
-        <v>2026-08-04T05:27:22.786Z</v>
+        <v>2026-08-04T08:17:45.657Z</v>
       </c>
     </row>
     <row r="26">
@@ -4185,7 +4196,7 @@
         <v>apify</v>
       </c>
       <c r="M26" t="str">
-        <v>2026-08-04T05:27:10.794Z</v>
+        <v>2026-08-04T08:17:31.120Z</v>
       </c>
       <c r="N26" t="str">
         <v>[]</v>
@@ -4194,19 +4205,19 @@
         <v>Ordered customized cake. Taste was really good and they customized the cake based on my preference.</v>
       </c>
       <c r="P26" t="str">
-        <v>2026-08-04T05:27:10.794Z</v>
+        <v>2026-08-04T08:17:31.120Z</v>
       </c>
       <c r="Q26" t="str">
-        <v>2026-08-04T05:27:16.703Z</v>
+        <v>2026-08-04T08:17:37.582Z</v>
       </c>
       <c r="R26" t="str">
         <v>[]</v>
       </c>
       <c r="S26" t="str">
-        <v>2026-06-05T05:27:11.319Z</v>
+        <v>2026-06-05T08:17:31.361Z</v>
       </c>
       <c r="T26" t="str">
-        <v>2026-08-04T05:27:22.786Z</v>
+        <v>2026-08-04T08:17:45.657Z</v>
       </c>
     </row>
     <row r="27">
@@ -4247,7 +4258,7 @@
         <v>apify</v>
       </c>
       <c r="M27" t="str">
-        <v>2026-08-04T05:27:10.794Z</v>
+        <v>2026-08-04T08:17:31.120Z</v>
       </c>
       <c r="N27" t="str">
         <v>[]</v>
@@ -4256,19 +4267,19 @@
         <v>Delicious cakes 😋 and great service and one of my favorite cake shop !!</v>
       </c>
       <c r="P27" t="str">
-        <v>2026-08-04T05:27:10.794Z</v>
+        <v>2026-08-04T08:17:31.120Z</v>
       </c>
       <c r="Q27" t="str">
-        <v>2026-08-04T05:27:16.826Z</v>
+        <v>2026-08-04T08:17:37.705Z</v>
       </c>
       <c r="R27" t="str">
         <v>["https://lh3.googleusercontent.com/grass-cs/ACvplmPOyYm8EGEtNp0qLiPcMfjVRURnxDznB2mpI1Tmnh9vNtXC2tsDOYX8Kilq2QE_xCBTc7YBxxU4vVjLiMDNjR-fvb295N2I9abXqIQbHgy3ZuvSz89148s_5eRDqUzCT9pgO1N73nJ2YqFg=w600-h450-p-k-no"]</v>
       </c>
       <c r="S27" t="str">
-        <v>2026-06-05T05:27:11.319Z</v>
+        <v>2026-06-05T08:17:33.323Z</v>
       </c>
       <c r="T27" t="str">
-        <v>2026-08-04T05:27:22.786Z</v>
+        <v>2026-08-04T08:17:45.657Z</v>
       </c>
     </row>
     <row r="28">
@@ -4309,7 +4320,7 @@
         <v>apify</v>
       </c>
       <c r="M28" t="str">
-        <v>2026-08-04T05:27:10.794Z</v>
+        <v>2026-08-04T08:17:31.120Z</v>
       </c>
       <c r="N28" t="str">
         <v>[]</v>
@@ -4318,19 +4329,19 @@
         <v>Tried chocolate truffle cake here and it was really awesome</v>
       </c>
       <c r="P28" t="str">
-        <v>2026-08-04T05:27:10.794Z</v>
+        <v>2026-08-04T08:17:31.120Z</v>
       </c>
       <c r="Q28" t="str">
-        <v>2026-08-04T05:27:16.920Z</v>
+        <v>2026-08-04T08:17:37.831Z</v>
       </c>
       <c r="R28" t="str">
         <v>[]</v>
       </c>
       <c r="S28" t="str">
-        <v>2026-06-05T05:27:13.649Z</v>
+        <v>2026-06-05T08:17:33.323Z</v>
       </c>
       <c r="T28" t="str">
-        <v>2026-08-04T05:27:22.786Z</v>
+        <v>2026-08-04T08:17:45.657Z</v>
       </c>
     </row>
     <row r="29" xml:space="preserve">
@@ -4371,7 +4382,7 @@
         <v>apify</v>
       </c>
       <c r="M29" t="str">
-        <v>2026-08-04T05:27:10.794Z</v>
+        <v>2026-08-04T08:17:31.120Z</v>
       </c>
       <c r="N29" t="str">
         <v>[]</v>
@@ -4382,19 +4393,19 @@
 Done exactly like the reference picture</v>
       </c>
       <c r="P29" t="str">
-        <v>2026-08-04T05:27:10.794Z</v>
+        <v>2026-08-04T08:17:31.120Z</v>
       </c>
       <c r="Q29" t="str">
-        <v>2026-08-04T05:27:17.030Z</v>
+        <v>2026-08-04T08:17:37.955Z</v>
       </c>
       <c r="R29" t="str">
         <v>[]</v>
       </c>
       <c r="S29" t="str">
-        <v>2026-06-05T05:27:13.649Z</v>
+        <v>2026-06-05T08:17:33.323Z</v>
       </c>
       <c r="T29" t="str">
-        <v>2026-08-04T05:27:22.786Z</v>
+        <v>2026-08-04T08:17:45.657Z</v>
       </c>
     </row>
     <row r="30">
@@ -4435,7 +4446,7 @@
         <v>apify</v>
       </c>
       <c r="M30" t="str">
-        <v>2026-08-04T05:27:10.794Z</v>
+        <v>2026-08-04T08:17:31.120Z</v>
       </c>
       <c r="N30" t="str">
         <v>[]</v>
@@ -4444,19 +4455,19 @@
         <v>We ordered Vannila flavour theme cake for our daughter birthday. It was upto the expected level both in taste and theme quality</v>
       </c>
       <c r="P30" t="str">
-        <v>2026-08-04T05:27:10.794Z</v>
+        <v>2026-08-04T08:17:31.120Z</v>
       </c>
       <c r="Q30" t="str">
-        <v>2026-08-04T05:27:17.139Z</v>
+        <v>2026-08-04T08:17:38.080Z</v>
       </c>
       <c r="R30" t="str">
         <v>["https://lh3.googleusercontent.com/grass-cs/ACvplmPqazGT7seHADgBYuM7nHMtdenj7ca55lDKxCXdBfT3ZDp6E2mts5nkDCCVFE7qRIEsqLKJbecGdGpSTF2zkCQcBeEVikiDha5V_c10_eq2sTMWJEqXYoVKpdl6rt8RDrfTPVQ4TSLrYyVS=w600-h450-p-k-no"]</v>
       </c>
       <c r="S30" t="str">
-        <v>2026-06-05T05:27:13.649Z</v>
+        <v>2026-06-05T08:17:33.323Z</v>
       </c>
       <c r="T30" t="str">
-        <v>2026-08-04T05:27:22.786Z</v>
+        <v>2026-08-04T08:17:45.658Z</v>
       </c>
     </row>
     <row r="31">
@@ -4497,7 +4508,7 @@
         <v>apify</v>
       </c>
       <c r="M31" t="str">
-        <v>2026-08-04T05:27:10.794Z</v>
+        <v>2026-08-04T08:17:31.120Z</v>
       </c>
       <c r="N31" t="str">
         <v>[]</v>
@@ -4506,19 +4517,19 @@
         <v>So delicious</v>
       </c>
       <c r="P31" t="str">
-        <v>2026-08-04T05:27:10.794Z</v>
+        <v>2026-08-04T08:17:31.120Z</v>
       </c>
       <c r="Q31" t="str">
-        <v>2026-08-04T05:27:17.248Z</v>
+        <v>2026-08-04T08:17:38.190Z</v>
       </c>
       <c r="R31" t="str">
         <v>[]</v>
       </c>
       <c r="S31" t="str">
-        <v>2026-06-05T05:27:13.649Z</v>
+        <v>2026-06-05T08:17:33.323Z</v>
       </c>
       <c r="T31" t="str">
-        <v>2026-08-04T05:27:22.786Z</v>
+        <v>2026-08-04T08:17:45.658Z</v>
       </c>
     </row>
     <row r="32">
@@ -4559,7 +4570,7 @@
         <v>apify</v>
       </c>
       <c r="M32" t="str">
-        <v>2026-08-04T05:27:10.794Z</v>
+        <v>2026-08-04T08:17:31.120Z</v>
       </c>
       <c r="N32" t="str">
         <v>[]</v>
@@ -4568,19 +4579,19 @@
         <v>Best place for fresh cakes and muffins</v>
       </c>
       <c r="P32" t="str">
-        <v>2026-08-04T05:27:10.794Z</v>
+        <v>2026-08-04T08:17:31.120Z</v>
       </c>
       <c r="Q32" t="str">
-        <v>2026-08-04T05:27:17.374Z</v>
+        <v>2026-08-04T08:17:38.330Z</v>
       </c>
       <c r="R32" t="str">
         <v>[]</v>
       </c>
       <c r="S32" t="str">
-        <v>2026-06-05T05:27:13.649Z</v>
+        <v>2026-06-05T08:17:35.289Z</v>
       </c>
       <c r="T32" t="str">
-        <v>2026-08-04T05:27:22.786Z</v>
+        <v>2026-08-04T08:17:45.658Z</v>
       </c>
     </row>
     <row r="33">
@@ -4621,7 +4632,7 @@
         <v>apify</v>
       </c>
       <c r="M33" t="str">
-        <v>2026-08-04T05:27:10.794Z</v>
+        <v>2026-08-04T08:17:31.120Z</v>
       </c>
       <c r="N33" t="str">
         <v>[]</v>
@@ -4630,19 +4641,19 @@
         <v>The veggie sandwich was delicious! So was the brownie milkshake which is a must try. The atmosphere is really good here and it's def an underrated café.</v>
       </c>
       <c r="P33" t="str">
-        <v>2026-08-04T05:27:10.794Z</v>
+        <v>2026-08-04T08:17:31.120Z</v>
       </c>
       <c r="Q33" t="str">
-        <v>2026-08-04T05:27:17.498Z</v>
+        <v>2026-08-04T08:17:38.456Z</v>
       </c>
       <c r="R33" t="str">
         <v>[]</v>
       </c>
       <c r="S33" t="str">
-        <v>2026-06-05T05:27:15.509Z</v>
+        <v>2026-06-05T08:17:35.289Z</v>
       </c>
       <c r="T33" t="str">
-        <v>2026-08-04T05:27:22.786Z</v>
+        <v>2026-08-04T08:17:45.658Z</v>
       </c>
     </row>
     <row r="34">
@@ -4683,7 +4694,7 @@
         <v>apify</v>
       </c>
       <c r="M34" t="str">
-        <v>2026-08-04T05:27:10.794Z</v>
+        <v>2026-08-04T08:17:31.120Z</v>
       </c>
       <c r="N34" t="str">
         <v>[]</v>
@@ -4692,10 +4703,10 @@
         <v>Excellent taste. Had fun. Excellent customer service. Tres lechues Cherry chocolate is mind blowing.</v>
       </c>
       <c r="P34" t="str">
-        <v>2026-08-04T05:27:10.794Z</v>
+        <v>2026-08-04T08:17:31.120Z</v>
       </c>
       <c r="Q34" t="str">
-        <v>2026-08-04T05:27:17.591Z</v>
+        <v>2026-08-04T08:17:38.563Z</v>
       </c>
       <c r="R34" t="str">
         <v>[]</v>
@@ -4704,7 +4715,7 @@
         <v/>
       </c>
       <c r="T34" t="str">
-        <v>2026-08-04T05:27:22.786Z</v>
+        <v>2026-08-04T08:17:45.658Z</v>
       </c>
     </row>
     <row r="35">
@@ -4745,7 +4756,7 @@
         <v>apify</v>
       </c>
       <c r="M35" t="str">
-        <v>2026-08-04T05:27:10.795Z</v>
+        <v>2026-08-04T08:17:31.120Z</v>
       </c>
       <c r="N35" t="str">
         <v>[]</v>
@@ -4754,10 +4765,10 @@
         <v>I ordered a birthday cake as I specified about cake with animals theme 🎂...I felt so good to taste and it's so good Thank you</v>
       </c>
       <c r="P35" t="str">
-        <v>2026-08-04T05:27:10.794Z</v>
+        <v>2026-08-04T08:17:31.120Z</v>
       </c>
       <c r="Q35" t="str">
-        <v>2026-08-04T05:27:17.687Z</v>
+        <v>2026-08-04T08:17:38.672Z</v>
       </c>
       <c r="R35" t="str">
         <v>[]</v>
@@ -4766,7 +4777,7 @@
         <v/>
       </c>
       <c r="T35" t="str">
-        <v>2026-08-04T05:27:22.786Z</v>
+        <v>2026-08-04T08:17:45.658Z</v>
       </c>
     </row>
     <row r="36">
@@ -4807,7 +4818,7 @@
         <v>apify</v>
       </c>
       <c r="M36" t="str">
-        <v>2026-08-04T05:27:10.795Z</v>
+        <v>2026-08-04T08:17:31.120Z</v>
       </c>
       <c r="N36" t="str">
         <v>[]</v>
@@ -4816,19 +4827,19 @@
         <v>Cake was very very tasty and look wise very beautiful and i really enjoy a lot and my family members thank you so much for your beautiful cake🥰🥰</v>
       </c>
       <c r="P36" t="str">
-        <v>2026-08-04T05:27:10.795Z</v>
+        <v>2026-08-04T08:17:31.120Z</v>
       </c>
       <c r="Q36" t="str">
-        <v>2026-08-04T05:27:17.795Z</v>
+        <v>2026-08-04T08:17:38.797Z</v>
       </c>
       <c r="R36" t="str">
         <v>["https://lh3.googleusercontent.com/grass-cs/ACvplmPEeUPLqKmsdMkTdKuoXGDOF8FLbqv6pUAcvH6GEzKqRC0N88UDcuyMnyhEE47x34SP-wdjoPtrNiWeTQScGKXIojC8hlTXcA3G2cchgSCF60cJOkkNYqh3mXXViIQSsepwVOopjTXtXOOC=w300-h450-p-k-no","https://lh3.googleusercontent.com/grass-cs/ACvplmP_Co_hhy-KcG2OYgEL3UMCuP7KpxjnLXtF8R2Xz_Mi20qsy3hYlcfgGZjDlGQMSXesFzJy4hqE7bEp_7q_GmY6sN1Rv335HQMy1osqlPznyQI2-q9Yj_z8MxIaUsvw84sV9ClZD_5cL3QI=w300-h450-p-k-no"]</v>
       </c>
       <c r="S36" t="str">
-        <v>2026-05-06T05:27:15.509Z</v>
+        <v>2026-05-06T08:17:35.289Z</v>
       </c>
       <c r="T36" t="str">
-        <v>2026-08-04T05:27:22.786Z</v>
+        <v>2026-08-04T08:17:45.658Z</v>
       </c>
     </row>
     <row r="37">
@@ -4869,7 +4880,7 @@
         <v>apify</v>
       </c>
       <c r="M37" t="str">
-        <v>2026-08-04T05:27:10.795Z</v>
+        <v>2026-08-04T08:17:31.120Z</v>
       </c>
       <c r="N37" t="str">
         <v>[]</v>
@@ -4878,19 +4889,19 @@
         <v>Very nice</v>
       </c>
       <c r="P37" t="str">
-        <v>2026-08-04T05:27:10.795Z</v>
+        <v>2026-08-04T08:17:31.120Z</v>
       </c>
       <c r="Q37" t="str">
-        <v>2026-08-04T05:27:17.920Z</v>
+        <v>2026-08-04T08:17:38.907Z</v>
       </c>
       <c r="R37" t="str">
-        <v>["https://lh3.googleusercontent.com/grass-cs/ACvplmPaK6IAJqFroL-Q3eCe1oY9R0jG9-WtqOMA7gc0Ui6H3F7VYJnet34e52FOD8o_mIOS8RVfOQoZs9DGhv1WdPfAx5WmDB8370r9Wrvhunzs_dtm0wlI0_v2YxJ6T4wmX7Ajb6IikdgTXCQ3=w300-h450-p-k-no","https://lh3.googleusercontent.com/grass-cs/ACvplmMvR5JqCiEyVYPEZHvHtmHzXLvQX8x01nBqyTFypOZv9xeTsnvLC0g3dUCAcFhZIa15HpWucboRVbvyEtxjevXgFS80E1q3ad8WndsshfBipdU4prPwjinanrFjBZ2SDP544Wk_hVokA3M=w300-h450-p-k-no"]</v>
+        <v>["https://lh3.googleusercontent.com/grass-cs/ACvplmOvXdkYfrMjALMZR-57O-Gnx2doUV8b5TwpE9h8U9eY1WFyeFXJgvIiiMx5XqGY53Jm6Cl3EqF-GVxW80zTQud1K_COc_AMGwcJexBvYc03meUJhAwWV0yT7CcsvImVchoP_SGWF7_3n_4T=w300-h450-p-k-no","https://lh3.googleusercontent.com/grass-cs/ACvplmMvR5JqCiEyVYPEZHvHtmHzXLvQX8x01nBqyTFypOZv9xeTsnvLC0g3dUCAcFhZIa15HpWucboRVbvyEtxjevXgFS80E1q3ad8WndsshfBipdU4prPwjinanrFjBZ2SDP544Wk_hVokA3M=w300-h450-p-k-no"]</v>
       </c>
       <c r="S37" t="str">
         <v/>
       </c>
       <c r="T37" t="str">
-        <v>2026-08-04T05:27:22.786Z</v>
+        <v>2026-08-04T08:17:45.658Z</v>
       </c>
     </row>
     <row r="38">
@@ -4931,7 +4942,7 @@
         <v>apify</v>
       </c>
       <c r="M38" t="str">
-        <v>2026-08-04T05:27:10.795Z</v>
+        <v>2026-08-04T08:17:31.120Z</v>
       </c>
       <c r="N38" t="str">
         <v>[]</v>
@@ -4940,19 +4951,19 @@
         <v>3 months agoOrder typeTake outMeal typeBrunchLike</v>
       </c>
       <c r="P38" t="str">
-        <v>2026-08-04T05:27:10.795Z</v>
+        <v>2026-08-04T08:17:31.120Z</v>
       </c>
       <c r="Q38" t="str">
-        <v>2026-08-04T05:27:18.156Z</v>
+        <v>2026-08-04T08:17:39.251Z</v>
       </c>
       <c r="R38" t="str">
         <v>[]</v>
       </c>
       <c r="S38" t="str">
-        <v>2026-05-06T05:27:17.630Z</v>
+        <v>2026-05-06T08:17:37.228Z</v>
       </c>
       <c r="T38" t="str">
-        <v>2026-08-04T05:27:22.786Z</v>
+        <v>2026-08-04T08:17:45.658Z</v>
       </c>
     </row>
     <row r="39">
@@ -4993,7 +5004,7 @@
         <v>apify</v>
       </c>
       <c r="M39" t="str">
-        <v>2026-08-04T05:27:10.795Z</v>
+        <v>2026-08-04T08:17:31.120Z</v>
       </c>
       <c r="N39" t="str">
         <v>[]</v>
@@ -5002,19 +5013,19 @@
         <v>Had ordered for a Rose Milk Birthday Cake few months before and it exceeded the expectation of everyone in taste. The order and Delicery experience was also very professional and able to feel the passion of the promoter. Today ordered their Mango Stick Melt Box, which again was yummy and felt very light. One of the must try dessert this summer</v>
       </c>
       <c r="P39" t="str">
-        <v>2026-08-04T05:27:10.795Z</v>
+        <v>2026-08-04T08:17:31.120Z</v>
       </c>
       <c r="Q39" t="str">
-        <v>2026-08-04T05:27:18.266Z</v>
+        <v>2026-08-04T08:17:39.361Z</v>
       </c>
       <c r="R39" t="str">
         <v>["https://lh3.googleusercontent.com/grass-cs/ACvplmO-N5w1dEs0O91N0FKZOducip4r_G6nJ-uRrXgwAY1ch2MpCdvyvzlbSP1qGIWVZTuEN-omDu6V2PCWMUAmZerRBJa6GjQeQhqwI2gXTWY0ovbtRUWjElq4ybDGU7AVZtKKh6QznqzFYYY=w300-h450-p-k-no","https://lh3.googleusercontent.com/grass-cs/ACvplmO-0GzWLqvrpb7tOp3qI8jtfk3fwsnUsUA10rG4a4GL4moYeolLxjyI81nOM5KUNSSMysTTa6iAv6pjZzKChSPhonfCcLmKs7sa8B5Py6dQSTyTGv3wQtbd7bCug0OVz_VCnjqDa9S4tK4=w300-h450-p-k-no"]</v>
       </c>
       <c r="S39" t="str">
-        <v>2026-05-06T05:27:17.630Z</v>
+        <v>2026-05-06T08:17:37.228Z</v>
       </c>
       <c r="T39" t="str">
-        <v>2026-08-04T05:27:22.786Z</v>
+        <v>2026-08-04T08:17:45.658Z</v>
       </c>
     </row>
     <row r="40" xml:space="preserve">
@@ -5055,7 +5066,7 @@
         <v>apify</v>
       </c>
       <c r="M40" t="str">
-        <v>2026-08-04T05:27:10.795Z</v>
+        <v>2026-08-04T08:17:31.120Z</v>
       </c>
       <c r="N40" t="str">
         <v>[]</v>
@@ -5065,10 +5076,10 @@
 More than we expected.. 💜</v>
       </c>
       <c r="P40" t="str">
-        <v>2026-08-04T05:27:10.795Z</v>
+        <v>2026-08-04T08:17:31.120Z</v>
       </c>
       <c r="Q40" t="str">
-        <v>2026-08-04T05:27:18.407Z</v>
+        <v>2026-08-04T08:17:39.487Z</v>
       </c>
       <c r="R40" t="str">
         <v>["https://lh3.googleusercontent.com/grass-cs/ACvplmPppG6bpan-PqNkdyYROI_GUqgKL5SkLkwHlc6hZ5UsjfEvZb4yh-p78ml_bBCSOInRHDlkn29mYeMDwxrT-JY98ScPev3xFp5suHXYhorK7cGUge725FmkytSMHvSBVPSF6iGGACO7S78A=w300-h450-p-k-no","https://lh3.googleusercontent.com/grass-cs/ACvplmNrLWqWwGL_tohqVBl0aPiP1kMOUy8TLbfusos_0QTI2tWQpLxNsI679f82klUWzN_bCY-t_QNGtX5VZcgiuVjoQhSGcns5ufrbyfskI0_195jt2luuUMKz-VsWvmgohBy_052p_T7fGtw=w300-h225-p-k-no","https://lh3.googleusercontent.com/grass-cs/ACvplmOKtfGwjXym7lYQbEevm97GAQcPGzeKUGYX-CC-Sw3CAAcsiQgO56UEte0FH539vVZoR3PsYCNTUJm0zijx7lVxA3BZb0zQJV1yJFuO9NqPERQ3fB93JgclNn9Enc7Kk8ElZoTtnrgixrpC=w300-h225-p-k-no"]</v>
@@ -5077,7 +5088,7 @@
         <v/>
       </c>
       <c r="T40" t="str">
-        <v>2026-08-04T05:27:22.786Z</v>
+        <v>2026-08-04T08:17:45.658Z</v>
       </c>
     </row>
     <row r="41">
@@ -5118,7 +5129,7 @@
         <v>apify</v>
       </c>
       <c r="M41" t="str">
-        <v>2026-08-04T05:27:10.795Z</v>
+        <v>2026-08-04T08:17:31.120Z</v>
       </c>
       <c r="N41" t="str">
         <v>[]</v>
@@ -5127,19 +5138,19 @@
         <v>That cake was for my daughter’s 11th birthday, she loved the vancho flavor and the cake was better than she expected! Thank you so much.</v>
       </c>
       <c r="P41" t="str">
-        <v>2026-08-04T05:27:10.795Z</v>
+        <v>2026-08-04T08:17:31.120Z</v>
       </c>
       <c r="Q41" t="str">
-        <v>2026-08-04T05:27:18.548Z</v>
+        <v>2026-08-04T08:17:39.644Z</v>
       </c>
       <c r="R41" t="str">
         <v>["https://lh3.googleusercontent.com/grass-cs/ACvplmNNmN-xWtfJDdu2OsGSKIuQu9KIGUeuEgDBezbgsCV2v5Ld2z1dXu7m523gMEDfkvgtNl-5SwbbgedzP-p_jynvs_TvSwW0jeE6BFTaHAA_-jtyx45gu_ULmiYjJ14_3oPgCe_s-p4cX3XM=w600-h450-p-k-no"]</v>
       </c>
       <c r="S41" t="str">
-        <v>2026-05-06T05:27:17.630Z</v>
+        <v>2026-05-06T08:17:37.228Z</v>
       </c>
       <c r="T41" t="str">
-        <v>2026-08-04T05:27:22.786Z</v>
+        <v>2026-08-04T08:17:45.658Z</v>
       </c>
     </row>
     <row r="42">
@@ -5180,7 +5191,7 @@
         <v>apify</v>
       </c>
       <c r="M42" t="str">
-        <v>2026-08-04T05:27:10.795Z</v>
+        <v>2026-08-04T08:17:31.120Z</v>
       </c>
       <c r="N42" t="str">
         <v>[]</v>
@@ -5189,19 +5200,19 @@
         <v>We ordered rose milk cake from chocolate mine. The cake was absolutely delicious and flavorful and very well customized as per our wish...Everyone loved it.. thank you for the wonderful cake</v>
       </c>
       <c r="P42" t="str">
-        <v>2026-08-04T05:27:10.795Z</v>
+        <v>2026-08-04T08:17:31.120Z</v>
       </c>
       <c r="Q42" t="str">
-        <v>2026-08-04T05:27:18.658Z</v>
+        <v>2026-08-04T08:17:39.768Z</v>
       </c>
       <c r="R42" t="str">
         <v>[]</v>
       </c>
       <c r="S42" t="str">
-        <v>2026-05-06T05:27:17.630Z</v>
+        <v>2026-05-06T08:17:37.228Z</v>
       </c>
       <c r="T42" t="str">
-        <v>2026-08-04T05:27:22.786Z</v>
+        <v>2026-08-04T08:17:45.658Z</v>
       </c>
     </row>
     <row r="43">
@@ -5242,7 +5253,7 @@
         <v>apify</v>
       </c>
       <c r="M43" t="str">
-        <v>2026-08-04T05:27:10.795Z</v>
+        <v>2026-08-04T08:17:31.120Z</v>
       </c>
       <c r="N43" t="str">
         <v>[]</v>
@@ -5251,19 +5262,19 @@
         <v>Choco Lava Cake and Cheese Cake must try😌😋</v>
       </c>
       <c r="P43" t="str">
-        <v>2026-08-04T05:27:10.795Z</v>
+        <v>2026-08-04T08:17:31.120Z</v>
       </c>
       <c r="Q43" t="str">
-        <v>2026-08-04T05:27:18.768Z</v>
+        <v>2026-08-04T08:17:39.893Z</v>
       </c>
       <c r="R43" t="str">
         <v>[]</v>
       </c>
       <c r="S43" t="str">
-        <v>2026-04-06T05:27:17.630Z</v>
+        <v>2026-04-06T08:17:39.393Z</v>
       </c>
       <c r="T43" t="str">
-        <v>2026-08-04T05:27:22.786Z</v>
+        <v>2026-08-04T08:17:45.658Z</v>
       </c>
     </row>
     <row r="44">
@@ -5304,7 +5315,7 @@
         <v>apify</v>
       </c>
       <c r="M44" t="str">
-        <v>2026-08-04T05:27:10.795Z</v>
+        <v>2026-08-04T08:17:31.120Z</v>
       </c>
       <c r="N44" t="str">
         <v>[]</v>
@@ -5313,19 +5324,19 @@
         <v>Thank you so much mam...it was a delicious cake for my daughter...all the children loved the cake and decoration was superb</v>
       </c>
       <c r="P44" t="str">
-        <v>2026-08-04T05:27:10.795Z</v>
+        <v>2026-08-04T08:17:31.120Z</v>
       </c>
       <c r="Q44" t="str">
-        <v>2026-08-04T05:27:18.890Z</v>
+        <v>2026-08-04T08:17:40.003Z</v>
       </c>
       <c r="R44" t="str">
         <v>["https://lh3.googleusercontent.com/grass-cs/ACvplmPA3y_aD66omtRox5jRa9j6deraN4g_Zl8hgzlp_W4viyqhRVtOFyZcsQkQ7sLel_luWGoGcKwwazGIa0HEUK_1w7MWiurNLcTLonU-zCnlzUbczjLnbVwz9UpwUMyEsTXcuyq3bjUPEByK=w600-h450-p-k-no"]</v>
       </c>
       <c r="S44" t="str">
-        <v>2026-04-06T05:27:19.909Z</v>
+        <v>2026-04-06T08:17:39.393Z</v>
       </c>
       <c r="T44" t="str">
-        <v>2026-08-04T05:27:22.786Z</v>
+        <v>2026-08-04T08:17:45.658Z</v>
       </c>
     </row>
     <row r="45">
@@ -5366,7 +5377,7 @@
         <v>apify</v>
       </c>
       <c r="M45" t="str">
-        <v>2026-08-04T05:27:10.795Z</v>
+        <v>2026-08-04T08:17:31.120Z</v>
       </c>
       <c r="N45" t="str">
         <v>[]</v>
@@ -5375,19 +5386,19 @@
         <v>We recently celebrated our lil ones bday at this cafe which turned out to be a full satisfied event for us! Throughout all the details and requests they were polite and served us the best. Spl mention- their hazelnut hot choc is a must try🥤🥰</v>
       </c>
       <c r="P45" t="str">
-        <v>2026-08-04T05:27:10.795Z</v>
+        <v>2026-08-04T08:17:31.120Z</v>
       </c>
       <c r="Q45" t="str">
-        <v>2026-08-04T05:27:19.000Z</v>
+        <v>2026-08-04T08:17:40.145Z</v>
       </c>
       <c r="R45" t="str">
         <v>["https://lh3.googleusercontent.com/grass-cs/ACvplmMfDKskGJQvaa59X160AGAtoF1jMbela-u825Lp0at4z3UpqyK-hvm_uDw7yTWzcZSrCHKFT8OnsRn91ItJlpvWD15of1EEkBAqOupf7eWscv-z_pweKZIV278buQ_4o3GTerHVFhqhg-Sa=w300-h450-p-k-no","https://lh3.googleusercontent.com/grass-cs/ACvplmPs7YFQk61QJJjB81iJcGqG3fZrT69mveX24qkda-HcKaWEJglWG9zwpJSW2wlf5YHHhYKmjviuXCJ1JzA4TxnTgzvwFGjdm6pQnwpOrgE4ioJ8sqlIPAsn2ooTEJ5eDCdRLTKO5OVvn3O3=w300-h450-p-k-no"]</v>
       </c>
       <c r="S45" t="str">
-        <v>2026-04-06T05:27:19.909Z</v>
+        <v>2026-04-06T08:17:39.393Z</v>
       </c>
       <c r="T45" t="str">
-        <v>2026-08-04T05:27:22.786Z</v>
+        <v>2026-08-04T08:17:45.658Z</v>
       </c>
     </row>
     <row r="46">
@@ -5428,7 +5439,7 @@
         <v>apify</v>
       </c>
       <c r="M46" t="str">
-        <v>2026-08-04T05:27:10.795Z</v>
+        <v>2026-08-04T08:17:31.120Z</v>
       </c>
       <c r="N46" t="str">
         <v>[]</v>
@@ -5437,19 +5448,19 @@
         <v>I ordered B'day bento cake for my loved one.......it takes good and also we are tres leches it tadte like topnotch......really enjoyed</v>
       </c>
       <c r="P46" t="str">
-        <v>2026-08-04T05:27:10.795Z</v>
+        <v>2026-08-04T08:17:31.120Z</v>
       </c>
       <c r="Q46" t="str">
-        <v>2026-08-04T05:27:19.093Z</v>
+        <v>2026-08-04T08:17:40.302Z</v>
       </c>
       <c r="R46" t="str">
         <v>[]</v>
       </c>
       <c r="S46" t="str">
-        <v>2026-04-06T05:27:19.909Z</v>
+        <v>2026-04-06T08:17:39.393Z</v>
       </c>
       <c r="T46" t="str">
-        <v>2026-08-04T05:27:22.786Z</v>
+        <v>2026-08-04T08:17:45.658Z</v>
       </c>
     </row>
     <row r="47">
@@ -5490,7 +5501,7 @@
         <v>apify</v>
       </c>
       <c r="M47" t="str">
-        <v>2026-08-04T05:27:10.795Z</v>
+        <v>2026-08-04T08:17:31.120Z</v>
       </c>
       <c r="N47" t="str">
         <v>[]</v>
@@ -5499,19 +5510,19 @@
         <v>The food was good, so was the coffee. It took a long time for the food to arrive once the order was placed</v>
       </c>
       <c r="P47" t="str">
-        <v>2026-08-04T05:27:10.795Z</v>
+        <v>2026-08-04T08:17:31.120Z</v>
       </c>
       <c r="Q47" t="str">
-        <v>2026-08-04T05:27:19.202Z</v>
+        <v>2026-08-04T08:17:40.411Z</v>
       </c>
       <c r="R47" t="str">
         <v>[]</v>
       </c>
       <c r="S47" t="str">
-        <v>2026-04-06T05:27:19.909Z</v>
+        <v>2026-04-06T08:17:39.393Z</v>
       </c>
       <c r="T47" t="str">
-        <v>2026-08-04T05:27:22.786Z</v>
+        <v>2026-08-04T08:17:45.658Z</v>
       </c>
     </row>
     <row r="48">
@@ -5552,7 +5563,7 @@
         <v>apify</v>
       </c>
       <c r="M48" t="str">
-        <v>2026-08-04T05:27:10.795Z</v>
+        <v>2026-08-04T08:17:31.120Z</v>
       </c>
       <c r="N48" t="str">
         <v>[]</v>
@@ -5561,19 +5572,19 @@
         <v>Very good service</v>
       </c>
       <c r="P48" t="str">
-        <v>2026-08-04T05:27:10.795Z</v>
+        <v>2026-08-04T08:17:31.120Z</v>
       </c>
       <c r="Q48" t="str">
-        <v>2026-08-04T05:27:19.297Z</v>
+        <v>2026-08-04T08:17:40.522Z</v>
       </c>
       <c r="R48" t="str">
         <v>[]</v>
       </c>
       <c r="S48" t="str">
-        <v>2026-04-06T05:27:19.909Z</v>
+        <v>2026-04-06T08:17:39.393Z</v>
       </c>
       <c r="T48" t="str">
-        <v>2026-08-04T05:27:22.786Z</v>
+        <v>2026-08-04T08:17:45.658Z</v>
       </c>
     </row>
     <row r="49">
@@ -5614,7 +5625,7 @@
         <v>apify</v>
       </c>
       <c r="M49" t="str">
-        <v>2026-08-04T05:27:10.795Z</v>
+        <v>2026-08-04T08:17:31.120Z</v>
       </c>
       <c r="N49" t="str">
         <v>[]</v>
@@ -5623,19 +5634,19 @@
         <v>Pleasant ambience and the taste was extraordinary ❤️</v>
       </c>
       <c r="P49" t="str">
-        <v>2026-08-04T05:27:10.795Z</v>
+        <v>2026-08-04T08:17:31.120Z</v>
       </c>
       <c r="Q49" t="str">
-        <v>2026-08-04T05:27:19.407Z</v>
+        <v>2026-08-04T08:17:40.645Z</v>
       </c>
       <c r="R49" t="str">
         <v>[]</v>
       </c>
       <c r="S49" t="str">
-        <v>2026-04-06T05:27:19.909Z</v>
+        <v>2026-04-06T08:17:39.393Z</v>
       </c>
       <c r="T49" t="str">
-        <v>2026-08-04T05:27:22.786Z</v>
+        <v>2026-08-04T08:17:45.658Z</v>
       </c>
     </row>
     <row r="50">
@@ -5676,7 +5687,7 @@
         <v>apify</v>
       </c>
       <c r="M50" t="str">
-        <v>2026-08-04T05:27:10.795Z</v>
+        <v>2026-08-04T08:17:31.120Z</v>
       </c>
       <c r="N50" t="str">
         <v>[]</v>
@@ -5685,19 +5696,19 @@
         <v>Chocolate coffee was top notch🤌🤌</v>
       </c>
       <c r="P50" t="str">
-        <v>2026-08-04T05:27:10.795Z</v>
+        <v>2026-08-04T08:17:31.120Z</v>
       </c>
       <c r="Q50" t="str">
-        <v>2026-08-04T05:27:19.515Z</v>
+        <v>2026-08-04T08:17:40.788Z</v>
       </c>
       <c r="R50" t="str">
         <v>[]</v>
       </c>
       <c r="S50" t="str">
-        <v>2026-04-06T05:27:19.909Z</v>
+        <v>2026-04-06T08:17:39.393Z</v>
       </c>
       <c r="T50" t="str">
-        <v>2026-08-04T05:27:22.786Z</v>
+        <v>2026-08-04T08:17:45.658Z</v>
       </c>
     </row>
     <row r="51">
@@ -5759,7 +5770,7 @@
         <v>2026-03-07T05:27:19.909Z</v>
       </c>
       <c r="T51" t="str">
-        <v>2026-08-04T05:27:22.786Z</v>
+        <v>2026-08-04T08:17:45.658Z</v>
       </c>
     </row>
     <row r="52">
@@ -5821,7 +5832,7 @@
         <v>2026-03-06T02:56:06.693Z</v>
       </c>
       <c r="T52" t="str">
-        <v>2026-08-04T05:27:22.786Z</v>
+        <v>2026-08-04T08:17:45.658Z</v>
       </c>
     </row>
     <row r="53">
@@ -5883,7 +5894,7 @@
         <v>2026-03-01T06:45:44.320Z</v>
       </c>
       <c r="T53" t="str">
-        <v>2026-08-04T05:27:22.786Z</v>
+        <v>2026-08-04T08:17:45.658Z</v>
       </c>
     </row>
     <row r="54">
@@ -5945,7 +5956,7 @@
         <v>2026-02-27T10:19:29.898Z</v>
       </c>
       <c r="T54" t="str">
-        <v>2026-08-04T05:27:22.787Z</v>
+        <v>2026-08-04T08:17:45.659Z</v>
       </c>
     </row>
     <row r="55">
@@ -6007,7 +6018,7 @@
         <v>2026-02-26T13:13:36.195Z</v>
       </c>
       <c r="T55" t="str">
-        <v>2026-08-04T05:27:22.787Z</v>
+        <v>2026-08-04T08:17:45.659Z</v>
       </c>
     </row>
     <row r="56">
@@ -6069,7 +6080,7 @@
         <v>2026-02-24T18:31:20.668Z</v>
       </c>
       <c r="T56" t="str">
-        <v>2026-08-04T05:27:22.787Z</v>
+        <v>2026-08-04T08:17:45.659Z</v>
       </c>
     </row>
     <row r="57">
@@ -6131,7 +6142,7 @@
         <v>2026-02-11T10:33:29.369Z</v>
       </c>
       <c r="T57" t="str">
-        <v>2026-08-04T05:27:22.787Z</v>
+        <v>2026-08-04T08:17:45.659Z</v>
       </c>
     </row>
     <row r="58" xml:space="preserve">
@@ -6194,7 +6205,7 @@
         <v>2026-03-06T08:34:24.383Z</v>
       </c>
       <c r="T58" t="str">
-        <v>2026-08-04T05:27:22.787Z</v>
+        <v>2026-08-04T08:17:45.659Z</v>
       </c>
     </row>
     <row r="59">
@@ -6256,7 +6267,7 @@
         <v>2026-03-06T08:34:24.383Z</v>
       </c>
       <c r="T59" t="str">
-        <v>2026-08-04T05:27:22.787Z</v>
+        <v>2026-08-04T08:17:45.659Z</v>
       </c>
     </row>
     <row r="60">
@@ -6318,7 +6329,7 @@
         <v>2026-03-06T08:34:24.383Z</v>
       </c>
       <c r="T60" t="str">
-        <v>2026-08-04T05:27:22.787Z</v>
+        <v>2026-08-04T08:17:45.659Z</v>
       </c>
     </row>
     <row r="61">
@@ -6380,7 +6391,7 @@
         <v>2026-03-06T08:34:24.383Z</v>
       </c>
       <c r="T61" t="str">
-        <v>2026-08-04T05:27:22.787Z</v>
+        <v>2026-08-04T08:17:45.659Z</v>
       </c>
     </row>
     <row r="62">
@@ -6442,7 +6453,7 @@
         <v>2026-03-06T08:34:24.383Z</v>
       </c>
       <c r="T62" t="str">
-        <v>2026-08-04T05:27:22.787Z</v>
+        <v>2026-08-04T08:17:45.659Z</v>
       </c>
     </row>
     <row r="63">
@@ -6504,7 +6515,7 @@
         <v>2026-02-04T08:34:24.383Z</v>
       </c>
       <c r="T63" t="str">
-        <v>2026-08-04T05:27:22.787Z</v>
+        <v>2026-08-04T08:17:45.659Z</v>
       </c>
     </row>
     <row r="64" xml:space="preserve">
@@ -6567,7 +6578,7 @@
         <v>2026-02-01T13:59:29.989Z</v>
       </c>
       <c r="T64" t="str">
-        <v>2026-08-04T05:27:22.787Z</v>
+        <v>2026-08-04T08:17:45.659Z</v>
       </c>
     </row>
     <row r="65">
@@ -6629,7 +6640,7 @@
         <v>2026-02-24T17:08:34.231Z</v>
       </c>
       <c r="T65" t="str">
-        <v>2026-08-04T05:27:22.787Z</v>
+        <v>2026-08-04T08:17:45.659Z</v>
       </c>
     </row>
     <row r="66">
@@ -6691,7 +6702,7 @@
         <v>2026-02-13T15:37:15.383Z</v>
       </c>
       <c r="T66" t="str">
-        <v>2026-08-04T05:27:22.787Z</v>
+        <v>2026-08-04T08:17:45.659Z</v>
       </c>
     </row>
     <row r="67" xml:space="preserve">
@@ -6757,7 +6768,7 @@
         <v>2026-02-13T15:37:15.383Z</v>
       </c>
       <c r="T67" t="str">
-        <v>2026-08-04T05:27:22.787Z</v>
+        <v>2026-08-04T08:17:45.659Z</v>
       </c>
     </row>
     <row r="68">
@@ -6819,7 +6830,7 @@
         <v>2026-02-13T15:37:17.562Z</v>
       </c>
       <c r="T68" t="str">
-        <v>2026-08-04T05:27:22.787Z</v>
+        <v>2026-08-04T08:17:45.659Z</v>
       </c>
     </row>
     <row r="69">
@@ -6881,7 +6892,7 @@
         <v>2026-02-13T15:37:17.562Z</v>
       </c>
       <c r="T69" t="str">
-        <v>2026-08-04T05:27:22.787Z</v>
+        <v>2026-08-04T08:17:45.659Z</v>
       </c>
     </row>
     <row r="70">
@@ -6943,7 +6954,7 @@
         <v>2026-02-13T15:37:17.562Z</v>
       </c>
       <c r="T70" t="str">
-        <v>2026-08-04T05:27:22.787Z</v>
+        <v>2026-08-04T08:17:45.659Z</v>
       </c>
     </row>
     <row r="71">
@@ -7005,7 +7016,7 @@
         <v>2026-01-14T15:37:17.562Z</v>
       </c>
       <c r="T71" t="str">
-        <v>2026-08-04T05:27:22.787Z</v>
+        <v>2026-08-04T08:17:45.659Z</v>
       </c>
     </row>
     <row r="72">
@@ -7067,7 +7078,7 @@
         <v>2026-01-14T15:26:08.566Z</v>
       </c>
       <c r="T72" t="str">
-        <v>2026-08-04T05:27:22.787Z</v>
+        <v>2026-08-04T08:17:45.659Z</v>
       </c>
     </row>
     <row r="73">
@@ -7126,7 +7137,7 @@
         <v>["https://lh3.googleusercontent.com/a-/ALV-UjX1CoTz92K_REISpy2kSrmfkUl8O2_fiev-hVBoxR0mWvdo3xi9hg=w36-h36-p-rp-mo-br100"]</v>
       </c>
       <c r="T73" t="str">
-        <v>2026-08-04T05:27:22.787Z</v>
+        <v>2026-08-04T08:17:45.659Z</v>
       </c>
     </row>
     <row r="74">
@@ -7188,7 +7199,7 @@
         <v>2026-06-15T13:04:41.344Z</v>
       </c>
       <c r="T74" t="str">
-        <v>2026-08-04T05:27:22.787Z</v>
+        <v>2026-08-04T08:17:45.659Z</v>
       </c>
     </row>
     <row r="75">
@@ -7250,7 +7261,7 @@
         <v>2026-05-25T17:13:36.799Z</v>
       </c>
       <c r="T75" t="str">
-        <v>2026-08-04T05:27:22.787Z</v>
+        <v>2026-08-04T08:17:45.659Z</v>
       </c>
     </row>
     <row r="76">
@@ -7312,7 +7323,7 @@
         <v>2026-06-03T16:50:09.620Z</v>
       </c>
       <c r="T76" t="str">
-        <v>2026-08-04T05:27:22.787Z</v>
+        <v>2026-08-04T08:17:45.659Z</v>
       </c>
     </row>
     <row r="77">
@@ -7374,7 +7385,7 @@
         <v>2026-04-21T05:25:07.829Z</v>
       </c>
       <c r="T77" t="str">
-        <v>2026-08-04T05:27:22.787Z</v>
+        <v>2026-08-04T08:17:45.659Z</v>
       </c>
     </row>
     <row r="78">
@@ -7436,7 +7447,7 @@
         <v>2026-02-27T10:36:46.583Z</v>
       </c>
       <c r="T78" t="str">
-        <v>2026-08-04T05:27:22.787Z</v>
+        <v>2026-08-04T08:17:45.659Z</v>
       </c>
     </row>
     <row r="79">
@@ -7498,7 +7509,7 @@
         <v>2026-01-28T10:36:46.583Z</v>
       </c>
       <c r="T79" t="str">
-        <v>2026-08-04T05:27:22.787Z</v>
+        <v>2026-08-04T08:17:45.659Z</v>
       </c>
     </row>
     <row r="80">
@@ -7539,7 +7550,7 @@
         <v>apify</v>
       </c>
       <c r="M80" t="str">
-        <v>2026-08-04T05:27:10.794Z</v>
+        <v>2026-08-04T08:17:31.119Z</v>
       </c>
       <c r="N80" t="str">
         <v>[]</v>
@@ -7548,19 +7559,19 @@
         <v>Good desserts 🤤🤤🤤🤤🤤🤤</v>
       </c>
       <c r="P80" t="str">
-        <v>2026-08-04T05:27:10.794Z</v>
+        <v>2026-08-04T08:17:31.119Z</v>
       </c>
       <c r="Q80" t="str">
-        <v>2026-08-04T05:27:14.533Z</v>
+        <v>2026-08-04T08:17:35.081Z</v>
       </c>
       <c r="R80" t="str">
         <v>[]</v>
       </c>
       <c r="S80" t="str">
-        <v>2026-07-05T05:27:07.537Z</v>
+        <v>2026-07-05T08:17:27.287Z</v>
       </c>
       <c r="T80" t="str">
-        <v>2026-08-04T05:27:22.787Z</v>
+        <v>2026-08-04T08:17:45.659Z</v>
       </c>
     </row>
     <row r="81">
@@ -7601,7 +7612,7 @@
         <v>apify</v>
       </c>
       <c r="M81" t="str">
-        <v>2026-08-04T05:27:10.794Z</v>
+        <v>2026-08-04T08:17:31.119Z</v>
       </c>
       <c r="N81" t="str">
         <v>[]</v>
@@ -7610,19 +7621,19 @@
         <v>Good service</v>
       </c>
       <c r="P81" t="str">
-        <v>2026-08-04T05:27:10.794Z</v>
+        <v>2026-08-04T08:17:31.119Z</v>
       </c>
       <c r="Q81" t="str">
-        <v>2026-08-04T05:27:14.674Z</v>
+        <v>2026-08-04T08:17:35.426Z</v>
       </c>
       <c r="R81" t="str">
         <v>[]</v>
       </c>
       <c r="S81" t="str">
-        <v>2026-07-05T05:27:07.537Z</v>
+        <v>2026-07-05T08:17:27.287Z</v>
       </c>
       <c r="T81" t="str">
-        <v>2026-08-04T05:27:22.787Z</v>
+        <v>2026-08-04T08:17:45.659Z</v>
       </c>
     </row>
     <row r="82">
@@ -7663,7 +7674,7 @@
         <v>apify</v>
       </c>
       <c r="M82" t="str">
-        <v>2026-08-04T05:27:10.794Z</v>
+        <v>2026-08-04T08:17:31.119Z</v>
       </c>
       <c r="N82" t="str">
         <v>[]</v>
@@ -7672,19 +7683,19 @@
         <v>Brownie was super appetising!!!</v>
       </c>
       <c r="P82" t="str">
-        <v>2026-08-04T05:27:10.794Z</v>
+        <v>2026-08-04T08:17:31.119Z</v>
       </c>
       <c r="Q82" t="str">
-        <v>2026-08-04T05:27:13.313Z</v>
+        <v>2026-08-04T08:17:33.969Z</v>
       </c>
       <c r="R82" t="str">
         <v>[]</v>
       </c>
       <c r="S82" t="str">
-        <v>2026-07-05T05:27:05.156Z</v>
+        <v>2026-07-05T08:17:24.912Z</v>
       </c>
       <c r="T82" t="str">
-        <v>2026-08-04T05:27:22.787Z</v>
+        <v>2026-08-04T08:17:45.659Z</v>
       </c>
     </row>
     <row r="83">
@@ -7725,7 +7736,7 @@
         <v>apify</v>
       </c>
       <c r="M83" t="str">
-        <v>2026-08-04T05:27:10.794Z</v>
+        <v>2026-08-04T08:17:31.119Z</v>
       </c>
       <c r="N83" t="str">
         <v>[]</v>
@@ -7734,19 +7745,19 @@
         <v>Always good 👍 …</v>
       </c>
       <c r="P83" t="str">
-        <v>2026-08-04T05:27:10.794Z</v>
+        <v>2026-08-04T08:17:31.119Z</v>
       </c>
       <c r="Q83" t="str">
-        <v>2026-08-04T05:27:13.453Z</v>
+        <v>2026-08-04T08:17:34.095Z</v>
       </c>
       <c r="R83" t="str">
         <v>[]</v>
       </c>
       <c r="S83" t="str">
-        <v>2026-07-05T05:27:05.156Z</v>
+        <v>2026-07-05T08:17:24.912Z</v>
       </c>
       <c r="T83" t="str">
-        <v>2026-08-04T05:27:22.787Z</v>
+        <v>2026-08-04T08:17:45.659Z</v>
       </c>
     </row>
     <row r="84">
@@ -7787,7 +7798,7 @@
         <v>apify</v>
       </c>
       <c r="M84" t="str">
-        <v>2026-08-04T05:27:10.794Z</v>
+        <v>2026-08-04T08:17:31.119Z</v>
       </c>
       <c r="N84" t="str">
         <v>[]</v>
@@ -7796,19 +7807,19 @@
         <v>I ordered a two-tier customized cake for my daughter's birthday, and it was absolutely amazing! The cake tasted delicious, and the customization was done beautifully, exactly as requested. The team was very responsive throughout the process, and the delivery was right on time. Thank you, Chocolate Mine, for making our special day even more memorable!</v>
       </c>
       <c r="P84" t="str">
-        <v>2026-08-04T05:27:10.794Z</v>
+        <v>2026-08-04T08:17:31.119Z</v>
       </c>
       <c r="Q84" t="str">
-        <v>2026-08-04T05:27:13.578Z</v>
+        <v>2026-08-04T08:17:34.189Z</v>
       </c>
       <c r="R84" t="str">
         <v>["https://lh3.googleusercontent.com/grass-cs/ACvplmNu77SJ-0-7NnAzJiHAAOABAGvqkbfljqSNTUryL9ONO_o3ixSkb_SByVgEktCnWa4-witFHfo4sil0aAB7hK1jbLWIJ3GnWVFQRVM2iGvfCVEpsuLEiXKbIWaaHsAK-r8ft91K7dxkx2SH=w300-h225-p-k-no","https://lh3.googleusercontent.com/grass-cs/ACvplmOYZR9CLhI8X2bpM9zsIE6IYWaqqZna4v1o1wZOkmFlEqswyPWzwT4pjKBkffu5vCQLRBUzTMhxP-e84z9NtB7h0xFYFuWiX_sf6JLz3RqnUm5EE3-vKLHAAPjvOqBOgGlARPf0FIB9V1M=w300-h225-p-k-no","https://lh3.googleusercontent.com/grass-cs/ACvplmONdyXH4lgUt4orpviuy7rfWhuQr7jC1FolwdOH6QSWQd-Ay9j8V--oGjs-ip_-nIeQ-ZDcr_BGD3R7Bwu3yhj6r8qwKzR1euBSuRMmdGEaTbsaDJnJ692NCKn0lt8gLXsREUUbkP_V0OS9=w300-h225-p-k-no","https://lh3.googleusercontent.com/grass-cs/ACvplmO68XpnXzoXJ7vBYiLgJjCtIhUhleb8qkUlBWeM3j_mB5fF8cE21n6M7geVk8dYzOHHtuksY0xDXL1E6OlMH3B4MpTw5ITyb4a4ZTvmRQC8gxqh2W3Eap31QuXdZ4Q3wPMKK_Zvzd6h_Swy=w300-h225-p-k-no"]</v>
       </c>
       <c r="S84" t="str">
-        <v>2026-07-05T05:27:05.156Z</v>
+        <v>2026-07-05T08:17:24.912Z</v>
       </c>
       <c r="T84" t="str">
-        <v>2026-08-04T05:27:22.787Z</v>
+        <v>2026-08-04T08:17:45.660Z</v>
       </c>
     </row>
     <row r="85">
@@ -7849,7 +7860,7 @@
         <v>apify</v>
       </c>
       <c r="M85" t="str">
-        <v>2026-08-04T05:27:10.794Z</v>
+        <v>2026-08-04T08:17:31.119Z</v>
       </c>
       <c r="N85" t="str">
         <v>[]</v>
@@ -7858,19 +7869,19 @@
         <v>Good desserts with calm atmosphere</v>
       </c>
       <c r="P85" t="str">
-        <v>2026-08-04T05:27:10.794Z</v>
+        <v>2026-08-04T08:17:31.119Z</v>
       </c>
       <c r="Q85" t="str">
-        <v>2026-08-04T05:27:13.702Z</v>
+        <v>2026-08-04T08:17:34.281Z</v>
       </c>
       <c r="R85" t="str">
         <v>[]</v>
       </c>
       <c r="S85" t="str">
-        <v>2026-07-05T05:27:05.156Z</v>
+        <v>2026-07-05T08:17:27.287Z</v>
       </c>
       <c r="T85" t="str">
-        <v>2026-08-04T05:27:22.788Z</v>
+        <v>2026-08-04T08:17:45.660Z</v>
       </c>
     </row>
     <row r="86">
@@ -7911,7 +7922,7 @@
         <v>apify</v>
       </c>
       <c r="M86" t="str">
-        <v>2026-08-04T05:27:10.794Z</v>
+        <v>2026-08-04T08:17:31.119Z</v>
       </c>
       <c r="N86" t="str">
         <v>[]</v>
@@ -7920,19 +7931,19 @@
         <v>Extraordinary ambience and wonderful service</v>
       </c>
       <c r="P86" t="str">
-        <v>2026-08-04T05:27:10.794Z</v>
+        <v>2026-08-04T08:17:31.119Z</v>
       </c>
       <c r="Q86" t="str">
-        <v>2026-08-04T05:27:13.811Z</v>
+        <v>2026-08-04T08:17:34.392Z</v>
       </c>
       <c r="R86" t="str">
         <v>[]</v>
       </c>
       <c r="S86" t="str">
-        <v>2026-07-05T05:27:07.537Z</v>
+        <v>2026-07-05T08:17:27.287Z</v>
       </c>
       <c r="T86" t="str">
-        <v>2026-08-04T05:27:22.788Z</v>
+        <v>2026-08-04T08:17:45.660Z</v>
       </c>
     </row>
     <row r="87">
@@ -7973,7 +7984,7 @@
         <v>apify</v>
       </c>
       <c r="M87" t="str">
-        <v>2026-08-04T05:27:10.794Z</v>
+        <v>2026-08-04T08:17:31.119Z</v>
       </c>
       <c r="N87" t="str">
         <v>[]</v>
@@ -7982,19 +7993,19 @@
         <v>Nice food.Thank you chocolate mine for your wonderful service.</v>
       </c>
       <c r="P87" t="str">
-        <v>2026-08-04T05:27:10.794Z</v>
+        <v>2026-08-04T08:17:31.119Z</v>
       </c>
       <c r="Q87" t="str">
-        <v>2026-08-04T05:27:13.923Z</v>
+        <v>2026-08-04T08:17:34.518Z</v>
       </c>
       <c r="R87" t="str">
         <v>[]</v>
       </c>
       <c r="S87" t="str">
-        <v>2026-07-05T05:27:07.537Z</v>
+        <v>2026-07-05T08:17:27.287Z</v>
       </c>
       <c r="T87" t="str">
-        <v>2026-08-04T05:27:22.788Z</v>
+        <v>2026-08-04T08:17:45.660Z</v>
       </c>
     </row>
     <row r="88">
@@ -8035,7 +8046,7 @@
         <v>apify</v>
       </c>
       <c r="M88" t="str">
-        <v>2026-08-04T05:27:10.794Z</v>
+        <v>2026-08-04T08:17:31.119Z</v>
       </c>
       <c r="N88" t="str">
         <v>[]</v>
@@ -8044,19 +8055,19 @@
         <v>Tried the Tres Leches Lotus Biscoff….which was very yummy. A good ambience with eggless cake ,waffles , shakes ,sandwiches , sundaes etc.</v>
       </c>
       <c r="P88" t="str">
-        <v>2026-08-04T05:27:10.794Z</v>
+        <v>2026-08-04T08:17:31.119Z</v>
       </c>
       <c r="Q88" t="str">
-        <v>2026-08-04T05:27:14.061Z</v>
+        <v>2026-08-04T08:17:34.627Z</v>
       </c>
       <c r="R88" t="str">
         <v>[]</v>
       </c>
       <c r="S88" t="str">
-        <v>2026-07-05T05:27:07.537Z</v>
+        <v>2026-07-05T08:17:27.287Z</v>
       </c>
       <c r="T88" t="str">
-        <v>2026-08-04T05:27:22.788Z</v>
+        <v>2026-08-04T08:17:45.660Z</v>
       </c>
     </row>
     <row r="89">
@@ -8097,7 +8108,7 @@
         <v>apify</v>
       </c>
       <c r="M89" t="str">
-        <v>2026-08-04T05:27:10.794Z</v>
+        <v>2026-08-04T08:17:31.119Z</v>
       </c>
       <c r="N89" t="str">
         <v>[]</v>
@@ -8106,19 +8117,19 @@
         <v>Peak milk cake…. Would come again fosho</v>
       </c>
       <c r="P89" t="str">
-        <v>2026-08-04T05:27:10.794Z</v>
+        <v>2026-08-04T08:17:31.119Z</v>
       </c>
       <c r="Q89" t="str">
-        <v>2026-08-04T05:27:14.170Z</v>
+        <v>2026-08-04T08:17:34.753Z</v>
       </c>
       <c r="R89" t="str">
         <v>[]</v>
       </c>
       <c r="S89" t="str">
-        <v>2026-07-05T05:27:07.537Z</v>
+        <v>2026-07-05T08:17:27.287Z</v>
       </c>
       <c r="T89" t="str">
-        <v>2026-08-04T05:27:22.788Z</v>
+        <v>2026-08-04T08:17:45.660Z</v>
       </c>
     </row>
     <row r="90">
@@ -8159,7 +8170,7 @@
         <v>apify</v>
       </c>
       <c r="M90" t="str">
-        <v>2026-08-04T05:27:10.794Z</v>
+        <v>2026-08-04T08:17:31.119Z</v>
       </c>
       <c r="N90" t="str">
         <v>[]</v>
@@ -8168,19 +8179,19 @@
         <v>Tres leches is very tasty....</v>
       </c>
       <c r="P90" t="str">
-        <v>2026-08-04T05:27:10.794Z</v>
+        <v>2026-08-04T08:17:31.119Z</v>
       </c>
       <c r="Q90" t="str">
-        <v>2026-08-04T05:27:14.313Z</v>
+        <v>2026-08-04T08:17:34.846Z</v>
       </c>
       <c r="R90" t="str">
         <v>[]</v>
       </c>
       <c r="S90" t="str">
-        <v>2026-07-05T05:27:07.537Z</v>
+        <v>2026-07-05T08:17:27.287Z</v>
       </c>
       <c r="T90" t="str">
-        <v>2026-08-04T05:27:22.788Z</v>
+        <v>2026-08-04T08:17:45.660Z</v>
       </c>
     </row>
     <row r="91">
@@ -8221,7 +8232,7 @@
         <v>apify</v>
       </c>
       <c r="M91" t="str">
-        <v>2026-08-04T05:27:10.794Z</v>
+        <v>2026-08-04T08:17:31.119Z</v>
       </c>
       <c r="N91" t="str">
         <v>[]</v>
@@ -8230,19 +8241,19 @@
         <v>a month agoOrder typeDine inMeal typeOtherPrice per person₹400–600Wait timeNo waitRecommendation for vegetariansHighly recommendVegetarian offeringsMenu is all vegetarianLike</v>
       </c>
       <c r="P91" t="str">
-        <v>2026-08-04T05:27:10.794Z</v>
+        <v>2026-08-04T08:17:31.119Z</v>
       </c>
       <c r="Q91" t="str">
-        <v>2026-08-04T05:27:14.439Z</v>
+        <v>2026-08-04T08:17:34.957Z</v>
       </c>
       <c r="R91" t="str">
         <v>["https://lh3.googleusercontent.com/grass-cs/ACvplmNFWWTsSL5awqvvE-dGukd2QmWgcb057uQFbOiiQUa8UQcqfUjNq8VeNyll1i6zF2LkdD0U2oMEneIiZGjRlUkNUFavPv8HjwcI3VzVphh8GK3c2BZhmdFp0w05IO4cKBBjHjPS50fNW7w=w600-h450-p-k-no"]</v>
       </c>
       <c r="S91" t="str">
-        <v>2026-07-05T05:27:07.537Z</v>
+        <v>2026-07-05T08:17:27.287Z</v>
       </c>
       <c r="T91" t="str">
-        <v>2026-08-04T05:27:22.788Z</v>
+        <v>2026-08-04T08:17:45.660Z</v>
       </c>
     </row>
     <row r="92">
@@ -8283,7 +8294,7 @@
         <v>apify</v>
       </c>
       <c r="M92" t="str">
-        <v>2026-08-04T05:27:10.794Z</v>
+        <v>2026-08-04T08:17:31.119Z</v>
       </c>
       <c r="N92" t="str">
         <v>[]</v>
@@ -8292,19 +8303,19 @@
         <v>Good</v>
       </c>
       <c r="P92" t="str">
-        <v>2026-08-04T05:27:10.794Z</v>
+        <v>2026-08-04T08:17:31.119Z</v>
       </c>
       <c r="Q92" t="str">
-        <v>2026-08-04T05:27:13.203Z</v>
+        <v>2026-08-04T08:17:33.826Z</v>
       </c>
       <c r="R92" t="str">
         <v>[]</v>
       </c>
       <c r="S92" t="str">
-        <v>2026-07-05T05:27:05.156Z</v>
+        <v>2026-07-05T08:17:24.912Z</v>
       </c>
       <c r="T92" t="str">
-        <v>2026-08-04T05:27:22.788Z</v>
+        <v>2026-08-04T08:17:45.660Z</v>
       </c>
     </row>
     <row r="93">
@@ -8366,7 +8377,7 @@
         <v>2026-06-20T06:58:37.945Z</v>
       </c>
       <c r="T93" t="str">
-        <v>2026-08-04T05:27:22.788Z</v>
+        <v>2026-08-04T08:17:45.660Z</v>
       </c>
     </row>
     <row r="94">
@@ -8428,7 +8439,7 @@
         <v>2026-06-06T13:17:22.024Z</v>
       </c>
       <c r="T94" t="str">
-        <v>2026-08-04T05:27:22.788Z</v>
+        <v>2026-08-04T08:17:45.660Z</v>
       </c>
     </row>
     <row r="95">
@@ -8469,7 +8480,7 @@
         <v>apify</v>
       </c>
       <c r="M95" t="str">
-        <v>2026-08-04T05:27:10.794Z</v>
+        <v>2026-08-04T08:17:31.119Z</v>
       </c>
       <c r="N95" t="str">
         <v>[]</v>
@@ -8478,19 +8489,19 @@
         <v>Cake mine is good. Kids love the cakes here</v>
       </c>
       <c r="P95" t="str">
-        <v>2026-08-04T05:27:10.794Z</v>
+        <v>2026-08-04T08:17:31.119Z</v>
       </c>
       <c r="Q95" t="str">
-        <v>2026-08-04T05:27:13.017Z</v>
+        <v>2026-08-04T08:17:33.702Z</v>
       </c>
       <c r="R95" t="str">
         <v>[]</v>
       </c>
       <c r="S95" t="str">
-        <v>2026-07-05T05:27:05.156Z</v>
+        <v>2026-07-05T08:17:24.912Z</v>
       </c>
       <c r="T95" t="str">
-        <v>2026-08-04T05:27:22.788Z</v>
+        <v>2026-08-04T08:17:45.660Z</v>
       </c>
     </row>
     <row r="96">
@@ -8552,7 +8563,7 @@
         <v>2026-07-01T16:29:51.259Z</v>
       </c>
       <c r="T96" t="str">
-        <v>2026-08-04T05:27:22.788Z</v>
+        <v>2026-08-04T08:17:45.660Z</v>
       </c>
     </row>
     <row r="97">
@@ -8593,7 +8604,7 @@
         <v>apify</v>
       </c>
       <c r="M97" t="str">
-        <v>2026-08-04T05:27:10.794Z</v>
+        <v>2026-08-04T08:17:31.119Z</v>
       </c>
       <c r="N97" t="str">
         <v>[]</v>
@@ -8602,19 +8613,19 @@
         <v>Belgian chocolate is a must try ❤️</v>
       </c>
       <c r="P97" t="str">
-        <v>2026-08-04T05:27:10.794Z</v>
+        <v>2026-08-04T08:17:31.119Z</v>
       </c>
       <c r="Q97" t="str">
-        <v>2026-08-04T05:27:12.923Z</v>
+        <v>2026-08-04T08:17:33.560Z</v>
       </c>
       <c r="R97" t="str">
         <v>["https://lh3.googleusercontent.com/grass-cs/ACvplmP8urg3bL_FWZrfK5uigGBtI5nsT_jz56zmz72aAg50_tCE449DwzBuVG3bpU9HLBRFL4t_koHbVaMg4qbsa2kbye2vT_u9BvSyXNgTehW8x3B8qr1W7thTQ_qtiw70hKprh_Ucp5HXzP3V=w600-h450-p-k-no"]</v>
       </c>
       <c r="S97" t="str">
-        <v>2026-07-05T05:27:05.156Z</v>
+        <v>2026-07-05T08:17:24.912Z</v>
       </c>
       <c r="T97" t="str">
-        <v>2026-08-04T05:27:22.788Z</v>
+        <v>2026-08-04T08:17:45.660Z</v>
       </c>
     </row>
     <row r="98">
@@ -8655,7 +8666,7 @@
         <v>apify</v>
       </c>
       <c r="M98" t="str">
-        <v>2026-08-04T05:27:10.794Z</v>
+        <v>2026-08-04T08:17:31.119Z</v>
       </c>
       <c r="N98" t="str">
         <v>[]</v>
@@ -8664,19 +8675,19 @@
         <v>Veryyy good and tasty!!!!</v>
       </c>
       <c r="P98" t="str">
-        <v>2026-08-04T05:27:10.794Z</v>
+        <v>2026-08-04T08:17:31.119Z</v>
       </c>
       <c r="Q98" t="str">
-        <v>2026-08-04T05:27:12.643Z</v>
+        <v>2026-08-04T08:17:33.058Z</v>
       </c>
       <c r="R98" t="str">
-        <v>["https://lh3.googleusercontent.com/grass-cs/ACvplmNbEkU69ERfyprZOnd3ce4a8jikXMVgNW1mdz4D69wljnvina7fNCC0UmN_5GsX4teH8aQncXdkZa6CqKu9R2Irr1DCH2lRhU2QW_0CjmGV4hESKUqE8H9mdwEhN2i0PD7KntHVCjfDPKRr=w600-h450-p-k-no"]</v>
+        <v>["https://lh3.googleusercontent.com/grass-cs/ACvplmPb7DNLUBGsJ7SOkxrAP76qFf-jafM8xG28paS1ikhX6QO7cogCZ0H2X7Y0uVwyZVzTdUFEbxugJbfvjDcbZIJWFm9cfXfygRAvPQrYkUycZkA0mNS0iuTDGD_4eubRSZYaIvieEIfIvyww=w600-h450-p-k-no"]</v>
       </c>
       <c r="S98" t="str">
-        <v>2026-07-05T05:27:05.156Z</v>
+        <v>2026-07-05T08:17:24.912Z</v>
       </c>
       <c r="T98" t="str">
-        <v>2026-08-04T05:27:22.788Z</v>
+        <v>2026-08-04T08:17:45.660Z</v>
       </c>
     </row>
     <row r="99">
@@ -8717,7 +8728,7 @@
         <v>apify</v>
       </c>
       <c r="M99" t="str">
-        <v>2026-08-04T05:27:10.794Z</v>
+        <v>2026-08-04T08:17:31.119Z</v>
       </c>
       <c r="N99" t="str">
         <v>[]</v>
@@ -8726,10 +8737,10 @@
         <v>Premium quality and taste</v>
       </c>
       <c r="P99" t="str">
-        <v>2026-08-04T05:27:10.794Z</v>
+        <v>2026-08-04T08:17:31.119Z</v>
       </c>
       <c r="Q99" t="str">
-        <v>2026-08-04T05:27:12.783Z</v>
+        <v>2026-08-04T08:17:33.182Z</v>
       </c>
       <c r="R99" t="str">
         <v>["https://lh3.googleusercontent.com/grass-cs/ACvplmPjqw76vV6Nbougq9wpheQAt46hrjl7JvzOXljVAhc-c_BA89VLDs1aKLcweDnXDTyRLpjR5hFWGK7A5eXQXT69P7x08CYK8Fhkwx3faQDD7Pig9RggitVZf0Jn9wW3zeSFitE18ycB8Syo=w600-h450-p-k-no"]</v>
@@ -8738,7 +8749,7 @@
         <v/>
       </c>
       <c r="T99" t="str">
-        <v>2026-08-04T05:27:22.788Z</v>
+        <v>2026-08-04T08:17:45.660Z</v>
       </c>
     </row>
     <row r="100">
@@ -8779,7 +8790,7 @@
         <v>apify</v>
       </c>
       <c r="M100" t="str">
-        <v>2026-08-04T05:27:10.794Z</v>
+        <v>2026-08-04T08:17:31.119Z</v>
       </c>
       <c r="N100" t="str">
         <v>[]</v>
@@ -8788,19 +8799,19 @@
         <v>Everything was perfect! The packaging was neat and secure, and the cake was fresh and looked beautiful. The taste was absolutely amazing-soft, rich, and so delicious. Everyone loved it. Thank you so much for this wonderful cake! Will definitely order again ma'am. ❤️Highly recommended</v>
       </c>
       <c r="P100" t="str">
-        <v>2026-08-04T05:27:10.794Z</v>
+        <v>2026-08-04T08:17:31.119Z</v>
       </c>
       <c r="Q100" t="str">
-        <v>2026-08-04T05:27:11.797Z</v>
+        <v>2026-08-04T08:17:32.231Z</v>
       </c>
       <c r="R100" t="str">
         <v>["https://lh3.googleusercontent.com/grass-cs/ACvplmNeA82iSR28f7uVGHRJJXLIjCCgye8aqyz0gn8FJ1G3Ww84OI547WQAU9AQFchO5VYaZopyErDlz0N7k9NLmVnyprAn28dZCGhBFE8ZOTqWp96MFz8DIWiykn89S7t-s94FUlrvOOhBlBsA=w300-h450-p-k-no","https://lh3.googleusercontent.com/grass-cs/ACvplmPK5RowQ4MR1Re2zHfDxajk3wTC0tB3IJmIDNb15EIJTjEs9YuepGuFRm3MumWIj8EGdq14Gg9kpHvyQwp143E4uLuVxYtKzIphx1rVnyNHbqTeKi6QHiqEhrBair6cKzH3ZBr9Fy6zhLVD=w300-h450-p-k-no"]</v>
       </c>
       <c r="S100" t="str">
-        <v>2026-07-14T05:27:03.198Z</v>
+        <v>2026-07-14T08:17:22.549Z</v>
       </c>
       <c r="T100" t="str">
-        <v>2026-08-04T05:27:22.788Z</v>
+        <v>2026-08-04T08:17:45.660Z</v>
       </c>
     </row>
     <row r="101">
@@ -8841,7 +8852,7 @@
         <v>apify</v>
       </c>
       <c r="M101" t="str">
-        <v>2026-08-04T05:27:10.794Z</v>
+        <v>2026-08-04T08:17:31.119Z</v>
       </c>
       <c r="N101" t="str">
         <v>[]</v>
@@ -8850,19 +8861,19 @@
         <v>We have ordered the cake, for my daughter's 1st birthday celebration.. The cake tastes too good and their service was speechless.. once again thank you so much..</v>
       </c>
       <c r="P101" t="str">
-        <v>2026-08-04T05:27:10.794Z</v>
+        <v>2026-08-04T08:17:31.119Z</v>
       </c>
       <c r="Q101" t="str">
-        <v>2026-08-04T05:27:11.906Z</v>
+        <v>2026-08-04T08:17:32.356Z</v>
       </c>
       <c r="R101" t="str">
         <v>[]</v>
       </c>
       <c r="S101" t="str">
-        <v>2026-07-14T05:27:03.198Z</v>
+        <v>2026-07-14T08:17:22.549Z</v>
       </c>
       <c r="T101" t="str">
-        <v>2026-08-04T05:27:22.788Z</v>
+        <v>2026-08-04T08:17:45.660Z</v>
       </c>
     </row>
     <row r="102">
@@ -8903,7 +8914,7 @@
         <v>apify</v>
       </c>
       <c r="M102" t="str">
-        <v>2026-08-04T05:27:10.794Z</v>
+        <v>2026-08-04T08:17:31.119Z</v>
       </c>
       <c r="N102" t="str">
         <v>[]</v>
@@ -8912,19 +8923,19 @@
         <v>Super happy with the cake! I ordered it last night, and it was delivered today exactly as I requested. Great quality and service! 🤸🏽🤠✌🏽:)) …</v>
       </c>
       <c r="P102" t="str">
-        <v>2026-08-04T05:27:10.794Z</v>
+        <v>2026-08-04T08:17:31.119Z</v>
       </c>
       <c r="Q102" t="str">
-        <v>2026-08-04T05:27:12.032Z</v>
+        <v>2026-08-04T08:17:32.449Z</v>
       </c>
       <c r="R102" t="str">
         <v>["https://lh3.googleusercontent.com/grass-cs/ACvplmN-fZ4ZbA56LmNiHVlExrbqgANFAZMy8bqKwQL2NZQoPLvsH32nLMA8NdeOB0u3oUSm80MLB3LqUA_CilitL9CMi_-quzFH8w85r3M8mAkOZ81DYaLY87FPXWd43Jpk0USLvFk1dmP2f3Iv=w300-h450-p-k-no","https://lh3.googleusercontent.com/grass-cs/ACvplmNi6EhLEBn0pUuQ0grFLJMdiKnbXeFMQPZhXPeNvy4Yal7mN4O5uq8vSm9SIjfeood1mazn_9DJHbzq33a8t0546WCFW6YgUSPNzK5GUuoRGB39wvuiLM_nh_Y0HVESvmWy6SoTNZov2giR=w300-h450-p-k-no"]</v>
       </c>
       <c r="S102" t="str">
-        <v>2026-07-14T05:27:03.198Z</v>
+        <v>2026-07-07T08:17:22.549Z</v>
       </c>
       <c r="T102" t="str">
-        <v>2026-08-04T05:27:22.788Z</v>
+        <v>2026-08-04T08:17:45.660Z</v>
       </c>
     </row>
     <row r="103">
@@ -8965,7 +8976,7 @@
         <v>apify</v>
       </c>
       <c r="M103" t="str">
-        <v>2026-08-04T05:27:10.794Z</v>
+        <v>2026-08-04T08:17:31.119Z</v>
       </c>
       <c r="N103" t="str">
         <v>[]</v>
@@ -8974,19 +8985,19 @@
         <v>The cake was absolutely delicious! It tasted fresh, had the perfect level of sweetness, and everyone loved it. Thank you for making my son's birthday extra special. Highly recommended!</v>
       </c>
       <c r="P103" t="str">
-        <v>2026-08-04T05:27:10.794Z</v>
+        <v>2026-08-04T08:17:31.119Z</v>
       </c>
       <c r="Q103" t="str">
-        <v>2026-08-04T05:27:12.158Z</v>
+        <v>2026-08-04T08:17:32.559Z</v>
       </c>
       <c r="R103" t="str">
         <v>["https://lh3.googleusercontent.com/grass-cs/ACvplmOC-Soy91lKLF7ldDi9z84NQYf-W_fCLXznQODBCUGMQMZpvcJ1O3qmFcvuJYT_m1cL70J-WK0r6nbr9eyIChJ3lSRh3Kv8a4I-Qdw7R_6xiyFK5AImavP_8a7upJ1QawqXlD_XwVTNJZYj=w600-h450-p-k-no"]</v>
       </c>
       <c r="S103" t="str">
-        <v>2026-07-07T05:27:03.198Z</v>
+        <v>2026-07-07T08:17:22.549Z</v>
       </c>
       <c r="T103" t="str">
-        <v>2026-08-04T05:27:22.788Z</v>
+        <v>2026-08-04T08:17:45.660Z</v>
       </c>
     </row>
     <row r="104">
@@ -9027,7 +9038,7 @@
         <v>apify</v>
       </c>
       <c r="M104" t="str">
-        <v>2026-08-04T05:27:10.794Z</v>
+        <v>2026-08-04T08:17:31.119Z</v>
       </c>
       <c r="N104" t="str">
         <v>[]</v>
@@ -9036,19 +9047,19 @@
         <v>Absolutely love this place! Ordered a chocolate truffle cake on very short notice and they came through beautifully. The taste was fantastic and the design was lovely too. Highly recommend to anyone looking for a truly special cake!</v>
       </c>
       <c r="P104" t="str">
-        <v>2026-08-04T05:27:10.794Z</v>
+        <v>2026-08-04T08:17:31.119Z</v>
       </c>
       <c r="Q104" t="str">
-        <v>2026-08-04T05:27:12.266Z</v>
+        <v>2026-08-04T08:17:32.683Z</v>
       </c>
       <c r="R104" t="str">
         <v>[]</v>
       </c>
       <c r="S104" t="str">
-        <v>2026-07-07T05:27:03.198Z</v>
+        <v>2026-07-07T08:17:22.549Z</v>
       </c>
       <c r="T104" t="str">
-        <v>2026-08-04T05:27:22.788Z</v>
+        <v>2026-08-04T08:17:45.660Z</v>
       </c>
     </row>
     <row r="105">
@@ -9089,7 +9100,7 @@
         <v>apify</v>
       </c>
       <c r="M105" t="str">
-        <v>2026-08-04T05:27:10.794Z</v>
+        <v>2026-08-04T08:17:31.119Z</v>
       </c>
       <c r="N105" t="str">
         <v>[]</v>
@@ -9098,19 +9109,19 @@
         <v>The taste was top-notch, the communication and delivery is hassle free. I would definitely order further. Thank you Chocolate mine</v>
       </c>
       <c r="P105" t="str">
-        <v>2026-08-04T05:27:10.794Z</v>
+        <v>2026-08-04T08:17:31.119Z</v>
       </c>
       <c r="Q105" t="str">
-        <v>2026-08-04T05:27:12.410Z</v>
+        <v>2026-08-04T08:17:32.809Z</v>
       </c>
       <c r="R105" t="str">
         <v>["https://lh3.googleusercontent.com/grass-cs/ACvplmPR_WMQjlt-SbR5yzkU84Ao-tE30pFrhqI1ZCXEaZpYhY8wE8FSceuLD9HawVtjhC9VLBeapJS4HvcndzOwpAvn-3rSweAIXyVBpJTnx5vUuE7-0pEAQc52vi3c7756lq10T8d6wishMQc=w300-h450-p-k-no","https://lh3.googleusercontent.com/grass-cs/ACvplmMfT5aWOXYVMky5tDsUIf1jZcEqaHrdzejhuI1RzxOLjpRSE4Pv8YFFlWxcLHOL3KQZj_KQpSp7-kro1W7bLmmVRWWEYMbeEvN4Tvg73FUKsvuG_RkYgYz3ATf9ElcG6HVnawHw8Eu2-RA=w300-h450-p-k-no"]</v>
       </c>
       <c r="S105" t="str">
-        <v>2026-07-07T05:27:03.198Z</v>
+        <v>2026-07-07T08:17:22.549Z</v>
       </c>
       <c r="T105" t="str">
-        <v>2026-08-04T05:27:22.788Z</v>
+        <v>2026-08-04T08:17:45.660Z</v>
       </c>
     </row>
     <row r="106">
@@ -9172,7 +9183,7 @@
         <v>2026-07-10T16:29:46.315Z</v>
       </c>
       <c r="T106" t="str">
-        <v>2026-08-04T05:27:22.788Z</v>
+        <v>2026-08-04T08:17:45.660Z</v>
       </c>
     </row>
     <row r="107">
@@ -9213,7 +9224,7 @@
         <v>apify</v>
       </c>
       <c r="M107" t="str">
-        <v>2026-08-04T05:27:10.794Z</v>
+        <v>2026-08-04T08:17:31.119Z</v>
       </c>
       <c r="N107" t="str">
         <v>[]</v>
@@ -9222,19 +9233,19 @@
         <v>I like the ambience of the shop and the food are tasty, personally highly recommend this shop</v>
       </c>
       <c r="P107" t="str">
-        <v>2026-08-04T05:27:10.794Z</v>
+        <v>2026-08-04T08:17:31.119Z</v>
       </c>
       <c r="Q107" t="str">
-        <v>2026-08-04T05:27:11.687Z</v>
+        <v>2026-08-04T08:17:32.107Z</v>
       </c>
       <c r="R107" t="str">
         <v>[]</v>
       </c>
       <c r="S107" t="str">
-        <v>2026-07-14T05:27:03.198Z</v>
+        <v>2026-07-14T08:17:22.549Z</v>
       </c>
       <c r="T107" t="str">
-        <v>2026-08-04T05:27:22.788Z</v>
+        <v>2026-08-04T08:17:45.660Z</v>
       </c>
     </row>
     <row r="108">
@@ -9275,7 +9286,7 @@
         <v>apify</v>
       </c>
       <c r="M108" t="str">
-        <v>2026-08-04T05:27:10.794Z</v>
+        <v>2026-08-04T08:17:31.119Z</v>
       </c>
       <c r="N108" t="str">
         <v>[]</v>
@@ -9284,19 +9295,19 @@
         <v>café. Great coffee. Amazing atmosphere. 🤍☕</v>
       </c>
       <c r="P108" t="str">
-        <v>2026-08-04T05:27:10.794Z</v>
+        <v>2026-08-04T08:17:31.119Z</v>
       </c>
       <c r="Q108" t="str">
-        <v>2026-08-04T05:27:11.562Z</v>
+        <v>2026-08-04T08:17:31.981Z</v>
       </c>
       <c r="R108" t="str">
         <v>["https://lh3.googleusercontent.com/grass-cs/ACvplmPErvV0RjZmfRwtWbuKzYbxI3DyAL2gb1GrWglchpKgPwarSFCwsoTrlyLASNHLwDW55Ufk5MAi7-IULkcS0fef8zE2yvqwosqfbN7OfzO9_jJqKxPQ2gk81L1VqxhQIzD78sGgvlTxUOXJ=w600-h450-p-k-no"]</v>
       </c>
       <c r="S108" t="str">
-        <v>2026-07-21T05:27:01.327Z</v>
+        <v>2026-07-21T08:17:22.549Z</v>
       </c>
       <c r="T108" t="str">
-        <v>2026-08-04T05:27:22.788Z</v>
+        <v>2026-08-04T08:17:45.660Z</v>
       </c>
     </row>
     <row r="109">
@@ -9337,7 +9348,7 @@
         <v>apify</v>
       </c>
       <c r="M109" t="str">
-        <v>2026-08-04T05:27:10.794Z</v>
+        <v>2026-08-04T08:17:31.119Z</v>
       </c>
       <c r="N109" t="str">
         <v>[]</v>
@@ -9346,19 +9357,19 @@
         <v>Very good... service Approach nice...food and packing delivery timeing also fine.</v>
       </c>
       <c r="P109" t="str">
-        <v>2026-08-04T05:27:10.794Z</v>
+        <v>2026-08-04T08:17:31.119Z</v>
       </c>
       <c r="Q109" t="str">
-        <v>2026-08-04T05:27:11.408Z</v>
+        <v>2026-08-04T08:17:31.873Z</v>
       </c>
       <c r="R109" t="str">
         <v>["https://lh3.googleusercontent.com/grass-cs/ACvplmN0f8fWy8F3hL8_U-LBJKkVlXesNa5kDRGcCWA7kKvIQLXR-K9uyrP2J0idLp1MGloyp-Y_i7VOPkFFe7bz6JnBLcsX4yw8Sz-sbLj81ehlHULAyEqCTDlIgSNBoZj0UqLRNPlZXyFkdnI=w600-h450-p-k-no"]</v>
       </c>
       <c r="S109" t="str">
-        <v>2026-07-21T05:27:01.327Z</v>
+        <v>2026-07-21T08:17:20.756Z</v>
       </c>
       <c r="T109" t="str">
-        <v>2026-08-04T05:27:22.788Z</v>
+        <v>2026-08-04T08:17:45.660Z</v>
       </c>
     </row>
     <row r="110">
@@ -9420,7 +9431,7 @@
         <v>2026-03-30T18:20:59.728Z</v>
       </c>
       <c r="T110" t="str">
-        <v>2026-08-04T05:27:22.788Z</v>
+        <v>2026-08-04T08:17:45.660Z</v>
       </c>
     </row>
     <row r="111">
@@ -9461,7 +9472,7 @@
         <v>apify</v>
       </c>
       <c r="M111" t="str">
-        <v>2026-08-04T05:27:10.794Z</v>
+        <v>2026-08-04T08:17:31.119Z</v>
       </c>
       <c r="N111" t="str">
         <v>[]</v>
@@ -9470,19 +9481,19 @@
         <v>Hi! We have ordered cake from you for the 3rd time. So satisfied with your cake flavours, the taste is very rich and everlasting thinking about ordering from you next time too😊</v>
       </c>
       <c r="P111" t="str">
-        <v>2026-08-04T05:27:10.794Z</v>
+        <v>2026-08-04T08:17:31.119Z</v>
       </c>
       <c r="Q111" t="str">
-        <v>2026-08-04T05:27:11.283Z</v>
+        <v>2026-08-04T08:17:31.748Z</v>
       </c>
       <c r="R111" t="str">
         <v>["https://lh3.googleusercontent.com/grass-cs/ACvplmNl9EVDKAAZnZ-rKcv8hxAlzRSzlVes9EWtNawzsvEjwnFtM_lIMWXTyShS7usn-z0Q6M4HuFlx3ogjSr1msZFsq4KUHvWpWmk8WcNgXEgt1OmVj4KWy1LihgBW4h-kS-7Sm2Lkuh6BS9Q=w600-h450-p-k-no"]</v>
       </c>
       <c r="S111" t="str">
-        <v>2026-07-28T05:27:01.327Z</v>
+        <v>2026-07-28T08:17:20.756Z</v>
       </c>
       <c r="T111" t="str">
-        <v>2026-08-04T05:27:22.788Z</v>
+        <v>2026-08-04T08:17:45.660Z</v>
       </c>
     </row>
     <row r="112">
@@ -9523,7 +9534,7 @@
         <v>apify</v>
       </c>
       <c r="M112" t="str">
-        <v>2026-08-04T05:27:10.794Z</v>
+        <v>2026-08-04T08:17:31.119Z</v>
       </c>
       <c r="N112" t="str">
         <v>[]</v>
@@ -9532,19 +9543,19 @@
         <v>The cake was awesome and i got it delivered at time</v>
       </c>
       <c r="P112" t="str">
-        <v>2026-08-04T05:27:10.793Z</v>
+        <v>2026-08-04T08:17:31.119Z</v>
       </c>
       <c r="Q112" t="str">
-        <v>2026-08-04T05:27:11.172Z</v>
+        <v>2026-08-04T08:17:31.638Z</v>
       </c>
       <c r="R112" t="str">
         <v>["https://lh3.googleusercontent.com/grass-cs/ACvplmP1bsAdlllZ_ejRfcAxNeSwJ_c7YRAg9VqbeFD_pKRfrxa39eClEX8fzlvNinxnupQYgdLXQM2ztNE_v8whaz-9t4sDYXSD_TzEFgn6I7AuadIvYndBsR69oKPxnrgOfErMZzCAEG6bPC9q=w600-h450-p-k-no"]</v>
       </c>
       <c r="S112" t="str">
-        <v>2026-07-28T05:27:01.327Z</v>
+        <v>2026-07-28T08:17:20.756Z</v>
       </c>
       <c r="T112" t="str">
-        <v>2026-08-04T05:27:22.788Z</v>
+        <v>2026-08-04T08:17:45.661Z</v>
       </c>
     </row>
     <row r="113">
@@ -9606,7 +9617,7 @@
         <v>2026-07-27T16:49:55.429Z</v>
       </c>
       <c r="T113" t="str">
-        <v>2026-08-04T05:27:22.788Z</v>
+        <v>2026-08-04T08:17:45.661Z</v>
       </c>
     </row>
     <row r="114">
@@ -9668,7 +9679,7 @@
         <v>2026-07-26T16:49:55.429Z</v>
       </c>
       <c r="T114" t="str">
-        <v>2026-08-04T05:27:22.788Z</v>
+        <v>2026-08-04T08:17:45.661Z</v>
       </c>
     </row>
     <row r="115">
@@ -9730,7 +9741,7 @@
         <v>2026-07-29T10:10:17.865Z</v>
       </c>
       <c r="T115" t="str">
-        <v>2026-08-04T05:27:22.789Z</v>
+        <v>2026-08-04T08:17:45.661Z</v>
       </c>
     </row>
     <row r="116">
@@ -9771,7 +9782,7 @@
         <v>apify</v>
       </c>
       <c r="M116" t="str">
-        <v>2026-08-04T05:27:10.794Z</v>
+        <v>2026-08-04T08:17:31.119Z</v>
       </c>
       <c r="N116" t="str">
         <v>[]</v>
@@ -9780,19 +9791,19 @@
         <v>Good Food and Good Ambience 🫠</v>
       </c>
       <c r="P116" t="str">
-        <v>2026-08-04T05:27:10.794Z</v>
+        <v>2026-08-04T08:17:31.119Z</v>
       </c>
       <c r="Q116" t="str">
-        <v>2026-08-04T05:27:12.533Z</v>
+        <v>2026-08-04T08:17:32.919Z</v>
       </c>
       <c r="R116" t="str">
         <v>["https://lh3.googleusercontent.com/grass-cs/ACvplmPbnMyGgr7ldw1VwH2l9EWxESZ8i2WiCTUTe8zQ29ZXhRAHSAkgj-eU4D0iR1XuNu5soHKcqzl6OEIFME7xPRSCpJCa_7otMLFbgnGUy47fc2F5UE8WGAeRUEOGKzRcYJ-4BUVoaCbt6pMN=w300-h225-p-k-no","https://lh3.googleusercontent.com/grass-cs/ACvplmMZ3T-J1z6ygeEsljvANBCm-33Prl5Hlb3l9vMQnNSj_kLI-6Bwz_j3_RsiMEtPi4cF2lfEeKHdpyLJaxcfEejKfhgfZWDFTIq7UoUUXQUthEeo35tEUD640_d8BqZpAkxoeXkJczkr6-oZ=w300-h225-p-k-no","https://lh3.googleusercontent.com/grass-cs/ACvplmP-O01jDu1yIZg3Tp7Wr8SaYhm5rPrpnv6WSHPO69y0EBP1XAC0a-MwoZyTtvCcGGIsu19-yYNTSMPZgBW5lx315eewd5GYs40UDOgdBUgmP29co1Tg8rgDYMQ2ELeNl_O0FW1SqJKz8k7c=w300-h225-p-k-no","https://lh3.googleusercontent.com/grass-cs/ACvplmOUaBLj7YaW6hX6SdiqRzi-t7aNyY6jBx6F-B_sWkYuThsNAH5r4VUSlpqByUGn8OTiqeZgRXL2GjrVYdhvw_AxvPu6XWXSiUOQwcd5ESDlbgF35kt4sPgp4HzvvtACFVYgZYyZAQ8i7o7J=w300-h225-p-k-no"]</v>
       </c>
       <c r="S116" t="str">
-        <v>2026-07-07T05:27:03.198Z</v>
+        <v>2026-07-07T08:17:24.912Z</v>
       </c>
       <c r="T116" t="str">
-        <v>2026-08-04T05:27:22.789Z</v>
+        <v>2026-08-04T08:17:45.661Z</v>
       </c>
     </row>
     <row r="117">
@@ -9833,7 +9844,7 @@
         <v>apify</v>
       </c>
       <c r="M117" t="str">
-        <v>2026-08-04T05:27:10.794Z</v>
+        <v>2026-08-04T08:17:31.119Z</v>
       </c>
       <c r="N117" t="str">
         <v>[]</v>
@@ -9842,19 +9853,19 @@
         <v>Must try paneer tikka sandwich..... Served fresh and hot... Soooo good!!!.</v>
       </c>
       <c r="P117" t="str">
-        <v>2026-08-04T05:27:10.794Z</v>
+        <v>2026-08-04T08:17:31.119Z</v>
       </c>
       <c r="Q117" t="str">
-        <v>2026-08-04T05:27:14.829Z</v>
+        <v>2026-08-04T08:17:35.534Z</v>
       </c>
       <c r="R117" t="str">
         <v>[]</v>
       </c>
       <c r="S117" t="str">
-        <v>2026-07-05T05:27:07.537Z</v>
+        <v>2026-07-05T08:17:29.399Z</v>
       </c>
       <c r="T117" t="str">
-        <v>2026-08-04T05:27:22.789Z</v>
+        <v>2026-08-04T08:17:45.661Z</v>
       </c>
     </row>
     <row r="118">
@@ -9895,7 +9906,7 @@
         <v>apify</v>
       </c>
       <c r="M118" t="str">
-        <v>2026-08-04T05:27:10.793Z</v>
+        <v>2026-08-04T08:17:31.119Z</v>
       </c>
       <c r="N118" t="str">
         <v>[]</v>
@@ -9904,19 +9915,19 @@
         <v>The cake was absolutely delicious! It was fresh, soft, and perfectly moist.It looked beautiful and tasted even better.</v>
       </c>
       <c r="P118" t="str">
-        <v>2026-08-04T05:27:10.793Z</v>
+        <v>2026-08-04T08:17:31.119Z</v>
       </c>
       <c r="Q118" t="str">
-        <v>2026-08-04T05:27:10.954Z</v>
+        <v>2026-08-04T08:17:31.233Z</v>
       </c>
       <c r="R118" t="str">
         <v>["https://lh3.googleusercontent.com/grass-cs/ACvplmOIh9ayyn4ckHl5HGioGFgtNJUmc6xw388f4REij1aAj0n57maHW_395fh6OZjj0IeDsP6hnuMvyi33e8sYRT1j3_0E7gP-CEcS6eKzxaHZoGnyrq5oSs_i0z-U3MxeUKLoQ4rBWo9YvjVc=w600-h450-p-k-no"]</v>
       </c>
       <c r="S118" t="str">
-        <v>2026-08-03T05:27:01.327Z</v>
+        <v>2026-08-03T08:17:20.756Z</v>
       </c>
       <c r="T118" t="str">
-        <v>2026-08-04T05:27:22.789Z</v>
+        <v>2026-08-04T08:17:45.661Z</v>
       </c>
     </row>
     <row r="119">
@@ -9957,7 +9968,7 @@
         <v>apify</v>
       </c>
       <c r="M119" t="str">
-        <v>2026-08-04T05:27:10.793Z</v>
+        <v>2026-08-04T08:17:31.119Z</v>
       </c>
       <c r="N119" t="str">
         <v>[]</v>
@@ -9966,19 +9977,19 @@
         <v>Quick and delicious service... What a wow Biscoff tres leches ...</v>
       </c>
       <c r="P119" t="str">
-        <v>2026-08-04T05:27:10.793Z</v>
+        <v>2026-08-04T08:17:31.119Z</v>
       </c>
       <c r="Q119" t="str">
-        <v>2026-08-04T05:27:11.079Z</v>
+        <v>2026-08-04T08:17:31.341Z</v>
       </c>
       <c r="R119" t="str">
         <v>[]</v>
       </c>
       <c r="S119" t="str">
-        <v>2026-08-03T05:27:01.327Z</v>
+        <v>2026-08-03T08:17:20.756Z</v>
       </c>
       <c r="T119" t="str">
-        <v>2026-08-04T05:27:22.789Z</v>
+        <v>2026-08-04T08:17:45.661Z</v>
       </c>
     </row>
     <row r="120">
@@ -10019,7 +10030,7 @@
         <v>apify</v>
       </c>
       <c r="M120" t="str">
-        <v>2026-08-04T05:27:10.793Z</v>
+        <v>2026-08-04T08:17:31.119Z</v>
       </c>
       <c r="N120" t="str">
         <v>[]</v>
@@ -10028,24 +10039,103 @@
         <v>I ordered choco fudge cake and it was a last minute order. But the owner was so sweet to deliver it very quickly. And the cake was so yum. Hope to order again!</v>
       </c>
       <c r="P120" t="str">
-        <v>2026-08-04T05:27:10.793Z</v>
+        <v>2026-08-04T08:17:31.118Z</v>
       </c>
       <c r="Q120" t="str">
-        <v>2026-08-04T05:27:10.798Z</v>
+        <v>2026-08-04T08:17:31.123Z</v>
       </c>
       <c r="R120" t="str">
         <v>[]</v>
       </c>
       <c r="S120" t="str">
-        <v>2026-08-04T04:53:01.327Z</v>
+        <v>2026-08-04T05:17:20.756Z</v>
       </c>
       <c r="T120" t="str">
-        <v>2026-08-04T05:27:22.789Z</v>
+        <v>2026-08-04T08:17:45.661Z</v>
       </c>
     </row>
   </sheetData>
   <ignoredErrors>
     <ignoredError numberStoredAsText="1" sqref="A1:T120"/>
+  </ignoredErrors>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet18.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
+  <dimension ref="A1:F3"/>
+  <cols>
+    <col min="1" max="1" width="26.83203125" customWidth="1"/>
+    <col min="2" max="2" width="52.83203125" customWidth="1"/>
+    <col min="3" max="3" width="26.83203125" customWidth="1"/>
+    <col min="4" max="4" width="17.83203125" customWidth="1"/>
+    <col min="5" max="5" width="26.83203125" customWidth="1"/>
+    <col min="6" max="6" width="26.83203125" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1">
+      <c r="A1" t="str">
+        <v>_id</v>
+      </c>
+      <c r="B1" t="str">
+        <v>token</v>
+      </c>
+      <c r="C1" t="str">
+        <v>createdAt</v>
+      </c>
+      <c r="D1" t="str">
+        <v>deviceName</v>
+      </c>
+      <c r="E1" t="str">
+        <v>userId</v>
+      </c>
+      <c r="F1" t="str">
+        <v>exportedAt</v>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" t="str">
+        <v>6a6b650bd7d857f1080f8920</v>
+      </c>
+      <c r="B2" t="str">
+        <v>dr_NR4O8AJ7owY0nZEkTHt:APA91bFioPFZa6WWAzUV05hxO9aNoPx7oJIw3crpk1xfvE0sKwHd8cwMkLtxeoHFWY_gcxEntXBvNi0-jfrQwo4IeYpnEd5Zhr7tUXCNS45i06qzKyVKNcE</v>
+      </c>
+      <c r="C2" t="str">
+        <v>2026-08-02T06:33:29.895Z</v>
+      </c>
+      <c r="D2" t="str">
+        <v>Windows Desktop</v>
+      </c>
+      <c r="E2" t="str">
+        <v>69e9c1ab766ae41a5f9612cd</v>
+      </c>
+      <c r="F2" t="str">
+        <v>2026-08-04T08:17:45.779Z</v>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="str">
+        <v>6a719d00f4526627301ab9d1</v>
+      </c>
+      <c r="B3" t="str">
+        <v>dpoXfI-2KZ-mo3b_zPTVNR:APA91bG9ZMTUrTy8QR3w3Q56smqrhcfJFjLKEfFEOJc_8iJaiTW7zKu-MrYCJk5RxZh3Wkwx4Jzwq3lRvE6hvJdFvfGhjQHo3oz-BWolskWWCQEMX4VKNz4</v>
+      </c>
+      <c r="C3" t="str">
+        <v>2026-08-04T08:17:16.052Z</v>
+      </c>
+      <c r="D3" t="str">
+        <v>Windows Desktop</v>
+      </c>
+      <c r="E3" t="str">
+        <v>69e9c1ab766ae41a5f9612cd</v>
+      </c>
+      <c r="F3" t="str">
+        <v>2026-08-04T08:17:45.779Z</v>
+      </c>
+    </row>
+  </sheetData>
+  <ignoredErrors>
+    <ignoredError numberStoredAsText="1" sqref="A1:F3"/>
   </ignoredErrors>
 </worksheet>
 </file>
@@ -10307,7 +10397,7 @@
         <v>[]</v>
       </c>
       <c r="AH2" t="str">
-        <v>2026-08-04T05:27:20.280Z</v>
+        <v>2026-08-04T08:17:41.808Z</v>
       </c>
     </row>
     <row r="3">
@@ -10411,7 +10501,7 @@
         <v>[]</v>
       </c>
       <c r="AH3" t="str">
-        <v>2026-08-04T05:27:20.280Z</v>
+        <v>2026-08-04T08:17:41.808Z</v>
       </c>
     </row>
     <row r="4">
@@ -10515,7 +10605,7 @@
         <v>[]</v>
       </c>
       <c r="AH4" t="str">
-        <v>2026-08-04T05:27:20.280Z</v>
+        <v>2026-08-04T08:17:41.808Z</v>
       </c>
     </row>
     <row r="5">
@@ -10619,7 +10709,7 @@
         <v>[]</v>
       </c>
       <c r="AH5" t="str">
-        <v>2026-08-04T05:27:20.280Z</v>
+        <v>2026-08-04T08:17:41.808Z</v>
       </c>
     </row>
     <row r="6">
@@ -10723,7 +10813,7 @@
         <v>[]</v>
       </c>
       <c r="AH6" t="str">
-        <v>2026-08-04T05:27:20.280Z</v>
+        <v>2026-08-04T08:17:41.808Z</v>
       </c>
     </row>
     <row r="7">
@@ -10827,7 +10917,7 @@
         <v>[]</v>
       </c>
       <c r="AH7" t="str">
-        <v>2026-08-04T05:27:20.280Z</v>
+        <v>2026-08-04T08:17:41.808Z</v>
       </c>
     </row>
     <row r="8">
@@ -10931,7 +11021,7 @@
         <v>[]</v>
       </c>
       <c r="AH8" t="str">
-        <v>2026-08-04T05:27:20.280Z</v>
+        <v>2026-08-04T08:17:41.808Z</v>
       </c>
     </row>
     <row r="9">
@@ -11035,7 +11125,7 @@
         <v>[]</v>
       </c>
       <c r="AH9" t="str">
-        <v>2026-08-04T05:27:20.280Z</v>
+        <v>2026-08-04T08:17:41.808Z</v>
       </c>
     </row>
     <row r="10">
@@ -11139,7 +11229,7 @@
         <v>[]</v>
       </c>
       <c r="AH10" t="str">
-        <v>2026-08-04T05:27:20.280Z</v>
+        <v>2026-08-04T08:17:41.808Z</v>
       </c>
     </row>
     <row r="11">
@@ -11243,7 +11333,7 @@
         <v>[]</v>
       </c>
       <c r="AH11" t="str">
-        <v>2026-08-04T05:27:20.280Z</v>
+        <v>2026-08-04T08:17:41.808Z</v>
       </c>
     </row>
     <row r="12">
@@ -11347,7 +11437,7 @@
         <v>[]</v>
       </c>
       <c r="AH12" t="str">
-        <v>2026-08-04T05:27:20.280Z</v>
+        <v>2026-08-04T08:17:41.808Z</v>
       </c>
     </row>
     <row r="13">
@@ -11451,7 +11541,7 @@
         <v>[]</v>
       </c>
       <c r="AH13" t="str">
-        <v>2026-08-04T05:27:20.280Z</v>
+        <v>2026-08-04T08:17:41.809Z</v>
       </c>
     </row>
     <row r="14">
@@ -11555,7 +11645,7 @@
         <v>[]</v>
       </c>
       <c r="AH14" t="str">
-        <v>2026-08-04T05:27:20.280Z</v>
+        <v>2026-08-04T08:17:41.809Z</v>
       </c>
     </row>
     <row r="15">
@@ -11650,7 +11740,7 @@
         <v>true</v>
       </c>
       <c r="AH15" t="str">
-        <v>2026-08-04T05:27:20.280Z</v>
+        <v>2026-08-04T08:17:41.809Z</v>
       </c>
     </row>
     <row r="16">
@@ -11754,7 +11844,7 @@
         <v>[]</v>
       </c>
       <c r="AH16" t="str">
-        <v>2026-08-04T05:27:20.280Z</v>
+        <v>2026-08-04T08:17:41.809Z</v>
       </c>
     </row>
     <row r="17">
@@ -11849,7 +11939,7 @@
         <v>true</v>
       </c>
       <c r="AH17" t="str">
-        <v>2026-08-04T05:27:20.281Z</v>
+        <v>2026-08-04T08:17:41.809Z</v>
       </c>
     </row>
     <row r="18">
@@ -11953,7 +12043,7 @@
         <v>[]</v>
       </c>
       <c r="AH18" t="str">
-        <v>2026-08-04T05:27:20.281Z</v>
+        <v>2026-08-04T08:17:41.809Z</v>
       </c>
     </row>
     <row r="19">
@@ -12057,7 +12147,7 @@
         <v>[]</v>
       </c>
       <c r="AH19" t="str">
-        <v>2026-08-04T05:27:20.281Z</v>
+        <v>2026-08-04T08:17:41.809Z</v>
       </c>
     </row>
     <row r="20">
@@ -12161,7 +12251,7 @@
         <v>[]</v>
       </c>
       <c r="AH20" t="str">
-        <v>2026-08-04T05:27:20.281Z</v>
+        <v>2026-08-04T08:17:41.809Z</v>
       </c>
     </row>
     <row r="21">
@@ -12265,7 +12355,7 @@
         <v>[]</v>
       </c>
       <c r="AH21" t="str">
-        <v>2026-08-04T05:27:20.281Z</v>
+        <v>2026-08-04T08:17:41.809Z</v>
       </c>
     </row>
     <row r="22">
@@ -12360,7 +12450,7 @@
         <v>true</v>
       </c>
       <c r="AH22" t="str">
-        <v>2026-08-04T05:27:20.281Z</v>
+        <v>2026-08-04T08:17:41.809Z</v>
       </c>
     </row>
     <row r="23">
@@ -12464,7 +12554,7 @@
         <v>[]</v>
       </c>
       <c r="AH23" t="str">
-        <v>2026-08-04T05:27:20.281Z</v>
+        <v>2026-08-04T08:17:41.809Z</v>
       </c>
     </row>
     <row r="24">
@@ -12559,7 +12649,7 @@
         <v>true</v>
       </c>
       <c r="AH24" t="str">
-        <v>2026-08-04T05:27:20.281Z</v>
+        <v>2026-08-04T08:17:41.809Z</v>
       </c>
     </row>
     <row r="25">
@@ -12663,7 +12753,7 @@
         <v>[]</v>
       </c>
       <c r="AH25" t="str">
-        <v>2026-08-04T05:27:20.281Z</v>
+        <v>2026-08-04T08:17:41.809Z</v>
       </c>
     </row>
     <row r="26">
@@ -12767,7 +12857,7 @@
         <v>[]</v>
       </c>
       <c r="AH26" t="str">
-        <v>2026-08-04T05:27:20.281Z</v>
+        <v>2026-08-04T08:17:41.809Z</v>
       </c>
     </row>
     <row r="27">
@@ -12871,7 +12961,7 @@
         <v>[]</v>
       </c>
       <c r="AH27" t="str">
-        <v>2026-08-04T05:27:20.281Z</v>
+        <v>2026-08-04T08:17:41.809Z</v>
       </c>
     </row>
     <row r="28">
@@ -12975,7 +13065,7 @@
         <v>[]</v>
       </c>
       <c r="AH28" t="str">
-        <v>2026-08-04T05:27:20.281Z</v>
+        <v>2026-08-04T08:17:41.809Z</v>
       </c>
     </row>
     <row r="29">
@@ -13070,7 +13160,7 @@
         <v>true</v>
       </c>
       <c r="AH29" t="str">
-        <v>2026-08-04T05:27:20.281Z</v>
+        <v>2026-08-04T08:17:41.809Z</v>
       </c>
     </row>
     <row r="30">
@@ -13174,7 +13264,7 @@
         <v>[]</v>
       </c>
       <c r="AH30" t="str">
-        <v>2026-08-04T05:27:20.281Z</v>
+        <v>2026-08-04T08:17:41.809Z</v>
       </c>
     </row>
     <row r="31">
@@ -13269,7 +13359,7 @@
         <v>true</v>
       </c>
       <c r="AH31" t="str">
-        <v>2026-08-04T05:27:20.281Z</v>
+        <v>2026-08-04T08:17:41.809Z</v>
       </c>
     </row>
     <row r="32">
@@ -13373,7 +13463,7 @@
         <v>[]</v>
       </c>
       <c r="AH32" t="str">
-        <v>2026-08-04T05:27:20.281Z</v>
+        <v>2026-08-04T08:17:41.809Z</v>
       </c>
     </row>
     <row r="33">
@@ -13477,7 +13567,7 @@
         <v>[]</v>
       </c>
       <c r="AH33" t="str">
-        <v>2026-08-04T05:27:20.281Z</v>
+        <v>2026-08-04T08:17:41.809Z</v>
       </c>
     </row>
     <row r="34">
@@ -13581,7 +13671,7 @@
         <v>[]</v>
       </c>
       <c r="AH34" t="str">
-        <v>2026-08-04T05:27:20.281Z</v>
+        <v>2026-08-04T08:17:41.809Z</v>
       </c>
     </row>
     <row r="35">
@@ -13676,7 +13766,7 @@
         <v>true</v>
       </c>
       <c r="AH35" t="str">
-        <v>2026-08-04T05:27:20.281Z</v>
+        <v>2026-08-04T08:17:41.809Z</v>
       </c>
     </row>
     <row r="36">
@@ -13780,7 +13870,7 @@
         <v>[]</v>
       </c>
       <c r="AH36" t="str">
-        <v>2026-08-04T05:27:20.281Z</v>
+        <v>2026-08-04T08:17:41.809Z</v>
       </c>
     </row>
     <row r="37">
@@ -13875,7 +13965,7 @@
         <v>true</v>
       </c>
       <c r="AH37" t="str">
-        <v>2026-08-04T05:27:20.281Z</v>
+        <v>2026-08-04T08:17:41.809Z</v>
       </c>
     </row>
     <row r="38">
@@ -13979,7 +14069,7 @@
         <v>[]</v>
       </c>
       <c r="AH38" t="str">
-        <v>2026-08-04T05:27:20.281Z</v>
+        <v>2026-08-04T08:17:41.809Z</v>
       </c>
     </row>
     <row r="39">
@@ -14083,7 +14173,7 @@
         <v>[]</v>
       </c>
       <c r="AH39" t="str">
-        <v>2026-08-04T05:27:20.281Z</v>
+        <v>2026-08-04T08:17:41.809Z</v>
       </c>
     </row>
     <row r="40">
@@ -14187,7 +14277,7 @@
         <v>[]</v>
       </c>
       <c r="AH40" t="str">
-        <v>2026-08-04T05:27:20.281Z</v>
+        <v>2026-08-04T08:17:41.809Z</v>
       </c>
     </row>
     <row r="41">
@@ -14291,7 +14381,7 @@
         <v>[]</v>
       </c>
       <c r="AH41" t="str">
-        <v>2026-08-04T05:27:20.281Z</v>
+        <v>2026-08-04T08:17:41.809Z</v>
       </c>
     </row>
     <row r="42">
@@ -14386,7 +14476,7 @@
         <v>true</v>
       </c>
       <c r="AH42" t="str">
-        <v>2026-08-04T05:27:20.281Z</v>
+        <v>2026-08-04T08:17:41.809Z</v>
       </c>
     </row>
     <row r="43">
@@ -14490,7 +14580,7 @@
         <v>[]</v>
       </c>
       <c r="AH43" t="str">
-        <v>2026-08-04T05:27:20.281Z</v>
+        <v>2026-08-04T08:17:41.809Z</v>
       </c>
     </row>
     <row r="44">
@@ -14594,7 +14684,7 @@
         <v>[]</v>
       </c>
       <c r="AH44" t="str">
-        <v>2026-08-04T05:27:20.281Z</v>
+        <v>2026-08-04T08:17:41.809Z</v>
       </c>
     </row>
     <row r="45">
@@ -14698,7 +14788,7 @@
         <v>[]</v>
       </c>
       <c r="AH45" t="str">
-        <v>2026-08-04T05:27:20.281Z</v>
+        <v>2026-08-04T08:17:41.809Z</v>
       </c>
     </row>
     <row r="46">
@@ -14802,7 +14892,7 @@
         <v>[]</v>
       </c>
       <c r="AH46" t="str">
-        <v>2026-08-04T05:27:20.281Z</v>
+        <v>2026-08-04T08:17:41.809Z</v>
       </c>
     </row>
     <row r="47">
@@ -14906,7 +14996,7 @@
         <v>[]</v>
       </c>
       <c r="AH47" t="str">
-        <v>2026-08-04T05:27:20.281Z</v>
+        <v>2026-08-04T08:17:41.809Z</v>
       </c>
       <c r="AI47" t="str">
         <v/>
@@ -15019,7 +15109,7 @@
         <v>[]</v>
       </c>
       <c r="AH48" t="str">
-        <v>2026-08-04T05:27:20.281Z</v>
+        <v>2026-08-04T08:17:41.809Z</v>
       </c>
       <c r="AI48" t="str">
         <v/>
@@ -15132,7 +15222,7 @@
         <v>[]</v>
       </c>
       <c r="AH49" t="str">
-        <v>2026-08-04T05:27:20.281Z</v>
+        <v>2026-08-04T08:17:41.809Z</v>
       </c>
       <c r="AI49" t="str">
         <v/>
@@ -15245,7 +15335,7 @@
         <v>[]</v>
       </c>
       <c r="AH50" t="str">
-        <v>2026-08-04T05:27:20.281Z</v>
+        <v>2026-08-04T08:17:41.809Z</v>
       </c>
       <c r="AI50" t="str">
         <v/>
@@ -15358,7 +15448,7 @@
         <v>[]</v>
       </c>
       <c r="AH51" t="str">
-        <v>2026-08-04T05:27:20.281Z</v>
+        <v>2026-08-04T08:17:41.809Z</v>
       </c>
       <c r="AI51" t="str">
         <v/>
@@ -15462,7 +15552,7 @@
         <v>false</v>
       </c>
       <c r="AH52" t="str">
-        <v>2026-08-04T05:27:20.281Z</v>
+        <v>2026-08-04T08:17:41.809Z</v>
       </c>
       <c r="AI52" t="str">
         <v/>
@@ -15566,7 +15656,7 @@
         <v>false</v>
       </c>
       <c r="AH53" t="str">
-        <v>2026-08-04T05:27:20.281Z</v>
+        <v>2026-08-04T08:17:41.809Z</v>
       </c>
       <c r="AI53" t="str">
         <v/>
@@ -15670,7 +15760,7 @@
         <v>false</v>
       </c>
       <c r="AH54" t="str">
-        <v>2026-08-04T05:27:20.281Z</v>
+        <v>2026-08-04T08:17:41.810Z</v>
       </c>
       <c r="AI54" t="str">
         <v/>
@@ -15774,7 +15864,7 @@
         <v>false</v>
       </c>
       <c r="AH55" t="str">
-        <v>2026-08-04T05:27:20.281Z</v>
+        <v>2026-08-04T08:17:41.810Z</v>
       </c>
       <c r="AI55" t="str">
         <v/>
@@ -15878,7 +15968,7 @@
         <v>false</v>
       </c>
       <c r="AH56" t="str">
-        <v>2026-08-04T05:27:20.281Z</v>
+        <v>2026-08-04T08:17:41.810Z</v>
       </c>
       <c r="AI56" t="str">
         <v/>
@@ -15982,7 +16072,7 @@
         <v>false</v>
       </c>
       <c r="AH57" t="str">
-        <v>2026-08-04T05:27:20.281Z</v>
+        <v>2026-08-04T08:17:41.810Z</v>
       </c>
       <c r="AI57" t="str">
         <v/>
@@ -16086,7 +16176,7 @@
         <v>false</v>
       </c>
       <c r="AH58" t="str">
-        <v>2026-08-04T05:27:20.282Z</v>
+        <v>2026-08-04T08:17:41.810Z</v>
       </c>
       <c r="AI58" t="str">
         <v/>
@@ -16190,7 +16280,7 @@
         <v>false</v>
       </c>
       <c r="AH59" t="str">
-        <v>2026-08-04T05:27:20.282Z</v>
+        <v>2026-08-04T08:17:41.810Z</v>
       </c>
       <c r="AI59" t="str">
         <v/>
@@ -16294,7 +16384,7 @@
         <v>false</v>
       </c>
       <c r="AH60" t="str">
-        <v>2026-08-04T05:27:20.282Z</v>
+        <v>2026-08-04T08:17:41.810Z</v>
       </c>
       <c r="AI60" t="str">
         <v/>
@@ -16398,7 +16488,7 @@
         <v>false</v>
       </c>
       <c r="AH61" t="str">
-        <v>2026-08-04T05:27:20.282Z</v>
+        <v>2026-08-04T08:17:41.810Z</v>
       </c>
       <c r="AI61" t="str">
         <v/>
@@ -16502,7 +16592,7 @@
         <v>[]</v>
       </c>
       <c r="AH62" t="str">
-        <v>2026-08-04T05:27:20.282Z</v>
+        <v>2026-08-04T08:17:41.810Z</v>
       </c>
       <c r="AI62" t="str">
         <v/>
@@ -16609,7 +16699,7 @@
         <v>false</v>
       </c>
       <c r="AH63" t="str">
-        <v>2026-08-04T05:27:20.282Z</v>
+        <v>2026-08-04T08:17:41.810Z</v>
       </c>
       <c r="AI63" t="str">
         <v/>
@@ -16713,7 +16803,7 @@
         <v>false</v>
       </c>
       <c r="AH64" t="str">
-        <v>2026-08-04T05:27:20.282Z</v>
+        <v>2026-08-04T08:17:41.810Z</v>
       </c>
       <c r="AI64" t="str">
         <v/>
@@ -16817,7 +16907,7 @@
         <v>false</v>
       </c>
       <c r="AH65" t="str">
-        <v>2026-08-04T05:27:20.282Z</v>
+        <v>2026-08-04T08:17:41.810Z</v>
       </c>
       <c r="AI65" t="str">
         <v/>
@@ -16912,7 +17002,7 @@
         <v>chocolates/wwosfnmcbprgc1pawgbe</v>
       </c>
       <c r="AH66" t="str">
-        <v>2026-08-04T05:27:20.282Z</v>
+        <v>2026-08-04T08:17:41.810Z</v>
       </c>
       <c r="AI66" t="str">
         <v/>
@@ -17016,7 +17106,7 @@
         <v>[]</v>
       </c>
       <c r="AH67" t="str">
-        <v>2026-08-04T05:27:20.282Z</v>
+        <v>2026-08-04T08:17:41.810Z</v>
       </c>
       <c r="AI67" t="str">
         <v/>
@@ -17123,7 +17213,7 @@
         <v>[]</v>
       </c>
       <c r="AH68" t="str">
-        <v>2026-08-04T05:27:20.282Z</v>
+        <v>2026-08-04T08:17:41.810Z</v>
       </c>
       <c r="AI68" t="str">
         <v/>
@@ -17230,7 +17320,7 @@
         <v>[]</v>
       </c>
       <c r="AH69" t="str">
-        <v>2026-08-04T05:27:20.282Z</v>
+        <v>2026-08-04T08:17:41.810Z</v>
       </c>
       <c r="AI69" t="str">
         <v/>
@@ -17337,7 +17427,7 @@
         <v>false</v>
       </c>
       <c r="AH70" t="str">
-        <v>2026-08-04T05:27:20.282Z</v>
+        <v>2026-08-04T08:17:41.810Z</v>
       </c>
       <c r="AI70" t="str">
         <v/>
@@ -17435,7 +17525,7 @@
         <v>false</v>
       </c>
       <c r="AH71" t="str">
-        <v>2026-08-04T05:27:20.282Z</v>
+        <v>2026-08-04T08:17:41.810Z</v>
       </c>
       <c r="AI71" t="str">
         <v/>
@@ -17533,7 +17623,7 @@
         <v>false</v>
       </c>
       <c r="AH72" t="str">
-        <v>2026-08-04T05:27:20.282Z</v>
+        <v>2026-08-04T08:17:41.810Z</v>
       </c>
       <c r="AI72" t="str">
         <v/>
@@ -17631,7 +17721,7 @@
         <v>false</v>
       </c>
       <c r="AH73" t="str">
-        <v>2026-08-04T05:27:20.282Z</v>
+        <v>2026-08-04T08:17:41.810Z</v>
       </c>
       <c r="AI73" t="str">
         <v/>
@@ -17729,7 +17819,7 @@
         <v>false</v>
       </c>
       <c r="AH74" t="str">
-        <v>2026-08-04T05:27:20.282Z</v>
+        <v>2026-08-04T08:17:41.810Z</v>
       </c>
       <c r="AI74" t="str">
         <v/>
@@ -17827,7 +17917,7 @@
         <v>false</v>
       </c>
       <c r="AH75" t="str">
-        <v>2026-08-04T05:27:20.282Z</v>
+        <v>2026-08-04T08:17:41.810Z</v>
       </c>
       <c r="AI75" t="str">
         <v/>
@@ -17925,7 +18015,7 @@
         <v>false</v>
       </c>
       <c r="AH76" t="str">
-        <v>2026-08-04T05:27:20.282Z</v>
+        <v>2026-08-04T08:17:41.810Z</v>
       </c>
       <c r="AI76" t="str">
         <v/>
@@ -18023,7 +18113,7 @@
         <v>false</v>
       </c>
       <c r="AH77" t="str">
-        <v>2026-08-04T05:27:20.282Z</v>
+        <v>2026-08-04T08:17:41.810Z</v>
       </c>
       <c r="AI77" t="str">
         <v/>
@@ -18121,7 +18211,7 @@
         <v>false</v>
       </c>
       <c r="AH78" t="str">
-        <v>2026-08-04T05:27:20.282Z</v>
+        <v>2026-08-04T08:17:41.810Z</v>
       </c>
       <c r="AI78" t="str">
         <v/>
@@ -18234,7 +18324,7 @@
         <v>[]</v>
       </c>
       <c r="AH79" t="str">
-        <v>2026-08-04T05:27:20.282Z</v>
+        <v>2026-08-04T08:17:41.810Z</v>
       </c>
       <c r="AI79" t="str">
         <v/>
@@ -18347,7 +18437,7 @@
         <v>[]</v>
       </c>
       <c r="AH80" t="str">
-        <v>2026-08-04T05:27:20.282Z</v>
+        <v>2026-08-04T08:17:41.810Z</v>
       </c>
       <c r="AI80" t="str">
         <v/>
@@ -18460,7 +18550,7 @@
         <v>[]</v>
       </c>
       <c r="AH81" t="str">
-        <v>2026-08-04T05:27:20.282Z</v>
+        <v>2026-08-04T08:17:41.810Z</v>
       </c>
       <c r="AI81" t="str">
         <v/>
@@ -18573,7 +18663,7 @@
         <v>[]</v>
       </c>
       <c r="AH82" t="str">
-        <v>2026-08-04T05:27:20.282Z</v>
+        <v>2026-08-04T08:17:41.810Z</v>
       </c>
       <c r="AI82" t="str">
         <v/>
@@ -18686,7 +18776,7 @@
         <v>[]</v>
       </c>
       <c r="AH83" t="str">
-        <v>2026-08-04T05:27:20.282Z</v>
+        <v>2026-08-04T08:17:41.810Z</v>
       </c>
       <c r="AI83" t="str">
         <v/>
@@ -18790,7 +18880,7 @@
         <v>false</v>
       </c>
       <c r="AH84" t="str">
-        <v>2026-08-04T05:27:20.282Z</v>
+        <v>2026-08-04T08:17:41.810Z</v>
       </c>
       <c r="AI84" t="str">
         <v/>
@@ -18894,7 +18984,7 @@
         <v>false</v>
       </c>
       <c r="AH85" t="str">
-        <v>2026-08-04T05:27:20.282Z</v>
+        <v>2026-08-04T08:17:41.810Z</v>
       </c>
       <c r="AI85" t="str">
         <v/>
@@ -18998,7 +19088,7 @@
         <v>false</v>
       </c>
       <c r="AH86" t="str">
-        <v>2026-08-04T05:27:20.282Z</v>
+        <v>2026-08-04T08:17:41.810Z</v>
       </c>
       <c r="AI86" t="str">
         <v/>
@@ -19111,7 +19201,7 @@
         <v>[]</v>
       </c>
       <c r="AH87" t="str">
-        <v>2026-08-04T05:27:20.282Z</v>
+        <v>2026-08-04T08:17:41.810Z</v>
       </c>
       <c r="AI87" t="str">
         <v/>
@@ -19215,7 +19305,7 @@
         <v>false</v>
       </c>
       <c r="AH88" t="str">
-        <v>2026-08-04T05:27:20.282Z</v>
+        <v>2026-08-04T08:17:41.810Z</v>
       </c>
       <c r="AI88" t="str">
         <v/>
@@ -19328,7 +19418,7 @@
         <v>[]</v>
       </c>
       <c r="AH89" t="str">
-        <v>2026-08-04T05:27:20.282Z</v>
+        <v>2026-08-04T08:17:41.810Z</v>
       </c>
       <c r="AI89" t="str">
         <v/>
@@ -19441,7 +19531,7 @@
         <v>[]</v>
       </c>
       <c r="AH90" t="str">
-        <v>2026-08-04T05:27:20.282Z</v>
+        <v>2026-08-04T08:17:41.810Z</v>
       </c>
       <c r="AI90" t="str">
         <v/>
@@ -19554,7 +19644,7 @@
         <v>[]</v>
       </c>
       <c r="AH91" t="str">
-        <v>2026-08-04T05:27:20.282Z</v>
+        <v>2026-08-04T08:17:41.810Z</v>
       </c>
       <c r="AI91" t="str">
         <v/>
@@ -19658,7 +19748,7 @@
         <v>false</v>
       </c>
       <c r="AH92" t="str">
-        <v>2026-08-04T05:27:20.282Z</v>
+        <v>2026-08-04T08:17:41.810Z</v>
       </c>
       <c r="AI92" t="str">
         <v/>
@@ -19762,7 +19852,7 @@
         <v>false</v>
       </c>
       <c r="AH93" t="str">
-        <v>2026-08-04T05:27:20.283Z</v>
+        <v>2026-08-04T08:17:41.811Z</v>
       </c>
       <c r="AI93" t="str">
         <v/>
@@ -19866,7 +19956,7 @@
         <v>false</v>
       </c>
       <c r="AH94" t="str">
-        <v>2026-08-04T05:27:20.283Z</v>
+        <v>2026-08-04T08:17:41.811Z</v>
       </c>
       <c r="AI94" t="str">
         <v/>
@@ -19970,7 +20060,7 @@
         <v>false</v>
       </c>
       <c r="AH95" t="str">
-        <v>2026-08-04T05:27:20.283Z</v>
+        <v>2026-08-04T08:17:41.811Z</v>
       </c>
       <c r="AI95" t="str">
         <v/>
@@ -20074,7 +20164,7 @@
         <v>false</v>
       </c>
       <c r="AH96" t="str">
-        <v>2026-08-04T05:27:20.283Z</v>
+        <v>2026-08-04T08:17:41.811Z</v>
       </c>
       <c r="AI96" t="str">
         <v/>
@@ -20178,7 +20268,7 @@
         <v>false</v>
       </c>
       <c r="AH97" t="str">
-        <v>2026-08-04T05:27:20.283Z</v>
+        <v>2026-08-04T08:17:41.811Z</v>
       </c>
       <c r="AI97" t="str">
         <v/>
@@ -20282,7 +20372,7 @@
         <v>false</v>
       </c>
       <c r="AH98" t="str">
-        <v>2026-08-04T05:27:20.283Z</v>
+        <v>2026-08-04T08:17:41.811Z</v>
       </c>
       <c r="AI98" t="str">
         <v/>
@@ -20386,7 +20476,7 @@
         <v>false</v>
       </c>
       <c r="AH99" t="str">
-        <v>2026-08-04T05:27:20.283Z</v>
+        <v>2026-08-04T08:17:41.811Z</v>
       </c>
       <c r="AI99" t="str">
         <v/>
@@ -20490,7 +20580,7 @@
         <v>false</v>
       </c>
       <c r="AH100" t="str">
-        <v>2026-08-04T05:27:20.283Z</v>
+        <v>2026-08-04T08:17:41.811Z</v>
       </c>
       <c r="AI100" t="str">
         <v/>
@@ -20603,7 +20693,7 @@
         <v>[]</v>
       </c>
       <c r="AH101" t="str">
-        <v>2026-08-04T05:27:20.283Z</v>
+        <v>2026-08-04T08:17:41.811Z</v>
       </c>
       <c r="AI101" t="str">
         <v/>
@@ -20707,7 +20797,7 @@
         <v>false</v>
       </c>
       <c r="AH102" t="str">
-        <v>2026-08-04T05:27:20.283Z</v>
+        <v>2026-08-04T08:17:41.811Z</v>
       </c>
       <c r="AI102" t="str">
         <v/>
@@ -20820,7 +20910,7 @@
         <v>[]</v>
       </c>
       <c r="AH103" t="str">
-        <v>2026-08-04T05:27:20.283Z</v>
+        <v>2026-08-04T08:17:41.811Z</v>
       </c>
       <c r="AI103" t="str">
         <v/>
@@ -20933,7 +21023,7 @@
         <v>[]</v>
       </c>
       <c r="AH104" t="str">
-        <v>2026-08-04T05:27:20.283Z</v>
+        <v>2026-08-04T08:17:41.811Z</v>
       </c>
       <c r="AI104" t="str">
         <v/>
@@ -21046,7 +21136,7 @@
         <v>[]</v>
       </c>
       <c r="AH105" t="str">
-        <v>2026-08-04T05:27:20.283Z</v>
+        <v>2026-08-04T08:17:41.811Z</v>
       </c>
       <c r="AI105" t="str">
         <v/>
@@ -21162,7 +21252,7 @@
         <v>[]</v>
       </c>
       <c r="AH106" t="str">
-        <v>2026-08-04T05:27:20.283Z</v>
+        <v>2026-08-04T08:17:41.811Z</v>
       </c>
       <c r="AI106" t="str">
         <v/>
@@ -21183,7 +21273,7 @@
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:AA15"/>
+  <dimension ref="A1:AA18"/>
   <cols>
     <col min="1" max="1" width="26.83203125" customWidth="1"/>
     <col min="2" max="2" width="26.83203125" customWidth="1"/>
@@ -21354,7 +21444,7 @@
         <v>2026-08-03T08:32:20.631Z</v>
       </c>
       <c r="U2" t="str">
-        <v>2026-08-04T05:27:20.391Z</v>
+        <v>2026-08-04T08:17:41.920Z</v>
       </c>
     </row>
     <row r="3" xml:space="preserve">
@@ -21420,7 +21510,7 @@
         <v>2026-08-03T11:31:03.986Z</v>
       </c>
       <c r="U3" t="str">
-        <v>2026-08-04T05:27:20.391Z</v>
+        <v>2026-08-04T08:17:41.920Z</v>
       </c>
     </row>
     <row r="4" xml:space="preserve">
@@ -21486,7 +21576,7 @@
         <v>2026-08-03T11:42:37.879Z</v>
       </c>
       <c r="U4" t="str">
-        <v>2026-08-04T05:27:20.391Z</v>
+        <v>2026-08-04T08:17:41.920Z</v>
       </c>
     </row>
     <row r="5" xml:space="preserve">
@@ -21552,7 +21642,7 @@
         <v>2026-08-04T02:54:51.282Z</v>
       </c>
       <c r="U5" t="str">
-        <v>2026-08-04T05:27:20.391Z</v>
+        <v>2026-08-04T08:17:41.920Z</v>
       </c>
     </row>
     <row r="6" xml:space="preserve">
@@ -21618,7 +21708,7 @@
         <v>2026-08-04T02:54:51.524Z</v>
       </c>
       <c r="U6" t="str">
-        <v>2026-08-04T05:27:20.391Z</v>
+        <v>2026-08-04T08:17:41.920Z</v>
       </c>
     </row>
     <row r="7" xml:space="preserve">
@@ -21684,7 +21774,7 @@
         <v>2026-08-04T02:56:57.266Z</v>
       </c>
       <c r="U7" t="str">
-        <v>2026-08-04T05:27:20.391Z</v>
+        <v>2026-08-04T08:17:41.920Z</v>
       </c>
     </row>
     <row r="8" xml:space="preserve">
@@ -21750,7 +21840,7 @@
         <v>2026-08-04T02:56:57.503Z</v>
       </c>
       <c r="U8" t="str">
-        <v>2026-08-04T05:27:20.391Z</v>
+        <v>2026-08-04T08:17:41.920Z</v>
       </c>
     </row>
     <row r="9" xml:space="preserve">
@@ -21816,7 +21906,7 @@
         <v>2026-08-04T02:58:17.874Z</v>
       </c>
       <c r="U9" t="str">
-        <v>2026-08-04T05:27:20.391Z</v>
+        <v>2026-08-04T08:17:41.920Z</v>
       </c>
     </row>
     <row r="10" xml:space="preserve">
@@ -21882,7 +21972,7 @@
         <v>2026-08-04T02:58:18.111Z</v>
       </c>
       <c r="U10" t="str">
-        <v>2026-08-04T05:27:20.392Z</v>
+        <v>2026-08-04T08:17:41.920Z</v>
       </c>
     </row>
     <row r="11">
@@ -21944,7 +22034,7 @@
         <v>2026-08-04T03:07:52.920Z</v>
       </c>
       <c r="U11" t="str">
-        <v>2026-08-04T05:27:20.392Z</v>
+        <v>2026-08-04T08:17:41.920Z</v>
       </c>
       <c r="V11" t="str">
         <v>6a7157484aac857cdce15f55</v>
@@ -22014,7 +22104,7 @@
         <v>2026-08-04T03:08:27.149Z</v>
       </c>
       <c r="U12" t="str">
-        <v>2026-08-04T05:27:20.392Z</v>
+        <v>2026-08-04T08:17:41.920Z</v>
       </c>
       <c r="V12" t="str">
         <v>6a7157484aac857cdce15f55</v>
@@ -22099,7 +22189,7 @@
         <v>2026-08-04T03:08:27.398Z</v>
       </c>
       <c r="U13" t="str">
-        <v>2026-08-04T05:27:20.392Z</v>
+        <v>2026-08-04T08:17:41.921Z</v>
       </c>
       <c r="V13" t="str">
         <v>6a7157484aac857cdce15f55</v>
@@ -22183,7 +22273,7 @@
         <v>2026-08-04T04:15:57.196Z</v>
       </c>
       <c r="U14" t="str">
-        <v>2026-08-04T05:27:20.392Z</v>
+        <v>2026-08-04T08:17:41.921Z</v>
       </c>
     </row>
     <row r="15" xml:space="preserve">
@@ -22249,12 +22339,247 @@
         <v>2026-08-04T04:15:57.434Z</v>
       </c>
       <c r="U15" t="str">
-        <v>2026-08-04T05:27:20.392Z</v>
+        <v>2026-08-04T08:17:41.921Z</v>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" t="str">
+        <v>6a718ce1f0f91c3459f1508d</v>
+      </c>
+      <c r="B16" t="str">
+        <v>6a718cc0f0f91c3459f15086</v>
+      </c>
+      <c r="C16" t="str">
+        <v>6a707e784aac857cdce1455f</v>
+      </c>
+      <c r="D16" t="str">
+        <v>user</v>
+      </c>
+      <c r="E16" t="str">
+        <v>Payment Failed 🔴</v>
+      </c>
+      <c r="F16" t="str">
+        <v>payment_failed</v>
+      </c>
+      <c r="G16" t="str">
+        <v>WEB</v>
+      </c>
+      <c r="H16" t="str">
+        <v>Your payment of ₹740 for order #TCM-2026-0004 failed. Please retry.</v>
+      </c>
+      <c r="I16" t="str">
+        <v>payment_failed</v>
+      </c>
+      <c r="K16" t="str">
+        <v>/account/orders/6a718cc0f0f91c3459f15086</v>
+      </c>
+      <c r="L16" t="str">
+        <v>false</v>
+      </c>
+      <c r="M16" t="str">
+        <v>SENT</v>
+      </c>
+      <c r="N16" t="str">
+        <v>true</v>
+      </c>
+      <c r="O16" t="str">
+        <v>false</v>
+      </c>
+      <c r="P16" t="str">
+        <v>false</v>
+      </c>
+      <c r="Q16" t="str">
+        <v>false</v>
+      </c>
+      <c r="R16" t="str">
+        <v>2026-08-04T06:55:29.223Z</v>
+      </c>
+      <c r="S16" t="str">
+        <v>2026-08-04T06:55:29.223Z</v>
+      </c>
+      <c r="T16" t="str">
+        <v>2026-08-04T06:55:29.223Z</v>
+      </c>
+      <c r="U16" t="str">
+        <v>2026-08-04T08:17:41.921Z</v>
+      </c>
+      <c r="V16" t="str">
+        <v>6a718cc0f0f91c3459f15086</v>
+      </c>
+    </row>
+    <row r="17" xml:space="preserve">
+      <c r="A17" t="str">
+        <v>6a718d05f0f91c3459f1508f</v>
+      </c>
+      <c r="B17" t="str">
+        <v>6a718cc0f0f91c3459f15086</v>
+      </c>
+      <c r="C17" t="str">
+        <v>69e9c1ab766ae41a5f9612cd</v>
+      </c>
+      <c r="D17" t="str">
+        <v>admin</v>
+      </c>
+      <c r="E17" t="str">
+        <v>⚠️ Payment Failed</v>
+      </c>
+      <c r="F17" t="str">
+        <v>admin_payment_failed</v>
+      </c>
+      <c r="G17" t="str">
+        <v>WEB</v>
+      </c>
+      <c r="H17" t="str" xml:space="preserve">
+        <v xml:space="preserve">Order #TCM-2026-0004 payment failed.
+Reason: User closed payment window before completion.
+Customer: Ak webflair technologies
+Phone: 9600732162
+Email: akwebflairtechnologies@gmail.com
+Amount: ₹740</v>
+      </c>
+      <c r="I17" t="str">
+        <v>admin_payment_failed</v>
+      </c>
+      <c r="K17" t="str">
+        <v>/admin/orders</v>
+      </c>
+      <c r="L17" t="str">
+        <v>false</v>
+      </c>
+      <c r="M17" t="str">
+        <v>SENT</v>
+      </c>
+      <c r="N17" t="str">
+        <v>true</v>
+      </c>
+      <c r="O17" t="str">
+        <v>false</v>
+      </c>
+      <c r="P17" t="str">
+        <v>false</v>
+      </c>
+      <c r="Q17" t="str">
+        <v>false</v>
+      </c>
+      <c r="R17" t="str">
+        <v>2026-08-04T06:56:05.002Z</v>
+      </c>
+      <c r="S17" t="str">
+        <v>2026-08-04T06:56:05.002Z</v>
+      </c>
+      <c r="T17" t="str">
+        <v>2026-08-04T06:56:05.002Z</v>
+      </c>
+      <c r="U17" t="str">
+        <v>2026-08-04T08:17:41.921Z</v>
+      </c>
+      <c r="V17" t="str">
+        <v>6a718cc0f0f91c3459f15086</v>
+      </c>
+      <c r="W17" t="str">
+        <v>6a707e784aac857cdce1455f</v>
+      </c>
+      <c r="X17" t="str">
+        <v>9600732162</v>
+      </c>
+      <c r="Y17" t="str">
+        <v>akwebflairtechnologies@gmail.com</v>
+      </c>
+      <c r="Z17" t="str">
+        <v>User closed payment window before completion.</v>
+      </c>
+      <c r="AA17" t="str">
+        <v>740</v>
+      </c>
+    </row>
+    <row r="18" xml:space="preserve">
+      <c r="A18" t="str">
+        <v>6a718d05f0f91c3459f15090</v>
+      </c>
+      <c r="B18" t="str">
+        <v>6a718cc0f0f91c3459f15086</v>
+      </c>
+      <c r="C18" t="str">
+        <v>6a69fbf4706daeab212127e9</v>
+      </c>
+      <c r="D18" t="str">
+        <v>admin</v>
+      </c>
+      <c r="E18" t="str">
+        <v>⚠️ Payment Failed</v>
+      </c>
+      <c r="F18" t="str">
+        <v>admin_payment_failed</v>
+      </c>
+      <c r="G18" t="str">
+        <v>WEB</v>
+      </c>
+      <c r="H18" t="str" xml:space="preserve">
+        <v xml:space="preserve">Order #TCM-2026-0004 payment failed.
+Reason: User closed payment window before completion.
+Customer: Ak webflair technologies
+Phone: 9600732162
+Email: akwebflairtechnologies@gmail.com
+Amount: ₹740</v>
+      </c>
+      <c r="I18" t="str">
+        <v>admin_payment_failed</v>
+      </c>
+      <c r="K18" t="str">
+        <v>/admin/orders</v>
+      </c>
+      <c r="L18" t="str">
+        <v>false</v>
+      </c>
+      <c r="M18" t="str">
+        <v>SENT</v>
+      </c>
+      <c r="N18" t="str">
+        <v>true</v>
+      </c>
+      <c r="O18" t="str">
+        <v>false</v>
+      </c>
+      <c r="P18" t="str">
+        <v>false</v>
+      </c>
+      <c r="Q18" t="str">
+        <v>false</v>
+      </c>
+      <c r="R18" t="str">
+        <v>2026-08-04T06:56:05.251Z</v>
+      </c>
+      <c r="S18" t="str">
+        <v>2026-08-04T06:56:05.252Z</v>
+      </c>
+      <c r="T18" t="str">
+        <v>2026-08-04T06:56:05.252Z</v>
+      </c>
+      <c r="U18" t="str">
+        <v>2026-08-04T08:17:41.921Z</v>
+      </c>
+      <c r="V18" t="str">
+        <v>6a718cc0f0f91c3459f15086</v>
+      </c>
+      <c r="W18" t="str">
+        <v>6a707e784aac857cdce1455f</v>
+      </c>
+      <c r="X18" t="str">
+        <v>9600732162</v>
+      </c>
+      <c r="Y18" t="str">
+        <v>akwebflairtechnologies@gmail.com</v>
+      </c>
+      <c r="Z18" t="str">
+        <v>User closed payment window before completion.</v>
+      </c>
+      <c r="AA18" t="str">
+        <v>740</v>
       </c>
     </row>
   </sheetData>
   <ignoredErrors>
-    <ignoredError numberStoredAsText="1" sqref="A1:AA15"/>
+    <ignoredError numberStoredAsText="1" sqref="A1:AA18"/>
   </ignoredErrors>
 </worksheet>
 </file>
@@ -22404,7 +22729,7 @@
         <v>2026-07-24T16:56:36.026Z</v>
       </c>
       <c r="R2" t="str">
-        <v>2026-08-04T05:27:21.180Z</v>
+        <v>2026-08-04T08:17:43.779Z</v>
       </c>
     </row>
     <row r="3">
@@ -22460,7 +22785,7 @@
         <v>2026-07-28T17:39:40.124Z</v>
       </c>
       <c r="R3" t="str">
-        <v>2026-08-04T05:27:21.180Z</v>
+        <v>2026-08-04T08:17:43.780Z</v>
       </c>
       <c r="S3" t="str">
         <v>[]</v>
@@ -22528,7 +22853,7 @@
         <v>2026-07-28T17:42:45.014Z</v>
       </c>
       <c r="R4" t="str">
-        <v>2026-08-04T05:27:21.181Z</v>
+        <v>2026-08-04T08:17:43.780Z</v>
       </c>
       <c r="S4" t="str">
         <v>[]</v>
@@ -22596,7 +22921,7 @@
         <v>2026-07-28T17:35:21.654Z</v>
       </c>
       <c r="R5" t="str">
-        <v>2026-08-04T05:27:21.181Z</v>
+        <v>2026-08-04T08:17:43.781Z</v>
       </c>
       <c r="S5" t="str">
         <v>[]</v>
@@ -22664,7 +22989,7 @@
         <v>2026-07-28T17:30:16.981Z</v>
       </c>
       <c r="R6" t="str">
-        <v>2026-08-04T05:27:21.181Z</v>
+        <v>2026-08-04T08:17:43.781Z</v>
       </c>
       <c r="S6" t="str">
         <v>[]</v>
@@ -22732,7 +23057,7 @@
         <v>2026-08-02T10:49:00.973Z</v>
       </c>
       <c r="R7" t="str">
-        <v>2026-08-04T05:27:21.182Z</v>
+        <v>2026-08-04T08:17:43.781Z</v>
       </c>
       <c r="S7" t="str">
         <v>[]</v>
@@ -22800,7 +23125,7 @@
         <v>2026-07-26T18:00:06.903Z</v>
       </c>
       <c r="R8" t="str">
-        <v>2026-08-04T05:27:21.182Z</v>
+        <v>2026-08-04T08:17:43.782Z</v>
       </c>
     </row>
     <row r="9">
@@ -22856,7 +23181,7 @@
         <v>2026-07-28T17:37:46.453Z</v>
       </c>
       <c r="R9" t="str">
-        <v>2026-08-04T05:27:21.182Z</v>
+        <v>2026-08-04T08:17:43.782Z</v>
       </c>
       <c r="S9" t="str">
         <v>[]</v>
@@ -22924,7 +23249,7 @@
         <v>2026-07-28T15:52:28.248Z</v>
       </c>
       <c r="R10" t="str">
-        <v>2026-08-04T05:27:21.183Z</v>
+        <v>2026-08-04T08:17:43.782Z</v>
       </c>
       <c r="S10" t="str">
         <v>[]</v>
@@ -22992,7 +23317,7 @@
         <v>2026-07-28T17:48:40.457Z</v>
       </c>
       <c r="R11" t="str">
-        <v>2026-08-04T05:27:21.183Z</v>
+        <v>2026-08-04T08:17:43.782Z</v>
       </c>
       <c r="S11" t="str">
         <v>[]</v>
@@ -23060,7 +23385,7 @@
         <v>2026-07-28T17:49:54.713Z</v>
       </c>
       <c r="R12" t="str">
-        <v>2026-08-04T05:27:21.183Z</v>
+        <v>2026-08-04T08:17:43.783Z</v>
       </c>
       <c r="S12" t="str">
         <v>[]</v>
@@ -23128,7 +23453,7 @@
         <v>2026-07-28T17:34:40.195Z</v>
       </c>
       <c r="R13" t="str">
-        <v>2026-08-04T05:27:21.184Z</v>
+        <v>2026-08-04T08:17:43.783Z</v>
       </c>
       <c r="S13" t="str">
         <v>[]</v>
@@ -23196,7 +23521,7 @@
         <v>2026-07-28T16:31:18.393Z</v>
       </c>
       <c r="R14" t="str">
-        <v>2026-08-04T05:27:21.184Z</v>
+        <v>2026-08-04T08:17:43.783Z</v>
       </c>
       <c r="S14" t="str">
         <v>[]</v>
@@ -23264,7 +23589,7 @@
         <v>2026-08-03T14:35:00.987Z</v>
       </c>
       <c r="R15" t="str">
-        <v>2026-08-04T05:27:21.184Z</v>
+        <v>2026-08-04T08:17:43.783Z</v>
       </c>
       <c r="S15" t="str">
         <v>[]</v>
@@ -23332,7 +23657,7 @@
         <v>2026-07-28T16:20:47.688Z</v>
       </c>
       <c r="R16" t="str">
-        <v>2026-08-04T05:27:21.184Z</v>
+        <v>2026-08-04T08:17:43.784Z</v>
       </c>
       <c r="S16" t="str">
         <v>[]</v>
@@ -23400,7 +23725,7 @@
         <v>2026-07-24T17:04:18.204Z</v>
       </c>
       <c r="R17" t="str">
-        <v>2026-08-04T05:27:21.185Z</v>
+        <v>2026-08-04T08:17:43.784Z</v>
       </c>
     </row>
     <row r="18">
@@ -23456,7 +23781,7 @@
         <v>2026-07-24T17:04:57.812Z</v>
       </c>
       <c r="R18" t="str">
-        <v>2026-08-04T05:27:21.185Z</v>
+        <v>2026-08-04T08:17:43.784Z</v>
       </c>
     </row>
     <row r="19">
@@ -23512,7 +23837,7 @@
         <v>2026-07-28T15:06:55.169Z</v>
       </c>
       <c r="R19" t="str">
-        <v>2026-08-04T05:27:21.186Z</v>
+        <v>2026-08-04T08:17:43.784Z</v>
       </c>
       <c r="S19" t="str">
         <v>[]</v>
@@ -23580,7 +23905,7 @@
         <v>2026-08-02T10:48:10.527Z</v>
       </c>
       <c r="R20" t="str">
-        <v>2026-08-04T05:27:21.186Z</v>
+        <v>2026-08-04T08:17:43.785Z</v>
       </c>
       <c r="S20" t="str">
         <v>[]</v>
@@ -23648,7 +23973,7 @@
         <v>2026-07-24T17:12:35.802Z</v>
       </c>
       <c r="R21" t="str">
-        <v>2026-08-04T05:27:21.187Z</v>
+        <v>2026-08-04T08:17:43.785Z</v>
       </c>
     </row>
     <row r="22">
@@ -23704,7 +24029,7 @@
         <v>2026-07-28T17:26:06.217Z</v>
       </c>
       <c r="R22" t="str">
-        <v>2026-08-04T05:27:21.188Z</v>
+        <v>2026-08-04T08:17:43.785Z</v>
       </c>
       <c r="S22" t="str">
         <v>[]</v>
@@ -23779,7 +24104,7 @@
         <v>2026-07-28T17:46:53.114Z</v>
       </c>
       <c r="R23" t="str">
-        <v>2026-08-04T05:27:21.188Z</v>
+        <v>2026-08-04T08:17:43.786Z</v>
       </c>
       <c r="S23" t="str">
         <v>[]</v>
@@ -23847,7 +24172,7 @@
         <v>2026-07-24T17:18:21.488Z</v>
       </c>
       <c r="R24" t="str">
-        <v>2026-08-04T05:27:21.189Z</v>
+        <v>2026-08-04T08:17:43.786Z</v>
       </c>
     </row>
     <row r="25">
@@ -23903,7 +24228,7 @@
         <v>2026-07-28T17:36:56.657Z</v>
       </c>
       <c r="R25" t="str">
-        <v>2026-08-04T05:27:21.189Z</v>
+        <v>2026-08-04T08:17:43.787Z</v>
       </c>
       <c r="S25" t="str">
         <v>[]</v>
@@ -23971,7 +24296,7 @@
         <v>2026-07-28T17:41:34.056Z</v>
       </c>
       <c r="R26" t="str">
-        <v>2026-08-04T05:27:21.190Z</v>
+        <v>2026-08-04T08:17:43.787Z</v>
       </c>
       <c r="S26" t="str">
         <v>[]</v>
@@ -24039,7 +24364,7 @@
         <v>2026-07-28T17:45:36.923Z</v>
       </c>
       <c r="R27" t="str">
-        <v>2026-08-04T05:27:21.190Z</v>
+        <v>2026-08-04T08:17:43.787Z</v>
       </c>
       <c r="S27" t="str">
         <v>[]</v>
@@ -24107,7 +24432,7 @@
         <v>2026-07-28T16:21:56.496Z</v>
       </c>
       <c r="R28" t="str">
-        <v>2026-08-04T05:27:21.190Z</v>
+        <v>2026-08-04T08:17:43.787Z</v>
       </c>
       <c r="S28" t="str">
         <v>[]</v>
@@ -24175,7 +24500,7 @@
         <v>2026-08-03T14:33:55.186Z</v>
       </c>
       <c r="R29" t="str">
-        <v>2026-08-04T05:27:21.190Z</v>
+        <v>2026-08-04T08:17:43.787Z</v>
       </c>
       <c r="S29" t="str">
         <v>[]</v>
@@ -24243,7 +24568,7 @@
         <v>2026-07-28T17:38:24.726Z</v>
       </c>
       <c r="R30" t="str">
-        <v>2026-08-04T05:27:21.191Z</v>
+        <v>2026-08-04T08:17:43.788Z</v>
       </c>
       <c r="S30" t="str">
         <v>[]</v>
@@ -24311,7 +24636,7 @@
         <v>2026-07-24T17:26:49.450Z</v>
       </c>
       <c r="R31" t="str">
-        <v>2026-08-04T05:27:21.191Z</v>
+        <v>2026-08-04T08:17:43.788Z</v>
       </c>
     </row>
     <row r="32">
@@ -24367,7 +24692,7 @@
         <v>2026-07-24T17:27:41.339Z</v>
       </c>
       <c r="R32" t="str">
-        <v>2026-08-04T05:27:21.191Z</v>
+        <v>2026-08-04T08:17:43.789Z</v>
       </c>
     </row>
     <row r="33">
@@ -24423,7 +24748,7 @@
         <v>2026-07-28T17:39:19.058Z</v>
       </c>
       <c r="R33" t="str">
-        <v>2026-08-04T05:27:21.191Z</v>
+        <v>2026-08-04T08:17:43.790Z</v>
       </c>
       <c r="S33" t="str">
         <v>[]</v>
@@ -24491,7 +24816,7 @@
         <v>2026-07-24T17:30:20.928Z</v>
       </c>
       <c r="R34" t="str">
-        <v>2026-08-04T05:27:21.192Z</v>
+        <v>2026-08-04T08:17:43.790Z</v>
       </c>
     </row>
     <row r="35">
@@ -24547,7 +24872,7 @@
         <v>2026-07-28T17:36:25.555Z</v>
       </c>
       <c r="R35" t="str">
-        <v>2026-08-04T05:27:21.192Z</v>
+        <v>2026-08-04T08:17:43.790Z</v>
       </c>
       <c r="S35" t="str">
         <v>[]</v>
@@ -24615,7 +24940,7 @@
         <v>2026-07-28T17:28:41.534Z</v>
       </c>
       <c r="R36" t="str">
-        <v>2026-08-04T05:27:21.192Z</v>
+        <v>2026-08-04T08:17:43.791Z</v>
       </c>
       <c r="S36" t="str">
         <v>[]</v>
@@ -24683,7 +25008,7 @@
         <v>2026-07-28T16:23:07.254Z</v>
       </c>
       <c r="R37" t="str">
-        <v>2026-08-04T05:27:21.193Z</v>
+        <v>2026-08-04T08:17:43.793Z</v>
       </c>
       <c r="S37" t="str">
         <v>[]</v>
@@ -24751,7 +25076,7 @@
         <v>2026-07-28T17:22:37.075Z</v>
       </c>
       <c r="R38" t="str">
-        <v>2026-08-04T05:27:21.193Z</v>
+        <v>2026-08-04T08:17:43.793Z</v>
       </c>
       <c r="S38" t="str">
         <v>[]</v>
@@ -24819,7 +25144,7 @@
         <v>2026-07-24T17:34:48.053Z</v>
       </c>
       <c r="R39" t="str">
-        <v>2026-08-04T05:27:21.193Z</v>
+        <v>2026-08-04T08:17:43.793Z</v>
       </c>
     </row>
     <row r="40">
@@ -24875,7 +25200,7 @@
         <v>2026-08-03T14:31:25.470Z</v>
       </c>
       <c r="R40" t="str">
-        <v>2026-08-04T05:27:21.193Z</v>
+        <v>2026-08-04T08:17:43.793Z</v>
       </c>
       <c r="S40" t="str">
         <v>[]</v>
@@ -24943,7 +25268,7 @@
         <v>2026-08-03T14:32:38.702Z</v>
       </c>
       <c r="R41" t="str">
-        <v>2026-08-04T05:27:21.193Z</v>
+        <v>2026-08-04T08:17:43.793Z</v>
       </c>
       <c r="S41" t="str">
         <v>[]</v>
@@ -25011,7 +25336,7 @@
         <v>2026-07-24T17:37:33.123Z</v>
       </c>
       <c r="R42" t="str">
-        <v>2026-08-04T05:27:21.193Z</v>
+        <v>2026-08-04T08:17:43.794Z</v>
       </c>
     </row>
     <row r="43">
@@ -25067,7 +25392,7 @@
         <v>2026-07-24T17:38:22.625Z</v>
       </c>
       <c r="R43" t="str">
-        <v>2026-08-04T05:27:21.194Z</v>
+        <v>2026-08-04T08:17:43.794Z</v>
       </c>
     </row>
     <row r="44">
@@ -25123,7 +25448,7 @@
         <v>2026-08-03T14:28:11.191Z</v>
       </c>
       <c r="R44" t="str">
-        <v>2026-08-04T05:27:21.194Z</v>
+        <v>2026-08-04T08:17:43.794Z</v>
       </c>
       <c r="S44" t="str">
         <v>[]</v>
@@ -25191,7 +25516,7 @@
         <v>2026-07-24T17:40:00.365Z</v>
       </c>
       <c r="R45" t="str">
-        <v>2026-08-04T05:27:21.194Z</v>
+        <v>2026-08-04T08:17:43.794Z</v>
       </c>
     </row>
     <row r="46">
@@ -25247,7 +25572,7 @@
         <v>2026-07-28T16:16:46.824Z</v>
       </c>
       <c r="R46" t="str">
-        <v>2026-08-04T05:27:21.194Z</v>
+        <v>2026-08-04T08:17:43.794Z</v>
       </c>
       <c r="S46" t="str">
         <v>[]</v>
@@ -25315,7 +25640,7 @@
         <v>2026-07-24T17:41:27.886Z</v>
       </c>
       <c r="R47" t="str">
-        <v>2026-08-04T05:27:21.195Z</v>
+        <v>2026-08-04T08:17:43.795Z</v>
       </c>
     </row>
     <row r="48">
@@ -25371,7 +25696,7 @@
         <v>2026-07-24T17:42:36.169Z</v>
       </c>
       <c r="R48" t="str">
-        <v>2026-08-04T05:27:21.195Z</v>
+        <v>2026-08-04T08:17:43.795Z</v>
       </c>
     </row>
     <row r="49">
@@ -25427,7 +25752,7 @@
         <v>2026-07-28T17:45:07.109Z</v>
       </c>
       <c r="R49" t="str">
-        <v>2026-08-04T05:27:21.195Z</v>
+        <v>2026-08-04T08:17:43.795Z</v>
       </c>
       <c r="S49" t="str">
         <v>[]</v>
@@ -25495,7 +25820,7 @@
         <v>2026-07-28T16:27:55.642Z</v>
       </c>
       <c r="R50" t="str">
-        <v>2026-08-04T05:27:21.196Z</v>
+        <v>2026-08-04T08:17:43.795Z</v>
       </c>
       <c r="S50" t="str">
         <v>[]</v>
@@ -25563,7 +25888,7 @@
         <v>2026-07-28T16:36:51.938Z</v>
       </c>
       <c r="R51" t="str">
-        <v>2026-08-04T05:27:21.196Z</v>
+        <v>2026-08-04T08:17:43.796Z</v>
       </c>
       <c r="S51" t="str">
         <v>[]</v>
@@ -25631,7 +25956,7 @@
         <v>2026-07-24T17:45:28.097Z</v>
       </c>
       <c r="R52" t="str">
-        <v>2026-08-04T05:27:21.196Z</v>
+        <v>2026-08-04T08:17:43.796Z</v>
       </c>
     </row>
     <row r="53">
@@ -25687,7 +26012,7 @@
         <v>2026-07-28T17:27:31.311Z</v>
       </c>
       <c r="R53" t="str">
-        <v>2026-08-04T05:27:21.196Z</v>
+        <v>2026-08-04T08:17:43.796Z</v>
       </c>
       <c r="S53" t="str">
         <v>[]</v>
@@ -25755,7 +26080,7 @@
         <v>2026-08-03T14:19:54.310Z</v>
       </c>
       <c r="R54" t="str">
-        <v>2026-08-04T05:27:21.196Z</v>
+        <v>2026-08-04T08:17:43.796Z</v>
       </c>
       <c r="S54" t="str">
         <v>[]</v>
@@ -25823,7 +26148,7 @@
         <v>2026-07-24T17:48:00.294Z</v>
       </c>
       <c r="R55" t="str">
-        <v>2026-08-04T05:27:21.197Z</v>
+        <v>2026-08-04T08:17:43.796Z</v>
       </c>
     </row>
     <row r="56">
@@ -25879,7 +26204,7 @@
         <v>2026-07-28T17:40:11.014Z</v>
       </c>
       <c r="R56" t="str">
-        <v>2026-08-04T05:27:21.197Z</v>
+        <v>2026-08-04T08:17:43.797Z</v>
       </c>
       <c r="S56" t="str">
         <v>[]</v>
@@ -25947,7 +26272,7 @@
         <v>2026-07-24T17:54:52.356Z</v>
       </c>
       <c r="R57" t="str">
-        <v>2026-08-04T05:27:21.197Z</v>
+        <v>2026-08-04T08:17:43.797Z</v>
       </c>
     </row>
     <row r="58">
@@ -26003,7 +26328,7 @@
         <v>2026-07-24T17:56:05.755Z</v>
       </c>
       <c r="R58" t="str">
-        <v>2026-08-04T05:27:21.197Z</v>
+        <v>2026-08-04T08:17:43.797Z</v>
       </c>
     </row>
     <row r="59">
@@ -26059,7 +26384,7 @@
         <v>2026-07-28T17:47:53.747Z</v>
       </c>
       <c r="R59" t="str">
-        <v>2026-08-04T05:27:21.198Z</v>
+        <v>2026-08-04T08:17:43.797Z</v>
       </c>
       <c r="S59" t="str">
         <v>[]</v>
@@ -26127,7 +26452,7 @@
         <v>2026-07-28T16:12:36.281Z</v>
       </c>
       <c r="R60" t="str">
-        <v>2026-08-04T05:27:21.198Z</v>
+        <v>2026-08-04T08:17:43.798Z</v>
       </c>
       <c r="S60" t="str">
         <v>[{"weight":"0.5kg","price":560,"_id":"6a68d4f432f685de96f72a57"}]</v>
@@ -26195,7 +26520,7 @@
         <v>2026-07-24T18:00:08.054Z</v>
       </c>
       <c r="R61" t="str">
-        <v>2026-08-04T05:27:21.198Z</v>
+        <v>2026-08-04T08:17:43.798Z</v>
       </c>
     </row>
     <row r="62">
@@ -26251,7 +26576,7 @@
         <v>2026-07-28T17:41:55.851Z</v>
       </c>
       <c r="R62" t="str">
-        <v>2026-08-04T05:27:21.199Z</v>
+        <v>2026-08-04T08:17:43.798Z</v>
       </c>
       <c r="S62" t="str">
         <v>[]</v>
@@ -26319,7 +26644,7 @@
         <v>2026-07-24T18:06:05.196Z</v>
       </c>
       <c r="R63" t="str">
-        <v>2026-08-04T05:27:21.199Z</v>
+        <v>2026-08-04T08:17:43.798Z</v>
       </c>
     </row>
     <row r="64">
@@ -26375,7 +26700,7 @@
         <v>2026-07-28T17:40:57.835Z</v>
       </c>
       <c r="R64" t="str">
-        <v>2026-08-04T05:27:21.199Z</v>
+        <v>2026-08-04T08:17:43.798Z</v>
       </c>
       <c r="S64" t="str">
         <v>[]</v>
@@ -26443,7 +26768,7 @@
         <v>2026-07-28T17:48:30.756Z</v>
       </c>
       <c r="R65" t="str">
-        <v>2026-08-04T05:27:21.199Z</v>
+        <v>2026-08-04T08:17:43.799Z</v>
       </c>
       <c r="S65" t="str">
         <v>[]</v>
@@ -26511,7 +26836,7 @@
         <v>2026-07-28T17:22:03.434Z</v>
       </c>
       <c r="R66" t="str">
-        <v>2026-08-04T05:27:21.200Z</v>
+        <v>2026-08-04T08:17:43.799Z</v>
       </c>
       <c r="S66" t="str">
         <v>[]</v>
@@ -26579,7 +26904,7 @@
         <v>2026-07-28T17:24:37.742Z</v>
       </c>
       <c r="R67" t="str">
-        <v>2026-08-04T05:27:21.200Z</v>
+        <v>2026-08-04T08:17:43.799Z</v>
       </c>
       <c r="S67" t="str">
         <v>[]</v>
@@ -26647,7 +26972,7 @@
         <v>2026-07-26T12:39:12.538Z</v>
       </c>
       <c r="R68" t="str">
-        <v>2026-08-04T05:27:21.200Z</v>
+        <v>2026-08-04T08:17:43.800Z</v>
       </c>
     </row>
     <row r="69">
@@ -26703,7 +27028,7 @@
         <v>2026-07-28T17:25:18.284Z</v>
       </c>
       <c r="R69" t="str">
-        <v>2026-08-04T05:27:21.201Z</v>
+        <v>2026-08-04T08:17:43.800Z</v>
       </c>
       <c r="S69" t="str">
         <v>[]</v>
@@ -26771,7 +27096,7 @@
         <v>2026-07-24T18:20:53.747Z</v>
       </c>
       <c r="R70" t="str">
-        <v>2026-08-04T05:27:21.201Z</v>
+        <v>2026-08-04T08:17:43.800Z</v>
       </c>
     </row>
     <row r="71">
@@ -26827,7 +27152,7 @@
         <v>2026-07-24T18:22:21.034Z</v>
       </c>
       <c r="R71" t="str">
-        <v>2026-08-04T05:27:21.201Z</v>
+        <v>2026-08-04T08:17:43.800Z</v>
       </c>
     </row>
     <row r="72">
@@ -26883,7 +27208,7 @@
         <v>2026-07-24T18:25:36.466Z</v>
       </c>
       <c r="R72" t="str">
-        <v>2026-08-04T05:27:21.202Z</v>
+        <v>2026-08-04T08:17:43.801Z</v>
       </c>
     </row>
     <row r="73">
@@ -26939,7 +27264,7 @@
         <v>2026-07-24T18:26:40.938Z</v>
       </c>
       <c r="R73" t="str">
-        <v>2026-08-04T05:27:21.202Z</v>
+        <v>2026-08-04T08:17:43.801Z</v>
       </c>
     </row>
     <row r="74">
@@ -26995,7 +27320,7 @@
         <v>2026-07-26T12:47:01.249Z</v>
       </c>
       <c r="R74" t="str">
-        <v>2026-08-04T05:27:21.202Z</v>
+        <v>2026-08-04T08:17:43.801Z</v>
       </c>
     </row>
     <row r="75">
@@ -27051,7 +27376,7 @@
         <v>2026-07-26T12:37:09.891Z</v>
       </c>
       <c r="R75" t="str">
-        <v>2026-08-04T05:27:21.202Z</v>
+        <v>2026-08-04T08:17:43.801Z</v>
       </c>
     </row>
     <row r="76">
@@ -27107,7 +27432,7 @@
         <v>2026-07-26T13:20:31.760Z</v>
       </c>
       <c r="R76" t="str">
-        <v>2026-08-04T05:27:21.203Z</v>
+        <v>2026-08-04T08:17:43.802Z</v>
       </c>
     </row>
     <row r="77">
@@ -27163,7 +27488,7 @@
         <v>2026-07-28T16:03:01.985Z</v>
       </c>
       <c r="R77" t="str">
-        <v>2026-08-04T05:27:21.203Z</v>
+        <v>2026-08-04T08:17:43.802Z</v>
       </c>
       <c r="S77" t="str">
         <v>[]</v>
@@ -27231,7 +27556,7 @@
         <v>2026-07-28T17:42:26.187Z</v>
       </c>
       <c r="R78" t="str">
-        <v>2026-08-04T05:27:21.203Z</v>
+        <v>2026-08-04T08:17:43.802Z</v>
       </c>
       <c r="S78" t="str">
         <v>[]</v>
@@ -27299,7 +27624,7 @@
         <v>2026-07-28T17:47:34.157Z</v>
       </c>
       <c r="R79" t="str">
-        <v>2026-08-04T05:27:21.203Z</v>
+        <v>2026-08-04T08:17:43.802Z</v>
       </c>
       <c r="S79" t="str">
         <v>[]</v>
@@ -27367,7 +27692,7 @@
         <v>2026-07-28T17:47:12.892Z</v>
       </c>
       <c r="R80" t="str">
-        <v>2026-08-04T05:27:21.204Z</v>
+        <v>2026-08-04T08:17:43.802Z</v>
       </c>
       <c r="S80" t="str">
         <v>[]</v>
@@ -27435,7 +27760,7 @@
         <v>2026-07-27T17:12:53.242Z</v>
       </c>
       <c r="R81" t="str">
-        <v>2026-08-04T05:27:21.204Z</v>
+        <v>2026-08-04T08:17:43.803Z</v>
       </c>
     </row>
     <row r="82">
@@ -27491,7 +27816,7 @@
         <v>2026-07-27T17:14:28.622Z</v>
       </c>
       <c r="R82" t="str">
-        <v>2026-08-04T05:27:21.204Z</v>
+        <v>2026-08-04T08:17:43.803Z</v>
       </c>
     </row>
     <row r="83">
@@ -27547,7 +27872,7 @@
         <v>2026-07-28T17:40:34.872Z</v>
       </c>
       <c r="R83" t="str">
-        <v>2026-08-04T05:27:21.204Z</v>
+        <v>2026-08-04T08:17:43.803Z</v>
       </c>
       <c r="S83" t="str">
         <v>[]</v>
@@ -27615,7 +27940,7 @@
         <v>2026-07-28T17:30:47.490Z</v>
       </c>
       <c r="R84" t="str">
-        <v>2026-08-04T05:27:21.205Z</v>
+        <v>2026-08-04T08:17:43.803Z</v>
       </c>
       <c r="S84" t="str">
         <v>[]</v>
@@ -27683,7 +28008,7 @@
         <v>2026-07-28T17:23:22.756Z</v>
       </c>
       <c r="R85" t="str">
-        <v>2026-08-04T05:27:21.205Z</v>
+        <v>2026-08-04T08:17:43.804Z</v>
       </c>
       <c r="S85" t="str">
         <v>[]</v>
@@ -27751,7 +28076,7 @@
         <v>2026-07-27T17:23:24.773Z</v>
       </c>
       <c r="R86" t="str">
-        <v>2026-08-04T05:27:21.205Z</v>
+        <v>2026-08-04T08:17:43.805Z</v>
       </c>
     </row>
     <row r="87">
@@ -27807,7 +28132,7 @@
         <v>2026-07-28T17:59:21.885Z</v>
       </c>
       <c r="R87" t="str">
-        <v>2026-08-04T05:27:21.205Z</v>
+        <v>2026-08-04T08:17:43.806Z</v>
       </c>
       <c r="S87" t="str">
         <v>[]</v>
@@ -27875,7 +28200,7 @@
         <v>2026-07-28T18:44:44.782Z</v>
       </c>
       <c r="R88" t="str">
-        <v>2026-08-04T05:27:21.206Z</v>
+        <v>2026-08-04T08:17:43.806Z</v>
       </c>
       <c r="S88" t="str">
         <v>[]</v>
@@ -27943,7 +28268,7 @@
         <v>2026-07-28T18:48:28.617Z</v>
       </c>
       <c r="R89" t="str">
-        <v>2026-08-04T05:27:21.206Z</v>
+        <v>2026-08-04T08:17:43.806Z</v>
       </c>
       <c r="S89" t="str">
         <v>[]</v>
@@ -28011,7 +28336,7 @@
         <v>2026-08-02T06:43:12.026Z</v>
       </c>
       <c r="R90" t="str">
-        <v>2026-08-04T05:27:21.206Z</v>
+        <v>2026-08-04T08:17:43.806Z</v>
       </c>
       <c r="S90" t="str">
         <v>[]</v>
@@ -28079,7 +28404,7 @@
         <v>2026-08-03T14:38:34.425Z</v>
       </c>
       <c r="R91" t="str">
-        <v>2026-08-04T05:27:21.206Z</v>
+        <v>2026-08-04T08:17:43.807Z</v>
       </c>
       <c r="S91" t="str">
         <v>[]</v>
@@ -28157,7 +28482,7 @@
         <v>2026-07-21T13:19:06.517Z</v>
       </c>
       <c r="G2" t="str">
-        <v>2026-08-04T05:27:21.327Z</v>
+        <v>2026-08-04T08:17:43.947Z</v>
       </c>
     </row>
     <row r="3">
@@ -28180,7 +28505,7 @@
         <v>2026-07-21T13:19:28.352Z</v>
       </c>
       <c r="G3" t="str">
-        <v>2026-08-04T05:27:21.327Z</v>
+        <v>2026-08-04T08:17:43.947Z</v>
       </c>
     </row>
     <row r="4">
@@ -28203,7 +28528,7 @@
         <v>2026-07-21T13:19:53.589Z</v>
       </c>
       <c r="G4" t="str">
-        <v>2026-08-04T05:27:21.327Z</v>
+        <v>2026-08-04T08:17:43.947Z</v>
       </c>
     </row>
     <row r="5">
@@ -28226,7 +28551,7 @@
         <v>2026-07-21T13:20:07.470Z</v>
       </c>
       <c r="G5" t="str">
-        <v>2026-08-04T05:27:21.327Z</v>
+        <v>2026-08-04T08:17:43.947Z</v>
       </c>
     </row>
     <row r="6">
@@ -28249,7 +28574,7 @@
         <v>2026-07-21T14:33:48.138Z</v>
       </c>
       <c r="G6" t="str">
-        <v>2026-08-04T05:27:21.327Z</v>
+        <v>2026-08-04T08:17:43.947Z</v>
       </c>
     </row>
     <row r="7">
@@ -28272,7 +28597,7 @@
         <v>2026-07-21T16:49:35.554Z</v>
       </c>
       <c r="G7" t="str">
-        <v>2026-08-04T05:27:21.327Z</v>
+        <v>2026-08-04T08:17:43.947Z</v>
       </c>
     </row>
     <row r="8">
@@ -28295,7 +28620,7 @@
         <v>2026-07-21T18:31:41.689Z</v>
       </c>
       <c r="G8" t="str">
-        <v>2026-08-04T05:27:21.327Z</v>
+        <v>2026-08-04T08:17:43.947Z</v>
       </c>
     </row>
     <row r="9">
@@ -28318,7 +28643,7 @@
         <v>2026-07-21T18:34:21.514Z</v>
       </c>
       <c r="G9" t="str">
-        <v>2026-08-04T05:27:21.327Z</v>
+        <v>2026-08-04T08:17:43.947Z</v>
       </c>
     </row>
   </sheetData>
@@ -28408,7 +28733,7 @@
         <v>2026-06-05T13:08:47.090Z</v>
       </c>
       <c r="I2" t="str">
-        <v>2026-08-04T05:27:21.549Z</v>
+        <v>2026-08-04T08:17:44.232Z</v>
       </c>
     </row>
     <row r="3">
@@ -28437,7 +28762,7 @@
         <v>2026-06-05T13:08:47.090Z</v>
       </c>
       <c r="I3" t="str">
-        <v>2026-08-04T05:27:21.549Z</v>
+        <v>2026-08-04T08:17:44.232Z</v>
       </c>
     </row>
     <row r="4">
@@ -28466,7 +28791,7 @@
         <v>2026-06-05T13:08:47.090Z</v>
       </c>
       <c r="I4" t="str">
-        <v>2026-08-04T05:27:21.549Z</v>
+        <v>2026-08-04T08:17:44.232Z</v>
       </c>
     </row>
     <row r="5">
@@ -28495,7 +28820,7 @@
         <v>2026-06-05T13:08:47.090Z</v>
       </c>
       <c r="I5" t="str">
-        <v>2026-08-04T05:27:21.549Z</v>
+        <v>2026-08-04T08:17:44.232Z</v>
       </c>
     </row>
     <row r="6">
@@ -28524,7 +28849,7 @@
         <v>2026-06-05T13:08:47.090Z</v>
       </c>
       <c r="I6" t="str">
-        <v>2026-08-04T05:27:21.549Z</v>
+        <v>2026-08-04T08:17:44.232Z</v>
       </c>
     </row>
     <row r="7">
@@ -28553,7 +28878,7 @@
         <v>2026-06-05T13:08:47.088Z</v>
       </c>
       <c r="I7" t="str">
-        <v>2026-08-04T05:27:21.549Z</v>
+        <v>2026-08-04T08:17:44.232Z</v>
       </c>
     </row>
     <row r="8">
@@ -28582,7 +28907,7 @@
         <v>2026-06-05T13:08:47.090Z</v>
       </c>
       <c r="I8" t="str">
-        <v>2026-08-04T05:27:21.549Z</v>
+        <v>2026-08-04T08:17:44.232Z</v>
       </c>
     </row>
     <row r="9">
@@ -28611,7 +28936,7 @@
         <v>2026-06-05T13:08:47.090Z</v>
       </c>
       <c r="I9" t="str">
-        <v>2026-08-04T05:27:21.549Z</v>
+        <v>2026-08-04T08:17:44.232Z</v>
       </c>
     </row>
     <row r="10">
@@ -28640,7 +28965,7 @@
         <v>2026-06-05T13:08:47.087Z</v>
       </c>
       <c r="I10" t="str">
-        <v>2026-08-04T05:27:21.549Z</v>
+        <v>2026-08-04T08:17:44.232Z</v>
       </c>
     </row>
     <row r="11">
@@ -28669,7 +28994,7 @@
         <v>2026-06-05T13:08:47.087Z</v>
       </c>
       <c r="I11" t="str">
-        <v>2026-08-04T05:27:21.549Z</v>
+        <v>2026-08-04T08:17:44.232Z</v>
       </c>
     </row>
     <row r="12">
@@ -28698,7 +29023,7 @@
         <v>2026-06-05T13:08:47.091Z</v>
       </c>
       <c r="I12" t="str">
-        <v>2026-08-04T05:27:21.549Z</v>
+        <v>2026-08-04T08:17:44.232Z</v>
       </c>
     </row>
     <row r="13">
@@ -28727,7 +29052,7 @@
         <v>2026-06-05T13:08:47.090Z</v>
       </c>
       <c r="I13" t="str">
-        <v>2026-08-04T05:27:21.549Z</v>
+        <v>2026-08-04T08:17:44.232Z</v>
       </c>
     </row>
     <row r="14">
@@ -28756,7 +29081,7 @@
         <v>2026-06-05T13:08:47.089Z</v>
       </c>
       <c r="I14" t="str">
-        <v>2026-08-04T05:27:21.549Z</v>
+        <v>2026-08-04T08:17:44.232Z</v>
       </c>
     </row>
     <row r="15">
@@ -28785,7 +29110,7 @@
         <v>2026-06-05T13:08:47.089Z</v>
       </c>
       <c r="I15" t="str">
-        <v>2026-08-04T05:27:21.549Z</v>
+        <v>2026-08-04T08:17:44.232Z</v>
       </c>
     </row>
     <row r="16">
@@ -28814,7 +29139,7 @@
         <v>2026-06-05T13:08:47.090Z</v>
       </c>
       <c r="I16" t="str">
-        <v>2026-08-04T05:27:21.549Z</v>
+        <v>2026-08-04T08:17:44.232Z</v>
       </c>
     </row>
     <row r="17">
@@ -28843,7 +29168,7 @@
         <v>2026-06-05T13:08:47.090Z</v>
       </c>
       <c r="I17" t="str">
-        <v>2026-08-04T05:27:21.549Z</v>
+        <v>2026-08-04T08:17:44.232Z</v>
       </c>
     </row>
     <row r="18">
@@ -28872,7 +29197,7 @@
         <v>2026-06-05T13:08:47.084Z</v>
       </c>
       <c r="I18" t="str">
-        <v>2026-08-04T05:27:21.549Z</v>
+        <v>2026-08-04T08:17:44.232Z</v>
       </c>
     </row>
     <row r="19">
@@ -28901,7 +29226,7 @@
         <v>2026-06-05T13:08:47.088Z</v>
       </c>
       <c r="I19" t="str">
-        <v>2026-08-04T05:27:21.549Z</v>
+        <v>2026-08-04T08:17:44.232Z</v>
       </c>
     </row>
     <row r="20">
@@ -28930,7 +29255,7 @@
         <v>2026-06-05T13:08:47.088Z</v>
       </c>
       <c r="I20" t="str">
-        <v>2026-08-04T05:27:21.549Z</v>
+        <v>2026-08-04T08:17:44.232Z</v>
       </c>
     </row>
     <row r="21">
@@ -28959,7 +29284,7 @@
         <v>2026-06-05T13:08:47.090Z</v>
       </c>
       <c r="I21" t="str">
-        <v>2026-08-04T05:27:21.549Z</v>
+        <v>2026-08-04T08:17:44.232Z</v>
       </c>
     </row>
     <row r="22">
@@ -28988,7 +29313,7 @@
         <v>2026-06-05T13:08:47.088Z</v>
       </c>
       <c r="I22" t="str">
-        <v>2026-08-04T05:27:21.549Z</v>
+        <v>2026-08-04T08:17:44.232Z</v>
       </c>
     </row>
     <row r="23">
@@ -29017,7 +29342,7 @@
         <v>2026-06-05T13:08:47.089Z</v>
       </c>
       <c r="I23" t="str">
-        <v>2026-08-04T05:27:21.549Z</v>
+        <v>2026-08-04T08:17:44.232Z</v>
       </c>
     </row>
     <row r="24">
@@ -29046,7 +29371,7 @@
         <v>2026-06-05T13:08:47.089Z</v>
       </c>
       <c r="I24" t="str">
-        <v>2026-08-04T05:27:21.549Z</v>
+        <v>2026-08-04T08:17:44.232Z</v>
       </c>
     </row>
     <row r="25">
@@ -29075,7 +29400,7 @@
         <v>2026-06-27T07:29:40.036Z</v>
       </c>
       <c r="I25" t="str">
-        <v>2026-08-04T05:27:21.549Z</v>
+        <v>2026-08-04T08:17:44.232Z</v>
       </c>
     </row>
     <row r="26">
@@ -29104,7 +29429,7 @@
         <v>2026-06-05T13:08:47.089Z</v>
       </c>
       <c r="I26" t="str">
-        <v>2026-08-04T05:27:21.549Z</v>
+        <v>2026-08-04T08:17:44.232Z</v>
       </c>
     </row>
     <row r="27">
@@ -29133,7 +29458,7 @@
         <v>2026-06-05T13:08:47.090Z</v>
       </c>
       <c r="I27" t="str">
-        <v>2026-08-04T05:27:21.549Z</v>
+        <v>2026-08-04T08:17:44.232Z</v>
       </c>
     </row>
     <row r="28">
@@ -29162,7 +29487,7 @@
         <v>2026-06-05T13:08:47.090Z</v>
       </c>
       <c r="I28" t="str">
-        <v>2026-08-04T05:27:21.549Z</v>
+        <v>2026-08-04T08:17:44.232Z</v>
       </c>
     </row>
     <row r="29">
@@ -29191,7 +29516,7 @@
         <v>2026-06-05T13:08:47.089Z</v>
       </c>
       <c r="I29" t="str">
-        <v>2026-08-04T05:27:21.550Z</v>
+        <v>2026-08-04T08:17:44.232Z</v>
       </c>
     </row>
     <row r="30">
@@ -29220,7 +29545,7 @@
         <v>2026-06-05T13:08:47.089Z</v>
       </c>
       <c r="I30" t="str">
-        <v>2026-08-04T05:27:21.550Z</v>
+        <v>2026-08-04T08:17:44.232Z</v>
       </c>
     </row>
     <row r="31">
@@ -29249,7 +29574,7 @@
         <v>2026-06-05T13:08:47.089Z</v>
       </c>
       <c r="I31" t="str">
-        <v>2026-08-04T05:27:21.550Z</v>
+        <v>2026-08-04T08:17:44.232Z</v>
       </c>
     </row>
     <row r="32">
@@ -29278,7 +29603,7 @@
         <v>2026-06-05T13:08:47.089Z</v>
       </c>
       <c r="I32" t="str">
-        <v>2026-08-04T05:27:21.550Z</v>
+        <v>2026-08-04T08:17:44.233Z</v>
       </c>
     </row>
     <row r="33">
@@ -29307,7 +29632,7 @@
         <v>2026-06-05T13:08:47.089Z</v>
       </c>
       <c r="I33" t="str">
-        <v>2026-08-04T05:27:21.550Z</v>
+        <v>2026-08-04T08:17:44.233Z</v>
       </c>
     </row>
     <row r="34">
@@ -29336,7 +29661,7 @@
         <v>2026-06-05T13:08:47.089Z</v>
       </c>
       <c r="I34" t="str">
-        <v>2026-08-04T05:27:21.550Z</v>
+        <v>2026-08-04T08:17:44.233Z</v>
       </c>
     </row>
     <row r="35">
@@ -29365,7 +29690,7 @@
         <v>2026-06-05T13:08:47.089Z</v>
       </c>
       <c r="I35" t="str">
-        <v>2026-08-04T05:27:21.550Z</v>
+        <v>2026-08-04T08:17:44.233Z</v>
       </c>
     </row>
     <row r="36">
@@ -29394,7 +29719,7 @@
         <v>2026-06-05T13:08:47.090Z</v>
       </c>
       <c r="I36" t="str">
-        <v>2026-08-04T05:27:21.550Z</v>
+        <v>2026-08-04T08:17:44.233Z</v>
       </c>
     </row>
     <row r="37">
@@ -29423,7 +29748,7 @@
         <v>2026-06-05T13:08:47.091Z</v>
       </c>
       <c r="I37" t="str">
-        <v>2026-08-04T05:27:21.550Z</v>
+        <v>2026-08-04T08:17:44.233Z</v>
       </c>
     </row>
     <row r="38">
@@ -29452,7 +29777,7 @@
         <v>2026-06-05T13:08:47.088Z</v>
       </c>
       <c r="I38" t="str">
-        <v>2026-08-04T05:27:21.550Z</v>
+        <v>2026-08-04T08:17:44.233Z</v>
       </c>
     </row>
   </sheetData>
@@ -29560,7 +29885,7 @@
         <v>ordinary</v>
       </c>
       <c r="M2" t="str">
-        <v>2026-08-04T05:27:21.657Z</v>
+        <v>2026-08-04T08:17:44.357Z</v>
       </c>
     </row>
     <row r="3">
@@ -29601,7 +29926,7 @@
         <v>custom</v>
       </c>
       <c r="M3" t="str">
-        <v>2026-08-04T05:27:21.657Z</v>
+        <v>2026-08-04T08:17:44.357Z</v>
       </c>
     </row>
     <row r="4">
@@ -29642,7 +29967,7 @@
         <v>ordinary</v>
       </c>
       <c r="M4" t="str">
-        <v>2026-08-04T05:27:21.657Z</v>
+        <v>2026-08-04T08:17:44.357Z</v>
       </c>
     </row>
     <row r="5">
@@ -29677,7 +30002,7 @@
         <v>ordinary</v>
       </c>
       <c r="M5" t="str">
-        <v>2026-08-04T05:27:21.657Z</v>
+        <v>2026-08-04T08:17:44.357Z</v>
       </c>
     </row>
     <row r="6">
@@ -29712,7 +30037,7 @@
         <v>ordinary</v>
       </c>
       <c r="M6" t="str">
-        <v>2026-08-04T05:27:21.657Z</v>
+        <v>2026-08-04T08:17:44.357Z</v>
       </c>
     </row>
     <row r="7">
@@ -29747,7 +30072,7 @@
         <v>ordinary</v>
       </c>
       <c r="M7" t="str">
-        <v>2026-08-04T05:27:21.657Z</v>
+        <v>2026-08-04T08:17:44.357Z</v>
       </c>
     </row>
     <row r="8">
@@ -29782,7 +30107,7 @@
         <v>custom</v>
       </c>
       <c r="M8" t="str">
-        <v>2026-08-04T05:27:21.657Z</v>
+        <v>2026-08-04T08:17:44.357Z</v>
       </c>
     </row>
     <row r="9">
@@ -29817,7 +30142,7 @@
         <v>ordinary</v>
       </c>
       <c r="M9" t="str">
-        <v>2026-08-04T05:27:21.657Z</v>
+        <v>2026-08-04T08:17:44.357Z</v>
       </c>
     </row>
   </sheetData>
@@ -29911,7 +30236,7 @@
         <v>2026-07-28T18:42:43.600Z</v>
       </c>
       <c r="K2" t="str">
-        <v>2026-08-04T05:27:21.782Z</v>
+        <v>2026-08-04T08:17:44.467Z</v>
       </c>
     </row>
     <row r="3">
@@ -29946,7 +30271,7 @@
         <v>2026-07-28T14:48:54.403Z</v>
       </c>
       <c r="K3" t="str">
-        <v>2026-08-04T05:27:21.782Z</v>
+        <v>2026-08-04T08:17:44.467Z</v>
       </c>
     </row>
     <row r="4">
@@ -29981,7 +30306,7 @@
         <v>2026-07-28T18:14:52.960Z</v>
       </c>
       <c r="K4" t="str">
-        <v>2026-08-04T05:27:21.782Z</v>
+        <v>2026-08-04T08:17:44.467Z</v>
       </c>
     </row>
   </sheetData>

--- a/backend/exports/master_export.xlsx
+++ b/backend/exports/master_export.xlsx
@@ -20,7 +20,6 @@
     <sheet name="Payment" sheetId="15" r:id="rId15"/>
     <sheet name="Review" sheetId="16" r:id="rId16"/>
     <sheet name="GoogleReview" sheetId="17" r:id="rId17"/>
-    <sheet name="AdminFcmToken" sheetId="18" r:id="rId18"/>
   </sheets>
 </workbook>
 </file>
@@ -431,7 +430,7 @@
     <col min="13" max="13" width="52.83203125" customWidth="1"/>
     <col min="14" max="14" width="23.83203125" customWidth="1"/>
     <col min="15" max="15" width="52.83203125" customWidth="1"/>
-    <col min="16" max="16" width="52.83203125" customWidth="1"/>
+    <col min="16" max="16" width="11.83203125" customWidth="1"/>
     <col min="17" max="17" width="21.83203125" customWidth="1"/>
     <col min="18" max="18" width="30.83203125" customWidth="1"/>
     <col min="19" max="19" width="26.83203125" customWidth="1"/>
@@ -552,7 +551,7 @@
         <v>["6a63a983a800f3907b955c53"]</v>
       </c>
       <c r="S2" t="str">
-        <v>2026-08-04T08:17:41.274Z</v>
+        <v>2026-08-04T08:53:46.190Z</v>
       </c>
     </row>
     <row r="3">
@@ -605,7 +604,7 @@
         <v>[]</v>
       </c>
       <c r="S3" t="str">
-        <v>2026-08-04T08:17:41.274Z</v>
+        <v>2026-08-04T08:53:46.190Z</v>
       </c>
     </row>
     <row r="4">
@@ -640,7 +639,7 @@
         <v>2026-08-02T17:06:28.042Z</v>
       </c>
       <c r="K4" t="str">
-        <v>2026-08-04T07:09:07.947Z</v>
+        <v>2026-08-04T08:24:00.254Z</v>
       </c>
       <c r="L4" t="str">
         <v>[]</v>
@@ -649,7 +648,7 @@
         <v>[]</v>
       </c>
       <c r="P4" t="str">
-        <v>[{"token":"fkS05Gk4TUiBWtUJwKFzHR:APA91bEbe3GKehQ4saJspl41KySjD8GUthqYpR2f7-3euQagWyA2yibbNj-CeYtGWWfYrYE7nIuQKPktxtvn8zQzGItn2pGtgLqBSXmxpPsgnUwye56DXQA","deviceName":"Windows Desktop","createdAt":"2026-08-04T07:09:07.947Z","_id":"6a701a6e1aed5008c4d24d7b"}]</v>
+        <v>[]</v>
       </c>
       <c r="Q4" t="str">
         <v>true</v>
@@ -658,7 +657,7 @@
         <v>[]</v>
       </c>
       <c r="S4" t="str">
-        <v>2026-08-04T08:17:41.275Z</v>
+        <v>2026-08-04T08:53:46.190Z</v>
       </c>
     </row>
     <row r="5">
@@ -711,7 +710,7 @@
         <v>[]</v>
       </c>
       <c r="S5" t="str">
-        <v>2026-08-04T08:17:41.275Z</v>
+        <v>2026-08-04T08:53:46.190Z</v>
       </c>
     </row>
     <row r="6">
@@ -746,7 +745,7 @@
         <v>2026-08-03T11:30:06.667Z</v>
       </c>
       <c r="K6" t="str">
-        <v>2026-08-03T11:37:32.755Z</v>
+        <v>2026-08-04T08:24:00.254Z</v>
       </c>
       <c r="L6" t="str">
         <v>[]</v>
@@ -755,7 +754,7 @@
         <v>[]</v>
       </c>
       <c r="P6" t="str">
-        <v>[{"token":"fGb7DBm3GT6XegrFEszd1o:APA91bG6GPnkbvqXNXeWTNQ-U0yxSNEh0mrvQXnut8HemUAdRQc3W1FSdA0Zb0krim6MkIwpRqiFss_qP1aAk8ftIhcPBEccQYBYvIw5CdCzQfpOqvCpka4","deviceName":"Windows Desktop","createdAt":"2026-08-03T11:37:32.753Z","_id":"6a707d7caab7ba55ee1ffdbb"}]</v>
+        <v>[]</v>
       </c>
       <c r="Q6" t="str">
         <v>true</v>
@@ -764,7 +763,7 @@
         <v>[]</v>
       </c>
       <c r="S6" t="str">
-        <v>2026-08-04T08:17:41.275Z</v>
+        <v>2026-08-04T08:53:46.190Z</v>
       </c>
     </row>
     <row r="7">
@@ -817,7 +816,7 @@
         <v>[]</v>
       </c>
       <c r="S7" t="str">
-        <v>2026-08-04T08:17:41.275Z</v>
+        <v>2026-08-04T08:53:46.190Z</v>
       </c>
     </row>
     <row r="8">
@@ -870,7 +869,7 @@
         <v>[]</v>
       </c>
       <c r="S8" t="str">
-        <v>2026-08-04T08:17:41.275Z</v>
+        <v>2026-08-04T08:53:46.190Z</v>
       </c>
     </row>
     <row r="9">
@@ -923,7 +922,7 @@
         <v>[]</v>
       </c>
       <c r="S9" t="str">
-        <v>2026-08-04T08:17:41.275Z</v>
+        <v>2026-08-04T08:53:46.190Z</v>
       </c>
     </row>
   </sheetData>
@@ -1027,7 +1026,7 @@
         <v>2026-08-03T13:43:50.194Z</v>
       </c>
       <c r="K2" t="str">
-        <v>2026-08-04T08:17:44.718Z</v>
+        <v>2026-08-04T08:53:48.716Z</v>
       </c>
     </row>
     <row r="3">
@@ -1062,7 +1061,7 @@
         <v>2026-08-02T11:15:41.649Z</v>
       </c>
       <c r="K3" t="str">
-        <v>2026-08-04T08:17:44.718Z</v>
+        <v>2026-08-04T08:53:48.716Z</v>
       </c>
     </row>
     <row r="4">
@@ -1097,7 +1096,7 @@
         <v>2026-08-03T13:43:35.459Z</v>
       </c>
       <c r="K4" t="str">
-        <v>2026-08-04T08:17:44.718Z</v>
+        <v>2026-08-04T08:53:48.716Z</v>
       </c>
     </row>
   </sheetData>
@@ -1177,7 +1176,7 @@
         <v>2026-08-02T11:44:43.854Z</v>
       </c>
       <c r="I2" t="str">
-        <v>2026-08-04T08:17:44.841Z</v>
+        <v>2026-08-04T08:53:48.919Z</v>
       </c>
     </row>
     <row r="3">
@@ -1206,7 +1205,7 @@
         <v>2026-08-02T11:45:37.177Z</v>
       </c>
       <c r="I3" t="str">
-        <v>2026-08-04T08:17:44.841Z</v>
+        <v>2026-08-04T08:53:48.919Z</v>
       </c>
     </row>
     <row r="4">
@@ -1235,7 +1234,7 @@
         <v>2026-08-02T11:45:18.169Z</v>
       </c>
       <c r="I4" t="str">
-        <v>2026-08-04T08:17:44.841Z</v>
+        <v>2026-08-04T08:53:48.919Z</v>
       </c>
     </row>
     <row r="5">
@@ -1264,7 +1263,7 @@
         <v>2026-08-02T11:45:03.112Z</v>
       </c>
       <c r="I5" t="str">
-        <v>2026-08-04T08:17:44.841Z</v>
+        <v>2026-08-04T08:53:48.919Z</v>
       </c>
     </row>
     <row r="6">
@@ -1293,7 +1292,7 @@
         <v>2026-08-02T11:24:43.615Z</v>
       </c>
       <c r="I6" t="str">
-        <v>2026-08-04T08:17:44.841Z</v>
+        <v>2026-08-04T08:53:48.919Z</v>
       </c>
     </row>
   </sheetData>
@@ -1579,7 +1578,7 @@
         <v>TCM-2026-0001</v>
       </c>
       <c r="AL2" t="str">
-        <v>2026-08-04T08:17:45.092Z</v>
+        <v>2026-08-04T08:53:49.123Z</v>
       </c>
     </row>
     <row r="3">
@@ -1695,7 +1694,7 @@
         <v>TCM-2026-0002</v>
       </c>
       <c r="AL3" t="str">
-        <v>2026-08-04T08:17:45.092Z</v>
+        <v>2026-08-04T08:53:49.123Z</v>
       </c>
       <c r="AM3" t="str">
         <v>User closed payment window before completion.</v>
@@ -1814,7 +1813,7 @@
         <v>TCM-2026-0003</v>
       </c>
       <c r="AL4" t="str">
-        <v>2026-08-04T08:17:45.092Z</v>
+        <v>2026-08-04T08:53:49.123Z</v>
       </c>
     </row>
     <row r="5">
@@ -1930,7 +1929,7 @@
         <v>TCM-2026-0004</v>
       </c>
       <c r="AL5" t="str">
-        <v>2026-08-04T08:17:45.092Z</v>
+        <v>2026-08-04T08:53:49.123Z</v>
       </c>
       <c r="AM5" t="str">
         <v>User closed payment window before completion.</v>
@@ -2051,7 +2050,7 @@
         <v>2026-08-04T03:02:01.248Z</v>
       </c>
       <c r="M2" t="str">
-        <v>2026-08-04T08:17:45.296Z</v>
+        <v>2026-08-04T08:53:49.312Z</v>
       </c>
     </row>
     <row r="3">
@@ -2092,7 +2091,7 @@
         <v>2026-08-04T03:07:35.154Z</v>
       </c>
       <c r="M3" t="str">
-        <v>2026-08-04T08:17:45.296Z</v>
+        <v>2026-08-04T08:53:49.312Z</v>
       </c>
     </row>
     <row r="4">
@@ -2133,7 +2132,7 @@
         <v>2026-08-04T03:13:26.310Z</v>
       </c>
       <c r="M4" t="str">
-        <v>2026-08-04T08:17:45.296Z</v>
+        <v>2026-08-04T08:53:49.312Z</v>
       </c>
     </row>
     <row r="5">
@@ -2174,7 +2173,7 @@
         <v>2026-08-04T06:55:13.137Z</v>
       </c>
       <c r="M5" t="str">
-        <v>2026-08-04T08:17:45.296Z</v>
+        <v>2026-08-04T08:53:49.312Z</v>
       </c>
     </row>
   </sheetData>
@@ -2275,7 +2274,7 @@
         <v>2026-04-25T05:16:45.245Z</v>
       </c>
       <c r="L2" t="str">
-        <v>2026-08-04T08:17:45.418Z</v>
+        <v>2026-08-04T08:53:49.392Z</v>
       </c>
     </row>
     <row r="3">
@@ -2313,7 +2312,7 @@
         <v>2026-04-26T13:01:08.188Z</v>
       </c>
       <c r="L3" t="str">
-        <v>2026-08-04T08:17:45.418Z</v>
+        <v>2026-08-04T08:53:49.392Z</v>
       </c>
     </row>
     <row r="4">
@@ -2351,7 +2350,7 @@
         <v>2026-04-26T15:36:57.443Z</v>
       </c>
       <c r="L4" t="str">
-        <v>2026-08-04T08:17:45.418Z</v>
+        <v>2026-08-04T08:53:49.392Z</v>
       </c>
     </row>
     <row r="5">
@@ -2389,7 +2388,7 @@
         <v>2026-04-28T15:26:52.023Z</v>
       </c>
       <c r="L5" t="str">
-        <v>2026-08-04T08:17:45.418Z</v>
+        <v>2026-08-04T08:53:49.392Z</v>
       </c>
     </row>
     <row r="6">
@@ -2427,7 +2426,7 @@
         <v>2026-06-07T14:24:10.694Z</v>
       </c>
       <c r="L6" t="str">
-        <v>2026-08-04T08:17:45.418Z</v>
+        <v>2026-08-04T08:53:49.392Z</v>
       </c>
     </row>
     <row r="7">
@@ -2465,7 +2464,7 @@
         <v>2026-06-10T17:55:28.556Z</v>
       </c>
       <c r="L7" t="str">
-        <v>2026-08-04T08:17:45.418Z</v>
+        <v>2026-08-04T08:53:49.392Z</v>
       </c>
     </row>
     <row r="8">
@@ -2503,7 +2502,7 @@
         <v>2026-06-13T16:20:41.698Z</v>
       </c>
       <c r="L8" t="str">
-        <v>2026-08-04T08:17:45.418Z</v>
+        <v>2026-08-04T08:53:49.392Z</v>
       </c>
     </row>
     <row r="9">
@@ -2541,7 +2540,7 @@
         <v>2026-06-13T16:25:47.423Z</v>
       </c>
       <c r="L9" t="str">
-        <v>2026-08-04T08:17:45.418Z</v>
+        <v>2026-08-04T08:53:49.392Z</v>
       </c>
     </row>
     <row r="10">
@@ -2579,7 +2578,7 @@
         <v>2026-07-11T10:23:53.937Z</v>
       </c>
       <c r="L10" t="str">
-        <v>2026-08-04T08:17:45.418Z</v>
+        <v>2026-08-04T08:53:49.392Z</v>
       </c>
     </row>
   </sheetData>
@@ -2736,7 +2735,7 @@
         <v>2026-03-05T10:51:19.227Z</v>
       </c>
       <c r="T2" t="str">
-        <v>2026-08-04T08:17:45.657Z</v>
+        <v>2026-08-04T08:53:49.860Z</v>
       </c>
     </row>
     <row r="3" xml:space="preserve">
@@ -2800,7 +2799,7 @@
         <v>2026-01-31T07:51:47.756Z</v>
       </c>
       <c r="T3" t="str">
-        <v>2026-08-04T08:17:45.657Z</v>
+        <v>2026-08-04T08:53:49.860Z</v>
       </c>
     </row>
     <row r="4">
@@ -2862,7 +2861,7 @@
         <v>2026-01-16T16:33:33.279Z</v>
       </c>
       <c r="T4" t="str">
-        <v>2026-08-04T08:17:45.657Z</v>
+        <v>2026-08-04T08:53:49.860Z</v>
       </c>
     </row>
     <row r="5">
@@ -2918,7 +2917,7 @@
         <v>2026-06-12T17:08:32.112Z</v>
       </c>
       <c r="T5" t="str">
-        <v>2026-08-04T08:17:45.657Z</v>
+        <v>2026-08-04T08:53:49.861Z</v>
       </c>
     </row>
     <row r="6">
@@ -2980,7 +2979,7 @@
         <v>2026-02-25T11:00:52.464Z</v>
       </c>
       <c r="T6" t="str">
-        <v>2026-08-04T08:17:45.657Z</v>
+        <v>2026-08-04T08:53:49.861Z</v>
       </c>
     </row>
     <row r="7">
@@ -3021,7 +3020,7 @@
         <v>apify</v>
       </c>
       <c r="M7" t="str">
-        <v>2026-08-04T08:17:31.120Z</v>
+        <v>2026-08-04T08:53:38.100Z</v>
       </c>
       <c r="N7" t="str">
         <v>[]</v>
@@ -3030,19 +3029,19 @@
         <v>I ordered fresh mango cake and the cake was delicious and subtle making me want to eat more and I needed the cake in a very short span and they delivered it soon and made the moment memorable</v>
       </c>
       <c r="P7" t="str">
-        <v>2026-08-04T08:17:31.120Z</v>
+        <v>2026-08-04T08:53:38.100Z</v>
       </c>
       <c r="Q7" t="str">
-        <v>2026-08-04T08:17:39.004Z</v>
+        <v>2026-08-04T08:53:44.641Z</v>
       </c>
       <c r="R7" t="str">
         <v>["https://lh3.googleusercontent.com/grass-cs/ACvplmO_pqUM6Inbd4_tYNoXGkmjVXuMvqW1k6_n3WKo5GFjIU-jy6NJXw54DGSD41LE-vcpvHH45HW9eD-aeGFYOmHWhIvTyxBBuqd6GwDjK2xkDrER4qts8deU47gt4tI5Du1u0drm0TLOEtN-=w600-h450-p-k-no"]</v>
       </c>
       <c r="S7" t="str">
-        <v>2026-05-06T08:17:37.228Z</v>
+        <v>2026-05-06T08:53:44.328Z</v>
       </c>
       <c r="T7" t="str">
-        <v>2026-08-04T08:17:45.657Z</v>
+        <v>2026-08-04T08:53:49.861Z</v>
       </c>
     </row>
     <row r="8">
@@ -3104,7 +3103,7 @@
         <v>2026-02-04T08:34:24.383Z</v>
       </c>
       <c r="T8" t="str">
-        <v>2026-08-04T08:17:45.657Z</v>
+        <v>2026-08-04T08:53:49.861Z</v>
       </c>
     </row>
     <row r="9">
@@ -3166,7 +3165,7 @@
         <v>2026-03-05T11:17:24.179Z</v>
       </c>
       <c r="T9" t="str">
-        <v>2026-08-04T08:17:45.657Z</v>
+        <v>2026-08-04T08:53:49.861Z</v>
       </c>
     </row>
     <row r="10">
@@ -3222,7 +3221,7 @@
         <v>2026-06-12T17:08:32.573Z</v>
       </c>
       <c r="T10" t="str">
-        <v>2026-08-04T08:17:45.657Z</v>
+        <v>2026-08-04T08:53:49.861Z</v>
       </c>
     </row>
     <row r="11">
@@ -3284,7 +3283,7 @@
         <v>2026-01-28T12:33:53.732Z</v>
       </c>
       <c r="T11" t="str">
-        <v>2026-08-04T08:17:45.657Z</v>
+        <v>2026-08-04T08:53:49.861Z</v>
       </c>
     </row>
     <row r="12">
@@ -3325,7 +3324,7 @@
         <v>apify</v>
       </c>
       <c r="M12" t="str">
-        <v>2026-08-04T08:17:31.119Z</v>
+        <v>2026-08-04T08:53:38.100Z</v>
       </c>
       <c r="N12" t="str">
         <v>[]</v>
@@ -3334,19 +3333,19 @@
         <v>Cake serious ah romba super ah irrunthuchu and really worth for Money and more over I really cannot forget how it was so perfectly baked and the softness is it was top norch and thanks for making my birthday so special with your wonderful cakes</v>
       </c>
       <c r="P12" t="str">
-        <v>2026-08-04T08:17:31.119Z</v>
+        <v>2026-08-04T08:53:38.100Z</v>
       </c>
       <c r="Q12" t="str">
-        <v>2026-08-04T08:17:35.658Z</v>
+        <v>2026-08-04T08:53:41.832Z</v>
       </c>
       <c r="R12" t="str">
         <v>["https://lh3.googleusercontent.com/grass-cs/ACvplmOG5juTOg0n2Beu1G4Z36P75AAYFcngApbdEIQ8bWX_kgVMQYhGX700QZt9X6SnFtaNFrjSkpsNLwwBdKw478tehnEh5yXt4pkMBvEOLUcvS7MXI7846rYwqVXbXXfdy_Ogx3Qhpql9SQ_n=w600-h450-p-k-no"]</v>
       </c>
       <c r="S12" t="str">
-        <v>2026-07-05T08:17:29.399Z</v>
+        <v>2026-07-05T08:53:36.302Z</v>
       </c>
       <c r="T12" t="str">
-        <v>2026-08-04T08:17:45.657Z</v>
+        <v>2026-08-04T08:53:49.861Z</v>
       </c>
     </row>
     <row r="13">
@@ -3387,7 +3386,7 @@
         <v>apify</v>
       </c>
       <c r="M13" t="str">
-        <v>2026-08-04T08:17:31.119Z</v>
+        <v>2026-08-04T08:53:38.100Z</v>
       </c>
       <c r="N13" t="str">
         <v>[]</v>
@@ -3396,19 +3395,19 @@
         <v>Thank you for making our special day even more special with your wonderful cake. It was absolutely fabulous, and everyone in my family loved it. The birthday girl especially loved it a lot We truly enjoyed it!</v>
       </c>
       <c r="P13" t="str">
-        <v>2026-08-04T08:17:31.119Z</v>
+        <v>2026-08-04T08:53:38.100Z</v>
       </c>
       <c r="Q13" t="str">
-        <v>2026-08-04T08:17:35.782Z</v>
+        <v>2026-08-04T08:53:41.940Z</v>
       </c>
       <c r="R13" t="str">
         <v>["https://lh3.googleusercontent.com/grass-cs/ACvplmO0A6fdSyS7vmWIkbQK4rcTInFQpzKUTtFRzho5FfZbx-wsVCA9CcTx_eSpgfwQC2ljTWZu0yS5FepZ1imnGZNTWgnEr_KRmzBB70noiCZos4L_R3pPU8Q6cGyz2qd76STVZm7Nf0p9AbFh=w600-h450-p-k-no"]</v>
       </c>
       <c r="S13" t="str">
-        <v>2026-07-05T08:17:29.399Z</v>
+        <v>2026-07-05T08:53:36.302Z</v>
       </c>
       <c r="T13" t="str">
-        <v>2026-08-04T08:17:45.657Z</v>
+        <v>2026-08-04T08:53:49.861Z</v>
       </c>
     </row>
     <row r="14">
@@ -3449,7 +3448,7 @@
         <v>apify</v>
       </c>
       <c r="M14" t="str">
-        <v>2026-08-04T08:17:31.119Z</v>
+        <v>2026-08-04T08:53:38.100Z</v>
       </c>
       <c r="N14" t="str">
         <v>[]</v>
@@ -3458,19 +3457,19 @@
         <v>Good</v>
       </c>
       <c r="P14" t="str">
-        <v>2026-08-04T08:17:31.119Z</v>
+        <v>2026-08-04T08:53:38.100Z</v>
       </c>
       <c r="Q14" t="str">
-        <v>2026-08-04T08:17:35.909Z</v>
+        <v>2026-08-04T08:53:42.049Z</v>
       </c>
       <c r="R14" t="str">
         <v>[]</v>
       </c>
       <c r="S14" t="str">
-        <v>2026-07-05T08:17:29.399Z</v>
+        <v>2026-07-05T08:53:36.302Z</v>
       </c>
       <c r="T14" t="str">
-        <v>2026-08-04T08:17:45.657Z</v>
+        <v>2026-08-04T08:53:49.861Z</v>
       </c>
     </row>
     <row r="15">
@@ -3511,7 +3510,7 @@
         <v>apify</v>
       </c>
       <c r="M15" t="str">
-        <v>2026-08-04T08:17:31.119Z</v>
+        <v>2026-08-04T08:53:38.100Z</v>
       </c>
       <c r="N15" t="str">
         <v>[]</v>
@@ -3520,19 +3519,19 @@
         <v>Ordered a chocolate truffle cake which was delicious &amp; loved by all and customised designed was too cute as expected!</v>
       </c>
       <c r="P15" t="str">
-        <v>2026-08-04T08:17:31.119Z</v>
+        <v>2026-08-04T08:53:38.100Z</v>
       </c>
       <c r="Q15" t="str">
-        <v>2026-08-04T08:17:36.065Z</v>
+        <v>2026-08-04T08:53:42.159Z</v>
       </c>
       <c r="R15" t="str">
         <v>[]</v>
       </c>
       <c r="S15" t="str">
-        <v>2026-07-05T08:17:29.399Z</v>
+        <v>2026-07-05T08:53:36.302Z</v>
       </c>
       <c r="T15" t="str">
-        <v>2026-08-04T08:17:45.657Z</v>
+        <v>2026-08-04T08:53:49.861Z</v>
       </c>
     </row>
     <row r="16" xml:space="preserve">
@@ -3573,7 +3572,7 @@
         <v>apify</v>
       </c>
       <c r="M16" t="str">
-        <v>2026-08-04T08:17:31.119Z</v>
+        <v>2026-08-04T08:53:38.100Z</v>
       </c>
       <c r="N16" t="str">
         <v>[]</v>
@@ -3583,10 +3582,10 @@
 Super tasty without egg.</v>
       </c>
       <c r="P16" t="str">
-        <v>2026-08-04T08:17:31.119Z</v>
+        <v>2026-08-04T08:53:38.100Z</v>
       </c>
       <c r="Q16" t="str">
-        <v>2026-08-04T08:17:36.191Z</v>
+        <v>2026-08-04T08:53:42.283Z</v>
       </c>
       <c r="R16" t="str">
         <v>["https://lh3.googleusercontent.com/grass-cs/ACvplmONtSSbB4uGez6qp_Oo8LiQdedj1qwfFuDdIJXVqvkKvZyR_cObSIrJJTDlYeKkfu1doLjLCI-wKgky_rYcMlkNyHQgmPX6FAqLSJhw39Sk2BGr1EmZiU4De_RNF8CN5uSsJ7FaqHSDAZqV=w600-h450-p-k-no"]</v>
@@ -3595,7 +3594,7 @@
         <v/>
       </c>
       <c r="T16" t="str">
-        <v>2026-08-04T08:17:45.657Z</v>
+        <v>2026-08-04T08:53:49.861Z</v>
       </c>
     </row>
     <row r="17">
@@ -3636,7 +3635,7 @@
         <v>apify</v>
       </c>
       <c r="M17" t="str">
-        <v>2026-08-04T08:17:31.119Z</v>
+        <v>2026-08-04T08:53:38.100Z</v>
       </c>
       <c r="N17" t="str">
         <v>[]</v>
@@ -3645,19 +3644,19 @@
         <v>Such a good ambience....and taste is too good</v>
       </c>
       <c r="P17" t="str">
-        <v>2026-08-04T08:17:31.119Z</v>
+        <v>2026-08-04T08:53:38.100Z</v>
       </c>
       <c r="Q17" t="str">
-        <v>2026-08-04T08:17:36.315Z</v>
+        <v>2026-08-04T08:53:42.393Z</v>
       </c>
       <c r="R17" t="str">
         <v>["https://lh3.googleusercontent.com/grass-cs/ACvplmO0kf3mosn0MhTEpsOSZW09MccHmzeA8TZsdRO-p3IGf3RxaIl4y6SPd1_0ef9GnSku92QtmySFuZfjG8vZOOx0oaU8KVlLu5q_qEap9rdGaHi608Mdw_slZC-my59ygMAPUb9sEZlnQQc=w600-h450-p-k-no"]</v>
       </c>
       <c r="S17" t="str">
-        <v>2026-07-05T08:17:29.399Z</v>
+        <v>2026-07-05T08:53:36.302Z</v>
       </c>
       <c r="T17" t="str">
-        <v>2026-08-04T08:17:45.657Z</v>
+        <v>2026-08-04T08:53:49.861Z</v>
       </c>
     </row>
     <row r="18">
@@ -3698,7 +3697,7 @@
         <v>apify</v>
       </c>
       <c r="M18" t="str">
-        <v>2026-08-04T08:17:31.119Z</v>
+        <v>2026-08-04T08:53:38.100Z</v>
       </c>
       <c r="N18" t="str">
         <v>[]</v>
@@ -3707,19 +3706,19 @@
         <v>a month agoRecommended dishesTiramisu, Sizzling Brownie, Black Forest Cake 500 G, Tres Leches RosemilkLike</v>
       </c>
       <c r="P18" t="str">
-        <v>2026-08-04T08:17:31.119Z</v>
+        <v>2026-08-04T08:53:38.100Z</v>
       </c>
       <c r="Q18" t="str">
-        <v>2026-08-04T08:17:36.456Z</v>
+        <v>2026-08-04T08:53:42.502Z</v>
       </c>
       <c r="R18" t="str">
         <v>[]</v>
       </c>
       <c r="S18" t="str">
-        <v>2026-07-05T08:17:29.399Z</v>
+        <v>2026-07-05T08:53:36.302Z</v>
       </c>
       <c r="T18" t="str">
-        <v>2026-08-04T08:17:45.657Z</v>
+        <v>2026-08-04T08:53:49.861Z</v>
       </c>
     </row>
     <row r="19">
@@ -3760,7 +3759,7 @@
         <v>apify</v>
       </c>
       <c r="M19" t="str">
-        <v>2026-08-04T08:17:31.119Z</v>
+        <v>2026-08-04T08:53:38.100Z</v>
       </c>
       <c r="N19" t="str">
         <v>[]</v>
@@ -3769,19 +3768,19 @@
         <v>Taste was very good...</v>
       </c>
       <c r="P19" t="str">
-        <v>2026-08-04T08:17:31.119Z</v>
+        <v>2026-08-04T08:53:38.100Z</v>
       </c>
       <c r="Q19" t="str">
-        <v>2026-08-04T08:17:36.596Z</v>
+        <v>2026-08-04T08:53:42.596Z</v>
       </c>
       <c r="R19" t="str">
         <v>["https://lh3.googleusercontent.com/grass-cs/ACvplmMQhLM__tf-fQLYIKdtORSGqBUtG5S298WNziQA0YLBa0qcmqlGp1pmBKP7Xufta2V6R_ZgJGv4QeX88I4JE3KFrMDsieR1Vota59d7i2OwAN4tNlHejKJUC3ppgv1lsBKPztomFcKY1cI3=w600-h450-p-k-no"]</v>
       </c>
       <c r="S19" t="str">
-        <v>2026-06-05T08:17:31.361Z</v>
+        <v>2026-06-05T08:53:38.722Z</v>
       </c>
       <c r="T19" t="str">
-        <v>2026-08-04T08:17:45.657Z</v>
+        <v>2026-08-04T08:53:49.861Z</v>
       </c>
     </row>
     <row r="20">
@@ -3822,7 +3821,7 @@
         <v>apify</v>
       </c>
       <c r="M20" t="str">
-        <v>2026-08-04T08:17:31.119Z</v>
+        <v>2026-08-04T08:53:38.100Z</v>
       </c>
       <c r="N20" t="str">
         <v>[]</v>
@@ -3831,19 +3830,19 @@
         <v>The hot chocolate was superb, the milkshake and chocolate brownie was so comforting. Love it</v>
       </c>
       <c r="P20" t="str">
-        <v>2026-08-04T08:17:31.119Z</v>
+        <v>2026-08-04T08:53:38.100Z</v>
       </c>
       <c r="Q20" t="str">
-        <v>2026-08-04T08:17:36.723Z</v>
+        <v>2026-08-04T08:53:42.690Z</v>
       </c>
       <c r="R20" t="str">
         <v>[]</v>
       </c>
       <c r="S20" t="str">
-        <v>2026-06-05T08:17:31.361Z</v>
+        <v>2026-06-05T08:53:38.722Z</v>
       </c>
       <c r="T20" t="str">
-        <v>2026-08-04T08:17:45.657Z</v>
+        <v>2026-08-04T08:53:49.861Z</v>
       </c>
     </row>
     <row r="21">
@@ -3884,7 +3883,7 @@
         <v>apify</v>
       </c>
       <c r="M21" t="str">
-        <v>2026-08-04T08:17:31.119Z</v>
+        <v>2026-08-04T08:53:38.100Z</v>
       </c>
       <c r="N21" t="str">
         <v>[]</v>
@@ -3893,19 +3892,19 @@
         <v>Comforting pastry, rich hot chocolate, and the perfect cozy combo. 🤎 Belgium hot chocolate was awesome. …</v>
       </c>
       <c r="P21" t="str">
-        <v>2026-08-04T08:17:31.119Z</v>
+        <v>2026-08-04T08:53:38.100Z</v>
       </c>
       <c r="Q21" t="str">
-        <v>2026-08-04T08:17:36.846Z</v>
+        <v>2026-08-04T08:53:42.924Z</v>
       </c>
       <c r="R21" t="str">
         <v>[]</v>
       </c>
       <c r="S21" t="str">
-        <v>2026-06-05T08:17:31.361Z</v>
+        <v>2026-06-05T08:53:38.722Z</v>
       </c>
       <c r="T21" t="str">
-        <v>2026-08-04T08:17:45.657Z</v>
+        <v>2026-08-04T08:53:49.861Z</v>
       </c>
     </row>
     <row r="22" xml:space="preserve">
@@ -3946,7 +3945,7 @@
         <v>apify</v>
       </c>
       <c r="M22" t="str">
-        <v>2026-08-04T08:17:31.119Z</v>
+        <v>2026-08-04T08:53:38.100Z</v>
       </c>
       <c r="N22" t="str">
         <v>[]</v>
@@ -3956,19 +3955,19 @@
 This place is worth its price 💯</v>
       </c>
       <c r="P22" t="str">
-        <v>2026-08-04T08:17:31.119Z</v>
+        <v>2026-08-04T08:53:38.100Z</v>
       </c>
       <c r="Q22" t="str">
-        <v>2026-08-04T08:17:36.956Z</v>
+        <v>2026-08-04T08:53:43.017Z</v>
       </c>
       <c r="R22" t="str">
         <v>[]</v>
       </c>
       <c r="S22" t="str">
-        <v>2026-06-05T08:17:31.361Z</v>
+        <v>2026-06-05T08:53:38.722Z</v>
       </c>
       <c r="T22" t="str">
-        <v>2026-08-04T08:17:45.657Z</v>
+        <v>2026-08-04T08:53:49.861Z</v>
       </c>
     </row>
     <row r="23">
@@ -4009,7 +4008,7 @@
         <v>apify</v>
       </c>
       <c r="M23" t="str">
-        <v>2026-08-04T08:17:31.119Z</v>
+        <v>2026-08-04T08:53:38.100Z</v>
       </c>
       <c r="N23" t="str">
         <v>[]</v>
@@ -4018,19 +4017,19 @@
         <v>Absolutely loved their Belgium hot chocolate and hazel nut hot chocolate. Also enjoyed their sandwich and burger..... Beautiful ambience and host ❤️</v>
       </c>
       <c r="P23" t="str">
-        <v>2026-08-04T08:17:31.119Z</v>
+        <v>2026-08-04T08:53:38.100Z</v>
       </c>
       <c r="Q23" t="str">
-        <v>2026-08-04T08:17:37.080Z</v>
+        <v>2026-08-04T08:53:43.097Z</v>
       </c>
       <c r="R23" t="str">
         <v>["https://lh3.googleusercontent.com/grass-cs/ACvplmOXAZUZBxNTEwmcNAOXzyMJILSZKCGgRdx_SRzeZcQgg2_2KoLfuNVhZbfhshPOOgJASJ3O_fM_Q9pVms4Um_jwyX3NwEE9oW8nI4vlm6jsmCPPE04Wpo-0HAeErO0yeZNUKXFsbaf87G0=w600-h450-p-k-no"]</v>
       </c>
       <c r="S23" t="str">
-        <v>2026-06-05T08:17:31.361Z</v>
+        <v>2026-06-05T08:53:38.722Z</v>
       </c>
       <c r="T23" t="str">
-        <v>2026-08-04T08:17:45.657Z</v>
+        <v>2026-08-04T08:53:49.861Z</v>
       </c>
     </row>
     <row r="24" xml:space="preserve">
@@ -4071,7 +4070,7 @@
         <v>apify</v>
       </c>
       <c r="M24" t="str">
-        <v>2026-08-04T08:17:31.120Z</v>
+        <v>2026-08-04T08:53:38.100Z</v>
       </c>
       <c r="N24" t="str">
         <v>[]</v>
@@ -4081,19 +4080,19 @@
 I would defenitely reach back here once again</v>
       </c>
       <c r="P24" t="str">
-        <v>2026-08-04T08:17:31.119Z</v>
+        <v>2026-08-04T08:53:38.100Z</v>
       </c>
       <c r="Q24" t="str">
-        <v>2026-08-04T08:17:37.316Z</v>
+        <v>2026-08-04T08:53:43.189Z</v>
       </c>
       <c r="R24" t="str">
         <v>[]</v>
       </c>
       <c r="S24" t="str">
-        <v>2026-06-05T08:17:31.361Z</v>
+        <v>2026-06-05T08:53:38.722Z</v>
       </c>
       <c r="T24" t="str">
-        <v>2026-08-04T08:17:45.657Z</v>
+        <v>2026-08-04T08:53:49.861Z</v>
       </c>
     </row>
     <row r="25">
@@ -4134,7 +4133,7 @@
         <v>apify</v>
       </c>
       <c r="M25" t="str">
-        <v>2026-08-04T08:17:31.120Z</v>
+        <v>2026-08-04T08:53:38.100Z</v>
       </c>
       <c r="N25" t="str">
         <v>[]</v>
@@ -4143,19 +4142,19 @@
         <v>Good</v>
       </c>
       <c r="P25" t="str">
-        <v>2026-08-04T08:17:31.120Z</v>
+        <v>2026-08-04T08:53:38.100Z</v>
       </c>
       <c r="Q25" t="str">
-        <v>2026-08-04T08:17:37.472Z</v>
+        <v>2026-08-04T08:53:43.282Z</v>
       </c>
       <c r="R25" t="str">
         <v>[]</v>
       </c>
       <c r="S25" t="str">
-        <v>2026-06-05T08:17:31.361Z</v>
+        <v>2026-06-05T08:53:38.722Z</v>
       </c>
       <c r="T25" t="str">
-        <v>2026-08-04T08:17:45.657Z</v>
+        <v>2026-08-04T08:53:49.861Z</v>
       </c>
     </row>
     <row r="26">
@@ -4196,7 +4195,7 @@
         <v>apify</v>
       </c>
       <c r="M26" t="str">
-        <v>2026-08-04T08:17:31.120Z</v>
+        <v>2026-08-04T08:53:38.100Z</v>
       </c>
       <c r="N26" t="str">
         <v>[]</v>
@@ -4205,19 +4204,19 @@
         <v>Ordered customized cake. Taste was really good and they customized the cake based on my preference.</v>
       </c>
       <c r="P26" t="str">
-        <v>2026-08-04T08:17:31.120Z</v>
+        <v>2026-08-04T08:53:38.100Z</v>
       </c>
       <c r="Q26" t="str">
-        <v>2026-08-04T08:17:37.582Z</v>
+        <v>2026-08-04T08:53:43.392Z</v>
       </c>
       <c r="R26" t="str">
         <v>[]</v>
       </c>
       <c r="S26" t="str">
-        <v>2026-06-05T08:17:31.361Z</v>
+        <v>2026-06-05T08:53:38.722Z</v>
       </c>
       <c r="T26" t="str">
-        <v>2026-08-04T08:17:45.657Z</v>
+        <v>2026-08-04T08:53:49.861Z</v>
       </c>
     </row>
     <row r="27">
@@ -4258,7 +4257,7 @@
         <v>apify</v>
       </c>
       <c r="M27" t="str">
-        <v>2026-08-04T08:17:31.120Z</v>
+        <v>2026-08-04T08:53:38.100Z</v>
       </c>
       <c r="N27" t="str">
         <v>[]</v>
@@ -4267,19 +4266,19 @@
         <v>Delicious cakes 😋 and great service and one of my favorite cake shop !!</v>
       </c>
       <c r="P27" t="str">
-        <v>2026-08-04T08:17:31.120Z</v>
+        <v>2026-08-04T08:53:38.100Z</v>
       </c>
       <c r="Q27" t="str">
-        <v>2026-08-04T08:17:37.705Z</v>
+        <v>2026-08-04T08:53:43.516Z</v>
       </c>
       <c r="R27" t="str">
         <v>["https://lh3.googleusercontent.com/grass-cs/ACvplmPOyYm8EGEtNp0qLiPcMfjVRURnxDznB2mpI1Tmnh9vNtXC2tsDOYX8Kilq2QE_xCBTc7YBxxU4vVjLiMDNjR-fvb295N2I9abXqIQbHgy3ZuvSz89148s_5eRDqUzCT9pgO1N73nJ2YqFg=w600-h450-p-k-no"]</v>
       </c>
       <c r="S27" t="str">
-        <v>2026-06-05T08:17:33.323Z</v>
+        <v>2026-06-05T08:53:40.513Z</v>
       </c>
       <c r="T27" t="str">
-        <v>2026-08-04T08:17:45.657Z</v>
+        <v>2026-08-04T08:53:49.861Z</v>
       </c>
     </row>
     <row r="28">
@@ -4320,7 +4319,7 @@
         <v>apify</v>
       </c>
       <c r="M28" t="str">
-        <v>2026-08-04T08:17:31.120Z</v>
+        <v>2026-08-04T08:53:38.100Z</v>
       </c>
       <c r="N28" t="str">
         <v>[]</v>
@@ -4329,19 +4328,19 @@
         <v>Tried chocolate truffle cake here and it was really awesome</v>
       </c>
       <c r="P28" t="str">
-        <v>2026-08-04T08:17:31.120Z</v>
+        <v>2026-08-04T08:53:38.100Z</v>
       </c>
       <c r="Q28" t="str">
-        <v>2026-08-04T08:17:37.831Z</v>
+        <v>2026-08-04T08:53:43.610Z</v>
       </c>
       <c r="R28" t="str">
         <v>[]</v>
       </c>
       <c r="S28" t="str">
-        <v>2026-06-05T08:17:33.323Z</v>
+        <v>2026-06-05T08:53:40.513Z</v>
       </c>
       <c r="T28" t="str">
-        <v>2026-08-04T08:17:45.657Z</v>
+        <v>2026-08-04T08:53:49.861Z</v>
       </c>
     </row>
     <row r="29" xml:space="preserve">
@@ -4382,7 +4381,7 @@
         <v>apify</v>
       </c>
       <c r="M29" t="str">
-        <v>2026-08-04T08:17:31.120Z</v>
+        <v>2026-08-04T08:53:38.100Z</v>
       </c>
       <c r="N29" t="str">
         <v>[]</v>
@@ -4393,19 +4392,19 @@
 Done exactly like the reference picture</v>
       </c>
       <c r="P29" t="str">
-        <v>2026-08-04T08:17:31.120Z</v>
+        <v>2026-08-04T08:53:38.100Z</v>
       </c>
       <c r="Q29" t="str">
-        <v>2026-08-04T08:17:37.955Z</v>
+        <v>2026-08-04T08:53:43.705Z</v>
       </c>
       <c r="R29" t="str">
         <v>[]</v>
       </c>
       <c r="S29" t="str">
-        <v>2026-06-05T08:17:33.323Z</v>
+        <v>2026-06-05T08:53:40.513Z</v>
       </c>
       <c r="T29" t="str">
-        <v>2026-08-04T08:17:45.657Z</v>
+        <v>2026-08-04T08:53:49.861Z</v>
       </c>
     </row>
     <row r="30">
@@ -4446,7 +4445,7 @@
         <v>apify</v>
       </c>
       <c r="M30" t="str">
-        <v>2026-08-04T08:17:31.120Z</v>
+        <v>2026-08-04T08:53:38.100Z</v>
       </c>
       <c r="N30" t="str">
         <v>[]</v>
@@ -4455,19 +4454,19 @@
         <v>We ordered Vannila flavour theme cake for our daughter birthday. It was upto the expected level both in taste and theme quality</v>
       </c>
       <c r="P30" t="str">
-        <v>2026-08-04T08:17:31.120Z</v>
+        <v>2026-08-04T08:53:38.100Z</v>
       </c>
       <c r="Q30" t="str">
-        <v>2026-08-04T08:17:38.080Z</v>
+        <v>2026-08-04T08:53:43.783Z</v>
       </c>
       <c r="R30" t="str">
         <v>["https://lh3.googleusercontent.com/grass-cs/ACvplmPqazGT7seHADgBYuM7nHMtdenj7ca55lDKxCXdBfT3ZDp6E2mts5nkDCCVFE7qRIEsqLKJbecGdGpSTF2zkCQcBeEVikiDha5V_c10_eq2sTMWJEqXYoVKpdl6rt8RDrfTPVQ4TSLrYyVS=w600-h450-p-k-no"]</v>
       </c>
       <c r="S30" t="str">
-        <v>2026-06-05T08:17:33.323Z</v>
+        <v>2026-06-05T08:53:40.513Z</v>
       </c>
       <c r="T30" t="str">
-        <v>2026-08-04T08:17:45.658Z</v>
+        <v>2026-08-04T08:53:49.861Z</v>
       </c>
     </row>
     <row r="31">
@@ -4508,7 +4507,7 @@
         <v>apify</v>
       </c>
       <c r="M31" t="str">
-        <v>2026-08-04T08:17:31.120Z</v>
+        <v>2026-08-04T08:53:38.100Z</v>
       </c>
       <c r="N31" t="str">
         <v>[]</v>
@@ -4517,19 +4516,19 @@
         <v>So delicious</v>
       </c>
       <c r="P31" t="str">
-        <v>2026-08-04T08:17:31.120Z</v>
+        <v>2026-08-04T08:53:38.100Z</v>
       </c>
       <c r="Q31" t="str">
-        <v>2026-08-04T08:17:38.190Z</v>
+        <v>2026-08-04T08:53:43.877Z</v>
       </c>
       <c r="R31" t="str">
         <v>[]</v>
       </c>
       <c r="S31" t="str">
-        <v>2026-06-05T08:17:33.323Z</v>
+        <v>2026-06-05T08:53:40.513Z</v>
       </c>
       <c r="T31" t="str">
-        <v>2026-08-04T08:17:45.658Z</v>
+        <v>2026-08-04T08:53:49.861Z</v>
       </c>
     </row>
     <row r="32">
@@ -4570,7 +4569,7 @@
         <v>apify</v>
       </c>
       <c r="M32" t="str">
-        <v>2026-08-04T08:17:31.120Z</v>
+        <v>2026-08-04T08:53:38.100Z</v>
       </c>
       <c r="N32" t="str">
         <v>[]</v>
@@ -4579,19 +4578,19 @@
         <v>Best place for fresh cakes and muffins</v>
       </c>
       <c r="P32" t="str">
-        <v>2026-08-04T08:17:31.120Z</v>
+        <v>2026-08-04T08:53:38.100Z</v>
       </c>
       <c r="Q32" t="str">
-        <v>2026-08-04T08:17:38.330Z</v>
+        <v>2026-08-04T08:53:44.002Z</v>
       </c>
       <c r="R32" t="str">
         <v>[]</v>
       </c>
       <c r="S32" t="str">
-        <v>2026-06-05T08:17:35.289Z</v>
+        <v>2026-06-05T08:53:42.532Z</v>
       </c>
       <c r="T32" t="str">
-        <v>2026-08-04T08:17:45.658Z</v>
+        <v>2026-08-04T08:53:49.861Z</v>
       </c>
     </row>
     <row r="33">
@@ -4632,7 +4631,7 @@
         <v>apify</v>
       </c>
       <c r="M33" t="str">
-        <v>2026-08-04T08:17:31.120Z</v>
+        <v>2026-08-04T08:53:38.100Z</v>
       </c>
       <c r="N33" t="str">
         <v>[]</v>
@@ -4641,19 +4640,19 @@
         <v>The veggie sandwich was delicious! So was the brownie milkshake which is a must try. The atmosphere is really good here and it's def an underrated café.</v>
       </c>
       <c r="P33" t="str">
-        <v>2026-08-04T08:17:31.120Z</v>
+        <v>2026-08-04T08:53:38.100Z</v>
       </c>
       <c r="Q33" t="str">
-        <v>2026-08-04T08:17:38.456Z</v>
+        <v>2026-08-04T08:53:44.095Z</v>
       </c>
       <c r="R33" t="str">
         <v>[]</v>
       </c>
       <c r="S33" t="str">
-        <v>2026-06-05T08:17:35.289Z</v>
+        <v>2026-06-05T08:53:42.532Z</v>
       </c>
       <c r="T33" t="str">
-        <v>2026-08-04T08:17:45.658Z</v>
+        <v>2026-08-04T08:53:49.862Z</v>
       </c>
     </row>
     <row r="34">
@@ -4694,7 +4693,7 @@
         <v>apify</v>
       </c>
       <c r="M34" t="str">
-        <v>2026-08-04T08:17:31.120Z</v>
+        <v>2026-08-04T08:53:38.100Z</v>
       </c>
       <c r="N34" t="str">
         <v>[]</v>
@@ -4703,10 +4702,10 @@
         <v>Excellent taste. Had fun. Excellent customer service. Tres lechues Cherry chocolate is mind blowing.</v>
       </c>
       <c r="P34" t="str">
-        <v>2026-08-04T08:17:31.120Z</v>
+        <v>2026-08-04T08:53:38.100Z</v>
       </c>
       <c r="Q34" t="str">
-        <v>2026-08-04T08:17:38.563Z</v>
+        <v>2026-08-04T08:53:44.218Z</v>
       </c>
       <c r="R34" t="str">
         <v>[]</v>
@@ -4715,7 +4714,7 @@
         <v/>
       </c>
       <c r="T34" t="str">
-        <v>2026-08-04T08:17:45.658Z</v>
+        <v>2026-08-04T08:53:49.862Z</v>
       </c>
     </row>
     <row r="35">
@@ -4756,7 +4755,7 @@
         <v>apify</v>
       </c>
       <c r="M35" t="str">
-        <v>2026-08-04T08:17:31.120Z</v>
+        <v>2026-08-04T08:53:38.100Z</v>
       </c>
       <c r="N35" t="str">
         <v>[]</v>
@@ -4765,10 +4764,10 @@
         <v>I ordered a birthday cake as I specified about cake with animals theme 🎂...I felt so good to taste and it's so good Thank you</v>
       </c>
       <c r="P35" t="str">
-        <v>2026-08-04T08:17:31.120Z</v>
+        <v>2026-08-04T08:53:38.100Z</v>
       </c>
       <c r="Q35" t="str">
-        <v>2026-08-04T08:17:38.672Z</v>
+        <v>2026-08-04T08:53:44.296Z</v>
       </c>
       <c r="R35" t="str">
         <v>[]</v>
@@ -4777,7 +4776,7 @@
         <v/>
       </c>
       <c r="T35" t="str">
-        <v>2026-08-04T08:17:45.658Z</v>
+        <v>2026-08-04T08:53:49.862Z</v>
       </c>
     </row>
     <row r="36">
@@ -4818,7 +4817,7 @@
         <v>apify</v>
       </c>
       <c r="M36" t="str">
-        <v>2026-08-04T08:17:31.120Z</v>
+        <v>2026-08-04T08:53:38.100Z</v>
       </c>
       <c r="N36" t="str">
         <v>[]</v>
@@ -4827,19 +4826,19 @@
         <v>Cake was very very tasty and look wise very beautiful and i really enjoy a lot and my family members thank you so much for your beautiful cake🥰🥰</v>
       </c>
       <c r="P36" t="str">
-        <v>2026-08-04T08:17:31.120Z</v>
+        <v>2026-08-04T08:53:38.100Z</v>
       </c>
       <c r="Q36" t="str">
-        <v>2026-08-04T08:17:38.797Z</v>
+        <v>2026-08-04T08:53:44.422Z</v>
       </c>
       <c r="R36" t="str">
         <v>["https://lh3.googleusercontent.com/grass-cs/ACvplmPEeUPLqKmsdMkTdKuoXGDOF8FLbqv6pUAcvH6GEzKqRC0N88UDcuyMnyhEE47x34SP-wdjoPtrNiWeTQScGKXIojC8hlTXcA3G2cchgSCF60cJOkkNYqh3mXXViIQSsepwVOopjTXtXOOC=w300-h450-p-k-no","https://lh3.googleusercontent.com/grass-cs/ACvplmP_Co_hhy-KcG2OYgEL3UMCuP7KpxjnLXtF8R2Xz_Mi20qsy3hYlcfgGZjDlGQMSXesFzJy4hqE7bEp_7q_GmY6sN1Rv335HQMy1osqlPznyQI2-q9Yj_z8MxIaUsvw84sV9ClZD_5cL3QI=w300-h450-p-k-no"]</v>
       </c>
       <c r="S36" t="str">
-        <v>2026-05-06T08:17:35.289Z</v>
+        <v>2026-05-06T08:53:42.532Z</v>
       </c>
       <c r="T36" t="str">
-        <v>2026-08-04T08:17:45.658Z</v>
+        <v>2026-08-04T08:53:49.862Z</v>
       </c>
     </row>
     <row r="37">
@@ -4880,7 +4879,7 @@
         <v>apify</v>
       </c>
       <c r="M37" t="str">
-        <v>2026-08-04T08:17:31.120Z</v>
+        <v>2026-08-04T08:53:38.100Z</v>
       </c>
       <c r="N37" t="str">
         <v>[]</v>
@@ -4889,10 +4888,10 @@
         <v>Very nice</v>
       </c>
       <c r="P37" t="str">
-        <v>2026-08-04T08:17:31.120Z</v>
+        <v>2026-08-04T08:53:38.100Z</v>
       </c>
       <c r="Q37" t="str">
-        <v>2026-08-04T08:17:38.907Z</v>
+        <v>2026-08-04T08:53:44.530Z</v>
       </c>
       <c r="R37" t="str">
         <v>["https://lh3.googleusercontent.com/grass-cs/ACvplmOvXdkYfrMjALMZR-57O-Gnx2doUV8b5TwpE9h8U9eY1WFyeFXJgvIiiMx5XqGY53Jm6Cl3EqF-GVxW80zTQud1K_COc_AMGwcJexBvYc03meUJhAwWV0yT7CcsvImVchoP_SGWF7_3n_4T=w300-h450-p-k-no","https://lh3.googleusercontent.com/grass-cs/ACvplmMvR5JqCiEyVYPEZHvHtmHzXLvQX8x01nBqyTFypOZv9xeTsnvLC0g3dUCAcFhZIa15HpWucboRVbvyEtxjevXgFS80E1q3ad8WndsshfBipdU4prPwjinanrFjBZ2SDP544Wk_hVokA3M=w300-h450-p-k-no"]</v>
@@ -4901,7 +4900,7 @@
         <v/>
       </c>
       <c r="T37" t="str">
-        <v>2026-08-04T08:17:45.658Z</v>
+        <v>2026-08-04T08:53:49.862Z</v>
       </c>
     </row>
     <row r="38">
@@ -4942,7 +4941,7 @@
         <v>apify</v>
       </c>
       <c r="M38" t="str">
-        <v>2026-08-04T08:17:31.120Z</v>
+        <v>2026-08-04T08:53:38.100Z</v>
       </c>
       <c r="N38" t="str">
         <v>[]</v>
@@ -4951,19 +4950,19 @@
         <v>3 months agoOrder typeTake outMeal typeBrunchLike</v>
       </c>
       <c r="P38" t="str">
-        <v>2026-08-04T08:17:31.120Z</v>
+        <v>2026-08-04T08:53:38.100Z</v>
       </c>
       <c r="Q38" t="str">
-        <v>2026-08-04T08:17:39.251Z</v>
+        <v>2026-08-04T08:53:44.736Z</v>
       </c>
       <c r="R38" t="str">
         <v>[]</v>
       </c>
       <c r="S38" t="str">
-        <v>2026-05-06T08:17:37.228Z</v>
+        <v>2026-05-06T08:53:44.328Z</v>
       </c>
       <c r="T38" t="str">
-        <v>2026-08-04T08:17:45.658Z</v>
+        <v>2026-08-04T08:53:49.862Z</v>
       </c>
     </row>
     <row r="39">
@@ -5004,7 +5003,7 @@
         <v>apify</v>
       </c>
       <c r="M39" t="str">
-        <v>2026-08-04T08:17:31.120Z</v>
+        <v>2026-08-04T08:53:38.100Z</v>
       </c>
       <c r="N39" t="str">
         <v>[]</v>
@@ -5013,19 +5012,19 @@
         <v>Had ordered for a Rose Milk Birthday Cake few months before and it exceeded the expectation of everyone in taste. The order and Delicery experience was also very professional and able to feel the passion of the promoter. Today ordered their Mango Stick Melt Box, which again was yummy and felt very light. One of the must try dessert this summer</v>
       </c>
       <c r="P39" t="str">
-        <v>2026-08-04T08:17:31.120Z</v>
+        <v>2026-08-04T08:53:38.100Z</v>
       </c>
       <c r="Q39" t="str">
-        <v>2026-08-04T08:17:39.361Z</v>
+        <v>2026-08-04T08:53:44.847Z</v>
       </c>
       <c r="R39" t="str">
         <v>["https://lh3.googleusercontent.com/grass-cs/ACvplmO-N5w1dEs0O91N0FKZOducip4r_G6nJ-uRrXgwAY1ch2MpCdvyvzlbSP1qGIWVZTuEN-omDu6V2PCWMUAmZerRBJa6GjQeQhqwI2gXTWY0ovbtRUWjElq4ybDGU7AVZtKKh6QznqzFYYY=w300-h450-p-k-no","https://lh3.googleusercontent.com/grass-cs/ACvplmO-0GzWLqvrpb7tOp3qI8jtfk3fwsnUsUA10rG4a4GL4moYeolLxjyI81nOM5KUNSSMysTTa6iAv6pjZzKChSPhonfCcLmKs7sa8B5Py6dQSTyTGv3wQtbd7bCug0OVz_VCnjqDa9S4tK4=w300-h450-p-k-no"]</v>
       </c>
       <c r="S39" t="str">
-        <v>2026-05-06T08:17:37.228Z</v>
+        <v>2026-05-06T08:53:44.328Z</v>
       </c>
       <c r="T39" t="str">
-        <v>2026-08-04T08:17:45.658Z</v>
+        <v>2026-08-04T08:53:49.862Z</v>
       </c>
     </row>
     <row r="40" xml:space="preserve">
@@ -5066,7 +5065,7 @@
         <v>apify</v>
       </c>
       <c r="M40" t="str">
-        <v>2026-08-04T08:17:31.120Z</v>
+        <v>2026-08-04T08:53:38.100Z</v>
       </c>
       <c r="N40" t="str">
         <v>[]</v>
@@ -5076,10 +5075,10 @@
 More than we expected.. 💜</v>
       </c>
       <c r="P40" t="str">
-        <v>2026-08-04T08:17:31.120Z</v>
+        <v>2026-08-04T08:53:38.100Z</v>
       </c>
       <c r="Q40" t="str">
-        <v>2026-08-04T08:17:39.487Z</v>
+        <v>2026-08-04T08:53:44.955Z</v>
       </c>
       <c r="R40" t="str">
         <v>["https://lh3.googleusercontent.com/grass-cs/ACvplmPppG6bpan-PqNkdyYROI_GUqgKL5SkLkwHlc6hZ5UsjfEvZb4yh-p78ml_bBCSOInRHDlkn29mYeMDwxrT-JY98ScPev3xFp5suHXYhorK7cGUge725FmkytSMHvSBVPSF6iGGACO7S78A=w300-h450-p-k-no","https://lh3.googleusercontent.com/grass-cs/ACvplmNrLWqWwGL_tohqVBl0aPiP1kMOUy8TLbfusos_0QTI2tWQpLxNsI679f82klUWzN_bCY-t_QNGtX5VZcgiuVjoQhSGcns5ufrbyfskI0_195jt2luuUMKz-VsWvmgohBy_052p_T7fGtw=w300-h225-p-k-no","https://lh3.googleusercontent.com/grass-cs/ACvplmOKtfGwjXym7lYQbEevm97GAQcPGzeKUGYX-CC-Sw3CAAcsiQgO56UEte0FH539vVZoR3PsYCNTUJm0zijx7lVxA3BZb0zQJV1yJFuO9NqPERQ3fB93JgclNn9Enc7Kk8ElZoTtnrgixrpC=w300-h225-p-k-no"]</v>
@@ -5088,7 +5087,7 @@
         <v/>
       </c>
       <c r="T40" t="str">
-        <v>2026-08-04T08:17:45.658Z</v>
+        <v>2026-08-04T08:53:49.862Z</v>
       </c>
     </row>
     <row r="41">
@@ -5129,7 +5128,7 @@
         <v>apify</v>
       </c>
       <c r="M41" t="str">
-        <v>2026-08-04T08:17:31.120Z</v>
+        <v>2026-08-04T08:53:38.100Z</v>
       </c>
       <c r="N41" t="str">
         <v>[]</v>
@@ -5138,19 +5137,19 @@
         <v>That cake was for my daughter’s 11th birthday, she loved the vancho flavor and the cake was better than she expected! Thank you so much.</v>
       </c>
       <c r="P41" t="str">
-        <v>2026-08-04T08:17:31.120Z</v>
+        <v>2026-08-04T08:53:38.100Z</v>
       </c>
       <c r="Q41" t="str">
-        <v>2026-08-04T08:17:39.644Z</v>
+        <v>2026-08-04T08:53:45.082Z</v>
       </c>
       <c r="R41" t="str">
         <v>["https://lh3.googleusercontent.com/grass-cs/ACvplmNNmN-xWtfJDdu2OsGSKIuQu9KIGUeuEgDBezbgsCV2v5Ld2z1dXu7m523gMEDfkvgtNl-5SwbbgedzP-p_jynvs_TvSwW0jeE6BFTaHAA_-jtyx45gu_ULmiYjJ14_3oPgCe_s-p4cX3XM=w600-h450-p-k-no"]</v>
       </c>
       <c r="S41" t="str">
-        <v>2026-05-06T08:17:37.228Z</v>
+        <v>2026-05-06T08:53:44.328Z</v>
       </c>
       <c r="T41" t="str">
-        <v>2026-08-04T08:17:45.658Z</v>
+        <v>2026-08-04T08:53:49.862Z</v>
       </c>
     </row>
     <row r="42">
@@ -5191,7 +5190,7 @@
         <v>apify</v>
       </c>
       <c r="M42" t="str">
-        <v>2026-08-04T08:17:31.120Z</v>
+        <v>2026-08-04T08:53:38.100Z</v>
       </c>
       <c r="N42" t="str">
         <v>[]</v>
@@ -5200,19 +5199,19 @@
         <v>We ordered rose milk cake from chocolate mine. The cake was absolutely delicious and flavorful and very well customized as per our wish...Everyone loved it.. thank you for the wonderful cake</v>
       </c>
       <c r="P42" t="str">
-        <v>2026-08-04T08:17:31.120Z</v>
+        <v>2026-08-04T08:53:38.100Z</v>
       </c>
       <c r="Q42" t="str">
-        <v>2026-08-04T08:17:39.768Z</v>
+        <v>2026-08-04T08:53:45.191Z</v>
       </c>
       <c r="R42" t="str">
         <v>[]</v>
       </c>
       <c r="S42" t="str">
-        <v>2026-05-06T08:17:37.228Z</v>
+        <v>2026-05-06T08:53:44.328Z</v>
       </c>
       <c r="T42" t="str">
-        <v>2026-08-04T08:17:45.658Z</v>
+        <v>2026-08-04T08:53:49.862Z</v>
       </c>
     </row>
     <row r="43">
@@ -5253,7 +5252,7 @@
         <v>apify</v>
       </c>
       <c r="M43" t="str">
-        <v>2026-08-04T08:17:31.120Z</v>
+        <v>2026-08-04T08:53:38.100Z</v>
       </c>
       <c r="N43" t="str">
         <v>[]</v>
@@ -5262,19 +5261,19 @@
         <v>Choco Lava Cake and Cheese Cake must try😌😋</v>
       </c>
       <c r="P43" t="str">
-        <v>2026-08-04T08:17:31.120Z</v>
+        <v>2026-08-04T08:53:38.100Z</v>
       </c>
       <c r="Q43" t="str">
-        <v>2026-08-04T08:17:39.893Z</v>
+        <v>2026-08-04T08:53:45.301Z</v>
       </c>
       <c r="R43" t="str">
         <v>[]</v>
       </c>
       <c r="S43" t="str">
-        <v>2026-04-06T08:17:39.393Z</v>
+        <v>2026-04-06T08:53:46.316Z</v>
       </c>
       <c r="T43" t="str">
-        <v>2026-08-04T08:17:45.658Z</v>
+        <v>2026-08-04T08:53:49.862Z</v>
       </c>
     </row>
     <row r="44">
@@ -5315,7 +5314,7 @@
         <v>apify</v>
       </c>
       <c r="M44" t="str">
-        <v>2026-08-04T08:17:31.120Z</v>
+        <v>2026-08-04T08:53:38.100Z</v>
       </c>
       <c r="N44" t="str">
         <v>[]</v>
@@ -5324,19 +5323,19 @@
         <v>Thank you so much mam...it was a delicious cake for my daughter...all the children loved the cake and decoration was superb</v>
       </c>
       <c r="P44" t="str">
-        <v>2026-08-04T08:17:31.120Z</v>
+        <v>2026-08-04T08:53:38.100Z</v>
       </c>
       <c r="Q44" t="str">
-        <v>2026-08-04T08:17:40.003Z</v>
+        <v>2026-08-04T08:53:45.409Z</v>
       </c>
       <c r="R44" t="str">
         <v>["https://lh3.googleusercontent.com/grass-cs/ACvplmPA3y_aD66omtRox5jRa9j6deraN4g_Zl8hgzlp_W4viyqhRVtOFyZcsQkQ7sLel_luWGoGcKwwazGIa0HEUK_1w7MWiurNLcTLonU-zCnlzUbczjLnbVwz9UpwUMyEsTXcuyq3bjUPEByK=w600-h450-p-k-no"]</v>
       </c>
       <c r="S44" t="str">
-        <v>2026-04-06T08:17:39.393Z</v>
+        <v>2026-04-06T08:53:46.316Z</v>
       </c>
       <c r="T44" t="str">
-        <v>2026-08-04T08:17:45.658Z</v>
+        <v>2026-08-04T08:53:49.862Z</v>
       </c>
     </row>
     <row r="45">
@@ -5377,7 +5376,7 @@
         <v>apify</v>
       </c>
       <c r="M45" t="str">
-        <v>2026-08-04T08:17:31.120Z</v>
+        <v>2026-08-04T08:53:38.101Z</v>
       </c>
       <c r="N45" t="str">
         <v>[]</v>
@@ -5386,19 +5385,19 @@
         <v>We recently celebrated our lil ones bday at this cafe which turned out to be a full satisfied event for us! Throughout all the details and requests they were polite and served us the best. Spl mention- their hazelnut hot choc is a must try🥤🥰</v>
       </c>
       <c r="P45" t="str">
-        <v>2026-08-04T08:17:31.120Z</v>
+        <v>2026-08-04T08:53:38.101Z</v>
       </c>
       <c r="Q45" t="str">
-        <v>2026-08-04T08:17:40.145Z</v>
+        <v>2026-08-04T08:53:45.504Z</v>
       </c>
       <c r="R45" t="str">
         <v>["https://lh3.googleusercontent.com/grass-cs/ACvplmMfDKskGJQvaa59X160AGAtoF1jMbela-u825Lp0at4z3UpqyK-hvm_uDw7yTWzcZSrCHKFT8OnsRn91ItJlpvWD15of1EEkBAqOupf7eWscv-z_pweKZIV278buQ_4o3GTerHVFhqhg-Sa=w300-h450-p-k-no","https://lh3.googleusercontent.com/grass-cs/ACvplmPs7YFQk61QJJjB81iJcGqG3fZrT69mveX24qkda-HcKaWEJglWG9zwpJSW2wlf5YHHhYKmjviuXCJ1JzA4TxnTgzvwFGjdm6pQnwpOrgE4ioJ8sqlIPAsn2ooTEJ5eDCdRLTKO5OVvn3O3=w300-h450-p-k-no"]</v>
       </c>
       <c r="S45" t="str">
-        <v>2026-04-06T08:17:39.393Z</v>
+        <v>2026-04-06T08:53:46.316Z</v>
       </c>
       <c r="T45" t="str">
-        <v>2026-08-04T08:17:45.658Z</v>
+        <v>2026-08-04T08:53:49.862Z</v>
       </c>
     </row>
     <row r="46">
@@ -5439,7 +5438,7 @@
         <v>apify</v>
       </c>
       <c r="M46" t="str">
-        <v>2026-08-04T08:17:31.120Z</v>
+        <v>2026-08-04T08:53:38.101Z</v>
       </c>
       <c r="N46" t="str">
         <v>[]</v>
@@ -5448,19 +5447,19 @@
         <v>I ordered B'day bento cake for my loved one.......it takes good and also we are tres leches it tadte like topnotch......really enjoyed</v>
       </c>
       <c r="P46" t="str">
-        <v>2026-08-04T08:17:31.120Z</v>
+        <v>2026-08-04T08:53:38.101Z</v>
       </c>
       <c r="Q46" t="str">
-        <v>2026-08-04T08:17:40.302Z</v>
+        <v>2026-08-04T08:53:45.613Z</v>
       </c>
       <c r="R46" t="str">
         <v>[]</v>
       </c>
       <c r="S46" t="str">
-        <v>2026-04-06T08:17:39.393Z</v>
+        <v>2026-04-06T08:53:46.316Z</v>
       </c>
       <c r="T46" t="str">
-        <v>2026-08-04T08:17:45.658Z</v>
+        <v>2026-08-04T08:53:49.862Z</v>
       </c>
     </row>
     <row r="47">
@@ -5501,7 +5500,7 @@
         <v>apify</v>
       </c>
       <c r="M47" t="str">
-        <v>2026-08-04T08:17:31.120Z</v>
+        <v>2026-08-04T08:53:38.101Z</v>
       </c>
       <c r="N47" t="str">
         <v>[]</v>
@@ -5510,19 +5509,19 @@
         <v>The food was good, so was the coffee. It took a long time for the food to arrive once the order was placed</v>
       </c>
       <c r="P47" t="str">
-        <v>2026-08-04T08:17:31.120Z</v>
+        <v>2026-08-04T08:53:38.101Z</v>
       </c>
       <c r="Q47" t="str">
-        <v>2026-08-04T08:17:40.411Z</v>
+        <v>2026-08-04T08:53:45.691Z</v>
       </c>
       <c r="R47" t="str">
         <v>[]</v>
       </c>
       <c r="S47" t="str">
-        <v>2026-04-06T08:17:39.393Z</v>
+        <v>2026-04-06T08:53:46.316Z</v>
       </c>
       <c r="T47" t="str">
-        <v>2026-08-04T08:17:45.658Z</v>
+        <v>2026-08-04T08:53:49.862Z</v>
       </c>
     </row>
     <row r="48">
@@ -5563,7 +5562,7 @@
         <v>apify</v>
       </c>
       <c r="M48" t="str">
-        <v>2026-08-04T08:17:31.120Z</v>
+        <v>2026-08-04T08:53:38.101Z</v>
       </c>
       <c r="N48" t="str">
         <v>[]</v>
@@ -5572,19 +5571,19 @@
         <v>Very good service</v>
       </c>
       <c r="P48" t="str">
-        <v>2026-08-04T08:17:31.120Z</v>
+        <v>2026-08-04T08:53:38.101Z</v>
       </c>
       <c r="Q48" t="str">
-        <v>2026-08-04T08:17:40.522Z</v>
+        <v>2026-08-04T08:53:45.785Z</v>
       </c>
       <c r="R48" t="str">
         <v>[]</v>
       </c>
       <c r="S48" t="str">
-        <v>2026-04-06T08:17:39.393Z</v>
+        <v>2026-04-06T08:53:46.316Z</v>
       </c>
       <c r="T48" t="str">
-        <v>2026-08-04T08:17:45.658Z</v>
+        <v>2026-08-04T08:53:49.862Z</v>
       </c>
     </row>
     <row r="49">
@@ -5625,7 +5624,7 @@
         <v>apify</v>
       </c>
       <c r="M49" t="str">
-        <v>2026-08-04T08:17:31.120Z</v>
+        <v>2026-08-04T08:53:38.101Z</v>
       </c>
       <c r="N49" t="str">
         <v>[]</v>
@@ -5634,19 +5633,19 @@
         <v>Pleasant ambience and the taste was extraordinary ❤️</v>
       </c>
       <c r="P49" t="str">
-        <v>2026-08-04T08:17:31.120Z</v>
+        <v>2026-08-04T08:53:38.101Z</v>
       </c>
       <c r="Q49" t="str">
-        <v>2026-08-04T08:17:40.645Z</v>
+        <v>2026-08-04T08:53:45.879Z</v>
       </c>
       <c r="R49" t="str">
         <v>[]</v>
       </c>
       <c r="S49" t="str">
-        <v>2026-04-06T08:17:39.393Z</v>
+        <v>2026-04-06T08:53:46.316Z</v>
       </c>
       <c r="T49" t="str">
-        <v>2026-08-04T08:17:45.658Z</v>
+        <v>2026-08-04T08:53:49.862Z</v>
       </c>
     </row>
     <row r="50">
@@ -5687,7 +5686,7 @@
         <v>apify</v>
       </c>
       <c r="M50" t="str">
-        <v>2026-08-04T08:17:31.120Z</v>
+        <v>2026-08-04T08:53:38.101Z</v>
       </c>
       <c r="N50" t="str">
         <v>[]</v>
@@ -5696,19 +5695,19 @@
         <v>Chocolate coffee was top notch🤌🤌</v>
       </c>
       <c r="P50" t="str">
-        <v>2026-08-04T08:17:31.120Z</v>
+        <v>2026-08-04T08:53:38.101Z</v>
       </c>
       <c r="Q50" t="str">
-        <v>2026-08-04T08:17:40.788Z</v>
+        <v>2026-08-04T08:53:45.988Z</v>
       </c>
       <c r="R50" t="str">
         <v>[]</v>
       </c>
       <c r="S50" t="str">
-        <v>2026-04-06T08:17:39.393Z</v>
+        <v>2026-04-06T08:53:46.316Z</v>
       </c>
       <c r="T50" t="str">
-        <v>2026-08-04T08:17:45.658Z</v>
+        <v>2026-08-04T08:53:49.862Z</v>
       </c>
     </row>
     <row r="51">
@@ -5770,7 +5769,7 @@
         <v>2026-03-07T05:27:19.909Z</v>
       </c>
       <c r="T51" t="str">
-        <v>2026-08-04T08:17:45.658Z</v>
+        <v>2026-08-04T08:53:49.862Z</v>
       </c>
     </row>
     <row r="52">
@@ -5832,7 +5831,7 @@
         <v>2026-03-06T02:56:06.693Z</v>
       </c>
       <c r="T52" t="str">
-        <v>2026-08-04T08:17:45.658Z</v>
+        <v>2026-08-04T08:53:49.862Z</v>
       </c>
     </row>
     <row r="53">
@@ -5894,7 +5893,7 @@
         <v>2026-03-01T06:45:44.320Z</v>
       </c>
       <c r="T53" t="str">
-        <v>2026-08-04T08:17:45.658Z</v>
+        <v>2026-08-04T08:53:49.862Z</v>
       </c>
     </row>
     <row r="54">
@@ -5956,7 +5955,7 @@
         <v>2026-02-27T10:19:29.898Z</v>
       </c>
       <c r="T54" t="str">
-        <v>2026-08-04T08:17:45.659Z</v>
+        <v>2026-08-04T08:53:49.862Z</v>
       </c>
     </row>
     <row r="55">
@@ -6018,7 +6017,7 @@
         <v>2026-02-26T13:13:36.195Z</v>
       </c>
       <c r="T55" t="str">
-        <v>2026-08-04T08:17:45.659Z</v>
+        <v>2026-08-04T08:53:49.862Z</v>
       </c>
     </row>
     <row r="56">
@@ -6080,7 +6079,7 @@
         <v>2026-02-24T18:31:20.668Z</v>
       </c>
       <c r="T56" t="str">
-        <v>2026-08-04T08:17:45.659Z</v>
+        <v>2026-08-04T08:53:49.862Z</v>
       </c>
     </row>
     <row r="57">
@@ -6142,7 +6141,7 @@
         <v>2026-02-11T10:33:29.369Z</v>
       </c>
       <c r="T57" t="str">
-        <v>2026-08-04T08:17:45.659Z</v>
+        <v>2026-08-04T08:53:49.862Z</v>
       </c>
     </row>
     <row r="58" xml:space="preserve">
@@ -6205,7 +6204,7 @@
         <v>2026-03-06T08:34:24.383Z</v>
       </c>
       <c r="T58" t="str">
-        <v>2026-08-04T08:17:45.659Z</v>
+        <v>2026-08-04T08:53:49.862Z</v>
       </c>
     </row>
     <row r="59">
@@ -6267,7 +6266,7 @@
         <v>2026-03-06T08:34:24.383Z</v>
       </c>
       <c r="T59" t="str">
-        <v>2026-08-04T08:17:45.659Z</v>
+        <v>2026-08-04T08:53:49.862Z</v>
       </c>
     </row>
     <row r="60">
@@ -6329,7 +6328,7 @@
         <v>2026-03-06T08:34:24.383Z</v>
       </c>
       <c r="T60" t="str">
-        <v>2026-08-04T08:17:45.659Z</v>
+        <v>2026-08-04T08:53:49.862Z</v>
       </c>
     </row>
     <row r="61">
@@ -6391,7 +6390,7 @@
         <v>2026-03-06T08:34:24.383Z</v>
       </c>
       <c r="T61" t="str">
-        <v>2026-08-04T08:17:45.659Z</v>
+        <v>2026-08-04T08:53:49.862Z</v>
       </c>
     </row>
     <row r="62">
@@ -6453,7 +6452,7 @@
         <v>2026-03-06T08:34:24.383Z</v>
       </c>
       <c r="T62" t="str">
-        <v>2026-08-04T08:17:45.659Z</v>
+        <v>2026-08-04T08:53:49.862Z</v>
       </c>
     </row>
     <row r="63">
@@ -6515,7 +6514,7 @@
         <v>2026-02-04T08:34:24.383Z</v>
       </c>
       <c r="T63" t="str">
-        <v>2026-08-04T08:17:45.659Z</v>
+        <v>2026-08-04T08:53:49.863Z</v>
       </c>
     </row>
     <row r="64" xml:space="preserve">
@@ -6578,7 +6577,7 @@
         <v>2026-02-01T13:59:29.989Z</v>
       </c>
       <c r="T64" t="str">
-        <v>2026-08-04T08:17:45.659Z</v>
+        <v>2026-08-04T08:53:49.863Z</v>
       </c>
     </row>
     <row r="65">
@@ -6640,7 +6639,7 @@
         <v>2026-02-24T17:08:34.231Z</v>
       </c>
       <c r="T65" t="str">
-        <v>2026-08-04T08:17:45.659Z</v>
+        <v>2026-08-04T08:53:49.863Z</v>
       </c>
     </row>
     <row r="66">
@@ -6702,7 +6701,7 @@
         <v>2026-02-13T15:37:15.383Z</v>
       </c>
       <c r="T66" t="str">
-        <v>2026-08-04T08:17:45.659Z</v>
+        <v>2026-08-04T08:53:49.863Z</v>
       </c>
     </row>
     <row r="67" xml:space="preserve">
@@ -6768,7 +6767,7 @@
         <v>2026-02-13T15:37:15.383Z</v>
       </c>
       <c r="T67" t="str">
-        <v>2026-08-04T08:17:45.659Z</v>
+        <v>2026-08-04T08:53:49.863Z</v>
       </c>
     </row>
     <row r="68">
@@ -6830,7 +6829,7 @@
         <v>2026-02-13T15:37:17.562Z</v>
       </c>
       <c r="T68" t="str">
-        <v>2026-08-04T08:17:45.659Z</v>
+        <v>2026-08-04T08:53:49.863Z</v>
       </c>
     </row>
     <row r="69">
@@ -6892,7 +6891,7 @@
         <v>2026-02-13T15:37:17.562Z</v>
       </c>
       <c r="T69" t="str">
-        <v>2026-08-04T08:17:45.659Z</v>
+        <v>2026-08-04T08:53:49.863Z</v>
       </c>
     </row>
     <row r="70">
@@ -6954,7 +6953,7 @@
         <v>2026-02-13T15:37:17.562Z</v>
       </c>
       <c r="T70" t="str">
-        <v>2026-08-04T08:17:45.659Z</v>
+        <v>2026-08-04T08:53:49.863Z</v>
       </c>
     </row>
     <row r="71">
@@ -7016,7 +7015,7 @@
         <v>2026-01-14T15:37:17.562Z</v>
       </c>
       <c r="T71" t="str">
-        <v>2026-08-04T08:17:45.659Z</v>
+        <v>2026-08-04T08:53:49.863Z</v>
       </c>
     </row>
     <row r="72">
@@ -7078,7 +7077,7 @@
         <v>2026-01-14T15:26:08.566Z</v>
       </c>
       <c r="T72" t="str">
-        <v>2026-08-04T08:17:45.659Z</v>
+        <v>2026-08-04T08:53:49.863Z</v>
       </c>
     </row>
     <row r="73">
@@ -7137,7 +7136,7 @@
         <v>["https://lh3.googleusercontent.com/a-/ALV-UjX1CoTz92K_REISpy2kSrmfkUl8O2_fiev-hVBoxR0mWvdo3xi9hg=w36-h36-p-rp-mo-br100"]</v>
       </c>
       <c r="T73" t="str">
-        <v>2026-08-04T08:17:45.659Z</v>
+        <v>2026-08-04T08:53:49.863Z</v>
       </c>
     </row>
     <row r="74">
@@ -7199,7 +7198,7 @@
         <v>2026-06-15T13:04:41.344Z</v>
       </c>
       <c r="T74" t="str">
-        <v>2026-08-04T08:17:45.659Z</v>
+        <v>2026-08-04T08:53:49.863Z</v>
       </c>
     </row>
     <row r="75">
@@ -7261,7 +7260,7 @@
         <v>2026-05-25T17:13:36.799Z</v>
       </c>
       <c r="T75" t="str">
-        <v>2026-08-04T08:17:45.659Z</v>
+        <v>2026-08-04T08:53:49.863Z</v>
       </c>
     </row>
     <row r="76">
@@ -7323,7 +7322,7 @@
         <v>2026-06-03T16:50:09.620Z</v>
       </c>
       <c r="T76" t="str">
-        <v>2026-08-04T08:17:45.659Z</v>
+        <v>2026-08-04T08:53:49.863Z</v>
       </c>
     </row>
     <row r="77">
@@ -7385,7 +7384,7 @@
         <v>2026-04-21T05:25:07.829Z</v>
       </c>
       <c r="T77" t="str">
-        <v>2026-08-04T08:17:45.659Z</v>
+        <v>2026-08-04T08:53:49.863Z</v>
       </c>
     </row>
     <row r="78">
@@ -7447,7 +7446,7 @@
         <v>2026-02-27T10:36:46.583Z</v>
       </c>
       <c r="T78" t="str">
-        <v>2026-08-04T08:17:45.659Z</v>
+        <v>2026-08-04T08:53:49.863Z</v>
       </c>
     </row>
     <row r="79">
@@ -7509,7 +7508,7 @@
         <v>2026-01-28T10:36:46.583Z</v>
       </c>
       <c r="T79" t="str">
-        <v>2026-08-04T08:17:45.659Z</v>
+        <v>2026-08-04T08:53:49.863Z</v>
       </c>
     </row>
     <row r="80">
@@ -7550,7 +7549,7 @@
         <v>apify</v>
       </c>
       <c r="M80" t="str">
-        <v>2026-08-04T08:17:31.119Z</v>
+        <v>2026-08-04T08:53:38.100Z</v>
       </c>
       <c r="N80" t="str">
         <v>[]</v>
@@ -7559,19 +7558,19 @@
         <v>Good desserts 🤤🤤🤤🤤🤤🤤</v>
       </c>
       <c r="P80" t="str">
-        <v>2026-08-04T08:17:31.119Z</v>
+        <v>2026-08-04T08:53:38.100Z</v>
       </c>
       <c r="Q80" t="str">
-        <v>2026-08-04T08:17:35.081Z</v>
+        <v>2026-08-04T08:53:41.548Z</v>
       </c>
       <c r="R80" t="str">
         <v>[]</v>
       </c>
       <c r="S80" t="str">
-        <v>2026-07-05T08:17:27.287Z</v>
+        <v>2026-07-05T08:53:34.387Z</v>
       </c>
       <c r="T80" t="str">
-        <v>2026-08-04T08:17:45.659Z</v>
+        <v>2026-08-04T08:53:49.863Z</v>
       </c>
     </row>
     <row r="81">
@@ -7612,7 +7611,7 @@
         <v>apify</v>
       </c>
       <c r="M81" t="str">
-        <v>2026-08-04T08:17:31.119Z</v>
+        <v>2026-08-04T08:53:38.100Z</v>
       </c>
       <c r="N81" t="str">
         <v>[]</v>
@@ -7621,19 +7620,19 @@
         <v>Good service</v>
       </c>
       <c r="P81" t="str">
-        <v>2026-08-04T08:17:31.119Z</v>
+        <v>2026-08-04T08:53:38.100Z</v>
       </c>
       <c r="Q81" t="str">
-        <v>2026-08-04T08:17:35.426Z</v>
+        <v>2026-08-04T08:53:41.627Z</v>
       </c>
       <c r="R81" t="str">
         <v>[]</v>
       </c>
       <c r="S81" t="str">
-        <v>2026-07-05T08:17:27.287Z</v>
+        <v>2026-07-05T08:53:34.387Z</v>
       </c>
       <c r="T81" t="str">
-        <v>2026-08-04T08:17:45.659Z</v>
+        <v>2026-08-04T08:53:49.863Z</v>
       </c>
     </row>
     <row r="82">
@@ -7674,7 +7673,7 @@
         <v>apify</v>
       </c>
       <c r="M82" t="str">
-        <v>2026-08-04T08:17:31.119Z</v>
+        <v>2026-08-04T08:53:38.100Z</v>
       </c>
       <c r="N82" t="str">
         <v>[]</v>
@@ -7683,19 +7682,19 @@
         <v>Brownie was super appetising!!!</v>
       </c>
       <c r="P82" t="str">
-        <v>2026-08-04T08:17:31.119Z</v>
+        <v>2026-08-04T08:53:38.100Z</v>
       </c>
       <c r="Q82" t="str">
-        <v>2026-08-04T08:17:33.969Z</v>
+        <v>2026-08-04T08:53:40.282Z</v>
       </c>
       <c r="R82" t="str">
         <v>[]</v>
       </c>
       <c r="S82" t="str">
-        <v>2026-07-05T08:17:24.912Z</v>
+        <v>2026-07-05T08:53:32.300Z</v>
       </c>
       <c r="T82" t="str">
-        <v>2026-08-04T08:17:45.659Z</v>
+        <v>2026-08-04T08:53:49.863Z</v>
       </c>
     </row>
     <row r="83">
@@ -7736,7 +7735,7 @@
         <v>apify</v>
       </c>
       <c r="M83" t="str">
-        <v>2026-08-04T08:17:31.119Z</v>
+        <v>2026-08-04T08:53:38.100Z</v>
       </c>
       <c r="N83" t="str">
         <v>[]</v>
@@ -7745,19 +7744,19 @@
         <v>Always good 👍 …</v>
       </c>
       <c r="P83" t="str">
-        <v>2026-08-04T08:17:31.119Z</v>
+        <v>2026-08-04T08:53:38.100Z</v>
       </c>
       <c r="Q83" t="str">
-        <v>2026-08-04T08:17:34.095Z</v>
+        <v>2026-08-04T08:53:40.407Z</v>
       </c>
       <c r="R83" t="str">
         <v>[]</v>
       </c>
       <c r="S83" t="str">
-        <v>2026-07-05T08:17:24.912Z</v>
+        <v>2026-07-05T08:53:32.300Z</v>
       </c>
       <c r="T83" t="str">
-        <v>2026-08-04T08:17:45.659Z</v>
+        <v>2026-08-04T08:53:49.863Z</v>
       </c>
     </row>
     <row r="84">
@@ -7798,7 +7797,7 @@
         <v>apify</v>
       </c>
       <c r="M84" t="str">
-        <v>2026-08-04T08:17:31.119Z</v>
+        <v>2026-08-04T08:53:38.100Z</v>
       </c>
       <c r="N84" t="str">
         <v>[]</v>
@@ -7807,19 +7806,19 @@
         <v>I ordered a two-tier customized cake for my daughter's birthday, and it was absolutely amazing! The cake tasted delicious, and the customization was done beautifully, exactly as requested. The team was very responsive throughout the process, and the delivery was right on time. Thank you, Chocolate Mine, for making our special day even more memorable!</v>
       </c>
       <c r="P84" t="str">
-        <v>2026-08-04T08:17:31.119Z</v>
+        <v>2026-08-04T08:53:38.100Z</v>
       </c>
       <c r="Q84" t="str">
-        <v>2026-08-04T08:17:34.189Z</v>
+        <v>2026-08-04T08:53:40.517Z</v>
       </c>
       <c r="R84" t="str">
         <v>["https://lh3.googleusercontent.com/grass-cs/ACvplmNu77SJ-0-7NnAzJiHAAOABAGvqkbfljqSNTUryL9ONO_o3ixSkb_SByVgEktCnWa4-witFHfo4sil0aAB7hK1jbLWIJ3GnWVFQRVM2iGvfCVEpsuLEiXKbIWaaHsAK-r8ft91K7dxkx2SH=w300-h225-p-k-no","https://lh3.googleusercontent.com/grass-cs/ACvplmOYZR9CLhI8X2bpM9zsIE6IYWaqqZna4v1o1wZOkmFlEqswyPWzwT4pjKBkffu5vCQLRBUzTMhxP-e84z9NtB7h0xFYFuWiX_sf6JLz3RqnUm5EE3-vKLHAAPjvOqBOgGlARPf0FIB9V1M=w300-h225-p-k-no","https://lh3.googleusercontent.com/grass-cs/ACvplmONdyXH4lgUt4orpviuy7rfWhuQr7jC1FolwdOH6QSWQd-Ay9j8V--oGjs-ip_-nIeQ-ZDcr_BGD3R7Bwu3yhj6r8qwKzR1euBSuRMmdGEaTbsaDJnJ692NCKn0lt8gLXsREUUbkP_V0OS9=w300-h225-p-k-no","https://lh3.googleusercontent.com/grass-cs/ACvplmO68XpnXzoXJ7vBYiLgJjCtIhUhleb8qkUlBWeM3j_mB5fF8cE21n6M7geVk8dYzOHHtuksY0xDXL1E6OlMH3B4MpTw5ITyb4a4ZTvmRQC8gxqh2W3Eap31QuXdZ4Q3wPMKK_Zvzd6h_Swy=w300-h225-p-k-no"]</v>
       </c>
       <c r="S84" t="str">
-        <v>2026-07-05T08:17:24.912Z</v>
+        <v>2026-07-05T08:53:32.300Z</v>
       </c>
       <c r="T84" t="str">
-        <v>2026-08-04T08:17:45.660Z</v>
+        <v>2026-08-04T08:53:49.863Z</v>
       </c>
     </row>
     <row r="85">
@@ -7860,7 +7859,7 @@
         <v>apify</v>
       </c>
       <c r="M85" t="str">
-        <v>2026-08-04T08:17:31.119Z</v>
+        <v>2026-08-04T08:53:38.100Z</v>
       </c>
       <c r="N85" t="str">
         <v>[]</v>
@@ -7869,19 +7868,19 @@
         <v>Good desserts with calm atmosphere</v>
       </c>
       <c r="P85" t="str">
-        <v>2026-08-04T08:17:31.119Z</v>
+        <v>2026-08-04T08:53:38.100Z</v>
       </c>
       <c r="Q85" t="str">
-        <v>2026-08-04T08:17:34.281Z</v>
+        <v>2026-08-04T08:53:40.625Z</v>
       </c>
       <c r="R85" t="str">
         <v>[]</v>
       </c>
       <c r="S85" t="str">
-        <v>2026-07-05T08:17:27.287Z</v>
+        <v>2026-07-05T08:53:34.387Z</v>
       </c>
       <c r="T85" t="str">
-        <v>2026-08-04T08:17:45.660Z</v>
+        <v>2026-08-04T08:53:49.863Z</v>
       </c>
     </row>
     <row r="86">
@@ -7922,7 +7921,7 @@
         <v>apify</v>
       </c>
       <c r="M86" t="str">
-        <v>2026-08-04T08:17:31.119Z</v>
+        <v>2026-08-04T08:53:38.100Z</v>
       </c>
       <c r="N86" t="str">
         <v>[]</v>
@@ -7931,19 +7930,19 @@
         <v>Extraordinary ambience and wonderful service</v>
       </c>
       <c r="P86" t="str">
-        <v>2026-08-04T08:17:31.119Z</v>
+        <v>2026-08-04T08:53:38.100Z</v>
       </c>
       <c r="Q86" t="str">
-        <v>2026-08-04T08:17:34.392Z</v>
+        <v>2026-08-04T08:53:40.735Z</v>
       </c>
       <c r="R86" t="str">
         <v>[]</v>
       </c>
       <c r="S86" t="str">
-        <v>2026-07-05T08:17:27.287Z</v>
+        <v>2026-07-05T08:53:34.387Z</v>
       </c>
       <c r="T86" t="str">
-        <v>2026-08-04T08:17:45.660Z</v>
+        <v>2026-08-04T08:53:49.863Z</v>
       </c>
     </row>
     <row r="87">
@@ -7984,7 +7983,7 @@
         <v>apify</v>
       </c>
       <c r="M87" t="str">
-        <v>2026-08-04T08:17:31.119Z</v>
+        <v>2026-08-04T08:53:38.100Z</v>
       </c>
       <c r="N87" t="str">
         <v>[]</v>
@@ -7993,19 +7992,19 @@
         <v>Nice food.Thank you chocolate mine for your wonderful service.</v>
       </c>
       <c r="P87" t="str">
-        <v>2026-08-04T08:17:31.119Z</v>
+        <v>2026-08-04T08:53:38.100Z</v>
       </c>
       <c r="Q87" t="str">
-        <v>2026-08-04T08:17:34.518Z</v>
+        <v>2026-08-04T08:53:41.002Z</v>
       </c>
       <c r="R87" t="str">
         <v>[]</v>
       </c>
       <c r="S87" t="str">
-        <v>2026-07-05T08:17:27.287Z</v>
+        <v>2026-07-05T08:53:34.387Z</v>
       </c>
       <c r="T87" t="str">
-        <v>2026-08-04T08:17:45.660Z</v>
+        <v>2026-08-04T08:53:49.863Z</v>
       </c>
     </row>
     <row r="88">
@@ -8046,7 +8045,7 @@
         <v>apify</v>
       </c>
       <c r="M88" t="str">
-        <v>2026-08-04T08:17:31.119Z</v>
+        <v>2026-08-04T08:53:38.100Z</v>
       </c>
       <c r="N88" t="str">
         <v>[]</v>
@@ -8055,19 +8054,19 @@
         <v>Tried the Tres Leches Lotus Biscoff….which was very yummy. A good ambience with eggless cake ,waffles , shakes ,sandwiches , sundaes etc.</v>
       </c>
       <c r="P88" t="str">
-        <v>2026-08-04T08:17:31.119Z</v>
+        <v>2026-08-04T08:53:38.100Z</v>
       </c>
       <c r="Q88" t="str">
-        <v>2026-08-04T08:17:34.627Z</v>
+        <v>2026-08-04T08:53:41.126Z</v>
       </c>
       <c r="R88" t="str">
         <v>[]</v>
       </c>
       <c r="S88" t="str">
-        <v>2026-07-05T08:17:27.287Z</v>
+        <v>2026-07-05T08:53:34.387Z</v>
       </c>
       <c r="T88" t="str">
-        <v>2026-08-04T08:17:45.660Z</v>
+        <v>2026-08-04T08:53:49.863Z</v>
       </c>
     </row>
     <row r="89">
@@ -8108,7 +8107,7 @@
         <v>apify</v>
       </c>
       <c r="M89" t="str">
-        <v>2026-08-04T08:17:31.119Z</v>
+        <v>2026-08-04T08:53:38.100Z</v>
       </c>
       <c r="N89" t="str">
         <v>[]</v>
@@ -8117,19 +8116,19 @@
         <v>Peak milk cake…. Would come again fosho</v>
       </c>
       <c r="P89" t="str">
-        <v>2026-08-04T08:17:31.119Z</v>
+        <v>2026-08-04T08:53:38.100Z</v>
       </c>
       <c r="Q89" t="str">
-        <v>2026-08-04T08:17:34.753Z</v>
+        <v>2026-08-04T08:53:41.237Z</v>
       </c>
       <c r="R89" t="str">
         <v>[]</v>
       </c>
       <c r="S89" t="str">
-        <v>2026-07-05T08:17:27.287Z</v>
+        <v>2026-07-05T08:53:34.387Z</v>
       </c>
       <c r="T89" t="str">
-        <v>2026-08-04T08:17:45.660Z</v>
+        <v>2026-08-04T08:53:49.863Z</v>
       </c>
     </row>
     <row r="90">
@@ -8170,7 +8169,7 @@
         <v>apify</v>
       </c>
       <c r="M90" t="str">
-        <v>2026-08-04T08:17:31.119Z</v>
+        <v>2026-08-04T08:53:38.100Z</v>
       </c>
       <c r="N90" t="str">
         <v>[]</v>
@@ -8179,19 +8178,19 @@
         <v>Tres leches is very tasty....</v>
       </c>
       <c r="P90" t="str">
-        <v>2026-08-04T08:17:31.119Z</v>
+        <v>2026-08-04T08:53:38.100Z</v>
       </c>
       <c r="Q90" t="str">
-        <v>2026-08-04T08:17:34.846Z</v>
+        <v>2026-08-04T08:53:41.361Z</v>
       </c>
       <c r="R90" t="str">
         <v>[]</v>
       </c>
       <c r="S90" t="str">
-        <v>2026-07-05T08:17:27.287Z</v>
+        <v>2026-07-05T08:53:34.387Z</v>
       </c>
       <c r="T90" t="str">
-        <v>2026-08-04T08:17:45.660Z</v>
+        <v>2026-08-04T08:53:49.863Z</v>
       </c>
     </row>
     <row r="91">
@@ -8232,7 +8231,7 @@
         <v>apify</v>
       </c>
       <c r="M91" t="str">
-        <v>2026-08-04T08:17:31.119Z</v>
+        <v>2026-08-04T08:53:38.100Z</v>
       </c>
       <c r="N91" t="str">
         <v>[]</v>
@@ -8241,19 +8240,19 @@
         <v>a month agoOrder typeDine inMeal typeOtherPrice per person₹400–600Wait timeNo waitRecommendation for vegetariansHighly recommendVegetarian offeringsMenu is all vegetarianLike</v>
       </c>
       <c r="P91" t="str">
-        <v>2026-08-04T08:17:31.119Z</v>
+        <v>2026-08-04T08:53:38.100Z</v>
       </c>
       <c r="Q91" t="str">
-        <v>2026-08-04T08:17:34.957Z</v>
+        <v>2026-08-04T08:53:41.456Z</v>
       </c>
       <c r="R91" t="str">
         <v>["https://lh3.googleusercontent.com/grass-cs/ACvplmNFWWTsSL5awqvvE-dGukd2QmWgcb057uQFbOiiQUa8UQcqfUjNq8VeNyll1i6zF2LkdD0U2oMEneIiZGjRlUkNUFavPv8HjwcI3VzVphh8GK3c2BZhmdFp0w05IO4cKBBjHjPS50fNW7w=w600-h450-p-k-no"]</v>
       </c>
       <c r="S91" t="str">
-        <v>2026-07-05T08:17:27.287Z</v>
+        <v>2026-07-05T08:53:34.387Z</v>
       </c>
       <c r="T91" t="str">
-        <v>2026-08-04T08:17:45.660Z</v>
+        <v>2026-08-04T08:53:49.863Z</v>
       </c>
     </row>
     <row r="92">
@@ -8294,7 +8293,7 @@
         <v>apify</v>
       </c>
       <c r="M92" t="str">
-        <v>2026-08-04T08:17:31.119Z</v>
+        <v>2026-08-04T08:53:38.100Z</v>
       </c>
       <c r="N92" t="str">
         <v>[]</v>
@@ -8303,19 +8302,19 @@
         <v>Good</v>
       </c>
       <c r="P92" t="str">
-        <v>2026-08-04T08:17:31.119Z</v>
+        <v>2026-08-04T08:53:38.100Z</v>
       </c>
       <c r="Q92" t="str">
-        <v>2026-08-04T08:17:33.826Z</v>
+        <v>2026-08-04T08:53:40.188Z</v>
       </c>
       <c r="R92" t="str">
         <v>[]</v>
       </c>
       <c r="S92" t="str">
-        <v>2026-07-05T08:17:24.912Z</v>
+        <v>2026-07-05T08:53:32.300Z</v>
       </c>
       <c r="T92" t="str">
-        <v>2026-08-04T08:17:45.660Z</v>
+        <v>2026-08-04T08:53:49.863Z</v>
       </c>
     </row>
     <row r="93">
@@ -8377,7 +8376,7 @@
         <v>2026-06-20T06:58:37.945Z</v>
       </c>
       <c r="T93" t="str">
-        <v>2026-08-04T08:17:45.660Z</v>
+        <v>2026-08-04T08:53:49.863Z</v>
       </c>
     </row>
     <row r="94">
@@ -8439,7 +8438,7 @@
         <v>2026-06-06T13:17:22.024Z</v>
       </c>
       <c r="T94" t="str">
-        <v>2026-08-04T08:17:45.660Z</v>
+        <v>2026-08-04T08:53:49.863Z</v>
       </c>
     </row>
     <row r="95">
@@ -8480,7 +8479,7 @@
         <v>apify</v>
       </c>
       <c r="M95" t="str">
-        <v>2026-08-04T08:17:31.119Z</v>
+        <v>2026-08-04T08:53:38.100Z</v>
       </c>
       <c r="N95" t="str">
         <v>[]</v>
@@ -8489,19 +8488,19 @@
         <v>Cake mine is good. Kids love the cakes here</v>
       </c>
       <c r="P95" t="str">
-        <v>2026-08-04T08:17:31.119Z</v>
+        <v>2026-08-04T08:53:38.100Z</v>
       </c>
       <c r="Q95" t="str">
-        <v>2026-08-04T08:17:33.702Z</v>
+        <v>2026-08-04T08:53:40.079Z</v>
       </c>
       <c r="R95" t="str">
         <v>[]</v>
       </c>
       <c r="S95" t="str">
-        <v>2026-07-05T08:17:24.912Z</v>
+        <v>2026-07-05T08:53:32.300Z</v>
       </c>
       <c r="T95" t="str">
-        <v>2026-08-04T08:17:45.660Z</v>
+        <v>2026-08-04T08:53:49.864Z</v>
       </c>
     </row>
     <row r="96">
@@ -8563,7 +8562,7 @@
         <v>2026-07-01T16:29:51.259Z</v>
       </c>
       <c r="T96" t="str">
-        <v>2026-08-04T08:17:45.660Z</v>
+        <v>2026-08-04T08:53:49.864Z</v>
       </c>
     </row>
     <row r="97">
@@ -8604,7 +8603,7 @@
         <v>apify</v>
       </c>
       <c r="M97" t="str">
-        <v>2026-08-04T08:17:31.119Z</v>
+        <v>2026-08-04T08:53:38.100Z</v>
       </c>
       <c r="N97" t="str">
         <v>[]</v>
@@ -8613,19 +8612,19 @@
         <v>Belgian chocolate is a must try ❤️</v>
       </c>
       <c r="P97" t="str">
-        <v>2026-08-04T08:17:31.119Z</v>
+        <v>2026-08-04T08:53:38.100Z</v>
       </c>
       <c r="Q97" t="str">
-        <v>2026-08-04T08:17:33.560Z</v>
+        <v>2026-08-04T08:53:40.001Z</v>
       </c>
       <c r="R97" t="str">
         <v>["https://lh3.googleusercontent.com/grass-cs/ACvplmP8urg3bL_FWZrfK5uigGBtI5nsT_jz56zmz72aAg50_tCE449DwzBuVG3bpU9HLBRFL4t_koHbVaMg4qbsa2kbye2vT_u9BvSyXNgTehW8x3B8qr1W7thTQ_qtiw70hKprh_Ucp5HXzP3V=w600-h450-p-k-no"]</v>
       </c>
       <c r="S97" t="str">
-        <v>2026-07-05T08:17:24.912Z</v>
+        <v>2026-07-05T08:53:32.300Z</v>
       </c>
       <c r="T97" t="str">
-        <v>2026-08-04T08:17:45.660Z</v>
+        <v>2026-08-04T08:53:49.864Z</v>
       </c>
     </row>
     <row r="98">
@@ -8666,7 +8665,7 @@
         <v>apify</v>
       </c>
       <c r="M98" t="str">
-        <v>2026-08-04T08:17:31.119Z</v>
+        <v>2026-08-04T08:53:38.100Z</v>
       </c>
       <c r="N98" t="str">
         <v>[]</v>
@@ -8675,19 +8674,19 @@
         <v>Veryyy good and tasty!!!!</v>
       </c>
       <c r="P98" t="str">
-        <v>2026-08-04T08:17:31.119Z</v>
+        <v>2026-08-04T08:53:38.100Z</v>
       </c>
       <c r="Q98" t="str">
-        <v>2026-08-04T08:17:33.058Z</v>
+        <v>2026-08-04T08:53:39.782Z</v>
       </c>
       <c r="R98" t="str">
         <v>["https://lh3.googleusercontent.com/grass-cs/ACvplmPb7DNLUBGsJ7SOkxrAP76qFf-jafM8xG28paS1ikhX6QO7cogCZ0H2X7Y0uVwyZVzTdUFEbxugJbfvjDcbZIJWFm9cfXfygRAvPQrYkUycZkA0mNS0iuTDGD_4eubRSZYaIvieEIfIvyww=w600-h450-p-k-no"]</v>
       </c>
       <c r="S98" t="str">
-        <v>2026-07-05T08:17:24.912Z</v>
+        <v>2026-07-05T08:53:32.300Z</v>
       </c>
       <c r="T98" t="str">
-        <v>2026-08-04T08:17:45.660Z</v>
+        <v>2026-08-04T08:53:49.864Z</v>
       </c>
     </row>
     <row r="99">
@@ -8728,7 +8727,7 @@
         <v>apify</v>
       </c>
       <c r="M99" t="str">
-        <v>2026-08-04T08:17:31.119Z</v>
+        <v>2026-08-04T08:53:38.100Z</v>
       </c>
       <c r="N99" t="str">
         <v>[]</v>
@@ -8737,10 +8736,10 @@
         <v>Premium quality and taste</v>
       </c>
       <c r="P99" t="str">
-        <v>2026-08-04T08:17:31.119Z</v>
+        <v>2026-08-04T08:53:38.100Z</v>
       </c>
       <c r="Q99" t="str">
-        <v>2026-08-04T08:17:33.182Z</v>
+        <v>2026-08-04T08:53:39.892Z</v>
       </c>
       <c r="R99" t="str">
         <v>["https://lh3.googleusercontent.com/grass-cs/ACvplmPjqw76vV6Nbougq9wpheQAt46hrjl7JvzOXljVAhc-c_BA89VLDs1aKLcweDnXDTyRLpjR5hFWGK7A5eXQXT69P7x08CYK8Fhkwx3faQDD7Pig9RggitVZf0Jn9wW3zeSFitE18ycB8Syo=w600-h450-p-k-no"]</v>
@@ -8749,7 +8748,7 @@
         <v/>
       </c>
       <c r="T99" t="str">
-        <v>2026-08-04T08:17:45.660Z</v>
+        <v>2026-08-04T08:53:49.864Z</v>
       </c>
     </row>
     <row r="100">
@@ -8790,7 +8789,7 @@
         <v>apify</v>
       </c>
       <c r="M100" t="str">
-        <v>2026-08-04T08:17:31.119Z</v>
+        <v>2026-08-04T08:53:38.100Z</v>
       </c>
       <c r="N100" t="str">
         <v>[]</v>
@@ -8799,19 +8798,19 @@
         <v>Everything was perfect! The packaging was neat and secure, and the cake was fresh and looked beautiful. The taste was absolutely amazing-soft, rich, and so delicious. Everyone loved it. Thank you so much for this wonderful cake! Will definitely order again ma'am. ❤️Highly recommended</v>
       </c>
       <c r="P100" t="str">
-        <v>2026-08-04T08:17:31.119Z</v>
+        <v>2026-08-04T08:53:38.100Z</v>
       </c>
       <c r="Q100" t="str">
-        <v>2026-08-04T08:17:32.231Z</v>
+        <v>2026-08-04T08:53:38.967Z</v>
       </c>
       <c r="R100" t="str">
         <v>["https://lh3.googleusercontent.com/grass-cs/ACvplmNeA82iSR28f7uVGHRJJXLIjCCgye8aqyz0gn8FJ1G3Ww84OI547WQAU9AQFchO5VYaZopyErDlz0N7k9NLmVnyprAn28dZCGhBFE8ZOTqWp96MFz8DIWiykn89S7t-s94FUlrvOOhBlBsA=w300-h450-p-k-no","https://lh3.googleusercontent.com/grass-cs/ACvplmPK5RowQ4MR1Re2zHfDxajk3wTC0tB3IJmIDNb15EIJTjEs9YuepGuFRm3MumWIj8EGdq14Gg9kpHvyQwp143E4uLuVxYtKzIphx1rVnyNHbqTeKi6QHiqEhrBair6cKzH3ZBr9Fy6zhLVD=w300-h450-p-k-no"]</v>
       </c>
       <c r="S100" t="str">
-        <v>2026-07-14T08:17:22.549Z</v>
+        <v>2026-07-14T08:53:30.496Z</v>
       </c>
       <c r="T100" t="str">
-        <v>2026-08-04T08:17:45.660Z</v>
+        <v>2026-08-04T08:53:49.864Z</v>
       </c>
     </row>
     <row r="101">
@@ -8852,7 +8851,7 @@
         <v>apify</v>
       </c>
       <c r="M101" t="str">
-        <v>2026-08-04T08:17:31.119Z</v>
+        <v>2026-08-04T08:53:38.100Z</v>
       </c>
       <c r="N101" t="str">
         <v>[]</v>
@@ -8861,19 +8860,19 @@
         <v>We have ordered the cake, for my daughter's 1st birthday celebration.. The cake tastes too good and their service was speechless.. once again thank you so much..</v>
       </c>
       <c r="P101" t="str">
-        <v>2026-08-04T08:17:31.119Z</v>
+        <v>2026-08-04T08:53:38.100Z</v>
       </c>
       <c r="Q101" t="str">
-        <v>2026-08-04T08:17:32.356Z</v>
+        <v>2026-08-04T08:53:39.078Z</v>
       </c>
       <c r="R101" t="str">
         <v>[]</v>
       </c>
       <c r="S101" t="str">
-        <v>2026-07-14T08:17:22.549Z</v>
+        <v>2026-07-14T08:53:30.496Z</v>
       </c>
       <c r="T101" t="str">
-        <v>2026-08-04T08:17:45.660Z</v>
+        <v>2026-08-04T08:53:49.864Z</v>
       </c>
     </row>
     <row r="102">
@@ -8914,7 +8913,7 @@
         <v>apify</v>
       </c>
       <c r="M102" t="str">
-        <v>2026-08-04T08:17:31.119Z</v>
+        <v>2026-08-04T08:53:38.100Z</v>
       </c>
       <c r="N102" t="str">
         <v>[]</v>
@@ -8923,19 +8922,19 @@
         <v>Super happy with the cake! I ordered it last night, and it was delivered today exactly as I requested. Great quality and service! 🤸🏽🤠✌🏽:)) …</v>
       </c>
       <c r="P102" t="str">
-        <v>2026-08-04T08:17:31.119Z</v>
+        <v>2026-08-04T08:53:38.100Z</v>
       </c>
       <c r="Q102" t="str">
-        <v>2026-08-04T08:17:32.449Z</v>
+        <v>2026-08-04T08:53:39.203Z</v>
       </c>
       <c r="R102" t="str">
         <v>["https://lh3.googleusercontent.com/grass-cs/ACvplmN-fZ4ZbA56LmNiHVlExrbqgANFAZMy8bqKwQL2NZQoPLvsH32nLMA8NdeOB0u3oUSm80MLB3LqUA_CilitL9CMi_-quzFH8w85r3M8mAkOZ81DYaLY87FPXWd43Jpk0USLvFk1dmP2f3Iv=w300-h450-p-k-no","https://lh3.googleusercontent.com/grass-cs/ACvplmNi6EhLEBn0pUuQ0grFLJMdiKnbXeFMQPZhXPeNvy4Yal7mN4O5uq8vSm9SIjfeood1mazn_9DJHbzq33a8t0546WCFW6YgUSPNzK5GUuoRGB39wvuiLM_nh_Y0HVESvmWy6SoTNZov2giR=w300-h450-p-k-no"]</v>
       </c>
       <c r="S102" t="str">
-        <v>2026-07-07T08:17:22.549Z</v>
+        <v>2026-07-07T08:53:30.496Z</v>
       </c>
       <c r="T102" t="str">
-        <v>2026-08-04T08:17:45.660Z</v>
+        <v>2026-08-04T08:53:49.864Z</v>
       </c>
     </row>
     <row r="103">
@@ -8976,7 +8975,7 @@
         <v>apify</v>
       </c>
       <c r="M103" t="str">
-        <v>2026-08-04T08:17:31.119Z</v>
+        <v>2026-08-04T08:53:38.100Z</v>
       </c>
       <c r="N103" t="str">
         <v>[]</v>
@@ -8985,19 +8984,19 @@
         <v>The cake was absolutely delicious! It tasted fresh, had the perfect level of sweetness, and everyone loved it. Thank you for making my son's birthday extra special. Highly recommended!</v>
       </c>
       <c r="P103" t="str">
-        <v>2026-08-04T08:17:31.119Z</v>
+        <v>2026-08-04T08:53:38.100Z</v>
       </c>
       <c r="Q103" t="str">
-        <v>2026-08-04T08:17:32.559Z</v>
+        <v>2026-08-04T08:53:39.312Z</v>
       </c>
       <c r="R103" t="str">
         <v>["https://lh3.googleusercontent.com/grass-cs/ACvplmOC-Soy91lKLF7ldDi9z84NQYf-W_fCLXznQODBCUGMQMZpvcJ1O3qmFcvuJYT_m1cL70J-WK0r6nbr9eyIChJ3lSRh3Kv8a4I-Qdw7R_6xiyFK5AImavP_8a7upJ1QawqXlD_XwVTNJZYj=w600-h450-p-k-no"]</v>
       </c>
       <c r="S103" t="str">
-        <v>2026-07-07T08:17:22.549Z</v>
+        <v>2026-07-07T08:53:30.496Z</v>
       </c>
       <c r="T103" t="str">
-        <v>2026-08-04T08:17:45.660Z</v>
+        <v>2026-08-04T08:53:49.864Z</v>
       </c>
     </row>
     <row r="104">
@@ -9038,7 +9037,7 @@
         <v>apify</v>
       </c>
       <c r="M104" t="str">
-        <v>2026-08-04T08:17:31.119Z</v>
+        <v>2026-08-04T08:53:38.100Z</v>
       </c>
       <c r="N104" t="str">
         <v>[]</v>
@@ -9047,19 +9046,19 @@
         <v>Absolutely love this place! Ordered a chocolate truffle cake on very short notice and they came through beautifully. The taste was fantastic and the design was lovely too. Highly recommend to anyone looking for a truly special cake!</v>
       </c>
       <c r="P104" t="str">
-        <v>2026-08-04T08:17:31.119Z</v>
+        <v>2026-08-04T08:53:38.100Z</v>
       </c>
       <c r="Q104" t="str">
-        <v>2026-08-04T08:17:32.683Z</v>
+        <v>2026-08-04T08:53:39.438Z</v>
       </c>
       <c r="R104" t="str">
         <v>[]</v>
       </c>
       <c r="S104" t="str">
-        <v>2026-07-07T08:17:22.549Z</v>
+        <v>2026-07-07T08:53:30.496Z</v>
       </c>
       <c r="T104" t="str">
-        <v>2026-08-04T08:17:45.660Z</v>
+        <v>2026-08-04T08:53:49.864Z</v>
       </c>
     </row>
     <row r="105">
@@ -9100,7 +9099,7 @@
         <v>apify</v>
       </c>
       <c r="M105" t="str">
-        <v>2026-08-04T08:17:31.119Z</v>
+        <v>2026-08-04T08:53:38.100Z</v>
       </c>
       <c r="N105" t="str">
         <v>[]</v>
@@ -9109,19 +9108,19 @@
         <v>The taste was top-notch, the communication and delivery is hassle free. I would definitely order further. Thank you Chocolate mine</v>
       </c>
       <c r="P105" t="str">
-        <v>2026-08-04T08:17:31.119Z</v>
+        <v>2026-08-04T08:53:38.100Z</v>
       </c>
       <c r="Q105" t="str">
-        <v>2026-08-04T08:17:32.809Z</v>
+        <v>2026-08-04T08:53:39.547Z</v>
       </c>
       <c r="R105" t="str">
         <v>["https://lh3.googleusercontent.com/grass-cs/ACvplmPR_WMQjlt-SbR5yzkU84Ao-tE30pFrhqI1ZCXEaZpYhY8wE8FSceuLD9HawVtjhC9VLBeapJS4HvcndzOwpAvn-3rSweAIXyVBpJTnx5vUuE7-0pEAQc52vi3c7756lq10T8d6wishMQc=w300-h450-p-k-no","https://lh3.googleusercontent.com/grass-cs/ACvplmMfT5aWOXYVMky5tDsUIf1jZcEqaHrdzejhuI1RzxOLjpRSE4Pv8YFFlWxcLHOL3KQZj_KQpSp7-kro1W7bLmmVRWWEYMbeEvN4Tvg73FUKsvuG_RkYgYz3ATf9ElcG6HVnawHw8Eu2-RA=w300-h450-p-k-no"]</v>
       </c>
       <c r="S105" t="str">
-        <v>2026-07-07T08:17:22.549Z</v>
+        <v>2026-07-07T08:53:30.496Z</v>
       </c>
       <c r="T105" t="str">
-        <v>2026-08-04T08:17:45.660Z</v>
+        <v>2026-08-04T08:53:49.864Z</v>
       </c>
     </row>
     <row r="106">
@@ -9183,7 +9182,7 @@
         <v>2026-07-10T16:29:46.315Z</v>
       </c>
       <c r="T106" t="str">
-        <v>2026-08-04T08:17:45.660Z</v>
+        <v>2026-08-04T08:53:49.864Z</v>
       </c>
     </row>
     <row r="107">
@@ -9224,7 +9223,7 @@
         <v>apify</v>
       </c>
       <c r="M107" t="str">
-        <v>2026-08-04T08:17:31.119Z</v>
+        <v>2026-08-04T08:53:38.100Z</v>
       </c>
       <c r="N107" t="str">
         <v>[]</v>
@@ -9233,19 +9232,19 @@
         <v>I like the ambience of the shop and the food are tasty, personally highly recommend this shop</v>
       </c>
       <c r="P107" t="str">
-        <v>2026-08-04T08:17:31.119Z</v>
+        <v>2026-08-04T08:53:38.100Z</v>
       </c>
       <c r="Q107" t="str">
-        <v>2026-08-04T08:17:32.107Z</v>
+        <v>2026-08-04T08:53:38.873Z</v>
       </c>
       <c r="R107" t="str">
         <v>[]</v>
       </c>
       <c r="S107" t="str">
-        <v>2026-07-14T08:17:22.549Z</v>
+        <v>2026-07-14T08:53:30.496Z</v>
       </c>
       <c r="T107" t="str">
-        <v>2026-08-04T08:17:45.660Z</v>
+        <v>2026-08-04T08:53:49.864Z</v>
       </c>
     </row>
     <row r="108">
@@ -9286,7 +9285,7 @@
         <v>apify</v>
       </c>
       <c r="M108" t="str">
-        <v>2026-08-04T08:17:31.119Z</v>
+        <v>2026-08-04T08:53:38.100Z</v>
       </c>
       <c r="N108" t="str">
         <v>[]</v>
@@ -9295,19 +9294,19 @@
         <v>café. Great coffee. Amazing atmosphere. 🤍☕</v>
       </c>
       <c r="P108" t="str">
-        <v>2026-08-04T08:17:31.119Z</v>
+        <v>2026-08-04T08:53:38.100Z</v>
       </c>
       <c r="Q108" t="str">
-        <v>2026-08-04T08:17:31.981Z</v>
+        <v>2026-08-04T08:53:38.748Z</v>
       </c>
       <c r="R108" t="str">
         <v>["https://lh3.googleusercontent.com/grass-cs/ACvplmPErvV0RjZmfRwtWbuKzYbxI3DyAL2gb1GrWglchpKgPwarSFCwsoTrlyLASNHLwDW55Ufk5MAi7-IULkcS0fef8zE2yvqwosqfbN7OfzO9_jJqKxPQ2gk81L1VqxhQIzD78sGgvlTxUOXJ=w600-h450-p-k-no"]</v>
       </c>
       <c r="S108" t="str">
-        <v>2026-07-21T08:17:22.549Z</v>
+        <v>2026-07-21T08:53:30.496Z</v>
       </c>
       <c r="T108" t="str">
-        <v>2026-08-04T08:17:45.660Z</v>
+        <v>2026-08-04T08:53:49.864Z</v>
       </c>
     </row>
     <row r="109">
@@ -9348,7 +9347,7 @@
         <v>apify</v>
       </c>
       <c r="M109" t="str">
-        <v>2026-08-04T08:17:31.119Z</v>
+        <v>2026-08-04T08:53:38.100Z</v>
       </c>
       <c r="N109" t="str">
         <v>[]</v>
@@ -9357,19 +9356,19 @@
         <v>Very good... service Approach nice...food and packing delivery timeing also fine.</v>
       </c>
       <c r="P109" t="str">
-        <v>2026-08-04T08:17:31.119Z</v>
+        <v>2026-08-04T08:53:38.100Z</v>
       </c>
       <c r="Q109" t="str">
-        <v>2026-08-04T08:17:31.873Z</v>
+        <v>2026-08-04T08:53:38.622Z</v>
       </c>
       <c r="R109" t="str">
         <v>["https://lh3.googleusercontent.com/grass-cs/ACvplmN0f8fWy8F3hL8_U-LBJKkVlXesNa5kDRGcCWA7kKvIQLXR-K9uyrP2J0idLp1MGloyp-Y_i7VOPkFFe7bz6JnBLcsX4yw8Sz-sbLj81ehlHULAyEqCTDlIgSNBoZj0UqLRNPlZXyFkdnI=w600-h450-p-k-no"]</v>
       </c>
       <c r="S109" t="str">
-        <v>2026-07-21T08:17:20.756Z</v>
+        <v>2026-07-21T08:53:28.404Z</v>
       </c>
       <c r="T109" t="str">
-        <v>2026-08-04T08:17:45.660Z</v>
+        <v>2026-08-04T08:53:49.864Z</v>
       </c>
     </row>
     <row r="110">
@@ -9431,7 +9430,7 @@
         <v>2026-03-30T18:20:59.728Z</v>
       </c>
       <c r="T110" t="str">
-        <v>2026-08-04T08:17:45.660Z</v>
+        <v>2026-08-04T08:53:49.864Z</v>
       </c>
     </row>
     <row r="111">
@@ -9472,7 +9471,7 @@
         <v>apify</v>
       </c>
       <c r="M111" t="str">
-        <v>2026-08-04T08:17:31.119Z</v>
+        <v>2026-08-04T08:53:38.100Z</v>
       </c>
       <c r="N111" t="str">
         <v>[]</v>
@@ -9481,19 +9480,19 @@
         <v>Hi! We have ordered cake from you for the 3rd time. So satisfied with your cake flavours, the taste is very rich and everlasting thinking about ordering from you next time too😊</v>
       </c>
       <c r="P111" t="str">
-        <v>2026-08-04T08:17:31.119Z</v>
+        <v>2026-08-04T08:53:38.100Z</v>
       </c>
       <c r="Q111" t="str">
-        <v>2026-08-04T08:17:31.748Z</v>
+        <v>2026-08-04T08:53:38.514Z</v>
       </c>
       <c r="R111" t="str">
         <v>["https://lh3.googleusercontent.com/grass-cs/ACvplmNl9EVDKAAZnZ-rKcv8hxAlzRSzlVes9EWtNawzsvEjwnFtM_lIMWXTyShS7usn-z0Q6M4HuFlx3ogjSr1msZFsq4KUHvWpWmk8WcNgXEgt1OmVj4KWy1LihgBW4h-kS-7Sm2Lkuh6BS9Q=w600-h450-p-k-no"]</v>
       </c>
       <c r="S111" t="str">
-        <v>2026-07-28T08:17:20.756Z</v>
+        <v>2026-07-28T08:53:28.404Z</v>
       </c>
       <c r="T111" t="str">
-        <v>2026-08-04T08:17:45.660Z</v>
+        <v>2026-08-04T08:53:49.864Z</v>
       </c>
     </row>
     <row r="112">
@@ -9534,7 +9533,7 @@
         <v>apify</v>
       </c>
       <c r="M112" t="str">
-        <v>2026-08-04T08:17:31.119Z</v>
+        <v>2026-08-04T08:53:38.100Z</v>
       </c>
       <c r="N112" t="str">
         <v>[]</v>
@@ -9543,19 +9542,19 @@
         <v>The cake was awesome and i got it delivered at time</v>
       </c>
       <c r="P112" t="str">
-        <v>2026-08-04T08:17:31.119Z</v>
+        <v>2026-08-04T08:53:38.100Z</v>
       </c>
       <c r="Q112" t="str">
-        <v>2026-08-04T08:17:31.638Z</v>
+        <v>2026-08-04T08:53:38.404Z</v>
       </c>
       <c r="R112" t="str">
         <v>["https://lh3.googleusercontent.com/grass-cs/ACvplmP1bsAdlllZ_ejRfcAxNeSwJ_c7YRAg9VqbeFD_pKRfrxa39eClEX8fzlvNinxnupQYgdLXQM2ztNE_v8whaz-9t4sDYXSD_TzEFgn6I7AuadIvYndBsR69oKPxnrgOfErMZzCAEG6bPC9q=w600-h450-p-k-no"]</v>
       </c>
       <c r="S112" t="str">
-        <v>2026-07-28T08:17:20.756Z</v>
+        <v>2026-07-28T08:53:28.404Z</v>
       </c>
       <c r="T112" t="str">
-        <v>2026-08-04T08:17:45.661Z</v>
+        <v>2026-08-04T08:53:49.864Z</v>
       </c>
     </row>
     <row r="113">
@@ -9617,7 +9616,7 @@
         <v>2026-07-27T16:49:55.429Z</v>
       </c>
       <c r="T113" t="str">
-        <v>2026-08-04T08:17:45.661Z</v>
+        <v>2026-08-04T08:53:49.864Z</v>
       </c>
     </row>
     <row r="114">
@@ -9679,7 +9678,7 @@
         <v>2026-07-26T16:49:55.429Z</v>
       </c>
       <c r="T114" t="str">
-        <v>2026-08-04T08:17:45.661Z</v>
+        <v>2026-08-04T08:53:49.864Z</v>
       </c>
     </row>
     <row r="115">
@@ -9741,7 +9740,7 @@
         <v>2026-07-29T10:10:17.865Z</v>
       </c>
       <c r="T115" t="str">
-        <v>2026-08-04T08:17:45.661Z</v>
+        <v>2026-08-04T08:53:49.864Z</v>
       </c>
     </row>
     <row r="116">
@@ -9782,7 +9781,7 @@
         <v>apify</v>
       </c>
       <c r="M116" t="str">
-        <v>2026-08-04T08:17:31.119Z</v>
+        <v>2026-08-04T08:53:38.100Z</v>
       </c>
       <c r="N116" t="str">
         <v>[]</v>
@@ -9791,19 +9790,19 @@
         <v>Good Food and Good Ambience 🫠</v>
       </c>
       <c r="P116" t="str">
-        <v>2026-08-04T08:17:31.119Z</v>
+        <v>2026-08-04T08:53:38.100Z</v>
       </c>
       <c r="Q116" t="str">
-        <v>2026-08-04T08:17:32.919Z</v>
+        <v>2026-08-04T08:53:39.671Z</v>
       </c>
       <c r="R116" t="str">
         <v>["https://lh3.googleusercontent.com/grass-cs/ACvplmPbnMyGgr7ldw1VwH2l9EWxESZ8i2WiCTUTe8zQ29ZXhRAHSAkgj-eU4D0iR1XuNu5soHKcqzl6OEIFME7xPRSCpJCa_7otMLFbgnGUy47fc2F5UE8WGAeRUEOGKzRcYJ-4BUVoaCbt6pMN=w300-h225-p-k-no","https://lh3.googleusercontent.com/grass-cs/ACvplmMZ3T-J1z6ygeEsljvANBCm-33Prl5Hlb3l9vMQnNSj_kLI-6Bwz_j3_RsiMEtPi4cF2lfEeKHdpyLJaxcfEejKfhgfZWDFTIq7UoUUXQUthEeo35tEUD640_d8BqZpAkxoeXkJczkr6-oZ=w300-h225-p-k-no","https://lh3.googleusercontent.com/grass-cs/ACvplmP-O01jDu1yIZg3Tp7Wr8SaYhm5rPrpnv6WSHPO69y0EBP1XAC0a-MwoZyTtvCcGGIsu19-yYNTSMPZgBW5lx315eewd5GYs40UDOgdBUgmP29co1Tg8rgDYMQ2ELeNl_O0FW1SqJKz8k7c=w300-h225-p-k-no","https://lh3.googleusercontent.com/grass-cs/ACvplmOUaBLj7YaW6hX6SdiqRzi-t7aNyY6jBx6F-B_sWkYuThsNAH5r4VUSlpqByUGn8OTiqeZgRXL2GjrVYdhvw_AxvPu6XWXSiUOQwcd5ESDlbgF35kt4sPgp4HzvvtACFVYgZYyZAQ8i7o7J=w300-h225-p-k-no"]</v>
       </c>
       <c r="S116" t="str">
-        <v>2026-07-07T08:17:24.912Z</v>
+        <v>2026-07-07T08:53:32.300Z</v>
       </c>
       <c r="T116" t="str">
-        <v>2026-08-04T08:17:45.661Z</v>
+        <v>2026-08-04T08:53:49.864Z</v>
       </c>
     </row>
     <row r="117">
@@ -9844,7 +9843,7 @@
         <v>apify</v>
       </c>
       <c r="M117" t="str">
-        <v>2026-08-04T08:17:31.119Z</v>
+        <v>2026-08-04T08:53:38.100Z</v>
       </c>
       <c r="N117" t="str">
         <v>[]</v>
@@ -9853,19 +9852,19 @@
         <v>Must try paneer tikka sandwich..... Served fresh and hot... Soooo good!!!.</v>
       </c>
       <c r="P117" t="str">
-        <v>2026-08-04T08:17:31.119Z</v>
+        <v>2026-08-04T08:53:38.100Z</v>
       </c>
       <c r="Q117" t="str">
-        <v>2026-08-04T08:17:35.534Z</v>
+        <v>2026-08-04T08:53:41.722Z</v>
       </c>
       <c r="R117" t="str">
         <v>[]</v>
       </c>
       <c r="S117" t="str">
-        <v>2026-07-05T08:17:29.399Z</v>
+        <v>2026-07-05T08:53:36.302Z</v>
       </c>
       <c r="T117" t="str">
-        <v>2026-08-04T08:17:45.661Z</v>
+        <v>2026-08-04T08:53:49.864Z</v>
       </c>
     </row>
     <row r="118">
@@ -9906,7 +9905,7 @@
         <v>apify</v>
       </c>
       <c r="M118" t="str">
-        <v>2026-08-04T08:17:31.119Z</v>
+        <v>2026-08-04T08:53:38.100Z</v>
       </c>
       <c r="N118" t="str">
         <v>[]</v>
@@ -9915,19 +9914,19 @@
         <v>The cake was absolutely delicious! It was fresh, soft, and perfectly moist.It looked beautiful and tasted even better.</v>
       </c>
       <c r="P118" t="str">
-        <v>2026-08-04T08:17:31.119Z</v>
+        <v>2026-08-04T08:53:38.100Z</v>
       </c>
       <c r="Q118" t="str">
-        <v>2026-08-04T08:17:31.233Z</v>
+        <v>2026-08-04T08:53:38.217Z</v>
       </c>
       <c r="R118" t="str">
         <v>["https://lh3.googleusercontent.com/grass-cs/ACvplmOIh9ayyn4ckHl5HGioGFgtNJUmc6xw388f4REij1aAj0n57maHW_395fh6OZjj0IeDsP6hnuMvyi33e8sYRT1j3_0E7gP-CEcS6eKzxaHZoGnyrq5oSs_i0z-U3MxeUKLoQ4rBWo9YvjVc=w600-h450-p-k-no"]</v>
       </c>
       <c r="S118" t="str">
-        <v>2026-08-03T08:17:20.756Z</v>
+        <v>2026-08-03T08:53:28.404Z</v>
       </c>
       <c r="T118" t="str">
-        <v>2026-08-04T08:17:45.661Z</v>
+        <v>2026-08-04T08:53:49.864Z</v>
       </c>
     </row>
     <row r="119">
@@ -9968,7 +9967,7 @@
         <v>apify</v>
       </c>
       <c r="M119" t="str">
-        <v>2026-08-04T08:17:31.119Z</v>
+        <v>2026-08-04T08:53:38.100Z</v>
       </c>
       <c r="N119" t="str">
         <v>[]</v>
@@ -9977,19 +9976,19 @@
         <v>Quick and delicious service... What a wow Biscoff tres leches ...</v>
       </c>
       <c r="P119" t="str">
-        <v>2026-08-04T08:17:31.119Z</v>
+        <v>2026-08-04T08:53:38.100Z</v>
       </c>
       <c r="Q119" t="str">
-        <v>2026-08-04T08:17:31.341Z</v>
+        <v>2026-08-04T08:53:38.294Z</v>
       </c>
       <c r="R119" t="str">
         <v>[]</v>
       </c>
       <c r="S119" t="str">
-        <v>2026-08-03T08:17:20.756Z</v>
+        <v>2026-08-03T08:53:28.404Z</v>
       </c>
       <c r="T119" t="str">
-        <v>2026-08-04T08:17:45.661Z</v>
+        <v>2026-08-04T08:53:49.864Z</v>
       </c>
     </row>
     <row r="120">
@@ -10030,7 +10029,7 @@
         <v>apify</v>
       </c>
       <c r="M120" t="str">
-        <v>2026-08-04T08:17:31.119Z</v>
+        <v>2026-08-04T08:53:38.100Z</v>
       </c>
       <c r="N120" t="str">
         <v>[]</v>
@@ -10039,103 +10038,24 @@
         <v>I ordered choco fudge cake and it was a last minute order. But the owner was so sweet to deliver it very quickly. And the cake was so yum. Hope to order again!</v>
       </c>
       <c r="P120" t="str">
-        <v>2026-08-04T08:17:31.118Z</v>
+        <v>2026-08-04T08:53:38.100Z</v>
       </c>
       <c r="Q120" t="str">
-        <v>2026-08-04T08:17:31.123Z</v>
+        <v>2026-08-04T08:53:38.103Z</v>
       </c>
       <c r="R120" t="str">
         <v>[]</v>
       </c>
       <c r="S120" t="str">
-        <v>2026-08-04T05:17:20.756Z</v>
+        <v>2026-08-04T04:53:28.404Z</v>
       </c>
       <c r="T120" t="str">
-        <v>2026-08-04T08:17:45.661Z</v>
+        <v>2026-08-04T08:53:49.864Z</v>
       </c>
     </row>
   </sheetData>
   <ignoredErrors>
     <ignoredError numberStoredAsText="1" sqref="A1:T120"/>
-  </ignoredErrors>
-</worksheet>
-</file>
-
-<file path=xl/worksheets/sheet18.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:F3"/>
-  <cols>
-    <col min="1" max="1" width="26.83203125" customWidth="1"/>
-    <col min="2" max="2" width="52.83203125" customWidth="1"/>
-    <col min="3" max="3" width="26.83203125" customWidth="1"/>
-    <col min="4" max="4" width="17.83203125" customWidth="1"/>
-    <col min="5" max="5" width="26.83203125" customWidth="1"/>
-    <col min="6" max="6" width="26.83203125" customWidth="1"/>
-  </cols>
-  <sheetData>
-    <row r="1">
-      <c r="A1" t="str">
-        <v>_id</v>
-      </c>
-      <c r="B1" t="str">
-        <v>token</v>
-      </c>
-      <c r="C1" t="str">
-        <v>createdAt</v>
-      </c>
-      <c r="D1" t="str">
-        <v>deviceName</v>
-      </c>
-      <c r="E1" t="str">
-        <v>userId</v>
-      </c>
-      <c r="F1" t="str">
-        <v>exportedAt</v>
-      </c>
-    </row>
-    <row r="2">
-      <c r="A2" t="str">
-        <v>6a6b650bd7d857f1080f8920</v>
-      </c>
-      <c r="B2" t="str">
-        <v>dr_NR4O8AJ7owY0nZEkTHt:APA91bFioPFZa6WWAzUV05hxO9aNoPx7oJIw3crpk1xfvE0sKwHd8cwMkLtxeoHFWY_gcxEntXBvNi0-jfrQwo4IeYpnEd5Zhr7tUXCNS45i06qzKyVKNcE</v>
-      </c>
-      <c r="C2" t="str">
-        <v>2026-08-02T06:33:29.895Z</v>
-      </c>
-      <c r="D2" t="str">
-        <v>Windows Desktop</v>
-      </c>
-      <c r="E2" t="str">
-        <v>69e9c1ab766ae41a5f9612cd</v>
-      </c>
-      <c r="F2" t="str">
-        <v>2026-08-04T08:17:45.779Z</v>
-      </c>
-    </row>
-    <row r="3">
-      <c r="A3" t="str">
-        <v>6a719d00f4526627301ab9d1</v>
-      </c>
-      <c r="B3" t="str">
-        <v>dpoXfI-2KZ-mo3b_zPTVNR:APA91bG9ZMTUrTy8QR3w3Q56smqrhcfJFjLKEfFEOJc_8iJaiTW7zKu-MrYCJk5RxZh3Wkwx4Jzwq3lRvE6hvJdFvfGhjQHo3oz-BWolskWWCQEMX4VKNz4</v>
-      </c>
-      <c r="C3" t="str">
-        <v>2026-08-04T08:17:16.052Z</v>
-      </c>
-      <c r="D3" t="str">
-        <v>Windows Desktop</v>
-      </c>
-      <c r="E3" t="str">
-        <v>69e9c1ab766ae41a5f9612cd</v>
-      </c>
-      <c r="F3" t="str">
-        <v>2026-08-04T08:17:45.779Z</v>
-      </c>
-    </row>
-  </sheetData>
-  <ignoredErrors>
-    <ignoredError numberStoredAsText="1" sqref="A1:F3"/>
   </ignoredErrors>
 </worksheet>
 </file>
@@ -10397,7 +10317,7 @@
         <v>[]</v>
       </c>
       <c r="AH2" t="str">
-        <v>2026-08-04T08:17:41.808Z</v>
+        <v>2026-08-04T08:53:46.610Z</v>
       </c>
     </row>
     <row r="3">
@@ -10501,7 +10421,7 @@
         <v>[]</v>
       </c>
       <c r="AH3" t="str">
-        <v>2026-08-04T08:17:41.808Z</v>
+        <v>2026-08-04T08:53:46.610Z</v>
       </c>
     </row>
     <row r="4">
@@ -10605,7 +10525,7 @@
         <v>[]</v>
       </c>
       <c r="AH4" t="str">
-        <v>2026-08-04T08:17:41.808Z</v>
+        <v>2026-08-04T08:53:46.610Z</v>
       </c>
     </row>
     <row r="5">
@@ -10709,7 +10629,7 @@
         <v>[]</v>
       </c>
       <c r="AH5" t="str">
-        <v>2026-08-04T08:17:41.808Z</v>
+        <v>2026-08-04T08:53:46.610Z</v>
       </c>
     </row>
     <row r="6">
@@ -10813,7 +10733,7 @@
         <v>[]</v>
       </c>
       <c r="AH6" t="str">
-        <v>2026-08-04T08:17:41.808Z</v>
+        <v>2026-08-04T08:53:46.610Z</v>
       </c>
     </row>
     <row r="7">
@@ -10917,7 +10837,7 @@
         <v>[]</v>
       </c>
       <c r="AH7" t="str">
-        <v>2026-08-04T08:17:41.808Z</v>
+        <v>2026-08-04T08:53:46.610Z</v>
       </c>
     </row>
     <row r="8">
@@ -11021,7 +10941,7 @@
         <v>[]</v>
       </c>
       <c r="AH8" t="str">
-        <v>2026-08-04T08:17:41.808Z</v>
+        <v>2026-08-04T08:53:46.610Z</v>
       </c>
     </row>
     <row r="9">
@@ -11125,7 +11045,7 @@
         <v>[]</v>
       </c>
       <c r="AH9" t="str">
-        <v>2026-08-04T08:17:41.808Z</v>
+        <v>2026-08-04T08:53:46.610Z</v>
       </c>
     </row>
     <row r="10">
@@ -11229,7 +11149,7 @@
         <v>[]</v>
       </c>
       <c r="AH10" t="str">
-        <v>2026-08-04T08:17:41.808Z</v>
+        <v>2026-08-04T08:53:46.610Z</v>
       </c>
     </row>
     <row r="11">
@@ -11333,7 +11253,7 @@
         <v>[]</v>
       </c>
       <c r="AH11" t="str">
-        <v>2026-08-04T08:17:41.808Z</v>
+        <v>2026-08-04T08:53:46.610Z</v>
       </c>
     </row>
     <row r="12">
@@ -11437,7 +11357,7 @@
         <v>[]</v>
       </c>
       <c r="AH12" t="str">
-        <v>2026-08-04T08:17:41.808Z</v>
+        <v>2026-08-04T08:53:46.610Z</v>
       </c>
     </row>
     <row r="13">
@@ -11541,7 +11461,7 @@
         <v>[]</v>
       </c>
       <c r="AH13" t="str">
-        <v>2026-08-04T08:17:41.809Z</v>
+        <v>2026-08-04T08:53:46.610Z</v>
       </c>
     </row>
     <row r="14">
@@ -11645,7 +11565,7 @@
         <v>[]</v>
       </c>
       <c r="AH14" t="str">
-        <v>2026-08-04T08:17:41.809Z</v>
+        <v>2026-08-04T08:53:46.610Z</v>
       </c>
     </row>
     <row r="15">
@@ -11740,7 +11660,7 @@
         <v>true</v>
       </c>
       <c r="AH15" t="str">
-        <v>2026-08-04T08:17:41.809Z</v>
+        <v>2026-08-04T08:53:46.611Z</v>
       </c>
     </row>
     <row r="16">
@@ -11844,7 +11764,7 @@
         <v>[]</v>
       </c>
       <c r="AH16" t="str">
-        <v>2026-08-04T08:17:41.809Z</v>
+        <v>2026-08-04T08:53:46.611Z</v>
       </c>
     </row>
     <row r="17">
@@ -11939,7 +11859,7 @@
         <v>true</v>
       </c>
       <c r="AH17" t="str">
-        <v>2026-08-04T08:17:41.809Z</v>
+        <v>2026-08-04T08:53:46.611Z</v>
       </c>
     </row>
     <row r="18">
@@ -12043,7 +11963,7 @@
         <v>[]</v>
       </c>
       <c r="AH18" t="str">
-        <v>2026-08-04T08:17:41.809Z</v>
+        <v>2026-08-04T08:53:46.611Z</v>
       </c>
     </row>
     <row r="19">
@@ -12147,7 +12067,7 @@
         <v>[]</v>
       </c>
       <c r="AH19" t="str">
-        <v>2026-08-04T08:17:41.809Z</v>
+        <v>2026-08-04T08:53:46.611Z</v>
       </c>
     </row>
     <row r="20">
@@ -12251,7 +12171,7 @@
         <v>[]</v>
       </c>
       <c r="AH20" t="str">
-        <v>2026-08-04T08:17:41.809Z</v>
+        <v>2026-08-04T08:53:46.611Z</v>
       </c>
     </row>
     <row r="21">
@@ -12355,7 +12275,7 @@
         <v>[]</v>
       </c>
       <c r="AH21" t="str">
-        <v>2026-08-04T08:17:41.809Z</v>
+        <v>2026-08-04T08:53:46.611Z</v>
       </c>
     </row>
     <row r="22">
@@ -12450,7 +12370,7 @@
         <v>true</v>
       </c>
       <c r="AH22" t="str">
-        <v>2026-08-04T08:17:41.809Z</v>
+        <v>2026-08-04T08:53:46.611Z</v>
       </c>
     </row>
     <row r="23">
@@ -12554,7 +12474,7 @@
         <v>[]</v>
       </c>
       <c r="AH23" t="str">
-        <v>2026-08-04T08:17:41.809Z</v>
+        <v>2026-08-04T08:53:46.611Z</v>
       </c>
     </row>
     <row r="24">
@@ -12649,7 +12569,7 @@
         <v>true</v>
       </c>
       <c r="AH24" t="str">
-        <v>2026-08-04T08:17:41.809Z</v>
+        <v>2026-08-04T08:53:46.611Z</v>
       </c>
     </row>
     <row r="25">
@@ -12753,7 +12673,7 @@
         <v>[]</v>
       </c>
       <c r="AH25" t="str">
-        <v>2026-08-04T08:17:41.809Z</v>
+        <v>2026-08-04T08:53:46.611Z</v>
       </c>
     </row>
     <row r="26">
@@ -12857,7 +12777,7 @@
         <v>[]</v>
       </c>
       <c r="AH26" t="str">
-        <v>2026-08-04T08:17:41.809Z</v>
+        <v>2026-08-04T08:53:46.611Z</v>
       </c>
     </row>
     <row r="27">
@@ -12961,7 +12881,7 @@
         <v>[]</v>
       </c>
       <c r="AH27" t="str">
-        <v>2026-08-04T08:17:41.809Z</v>
+        <v>2026-08-04T08:53:46.611Z</v>
       </c>
     </row>
     <row r="28">
@@ -13065,7 +12985,7 @@
         <v>[]</v>
       </c>
       <c r="AH28" t="str">
-        <v>2026-08-04T08:17:41.809Z</v>
+        <v>2026-08-04T08:53:46.611Z</v>
       </c>
     </row>
     <row r="29">
@@ -13160,7 +13080,7 @@
         <v>true</v>
       </c>
       <c r="AH29" t="str">
-        <v>2026-08-04T08:17:41.809Z</v>
+        <v>2026-08-04T08:53:46.611Z</v>
       </c>
     </row>
     <row r="30">
@@ -13264,7 +13184,7 @@
         <v>[]</v>
       </c>
       <c r="AH30" t="str">
-        <v>2026-08-04T08:17:41.809Z</v>
+        <v>2026-08-04T08:53:46.611Z</v>
       </c>
     </row>
     <row r="31">
@@ -13359,7 +13279,7 @@
         <v>true</v>
       </c>
       <c r="AH31" t="str">
-        <v>2026-08-04T08:17:41.809Z</v>
+        <v>2026-08-04T08:53:46.611Z</v>
       </c>
     </row>
     <row r="32">
@@ -13463,7 +13383,7 @@
         <v>[]</v>
       </c>
       <c r="AH32" t="str">
-        <v>2026-08-04T08:17:41.809Z</v>
+        <v>2026-08-04T08:53:46.611Z</v>
       </c>
     </row>
     <row r="33">
@@ -13567,7 +13487,7 @@
         <v>[]</v>
       </c>
       <c r="AH33" t="str">
-        <v>2026-08-04T08:17:41.809Z</v>
+        <v>2026-08-04T08:53:46.611Z</v>
       </c>
     </row>
     <row r="34">
@@ -13671,7 +13591,7 @@
         <v>[]</v>
       </c>
       <c r="AH34" t="str">
-        <v>2026-08-04T08:17:41.809Z</v>
+        <v>2026-08-04T08:53:46.611Z</v>
       </c>
     </row>
     <row r="35">
@@ -13766,7 +13686,7 @@
         <v>true</v>
       </c>
       <c r="AH35" t="str">
-        <v>2026-08-04T08:17:41.809Z</v>
+        <v>2026-08-04T08:53:46.611Z</v>
       </c>
     </row>
     <row r="36">
@@ -13870,7 +13790,7 @@
         <v>[]</v>
       </c>
       <c r="AH36" t="str">
-        <v>2026-08-04T08:17:41.809Z</v>
+        <v>2026-08-04T08:53:46.611Z</v>
       </c>
     </row>
     <row r="37">
@@ -13965,7 +13885,7 @@
         <v>true</v>
       </c>
       <c r="AH37" t="str">
-        <v>2026-08-04T08:17:41.809Z</v>
+        <v>2026-08-04T08:53:46.611Z</v>
       </c>
     </row>
     <row r="38">
@@ -14069,7 +13989,7 @@
         <v>[]</v>
       </c>
       <c r="AH38" t="str">
-        <v>2026-08-04T08:17:41.809Z</v>
+        <v>2026-08-04T08:53:46.611Z</v>
       </c>
     </row>
     <row r="39">
@@ -14173,7 +14093,7 @@
         <v>[]</v>
       </c>
       <c r="AH39" t="str">
-        <v>2026-08-04T08:17:41.809Z</v>
+        <v>2026-08-04T08:53:46.611Z</v>
       </c>
     </row>
     <row r="40">
@@ -14277,7 +14197,7 @@
         <v>[]</v>
       </c>
       <c r="AH40" t="str">
-        <v>2026-08-04T08:17:41.809Z</v>
+        <v>2026-08-04T08:53:46.611Z</v>
       </c>
     </row>
     <row r="41">
@@ -14381,7 +14301,7 @@
         <v>[]</v>
       </c>
       <c r="AH41" t="str">
-        <v>2026-08-04T08:17:41.809Z</v>
+        <v>2026-08-04T08:53:46.612Z</v>
       </c>
     </row>
     <row r="42">
@@ -14476,7 +14396,7 @@
         <v>true</v>
       </c>
       <c r="AH42" t="str">
-        <v>2026-08-04T08:17:41.809Z</v>
+        <v>2026-08-04T08:53:46.612Z</v>
       </c>
     </row>
     <row r="43">
@@ -14580,7 +14500,7 @@
         <v>[]</v>
       </c>
       <c r="AH43" t="str">
-        <v>2026-08-04T08:17:41.809Z</v>
+        <v>2026-08-04T08:53:46.612Z</v>
       </c>
     </row>
     <row r="44">
@@ -14684,7 +14604,7 @@
         <v>[]</v>
       </c>
       <c r="AH44" t="str">
-        <v>2026-08-04T08:17:41.809Z</v>
+        <v>2026-08-04T08:53:46.612Z</v>
       </c>
     </row>
     <row r="45">
@@ -14692,7 +14612,7 @@
         <v>6a299407c4fc5fbd6d56d02c</v>
       </c>
       <c r="B45" t="str">
-        <v>Choco Pistachio</v>
+        <v>Choco pistachio</v>
       </c>
       <c r="C45" t="str">
         <v>choco-pistachio</v>
@@ -14713,7 +14633,7 @@
         <v>Pistachio with cream &amp; white chocolate</v>
       </c>
       <c r="I45" t="str">
-        <v>https://res.cloudinary.com/djkfvoxpx/image/upload/v1783017588/birthday%20cakes/deb2qdo7ca2dgf7bvrqj.png</v>
+        <v>https://res.cloudinary.com/ju3bqezy/image/upload/v1785832567/products/uc9bfxlkrh5epxib1uqi.webp</v>
       </c>
       <c r="J45" t="str">
         <v>true</v>
@@ -14761,7 +14681,7 @@
         <v>chocolate-cakes</v>
       </c>
       <c r="Y45" t="str">
-        <v>2026-07-28T15:08:52.102Z</v>
+        <v>2026-08-04T08:36:08.118Z</v>
       </c>
       <c r="Z45" t="str">
         <v>[]</v>
@@ -14770,7 +14690,7 @@
         <v>[]</v>
       </c>
       <c r="AB45" t="str">
-        <v>birthday cakes/deb2qdo7ca2dgf7bvrqj</v>
+        <v>products/uc9bfxlkrh5epxib1uqi</v>
       </c>
       <c r="AC45" t="str">
         <v>[]</v>
@@ -14788,7 +14708,7 @@
         <v>[]</v>
       </c>
       <c r="AH45" t="str">
-        <v>2026-08-04T08:17:41.809Z</v>
+        <v>2026-08-04T08:53:46.612Z</v>
       </c>
     </row>
     <row r="46">
@@ -14892,7 +14812,7 @@
         <v>[]</v>
       </c>
       <c r="AH46" t="str">
-        <v>2026-08-04T08:17:41.809Z</v>
+        <v>2026-08-04T08:53:46.612Z</v>
       </c>
     </row>
     <row r="47">
@@ -14996,7 +14916,7 @@
         <v>[]</v>
       </c>
       <c r="AH47" t="str">
-        <v>2026-08-04T08:17:41.809Z</v>
+        <v>2026-08-04T08:53:46.612Z</v>
       </c>
       <c r="AI47" t="str">
         <v/>
@@ -15109,7 +15029,7 @@
         <v>[]</v>
       </c>
       <c r="AH48" t="str">
-        <v>2026-08-04T08:17:41.809Z</v>
+        <v>2026-08-04T08:53:46.612Z</v>
       </c>
       <c r="AI48" t="str">
         <v/>
@@ -15222,7 +15142,7 @@
         <v>[]</v>
       </c>
       <c r="AH49" t="str">
-        <v>2026-08-04T08:17:41.809Z</v>
+        <v>2026-08-04T08:53:46.612Z</v>
       </c>
       <c r="AI49" t="str">
         <v/>
@@ -15335,7 +15255,7 @@
         <v>[]</v>
       </c>
       <c r="AH50" t="str">
-        <v>2026-08-04T08:17:41.809Z</v>
+        <v>2026-08-04T08:53:46.612Z</v>
       </c>
       <c r="AI50" t="str">
         <v/>
@@ -15448,7 +15368,7 @@
         <v>[]</v>
       </c>
       <c r="AH51" t="str">
-        <v>2026-08-04T08:17:41.809Z</v>
+        <v>2026-08-04T08:53:46.612Z</v>
       </c>
       <c r="AI51" t="str">
         <v/>
@@ -15552,7 +15472,7 @@
         <v>false</v>
       </c>
       <c r="AH52" t="str">
-        <v>2026-08-04T08:17:41.809Z</v>
+        <v>2026-08-04T08:53:46.612Z</v>
       </c>
       <c r="AI52" t="str">
         <v/>
@@ -15656,7 +15576,7 @@
         <v>false</v>
       </c>
       <c r="AH53" t="str">
-        <v>2026-08-04T08:17:41.809Z</v>
+        <v>2026-08-04T08:53:46.612Z</v>
       </c>
       <c r="AI53" t="str">
         <v/>
@@ -15760,7 +15680,7 @@
         <v>false</v>
       </c>
       <c r="AH54" t="str">
-        <v>2026-08-04T08:17:41.810Z</v>
+        <v>2026-08-04T08:53:46.612Z</v>
       </c>
       <c r="AI54" t="str">
         <v/>
@@ -15864,7 +15784,7 @@
         <v>false</v>
       </c>
       <c r="AH55" t="str">
-        <v>2026-08-04T08:17:41.810Z</v>
+        <v>2026-08-04T08:53:46.612Z</v>
       </c>
       <c r="AI55" t="str">
         <v/>
@@ -15968,7 +15888,7 @@
         <v>false</v>
       </c>
       <c r="AH56" t="str">
-        <v>2026-08-04T08:17:41.810Z</v>
+        <v>2026-08-04T08:53:46.612Z</v>
       </c>
       <c r="AI56" t="str">
         <v/>
@@ -16072,7 +15992,7 @@
         <v>false</v>
       </c>
       <c r="AH57" t="str">
-        <v>2026-08-04T08:17:41.810Z</v>
+        <v>2026-08-04T08:53:46.612Z</v>
       </c>
       <c r="AI57" t="str">
         <v/>
@@ -16176,7 +16096,7 @@
         <v>false</v>
       </c>
       <c r="AH58" t="str">
-        <v>2026-08-04T08:17:41.810Z</v>
+        <v>2026-08-04T08:53:46.612Z</v>
       </c>
       <c r="AI58" t="str">
         <v/>
@@ -16280,7 +16200,7 @@
         <v>false</v>
       </c>
       <c r="AH59" t="str">
-        <v>2026-08-04T08:17:41.810Z</v>
+        <v>2026-08-04T08:53:46.613Z</v>
       </c>
       <c r="AI59" t="str">
         <v/>
@@ -16384,7 +16304,7 @@
         <v>false</v>
       </c>
       <c r="AH60" t="str">
-        <v>2026-08-04T08:17:41.810Z</v>
+        <v>2026-08-04T08:53:46.613Z</v>
       </c>
       <c r="AI60" t="str">
         <v/>
@@ -16488,7 +16408,7 @@
         <v>false</v>
       </c>
       <c r="AH61" t="str">
-        <v>2026-08-04T08:17:41.810Z</v>
+        <v>2026-08-04T08:53:46.613Z</v>
       </c>
       <c r="AI61" t="str">
         <v/>
@@ -16592,7 +16512,7 @@
         <v>[]</v>
       </c>
       <c r="AH62" t="str">
-        <v>2026-08-04T08:17:41.810Z</v>
+        <v>2026-08-04T08:53:46.613Z</v>
       </c>
       <c r="AI62" t="str">
         <v/>
@@ -16699,7 +16619,7 @@
         <v>false</v>
       </c>
       <c r="AH63" t="str">
-        <v>2026-08-04T08:17:41.810Z</v>
+        <v>2026-08-04T08:53:46.613Z</v>
       </c>
       <c r="AI63" t="str">
         <v/>
@@ -16803,7 +16723,7 @@
         <v>false</v>
       </c>
       <c r="AH64" t="str">
-        <v>2026-08-04T08:17:41.810Z</v>
+        <v>2026-08-04T08:53:46.613Z</v>
       </c>
       <c r="AI64" t="str">
         <v/>
@@ -16907,7 +16827,7 @@
         <v>false</v>
       </c>
       <c r="AH65" t="str">
-        <v>2026-08-04T08:17:41.810Z</v>
+        <v>2026-08-04T08:53:46.613Z</v>
       </c>
       <c r="AI65" t="str">
         <v/>
@@ -17002,7 +16922,7 @@
         <v>chocolates/wwosfnmcbprgc1pawgbe</v>
       </c>
       <c r="AH66" t="str">
-        <v>2026-08-04T08:17:41.810Z</v>
+        <v>2026-08-04T08:53:46.613Z</v>
       </c>
       <c r="AI66" t="str">
         <v/>
@@ -17106,7 +17026,7 @@
         <v>[]</v>
       </c>
       <c r="AH67" t="str">
-        <v>2026-08-04T08:17:41.810Z</v>
+        <v>2026-08-04T08:53:46.613Z</v>
       </c>
       <c r="AI67" t="str">
         <v/>
@@ -17213,7 +17133,7 @@
         <v>[]</v>
       </c>
       <c r="AH68" t="str">
-        <v>2026-08-04T08:17:41.810Z</v>
+        <v>2026-08-04T08:53:46.613Z</v>
       </c>
       <c r="AI68" t="str">
         <v/>
@@ -17320,7 +17240,7 @@
         <v>[]</v>
       </c>
       <c r="AH69" t="str">
-        <v>2026-08-04T08:17:41.810Z</v>
+        <v>2026-08-04T08:53:46.613Z</v>
       </c>
       <c r="AI69" t="str">
         <v/>
@@ -17427,7 +17347,7 @@
         <v>false</v>
       </c>
       <c r="AH70" t="str">
-        <v>2026-08-04T08:17:41.810Z</v>
+        <v>2026-08-04T08:53:46.613Z</v>
       </c>
       <c r="AI70" t="str">
         <v/>
@@ -17525,7 +17445,7 @@
         <v>false</v>
       </c>
       <c r="AH71" t="str">
-        <v>2026-08-04T08:17:41.810Z</v>
+        <v>2026-08-04T08:53:46.613Z</v>
       </c>
       <c r="AI71" t="str">
         <v/>
@@ -17623,7 +17543,7 @@
         <v>false</v>
       </c>
       <c r="AH72" t="str">
-        <v>2026-08-04T08:17:41.810Z</v>
+        <v>2026-08-04T08:53:46.613Z</v>
       </c>
       <c r="AI72" t="str">
         <v/>
@@ -17721,7 +17641,7 @@
         <v>false</v>
       </c>
       <c r="AH73" t="str">
-        <v>2026-08-04T08:17:41.810Z</v>
+        <v>2026-08-04T08:53:46.613Z</v>
       </c>
       <c r="AI73" t="str">
         <v/>
@@ -17819,7 +17739,7 @@
         <v>false</v>
       </c>
       <c r="AH74" t="str">
-        <v>2026-08-04T08:17:41.810Z</v>
+        <v>2026-08-04T08:53:46.613Z</v>
       </c>
       <c r="AI74" t="str">
         <v/>
@@ -17917,7 +17837,7 @@
         <v>false</v>
       </c>
       <c r="AH75" t="str">
-        <v>2026-08-04T08:17:41.810Z</v>
+        <v>2026-08-04T08:53:46.613Z</v>
       </c>
       <c r="AI75" t="str">
         <v/>
@@ -18015,7 +17935,7 @@
         <v>false</v>
       </c>
       <c r="AH76" t="str">
-        <v>2026-08-04T08:17:41.810Z</v>
+        <v>2026-08-04T08:53:46.613Z</v>
       </c>
       <c r="AI76" t="str">
         <v/>
@@ -18113,7 +18033,7 @@
         <v>false</v>
       </c>
       <c r="AH77" t="str">
-        <v>2026-08-04T08:17:41.810Z</v>
+        <v>2026-08-04T08:53:46.613Z</v>
       </c>
       <c r="AI77" t="str">
         <v/>
@@ -18211,7 +18131,7 @@
         <v>false</v>
       </c>
       <c r="AH78" t="str">
-        <v>2026-08-04T08:17:41.810Z</v>
+        <v>2026-08-04T08:53:46.613Z</v>
       </c>
       <c r="AI78" t="str">
         <v/>
@@ -18324,7 +18244,7 @@
         <v>[]</v>
       </c>
       <c r="AH79" t="str">
-        <v>2026-08-04T08:17:41.810Z</v>
+        <v>2026-08-04T08:53:46.613Z</v>
       </c>
       <c r="AI79" t="str">
         <v/>
@@ -18437,7 +18357,7 @@
         <v>[]</v>
       </c>
       <c r="AH80" t="str">
-        <v>2026-08-04T08:17:41.810Z</v>
+        <v>2026-08-04T08:53:46.614Z</v>
       </c>
       <c r="AI80" t="str">
         <v/>
@@ -18550,7 +18470,7 @@
         <v>[]</v>
       </c>
       <c r="AH81" t="str">
-        <v>2026-08-04T08:17:41.810Z</v>
+        <v>2026-08-04T08:53:46.614Z</v>
       </c>
       <c r="AI81" t="str">
         <v/>
@@ -18663,7 +18583,7 @@
         <v>[]</v>
       </c>
       <c r="AH82" t="str">
-        <v>2026-08-04T08:17:41.810Z</v>
+        <v>2026-08-04T08:53:46.614Z</v>
       </c>
       <c r="AI82" t="str">
         <v/>
@@ -18776,7 +18696,7 @@
         <v>[]</v>
       </c>
       <c r="AH83" t="str">
-        <v>2026-08-04T08:17:41.810Z</v>
+        <v>2026-08-04T08:53:46.614Z</v>
       </c>
       <c r="AI83" t="str">
         <v/>
@@ -18880,7 +18800,7 @@
         <v>false</v>
       </c>
       <c r="AH84" t="str">
-        <v>2026-08-04T08:17:41.810Z</v>
+        <v>2026-08-04T08:53:46.614Z</v>
       </c>
       <c r="AI84" t="str">
         <v/>
@@ -18984,7 +18904,7 @@
         <v>false</v>
       </c>
       <c r="AH85" t="str">
-        <v>2026-08-04T08:17:41.810Z</v>
+        <v>2026-08-04T08:53:46.614Z</v>
       </c>
       <c r="AI85" t="str">
         <v/>
@@ -19088,7 +19008,7 @@
         <v>false</v>
       </c>
       <c r="AH86" t="str">
-        <v>2026-08-04T08:17:41.810Z</v>
+        <v>2026-08-04T08:53:46.614Z</v>
       </c>
       <c r="AI86" t="str">
         <v/>
@@ -19201,7 +19121,7 @@
         <v>[]</v>
       </c>
       <c r="AH87" t="str">
-        <v>2026-08-04T08:17:41.810Z</v>
+        <v>2026-08-04T08:53:46.614Z</v>
       </c>
       <c r="AI87" t="str">
         <v/>
@@ -19305,7 +19225,7 @@
         <v>false</v>
       </c>
       <c r="AH88" t="str">
-        <v>2026-08-04T08:17:41.810Z</v>
+        <v>2026-08-04T08:53:46.614Z</v>
       </c>
       <c r="AI88" t="str">
         <v/>
@@ -19418,7 +19338,7 @@
         <v>[]</v>
       </c>
       <c r="AH89" t="str">
-        <v>2026-08-04T08:17:41.810Z</v>
+        <v>2026-08-04T08:53:46.614Z</v>
       </c>
       <c r="AI89" t="str">
         <v/>
@@ -19531,7 +19451,7 @@
         <v>[]</v>
       </c>
       <c r="AH90" t="str">
-        <v>2026-08-04T08:17:41.810Z</v>
+        <v>2026-08-04T08:53:46.614Z</v>
       </c>
       <c r="AI90" t="str">
         <v/>
@@ -19644,7 +19564,7 @@
         <v>[]</v>
       </c>
       <c r="AH91" t="str">
-        <v>2026-08-04T08:17:41.810Z</v>
+        <v>2026-08-04T08:53:46.614Z</v>
       </c>
       <c r="AI91" t="str">
         <v/>
@@ -19748,7 +19668,7 @@
         <v>false</v>
       </c>
       <c r="AH92" t="str">
-        <v>2026-08-04T08:17:41.810Z</v>
+        <v>2026-08-04T08:53:46.615Z</v>
       </c>
       <c r="AI92" t="str">
         <v/>
@@ -19852,7 +19772,7 @@
         <v>false</v>
       </c>
       <c r="AH93" t="str">
-        <v>2026-08-04T08:17:41.811Z</v>
+        <v>2026-08-04T08:53:46.615Z</v>
       </c>
       <c r="AI93" t="str">
         <v/>
@@ -19956,7 +19876,7 @@
         <v>false</v>
       </c>
       <c r="AH94" t="str">
-        <v>2026-08-04T08:17:41.811Z</v>
+        <v>2026-08-04T08:53:46.615Z</v>
       </c>
       <c r="AI94" t="str">
         <v/>
@@ -20060,7 +19980,7 @@
         <v>false</v>
       </c>
       <c r="AH95" t="str">
-        <v>2026-08-04T08:17:41.811Z</v>
+        <v>2026-08-04T08:53:46.615Z</v>
       </c>
       <c r="AI95" t="str">
         <v/>
@@ -20164,7 +20084,7 @@
         <v>false</v>
       </c>
       <c r="AH96" t="str">
-        <v>2026-08-04T08:17:41.811Z</v>
+        <v>2026-08-04T08:53:46.615Z</v>
       </c>
       <c r="AI96" t="str">
         <v/>
@@ -20268,7 +20188,7 @@
         <v>false</v>
       </c>
       <c r="AH97" t="str">
-        <v>2026-08-04T08:17:41.811Z</v>
+        <v>2026-08-04T08:53:46.615Z</v>
       </c>
       <c r="AI97" t="str">
         <v/>
@@ -20372,7 +20292,7 @@
         <v>false</v>
       </c>
       <c r="AH98" t="str">
-        <v>2026-08-04T08:17:41.811Z</v>
+        <v>2026-08-04T08:53:46.615Z</v>
       </c>
       <c r="AI98" t="str">
         <v/>
@@ -20476,7 +20396,7 @@
         <v>false</v>
       </c>
       <c r="AH99" t="str">
-        <v>2026-08-04T08:17:41.811Z</v>
+        <v>2026-08-04T08:53:46.615Z</v>
       </c>
       <c r="AI99" t="str">
         <v/>
@@ -20580,7 +20500,7 @@
         <v>false</v>
       </c>
       <c r="AH100" t="str">
-        <v>2026-08-04T08:17:41.811Z</v>
+        <v>2026-08-04T08:53:46.615Z</v>
       </c>
       <c r="AI100" t="str">
         <v/>
@@ -20693,7 +20613,7 @@
         <v>[]</v>
       </c>
       <c r="AH101" t="str">
-        <v>2026-08-04T08:17:41.811Z</v>
+        <v>2026-08-04T08:53:46.615Z</v>
       </c>
       <c r="AI101" t="str">
         <v/>
@@ -20797,7 +20717,7 @@
         <v>false</v>
       </c>
       <c r="AH102" t="str">
-        <v>2026-08-04T08:17:41.811Z</v>
+        <v>2026-08-04T08:53:46.615Z</v>
       </c>
       <c r="AI102" t="str">
         <v/>
@@ -20910,7 +20830,7 @@
         <v>[]</v>
       </c>
       <c r="AH103" t="str">
-        <v>2026-08-04T08:17:41.811Z</v>
+        <v>2026-08-04T08:53:46.615Z</v>
       </c>
       <c r="AI103" t="str">
         <v/>
@@ -21023,7 +20943,7 @@
         <v>[]</v>
       </c>
       <c r="AH104" t="str">
-        <v>2026-08-04T08:17:41.811Z</v>
+        <v>2026-08-04T08:53:46.615Z</v>
       </c>
       <c r="AI104" t="str">
         <v/>
@@ -21136,7 +21056,7 @@
         <v>[]</v>
       </c>
       <c r="AH105" t="str">
-        <v>2026-08-04T08:17:41.811Z</v>
+        <v>2026-08-04T08:53:46.616Z</v>
       </c>
       <c r="AI105" t="str">
         <v/>
@@ -21252,7 +21172,7 @@
         <v>[]</v>
       </c>
       <c r="AH106" t="str">
-        <v>2026-08-04T08:17:41.811Z</v>
+        <v>2026-08-04T08:53:46.616Z</v>
       </c>
       <c r="AI106" t="str">
         <v/>
@@ -21273,7 +21193,7 @@
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:AA18"/>
+  <dimension ref="A1:AB28"/>
   <cols>
     <col min="1" max="1" width="26.83203125" customWidth="1"/>
     <col min="2" max="2" width="26.83203125" customWidth="1"/>
@@ -21380,6 +21300,9 @@
       <c r="AA1" t="str">
         <v>data_amount</v>
       </c>
+      <c r="AB1" t="str">
+        <v>data_productId</v>
+      </c>
     </row>
     <row r="2" xml:space="preserve">
       <c r="A2" t="str">
@@ -21444,7 +21367,7 @@
         <v>2026-08-03T08:32:20.631Z</v>
       </c>
       <c r="U2" t="str">
-        <v>2026-08-04T08:17:41.920Z</v>
+        <v>2026-08-04T08:53:46.722Z</v>
       </c>
     </row>
     <row r="3" xml:space="preserve">
@@ -21510,7 +21433,7 @@
         <v>2026-08-03T11:31:03.986Z</v>
       </c>
       <c r="U3" t="str">
-        <v>2026-08-04T08:17:41.920Z</v>
+        <v>2026-08-04T08:53:46.722Z</v>
       </c>
     </row>
     <row r="4" xml:space="preserve">
@@ -21576,7 +21499,7 @@
         <v>2026-08-03T11:42:37.879Z</v>
       </c>
       <c r="U4" t="str">
-        <v>2026-08-04T08:17:41.920Z</v>
+        <v>2026-08-04T08:53:46.722Z</v>
       </c>
     </row>
     <row r="5" xml:space="preserve">
@@ -21642,7 +21565,7 @@
         <v>2026-08-04T02:54:51.282Z</v>
       </c>
       <c r="U5" t="str">
-        <v>2026-08-04T08:17:41.920Z</v>
+        <v>2026-08-04T08:53:46.722Z</v>
       </c>
     </row>
     <row r="6" xml:space="preserve">
@@ -21708,7 +21631,7 @@
         <v>2026-08-04T02:54:51.524Z</v>
       </c>
       <c r="U6" t="str">
-        <v>2026-08-04T08:17:41.920Z</v>
+        <v>2026-08-04T08:53:46.722Z</v>
       </c>
     </row>
     <row r="7" xml:space="preserve">
@@ -21774,7 +21697,7 @@
         <v>2026-08-04T02:56:57.266Z</v>
       </c>
       <c r="U7" t="str">
-        <v>2026-08-04T08:17:41.920Z</v>
+        <v>2026-08-04T08:53:46.722Z</v>
       </c>
     </row>
     <row r="8" xml:space="preserve">
@@ -21840,7 +21763,7 @@
         <v>2026-08-04T02:56:57.503Z</v>
       </c>
       <c r="U8" t="str">
-        <v>2026-08-04T08:17:41.920Z</v>
+        <v>2026-08-04T08:53:46.722Z</v>
       </c>
     </row>
     <row r="9" xml:space="preserve">
@@ -21906,7 +21829,7 @@
         <v>2026-08-04T02:58:17.874Z</v>
       </c>
       <c r="U9" t="str">
-        <v>2026-08-04T08:17:41.920Z</v>
+        <v>2026-08-04T08:53:46.722Z</v>
       </c>
     </row>
     <row r="10" xml:space="preserve">
@@ -21972,7 +21895,7 @@
         <v>2026-08-04T02:58:18.111Z</v>
       </c>
       <c r="U10" t="str">
-        <v>2026-08-04T08:17:41.920Z</v>
+        <v>2026-08-04T08:53:46.722Z</v>
       </c>
     </row>
     <row r="11">
@@ -22034,7 +21957,7 @@
         <v>2026-08-04T03:07:52.920Z</v>
       </c>
       <c r="U11" t="str">
-        <v>2026-08-04T08:17:41.920Z</v>
+        <v>2026-08-04T08:53:46.722Z</v>
       </c>
       <c r="V11" t="str">
         <v>6a7157484aac857cdce15f55</v>
@@ -22104,7 +22027,7 @@
         <v>2026-08-04T03:08:27.149Z</v>
       </c>
       <c r="U12" t="str">
-        <v>2026-08-04T08:17:41.920Z</v>
+        <v>2026-08-04T08:53:46.723Z</v>
       </c>
       <c r="V12" t="str">
         <v>6a7157484aac857cdce15f55</v>
@@ -22189,7 +22112,7 @@
         <v>2026-08-04T03:08:27.398Z</v>
       </c>
       <c r="U13" t="str">
-        <v>2026-08-04T08:17:41.921Z</v>
+        <v>2026-08-04T08:53:46.723Z</v>
       </c>
       <c r="V13" t="str">
         <v>6a7157484aac857cdce15f55</v>
@@ -22273,7 +22196,7 @@
         <v>2026-08-04T04:15:57.196Z</v>
       </c>
       <c r="U14" t="str">
-        <v>2026-08-04T08:17:41.921Z</v>
+        <v>2026-08-04T08:53:46.723Z</v>
       </c>
     </row>
     <row r="15" xml:space="preserve">
@@ -22339,7 +22262,7 @@
         <v>2026-08-04T04:15:57.434Z</v>
       </c>
       <c r="U15" t="str">
-        <v>2026-08-04T08:17:41.921Z</v>
+        <v>2026-08-04T08:53:46.723Z</v>
       </c>
     </row>
     <row r="16">
@@ -22401,7 +22324,7 @@
         <v>2026-08-04T06:55:29.223Z</v>
       </c>
       <c r="U16" t="str">
-        <v>2026-08-04T08:17:41.921Z</v>
+        <v>2026-08-04T08:53:46.723Z</v>
       </c>
       <c r="V16" t="str">
         <v>6a718cc0f0f91c3459f15086</v>
@@ -22471,7 +22394,7 @@
         <v>2026-08-04T06:56:05.002Z</v>
       </c>
       <c r="U17" t="str">
-        <v>2026-08-04T08:17:41.921Z</v>
+        <v>2026-08-04T08:53:46.723Z</v>
       </c>
       <c r="V17" t="str">
         <v>6a718cc0f0f91c3459f15086</v>
@@ -22556,7 +22479,7 @@
         <v>2026-08-04T06:56:05.252Z</v>
       </c>
       <c r="U18" t="str">
-        <v>2026-08-04T08:17:41.921Z</v>
+        <v>2026-08-04T08:53:46.723Z</v>
       </c>
       <c r="V18" t="str">
         <v>6a718cc0f0f91c3459f15086</v>
@@ -22577,9 +22500,629 @@
         <v>740</v>
       </c>
     </row>
+    <row r="19">
+      <c r="A19" t="str">
+        <v>6a71a19e3e9bc88cd96d4bc5</v>
+      </c>
+      <c r="C19" t="str">
+        <v>6a7078161aed5008c4d25733</v>
+      </c>
+      <c r="D19" t="str">
+        <v>user</v>
+      </c>
+      <c r="E19" t="str">
+        <v>🔄 Product Updated</v>
+      </c>
+      <c r="F19" t="str">
+        <v>product_updated</v>
+      </c>
+      <c r="G19" t="str">
+        <v>WEB</v>
+      </c>
+      <c r="H19" t="str">
+        <v>Choco pistachio has been updated with new details!</v>
+      </c>
+      <c r="I19" t="str">
+        <v>product_updated</v>
+      </c>
+      <c r="K19" t="str">
+        <v>/product/choco-pistachio</v>
+      </c>
+      <c r="L19" t="str">
+        <v>false</v>
+      </c>
+      <c r="M19" t="str">
+        <v>SENT</v>
+      </c>
+      <c r="N19" t="str">
+        <v>true</v>
+      </c>
+      <c r="O19" t="str">
+        <v>false</v>
+      </c>
+      <c r="P19" t="str">
+        <v>false</v>
+      </c>
+      <c r="Q19" t="str">
+        <v>false</v>
+      </c>
+      <c r="R19" t="str">
+        <v>2026-08-04T08:23:58.498Z</v>
+      </c>
+      <c r="S19" t="str">
+        <v>2026-08-04T08:23:58.503Z</v>
+      </c>
+      <c r="T19" t="str">
+        <v>2026-08-04T08:23:58.503Z</v>
+      </c>
+      <c r="U19" t="str">
+        <v>2026-08-04T08:53:46.723Z</v>
+      </c>
+      <c r="AB19" t="str">
+        <v>6a299407c4fc5fbd6d56d02c</v>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" t="str">
+        <v>6a71a19e3e9bc88cd96d4bc6</v>
+      </c>
+      <c r="C20" t="str">
+        <v>6a707bbeaab7ba55ee1ffdb7</v>
+      </c>
+      <c r="D20" t="str">
+        <v>user</v>
+      </c>
+      <c r="E20" t="str">
+        <v>🔄 Product Updated</v>
+      </c>
+      <c r="F20" t="str">
+        <v>product_updated</v>
+      </c>
+      <c r="G20" t="str">
+        <v>WEB</v>
+      </c>
+      <c r="H20" t="str">
+        <v>Choco pistachio has been updated with new details!</v>
+      </c>
+      <c r="I20" t="str">
+        <v>product_updated</v>
+      </c>
+      <c r="K20" t="str">
+        <v>/product/choco-pistachio</v>
+      </c>
+      <c r="L20" t="str">
+        <v>false</v>
+      </c>
+      <c r="M20" t="str">
+        <v>SENT</v>
+      </c>
+      <c r="N20" t="str">
+        <v>true</v>
+      </c>
+      <c r="O20" t="str">
+        <v>false</v>
+      </c>
+      <c r="P20" t="str">
+        <v>false</v>
+      </c>
+      <c r="Q20" t="str">
+        <v>false</v>
+      </c>
+      <c r="R20" t="str">
+        <v>2026-08-04T08:23:58.612Z</v>
+      </c>
+      <c r="S20" t="str">
+        <v>2026-08-04T08:23:58.613Z</v>
+      </c>
+      <c r="T20" t="str">
+        <v>2026-08-04T08:23:58.613Z</v>
+      </c>
+      <c r="U20" t="str">
+        <v>2026-08-04T08:53:46.723Z</v>
+      </c>
+      <c r="AB20" t="str">
+        <v>6a299407c4fc5fbd6d56d02c</v>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" t="str">
+        <v>6a71a19e3e9bc88cd96d4bc7</v>
+      </c>
+      <c r="C21" t="str">
+        <v>6a707e784aac857cdce1455f</v>
+      </c>
+      <c r="D21" t="str">
+        <v>user</v>
+      </c>
+      <c r="E21" t="str">
+        <v>🔄 Product Updated</v>
+      </c>
+      <c r="F21" t="str">
+        <v>product_updated</v>
+      </c>
+      <c r="G21" t="str">
+        <v>WEB</v>
+      </c>
+      <c r="H21" t="str">
+        <v>Choco pistachio has been updated with new details!</v>
+      </c>
+      <c r="I21" t="str">
+        <v>product_updated</v>
+      </c>
+      <c r="K21" t="str">
+        <v>/product/choco-pistachio</v>
+      </c>
+      <c r="L21" t="str">
+        <v>false</v>
+      </c>
+      <c r="M21" t="str">
+        <v>SENT</v>
+      </c>
+      <c r="N21" t="str">
+        <v>true</v>
+      </c>
+      <c r="O21" t="str">
+        <v>false</v>
+      </c>
+      <c r="P21" t="str">
+        <v>false</v>
+      </c>
+      <c r="Q21" t="str">
+        <v>false</v>
+      </c>
+      <c r="R21" t="str">
+        <v>2026-08-04T08:23:58.725Z</v>
+      </c>
+      <c r="S21" t="str">
+        <v>2026-08-04T08:23:58.726Z</v>
+      </c>
+      <c r="T21" t="str">
+        <v>2026-08-04T08:23:58.726Z</v>
+      </c>
+      <c r="U21" t="str">
+        <v>2026-08-04T08:53:46.723Z</v>
+      </c>
+      <c r="AB21" t="str">
+        <v>6a299407c4fc5fbd6d56d02c</v>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" t="str">
+        <v>6a71a19e3e9bc88cd96d4bc8</v>
+      </c>
+      <c r="C22" t="str">
+        <v>6a7154b74aac857cdce15cbd</v>
+      </c>
+      <c r="D22" t="str">
+        <v>user</v>
+      </c>
+      <c r="E22" t="str">
+        <v>🔄 Product Updated</v>
+      </c>
+      <c r="F22" t="str">
+        <v>product_updated</v>
+      </c>
+      <c r="G22" t="str">
+        <v>WEB</v>
+      </c>
+      <c r="H22" t="str">
+        <v>Choco pistachio has been updated with new details!</v>
+      </c>
+      <c r="I22" t="str">
+        <v>product_updated</v>
+      </c>
+      <c r="K22" t="str">
+        <v>/product/choco-pistachio</v>
+      </c>
+      <c r="L22" t="str">
+        <v>false</v>
+      </c>
+      <c r="M22" t="str">
+        <v>SENT</v>
+      </c>
+      <c r="N22" t="str">
+        <v>true</v>
+      </c>
+      <c r="O22" t="str">
+        <v>false</v>
+      </c>
+      <c r="P22" t="str">
+        <v>false</v>
+      </c>
+      <c r="Q22" t="str">
+        <v>false</v>
+      </c>
+      <c r="R22" t="str">
+        <v>2026-08-04T08:23:58.859Z</v>
+      </c>
+      <c r="S22" t="str">
+        <v>2026-08-04T08:23:58.860Z</v>
+      </c>
+      <c r="T22" t="str">
+        <v>2026-08-04T08:23:58.860Z</v>
+      </c>
+      <c r="U22" t="str">
+        <v>2026-08-04T08:53:46.723Z</v>
+      </c>
+      <c r="AB22" t="str">
+        <v>6a299407c4fc5fbd6d56d02c</v>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" t="str">
+        <v>6a71a19e3e9bc88cd96d4bc9</v>
+      </c>
+      <c r="C23" t="str">
+        <v>6a7154f14aac857cdce15cc0</v>
+      </c>
+      <c r="D23" t="str">
+        <v>user</v>
+      </c>
+      <c r="E23" t="str">
+        <v>🔄 Product Updated</v>
+      </c>
+      <c r="F23" t="str">
+        <v>product_updated</v>
+      </c>
+      <c r="G23" t="str">
+        <v>WEB</v>
+      </c>
+      <c r="H23" t="str">
+        <v>Choco pistachio has been updated with new details!</v>
+      </c>
+      <c r="I23" t="str">
+        <v>product_updated</v>
+      </c>
+      <c r="K23" t="str">
+        <v>/product/choco-pistachio</v>
+      </c>
+      <c r="L23" t="str">
+        <v>false</v>
+      </c>
+      <c r="M23" t="str">
+        <v>SENT</v>
+      </c>
+      <c r="N23" t="str">
+        <v>true</v>
+      </c>
+      <c r="O23" t="str">
+        <v>false</v>
+      </c>
+      <c r="P23" t="str">
+        <v>false</v>
+      </c>
+      <c r="Q23" t="str">
+        <v>false</v>
+      </c>
+      <c r="R23" t="str">
+        <v>2026-08-04T08:23:58.967Z</v>
+      </c>
+      <c r="S23" t="str">
+        <v>2026-08-04T08:23:58.968Z</v>
+      </c>
+      <c r="T23" t="str">
+        <v>2026-08-04T08:23:58.968Z</v>
+      </c>
+      <c r="U23" t="str">
+        <v>2026-08-04T08:53:46.723Z</v>
+      </c>
+      <c r="AB23" t="str">
+        <v>6a299407c4fc5fbd6d56d02c</v>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" t="str">
+        <v>6a71a478f130b074095a33d7</v>
+      </c>
+      <c r="C24" t="str">
+        <v>6a7078161aed5008c4d25733</v>
+      </c>
+      <c r="D24" t="str">
+        <v>user</v>
+      </c>
+      <c r="E24" t="str">
+        <v>🔄 Product Updated</v>
+      </c>
+      <c r="F24" t="str">
+        <v>product_updated</v>
+      </c>
+      <c r="G24" t="str">
+        <v>WEB</v>
+      </c>
+      <c r="H24" t="str">
+        <v>Choco pistachio has been updated with new details!</v>
+      </c>
+      <c r="I24" t="str">
+        <v>product_updated</v>
+      </c>
+      <c r="K24" t="str">
+        <v>/product/choco-pistachio</v>
+      </c>
+      <c r="L24" t="str">
+        <v>false</v>
+      </c>
+      <c r="M24" t="str">
+        <v>SENT</v>
+      </c>
+      <c r="N24" t="str">
+        <v>true</v>
+      </c>
+      <c r="O24" t="str">
+        <v>false</v>
+      </c>
+      <c r="P24" t="str">
+        <v>false</v>
+      </c>
+      <c r="Q24" t="str">
+        <v>false</v>
+      </c>
+      <c r="R24" t="str">
+        <v>2026-08-04T08:36:08.691Z</v>
+      </c>
+      <c r="S24" t="str">
+        <v>2026-08-04T08:36:08.694Z</v>
+      </c>
+      <c r="T24" t="str">
+        <v>2026-08-04T08:36:08.694Z</v>
+      </c>
+      <c r="U24" t="str">
+        <v>2026-08-04T08:53:46.723Z</v>
+      </c>
+      <c r="AB24" t="str">
+        <v>6a299407c4fc5fbd6d56d02c</v>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" t="str">
+        <v>6a71a478f130b074095a33d8</v>
+      </c>
+      <c r="C25" t="str">
+        <v>6a707bbeaab7ba55ee1ffdb7</v>
+      </c>
+      <c r="D25" t="str">
+        <v>user</v>
+      </c>
+      <c r="E25" t="str">
+        <v>🔄 Product Updated</v>
+      </c>
+      <c r="F25" t="str">
+        <v>product_updated</v>
+      </c>
+      <c r="G25" t="str">
+        <v>WEB</v>
+      </c>
+      <c r="H25" t="str">
+        <v>Choco pistachio has been updated with new details!</v>
+      </c>
+      <c r="I25" t="str">
+        <v>product_updated</v>
+      </c>
+      <c r="K25" t="str">
+        <v>/product/choco-pistachio</v>
+      </c>
+      <c r="L25" t="str">
+        <v>false</v>
+      </c>
+      <c r="M25" t="str">
+        <v>SENT</v>
+      </c>
+      <c r="N25" t="str">
+        <v>true</v>
+      </c>
+      <c r="O25" t="str">
+        <v>false</v>
+      </c>
+      <c r="P25" t="str">
+        <v>false</v>
+      </c>
+      <c r="Q25" t="str">
+        <v>false</v>
+      </c>
+      <c r="R25" t="str">
+        <v>2026-08-04T08:36:08.934Z</v>
+      </c>
+      <c r="S25" t="str">
+        <v>2026-08-04T08:36:08.934Z</v>
+      </c>
+      <c r="T25" t="str">
+        <v>2026-08-04T08:36:08.934Z</v>
+      </c>
+      <c r="U25" t="str">
+        <v>2026-08-04T08:53:46.723Z</v>
+      </c>
+      <c r="AB25" t="str">
+        <v>6a299407c4fc5fbd6d56d02c</v>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" t="str">
+        <v>6a71a479f130b074095a33d9</v>
+      </c>
+      <c r="C26" t="str">
+        <v>6a707e784aac857cdce1455f</v>
+      </c>
+      <c r="D26" t="str">
+        <v>user</v>
+      </c>
+      <c r="E26" t="str">
+        <v>🔄 Product Updated</v>
+      </c>
+      <c r="F26" t="str">
+        <v>product_updated</v>
+      </c>
+      <c r="G26" t="str">
+        <v>WEB</v>
+      </c>
+      <c r="H26" t="str">
+        <v>Choco pistachio has been updated with new details!</v>
+      </c>
+      <c r="I26" t="str">
+        <v>product_updated</v>
+      </c>
+      <c r="K26" t="str">
+        <v>/product/choco-pistachio</v>
+      </c>
+      <c r="L26" t="str">
+        <v>false</v>
+      </c>
+      <c r="M26" t="str">
+        <v>SENT</v>
+      </c>
+      <c r="N26" t="str">
+        <v>true</v>
+      </c>
+      <c r="O26" t="str">
+        <v>false</v>
+      </c>
+      <c r="P26" t="str">
+        <v>false</v>
+      </c>
+      <c r="Q26" t="str">
+        <v>false</v>
+      </c>
+      <c r="R26" t="str">
+        <v>2026-08-04T08:36:09.170Z</v>
+      </c>
+      <c r="S26" t="str">
+        <v>2026-08-04T08:36:09.171Z</v>
+      </c>
+      <c r="T26" t="str">
+        <v>2026-08-04T08:36:09.171Z</v>
+      </c>
+      <c r="U26" t="str">
+        <v>2026-08-04T08:53:46.723Z</v>
+      </c>
+      <c r="AB26" t="str">
+        <v>6a299407c4fc5fbd6d56d02c</v>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" t="str">
+        <v>6a71a479f130b074095a33da</v>
+      </c>
+      <c r="C27" t="str">
+        <v>6a7154b74aac857cdce15cbd</v>
+      </c>
+      <c r="D27" t="str">
+        <v>user</v>
+      </c>
+      <c r="E27" t="str">
+        <v>🔄 Product Updated</v>
+      </c>
+      <c r="F27" t="str">
+        <v>product_updated</v>
+      </c>
+      <c r="G27" t="str">
+        <v>WEB</v>
+      </c>
+      <c r="H27" t="str">
+        <v>Choco pistachio has been updated with new details!</v>
+      </c>
+      <c r="I27" t="str">
+        <v>product_updated</v>
+      </c>
+      <c r="K27" t="str">
+        <v>/product/choco-pistachio</v>
+      </c>
+      <c r="L27" t="str">
+        <v>false</v>
+      </c>
+      <c r="M27" t="str">
+        <v>SENT</v>
+      </c>
+      <c r="N27" t="str">
+        <v>true</v>
+      </c>
+      <c r="O27" t="str">
+        <v>false</v>
+      </c>
+      <c r="P27" t="str">
+        <v>false</v>
+      </c>
+      <c r="Q27" t="str">
+        <v>false</v>
+      </c>
+      <c r="R27" t="str">
+        <v>2026-08-04T08:36:09.407Z</v>
+      </c>
+      <c r="S27" t="str">
+        <v>2026-08-04T08:36:09.408Z</v>
+      </c>
+      <c r="T27" t="str">
+        <v>2026-08-04T08:36:09.408Z</v>
+      </c>
+      <c r="U27" t="str">
+        <v>2026-08-04T08:53:46.723Z</v>
+      </c>
+      <c r="AB27" t="str">
+        <v>6a299407c4fc5fbd6d56d02c</v>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" t="str">
+        <v>6a71a479f130b074095a33db</v>
+      </c>
+      <c r="C28" t="str">
+        <v>6a7154f14aac857cdce15cc0</v>
+      </c>
+      <c r="D28" t="str">
+        <v>user</v>
+      </c>
+      <c r="E28" t="str">
+        <v>🔄 Product Updated</v>
+      </c>
+      <c r="F28" t="str">
+        <v>product_updated</v>
+      </c>
+      <c r="G28" t="str">
+        <v>WEB</v>
+      </c>
+      <c r="H28" t="str">
+        <v>Choco pistachio has been updated with new details!</v>
+      </c>
+      <c r="I28" t="str">
+        <v>product_updated</v>
+      </c>
+      <c r="K28" t="str">
+        <v>/product/choco-pistachio</v>
+      </c>
+      <c r="L28" t="str">
+        <v>false</v>
+      </c>
+      <c r="M28" t="str">
+        <v>SENT</v>
+      </c>
+      <c r="N28" t="str">
+        <v>true</v>
+      </c>
+      <c r="O28" t="str">
+        <v>false</v>
+      </c>
+      <c r="P28" t="str">
+        <v>false</v>
+      </c>
+      <c r="Q28" t="str">
+        <v>false</v>
+      </c>
+      <c r="R28" t="str">
+        <v>2026-08-04T08:36:09.644Z</v>
+      </c>
+      <c r="S28" t="str">
+        <v>2026-08-04T08:36:09.645Z</v>
+      </c>
+      <c r="T28" t="str">
+        <v>2026-08-04T08:36:09.645Z</v>
+      </c>
+      <c r="U28" t="str">
+        <v>2026-08-04T08:53:46.723Z</v>
+      </c>
+      <c r="AB28" t="str">
+        <v>6a299407c4fc5fbd6d56d02c</v>
+      </c>
+    </row>
   </sheetData>
   <ignoredErrors>
-    <ignoredError numberStoredAsText="1" sqref="A1:AA18"/>
+    <ignoredError numberStoredAsText="1" sqref="A1:AB28"/>
   </ignoredErrors>
 </worksheet>
 </file>
@@ -22729,7 +23272,7 @@
         <v>2026-07-24T16:56:36.026Z</v>
       </c>
       <c r="R2" t="str">
-        <v>2026-08-04T08:17:43.779Z</v>
+        <v>2026-08-04T08:53:47.347Z</v>
       </c>
     </row>
     <row r="3">
@@ -22785,7 +23328,7 @@
         <v>2026-07-28T17:39:40.124Z</v>
       </c>
       <c r="R3" t="str">
-        <v>2026-08-04T08:17:43.780Z</v>
+        <v>2026-08-04T08:53:47.348Z</v>
       </c>
       <c r="S3" t="str">
         <v>[]</v>
@@ -22853,7 +23396,7 @@
         <v>2026-07-28T17:42:45.014Z</v>
       </c>
       <c r="R4" t="str">
-        <v>2026-08-04T08:17:43.780Z</v>
+        <v>2026-08-04T08:53:47.348Z</v>
       </c>
       <c r="S4" t="str">
         <v>[]</v>
@@ -22921,7 +23464,7 @@
         <v>2026-07-28T17:35:21.654Z</v>
       </c>
       <c r="R5" t="str">
-        <v>2026-08-04T08:17:43.781Z</v>
+        <v>2026-08-04T08:53:47.349Z</v>
       </c>
       <c r="S5" t="str">
         <v>[]</v>
@@ -22989,7 +23532,7 @@
         <v>2026-07-28T17:30:16.981Z</v>
       </c>
       <c r="R6" t="str">
-        <v>2026-08-04T08:17:43.781Z</v>
+        <v>2026-08-04T08:53:47.349Z</v>
       </c>
       <c r="S6" t="str">
         <v>[]</v>
@@ -23057,7 +23600,7 @@
         <v>2026-08-02T10:49:00.973Z</v>
       </c>
       <c r="R7" t="str">
-        <v>2026-08-04T08:17:43.781Z</v>
+        <v>2026-08-04T08:53:47.349Z</v>
       </c>
       <c r="S7" t="str">
         <v>[]</v>
@@ -23125,7 +23668,7 @@
         <v>2026-07-26T18:00:06.903Z</v>
       </c>
       <c r="R8" t="str">
-        <v>2026-08-04T08:17:43.782Z</v>
+        <v>2026-08-04T08:53:47.350Z</v>
       </c>
     </row>
     <row r="9">
@@ -23181,7 +23724,7 @@
         <v>2026-07-28T17:37:46.453Z</v>
       </c>
       <c r="R9" t="str">
-        <v>2026-08-04T08:17:43.782Z</v>
+        <v>2026-08-04T08:53:47.350Z</v>
       </c>
       <c r="S9" t="str">
         <v>[]</v>
@@ -23249,7 +23792,7 @@
         <v>2026-07-28T15:52:28.248Z</v>
       </c>
       <c r="R10" t="str">
-        <v>2026-08-04T08:17:43.782Z</v>
+        <v>2026-08-04T08:53:47.350Z</v>
       </c>
       <c r="S10" t="str">
         <v>[]</v>
@@ -23317,7 +23860,7 @@
         <v>2026-07-28T17:48:40.457Z</v>
       </c>
       <c r="R11" t="str">
-        <v>2026-08-04T08:17:43.782Z</v>
+        <v>2026-08-04T08:53:47.350Z</v>
       </c>
       <c r="S11" t="str">
         <v>[]</v>
@@ -23385,7 +23928,7 @@
         <v>2026-07-28T17:49:54.713Z</v>
       </c>
       <c r="R12" t="str">
-        <v>2026-08-04T08:17:43.783Z</v>
+        <v>2026-08-04T08:53:47.351Z</v>
       </c>
       <c r="S12" t="str">
         <v>[]</v>
@@ -23453,7 +23996,7 @@
         <v>2026-07-28T17:34:40.195Z</v>
       </c>
       <c r="R13" t="str">
-        <v>2026-08-04T08:17:43.783Z</v>
+        <v>2026-08-04T08:53:47.351Z</v>
       </c>
       <c r="S13" t="str">
         <v>[]</v>
@@ -23521,7 +24064,7 @@
         <v>2026-07-28T16:31:18.393Z</v>
       </c>
       <c r="R14" t="str">
-        <v>2026-08-04T08:17:43.783Z</v>
+        <v>2026-08-04T08:53:47.352Z</v>
       </c>
       <c r="S14" t="str">
         <v>[]</v>
@@ -23589,7 +24132,7 @@
         <v>2026-08-03T14:35:00.987Z</v>
       </c>
       <c r="R15" t="str">
-        <v>2026-08-04T08:17:43.783Z</v>
+        <v>2026-08-04T08:53:47.352Z</v>
       </c>
       <c r="S15" t="str">
         <v>[]</v>
@@ -23657,7 +24200,7 @@
         <v>2026-07-28T16:20:47.688Z</v>
       </c>
       <c r="R16" t="str">
-        <v>2026-08-04T08:17:43.784Z</v>
+        <v>2026-08-04T08:53:47.352Z</v>
       </c>
       <c r="S16" t="str">
         <v>[]</v>
@@ -23725,7 +24268,7 @@
         <v>2026-07-24T17:04:18.204Z</v>
       </c>
       <c r="R17" t="str">
-        <v>2026-08-04T08:17:43.784Z</v>
+        <v>2026-08-04T08:53:47.352Z</v>
       </c>
     </row>
     <row r="18">
@@ -23781,7 +24324,7 @@
         <v>2026-07-24T17:04:57.812Z</v>
       </c>
       <c r="R18" t="str">
-        <v>2026-08-04T08:17:43.784Z</v>
+        <v>2026-08-04T08:53:47.353Z</v>
       </c>
     </row>
     <row r="19">
@@ -23837,7 +24380,7 @@
         <v>2026-07-28T15:06:55.169Z</v>
       </c>
       <c r="R19" t="str">
-        <v>2026-08-04T08:17:43.784Z</v>
+        <v>2026-08-04T08:53:47.353Z</v>
       </c>
       <c r="S19" t="str">
         <v>[]</v>
@@ -23905,7 +24448,7 @@
         <v>2026-08-02T10:48:10.527Z</v>
       </c>
       <c r="R20" t="str">
-        <v>2026-08-04T08:17:43.785Z</v>
+        <v>2026-08-04T08:53:47.354Z</v>
       </c>
       <c r="S20" t="str">
         <v>[]</v>
@@ -23973,7 +24516,7 @@
         <v>2026-07-24T17:12:35.802Z</v>
       </c>
       <c r="R21" t="str">
-        <v>2026-08-04T08:17:43.785Z</v>
+        <v>2026-08-04T08:53:47.354Z</v>
       </c>
     </row>
     <row r="22">
@@ -24029,7 +24572,7 @@
         <v>2026-07-28T17:26:06.217Z</v>
       </c>
       <c r="R22" t="str">
-        <v>2026-08-04T08:17:43.785Z</v>
+        <v>2026-08-04T08:53:47.354Z</v>
       </c>
       <c r="S22" t="str">
         <v>[]</v>
@@ -24104,7 +24647,7 @@
         <v>2026-07-28T17:46:53.114Z</v>
       </c>
       <c r="R23" t="str">
-        <v>2026-08-04T08:17:43.786Z</v>
+        <v>2026-08-04T08:53:47.355Z</v>
       </c>
       <c r="S23" t="str">
         <v>[]</v>
@@ -24172,7 +24715,7 @@
         <v>2026-07-24T17:18:21.488Z</v>
       </c>
       <c r="R24" t="str">
-        <v>2026-08-04T08:17:43.786Z</v>
+        <v>2026-08-04T08:53:47.355Z</v>
       </c>
     </row>
     <row r="25">
@@ -24228,7 +24771,7 @@
         <v>2026-07-28T17:36:56.657Z</v>
       </c>
       <c r="R25" t="str">
-        <v>2026-08-04T08:17:43.787Z</v>
+        <v>2026-08-04T08:53:47.355Z</v>
       </c>
       <c r="S25" t="str">
         <v>[]</v>
@@ -24296,7 +24839,7 @@
         <v>2026-07-28T17:41:34.056Z</v>
       </c>
       <c r="R26" t="str">
-        <v>2026-08-04T08:17:43.787Z</v>
+        <v>2026-08-04T08:53:47.355Z</v>
       </c>
       <c r="S26" t="str">
         <v>[]</v>
@@ -24364,7 +24907,7 @@
         <v>2026-07-28T17:45:36.923Z</v>
       </c>
       <c r="R27" t="str">
-        <v>2026-08-04T08:17:43.787Z</v>
+        <v>2026-08-04T08:53:47.356Z</v>
       </c>
       <c r="S27" t="str">
         <v>[]</v>
@@ -24432,7 +24975,7 @@
         <v>2026-07-28T16:21:56.496Z</v>
       </c>
       <c r="R28" t="str">
-        <v>2026-08-04T08:17:43.787Z</v>
+        <v>2026-08-04T08:53:47.356Z</v>
       </c>
       <c r="S28" t="str">
         <v>[]</v>
@@ -24500,7 +25043,7 @@
         <v>2026-08-03T14:33:55.186Z</v>
       </c>
       <c r="R29" t="str">
-        <v>2026-08-04T08:17:43.787Z</v>
+        <v>2026-08-04T08:53:47.356Z</v>
       </c>
       <c r="S29" t="str">
         <v>[]</v>
@@ -24568,7 +25111,7 @@
         <v>2026-07-28T17:38:24.726Z</v>
       </c>
       <c r="R30" t="str">
-        <v>2026-08-04T08:17:43.788Z</v>
+        <v>2026-08-04T08:53:47.357Z</v>
       </c>
       <c r="S30" t="str">
         <v>[]</v>
@@ -24636,7 +25179,7 @@
         <v>2026-07-24T17:26:49.450Z</v>
       </c>
       <c r="R31" t="str">
-        <v>2026-08-04T08:17:43.788Z</v>
+        <v>2026-08-04T08:53:47.357Z</v>
       </c>
     </row>
     <row r="32">
@@ -24692,7 +25235,7 @@
         <v>2026-07-24T17:27:41.339Z</v>
       </c>
       <c r="R32" t="str">
-        <v>2026-08-04T08:17:43.789Z</v>
+        <v>2026-08-04T08:53:47.357Z</v>
       </c>
     </row>
     <row r="33">
@@ -24748,7 +25291,7 @@
         <v>2026-07-28T17:39:19.058Z</v>
       </c>
       <c r="R33" t="str">
-        <v>2026-08-04T08:17:43.790Z</v>
+        <v>2026-08-04T08:53:47.357Z</v>
       </c>
       <c r="S33" t="str">
         <v>[]</v>
@@ -24816,7 +25359,7 @@
         <v>2026-07-24T17:30:20.928Z</v>
       </c>
       <c r="R34" t="str">
-        <v>2026-08-04T08:17:43.790Z</v>
+        <v>2026-08-04T08:53:47.358Z</v>
       </c>
     </row>
     <row r="35">
@@ -24872,7 +25415,7 @@
         <v>2026-07-28T17:36:25.555Z</v>
       </c>
       <c r="R35" t="str">
-        <v>2026-08-04T08:17:43.790Z</v>
+        <v>2026-08-04T08:53:47.358Z</v>
       </c>
       <c r="S35" t="str">
         <v>[]</v>
@@ -24940,7 +25483,7 @@
         <v>2026-07-28T17:28:41.534Z</v>
       </c>
       <c r="R36" t="str">
-        <v>2026-08-04T08:17:43.791Z</v>
+        <v>2026-08-04T08:53:47.358Z</v>
       </c>
       <c r="S36" t="str">
         <v>[]</v>
@@ -25008,7 +25551,7 @@
         <v>2026-07-28T16:23:07.254Z</v>
       </c>
       <c r="R37" t="str">
-        <v>2026-08-04T08:17:43.793Z</v>
+        <v>2026-08-04T08:53:47.359Z</v>
       </c>
       <c r="S37" t="str">
         <v>[]</v>
@@ -25076,7 +25619,7 @@
         <v>2026-07-28T17:22:37.075Z</v>
       </c>
       <c r="R38" t="str">
-        <v>2026-08-04T08:17:43.793Z</v>
+        <v>2026-08-04T08:53:47.359Z</v>
       </c>
       <c r="S38" t="str">
         <v>[]</v>
@@ -25144,7 +25687,7 @@
         <v>2026-07-24T17:34:48.053Z</v>
       </c>
       <c r="R39" t="str">
-        <v>2026-08-04T08:17:43.793Z</v>
+        <v>2026-08-04T08:53:47.359Z</v>
       </c>
     </row>
     <row r="40">
@@ -25200,7 +25743,7 @@
         <v>2026-08-03T14:31:25.470Z</v>
       </c>
       <c r="R40" t="str">
-        <v>2026-08-04T08:17:43.793Z</v>
+        <v>2026-08-04T08:53:47.359Z</v>
       </c>
       <c r="S40" t="str">
         <v>[]</v>
@@ -25268,7 +25811,7 @@
         <v>2026-08-03T14:32:38.702Z</v>
       </c>
       <c r="R41" t="str">
-        <v>2026-08-04T08:17:43.793Z</v>
+        <v>2026-08-04T08:53:47.359Z</v>
       </c>
       <c r="S41" t="str">
         <v>[]</v>
@@ -25336,7 +25879,7 @@
         <v>2026-07-24T17:37:33.123Z</v>
       </c>
       <c r="R42" t="str">
-        <v>2026-08-04T08:17:43.794Z</v>
+        <v>2026-08-04T08:53:47.360Z</v>
       </c>
     </row>
     <row r="43">
@@ -25392,7 +25935,7 @@
         <v>2026-07-24T17:38:22.625Z</v>
       </c>
       <c r="R43" t="str">
-        <v>2026-08-04T08:17:43.794Z</v>
+        <v>2026-08-04T08:53:47.360Z</v>
       </c>
     </row>
     <row r="44">
@@ -25448,7 +25991,7 @@
         <v>2026-08-03T14:28:11.191Z</v>
       </c>
       <c r="R44" t="str">
-        <v>2026-08-04T08:17:43.794Z</v>
+        <v>2026-08-04T08:53:47.360Z</v>
       </c>
       <c r="S44" t="str">
         <v>[]</v>
@@ -25516,7 +26059,7 @@
         <v>2026-07-24T17:40:00.365Z</v>
       </c>
       <c r="R45" t="str">
-        <v>2026-08-04T08:17:43.794Z</v>
+        <v>2026-08-04T08:53:47.360Z</v>
       </c>
     </row>
     <row r="46">
@@ -25572,7 +26115,7 @@
         <v>2026-07-28T16:16:46.824Z</v>
       </c>
       <c r="R46" t="str">
-        <v>2026-08-04T08:17:43.794Z</v>
+        <v>2026-08-04T08:53:47.361Z</v>
       </c>
       <c r="S46" t="str">
         <v>[]</v>
@@ -25640,7 +26183,7 @@
         <v>2026-07-24T17:41:27.886Z</v>
       </c>
       <c r="R47" t="str">
-        <v>2026-08-04T08:17:43.795Z</v>
+        <v>2026-08-04T08:53:47.361Z</v>
       </c>
     </row>
     <row r="48">
@@ -25696,7 +26239,7 @@
         <v>2026-07-24T17:42:36.169Z</v>
       </c>
       <c r="R48" t="str">
-        <v>2026-08-04T08:17:43.795Z</v>
+        <v>2026-08-04T08:53:47.361Z</v>
       </c>
     </row>
     <row r="49">
@@ -25752,7 +26295,7 @@
         <v>2026-07-28T17:45:07.109Z</v>
       </c>
       <c r="R49" t="str">
-        <v>2026-08-04T08:17:43.795Z</v>
+        <v>2026-08-04T08:53:47.362Z</v>
       </c>
       <c r="S49" t="str">
         <v>[]</v>
@@ -25820,7 +26363,7 @@
         <v>2026-07-28T16:27:55.642Z</v>
       </c>
       <c r="R50" t="str">
-        <v>2026-08-04T08:17:43.795Z</v>
+        <v>2026-08-04T08:53:47.362Z</v>
       </c>
       <c r="S50" t="str">
         <v>[]</v>
@@ -25888,7 +26431,7 @@
         <v>2026-07-28T16:36:51.938Z</v>
       </c>
       <c r="R51" t="str">
-        <v>2026-08-04T08:17:43.796Z</v>
+        <v>2026-08-04T08:53:47.362Z</v>
       </c>
       <c r="S51" t="str">
         <v>[]</v>
@@ -25956,7 +26499,7 @@
         <v>2026-07-24T17:45:28.097Z</v>
       </c>
       <c r="R52" t="str">
-        <v>2026-08-04T08:17:43.796Z</v>
+        <v>2026-08-04T08:53:47.363Z</v>
       </c>
     </row>
     <row r="53">
@@ -26012,7 +26555,7 @@
         <v>2026-07-28T17:27:31.311Z</v>
       </c>
       <c r="R53" t="str">
-        <v>2026-08-04T08:17:43.796Z</v>
+        <v>2026-08-04T08:53:47.363Z</v>
       </c>
       <c r="S53" t="str">
         <v>[]</v>
@@ -26080,7 +26623,7 @@
         <v>2026-08-03T14:19:54.310Z</v>
       </c>
       <c r="R54" t="str">
-        <v>2026-08-04T08:17:43.796Z</v>
+        <v>2026-08-04T08:53:47.363Z</v>
       </c>
       <c r="S54" t="str">
         <v>[]</v>
@@ -26148,7 +26691,7 @@
         <v>2026-07-24T17:48:00.294Z</v>
       </c>
       <c r="R55" t="str">
-        <v>2026-08-04T08:17:43.796Z</v>
+        <v>2026-08-04T08:53:47.363Z</v>
       </c>
     </row>
     <row r="56">
@@ -26204,7 +26747,7 @@
         <v>2026-07-28T17:40:11.014Z</v>
       </c>
       <c r="R56" t="str">
-        <v>2026-08-04T08:17:43.797Z</v>
+        <v>2026-08-04T08:53:47.364Z</v>
       </c>
       <c r="S56" t="str">
         <v>[]</v>
@@ -26272,7 +26815,7 @@
         <v>2026-07-24T17:54:52.356Z</v>
       </c>
       <c r="R57" t="str">
-        <v>2026-08-04T08:17:43.797Z</v>
+        <v>2026-08-04T08:53:47.364Z</v>
       </c>
     </row>
     <row r="58">
@@ -26328,7 +26871,7 @@
         <v>2026-07-24T17:56:05.755Z</v>
       </c>
       <c r="R58" t="str">
-        <v>2026-08-04T08:17:43.797Z</v>
+        <v>2026-08-04T08:53:47.365Z</v>
       </c>
     </row>
     <row r="59">
@@ -26384,7 +26927,7 @@
         <v>2026-07-28T17:47:53.747Z</v>
       </c>
       <c r="R59" t="str">
-        <v>2026-08-04T08:17:43.797Z</v>
+        <v>2026-08-04T08:53:47.365Z</v>
       </c>
       <c r="S59" t="str">
         <v>[]</v>
@@ -26452,7 +26995,7 @@
         <v>2026-07-28T16:12:36.281Z</v>
       </c>
       <c r="R60" t="str">
-        <v>2026-08-04T08:17:43.798Z</v>
+        <v>2026-08-04T08:53:47.366Z</v>
       </c>
       <c r="S60" t="str">
         <v>[{"weight":"0.5kg","price":560,"_id":"6a68d4f432f685de96f72a57"}]</v>
@@ -26520,7 +27063,7 @@
         <v>2026-07-24T18:00:08.054Z</v>
       </c>
       <c r="R61" t="str">
-        <v>2026-08-04T08:17:43.798Z</v>
+        <v>2026-08-04T08:53:47.366Z</v>
       </c>
     </row>
     <row r="62">
@@ -26576,7 +27119,7 @@
         <v>2026-07-28T17:41:55.851Z</v>
       </c>
       <c r="R62" t="str">
-        <v>2026-08-04T08:17:43.798Z</v>
+        <v>2026-08-04T08:53:47.366Z</v>
       </c>
       <c r="S62" t="str">
         <v>[]</v>
@@ -26644,7 +27187,7 @@
         <v>2026-07-24T18:06:05.196Z</v>
       </c>
       <c r="R63" t="str">
-        <v>2026-08-04T08:17:43.798Z</v>
+        <v>2026-08-04T08:53:47.366Z</v>
       </c>
     </row>
     <row r="64">
@@ -26700,7 +27243,7 @@
         <v>2026-07-28T17:40:57.835Z</v>
       </c>
       <c r="R64" t="str">
-        <v>2026-08-04T08:17:43.798Z</v>
+        <v>2026-08-04T08:53:47.366Z</v>
       </c>
       <c r="S64" t="str">
         <v>[]</v>
@@ -26768,7 +27311,7 @@
         <v>2026-07-28T17:48:30.756Z</v>
       </c>
       <c r="R65" t="str">
-        <v>2026-08-04T08:17:43.799Z</v>
+        <v>2026-08-04T08:53:47.367Z</v>
       </c>
       <c r="S65" t="str">
         <v>[]</v>
@@ -26836,7 +27379,7 @@
         <v>2026-07-28T17:22:03.434Z</v>
       </c>
       <c r="R66" t="str">
-        <v>2026-08-04T08:17:43.799Z</v>
+        <v>2026-08-04T08:53:47.367Z</v>
       </c>
       <c r="S66" t="str">
         <v>[]</v>
@@ -26904,7 +27447,7 @@
         <v>2026-07-28T17:24:37.742Z</v>
       </c>
       <c r="R67" t="str">
-        <v>2026-08-04T08:17:43.799Z</v>
+        <v>2026-08-04T08:53:47.367Z</v>
       </c>
       <c r="S67" t="str">
         <v>[]</v>
@@ -26972,7 +27515,7 @@
         <v>2026-07-26T12:39:12.538Z</v>
       </c>
       <c r="R68" t="str">
-        <v>2026-08-04T08:17:43.800Z</v>
+        <v>2026-08-04T08:53:47.368Z</v>
       </c>
     </row>
     <row r="69">
@@ -27028,7 +27571,7 @@
         <v>2026-07-28T17:25:18.284Z</v>
       </c>
       <c r="R69" t="str">
-        <v>2026-08-04T08:17:43.800Z</v>
+        <v>2026-08-04T08:53:47.368Z</v>
       </c>
       <c r="S69" t="str">
         <v>[]</v>
@@ -27096,7 +27639,7 @@
         <v>2026-07-24T18:20:53.747Z</v>
       </c>
       <c r="R70" t="str">
-        <v>2026-08-04T08:17:43.800Z</v>
+        <v>2026-08-04T08:53:47.368Z</v>
       </c>
     </row>
     <row r="71">
@@ -27152,7 +27695,7 @@
         <v>2026-07-24T18:22:21.034Z</v>
       </c>
       <c r="R71" t="str">
-        <v>2026-08-04T08:17:43.800Z</v>
+        <v>2026-08-04T08:53:47.368Z</v>
       </c>
     </row>
     <row r="72">
@@ -27208,7 +27751,7 @@
         <v>2026-07-24T18:25:36.466Z</v>
       </c>
       <c r="R72" t="str">
-        <v>2026-08-04T08:17:43.801Z</v>
+        <v>2026-08-04T08:53:47.369Z</v>
       </c>
     </row>
     <row r="73">
@@ -27264,7 +27807,7 @@
         <v>2026-07-24T18:26:40.938Z</v>
       </c>
       <c r="R73" t="str">
-        <v>2026-08-04T08:17:43.801Z</v>
+        <v>2026-08-04T08:53:47.369Z</v>
       </c>
     </row>
     <row r="74">
@@ -27320,7 +27863,7 @@
         <v>2026-07-26T12:47:01.249Z</v>
       </c>
       <c r="R74" t="str">
-        <v>2026-08-04T08:17:43.801Z</v>
+        <v>2026-08-04T08:53:47.370Z</v>
       </c>
     </row>
     <row r="75">
@@ -27376,7 +27919,7 @@
         <v>2026-07-26T12:37:09.891Z</v>
       </c>
       <c r="R75" t="str">
-        <v>2026-08-04T08:17:43.801Z</v>
+        <v>2026-08-04T08:53:47.370Z</v>
       </c>
     </row>
     <row r="76">
@@ -27432,7 +27975,7 @@
         <v>2026-07-26T13:20:31.760Z</v>
       </c>
       <c r="R76" t="str">
-        <v>2026-08-04T08:17:43.802Z</v>
+        <v>2026-08-04T08:53:47.371Z</v>
       </c>
     </row>
     <row r="77">
@@ -27488,7 +28031,7 @@
         <v>2026-07-28T16:03:01.985Z</v>
       </c>
       <c r="R77" t="str">
-        <v>2026-08-04T08:17:43.802Z</v>
+        <v>2026-08-04T08:53:47.371Z</v>
       </c>
       <c r="S77" t="str">
         <v>[]</v>
@@ -27556,7 +28099,7 @@
         <v>2026-07-28T17:42:26.187Z</v>
       </c>
       <c r="R78" t="str">
-        <v>2026-08-04T08:17:43.802Z</v>
+        <v>2026-08-04T08:53:47.371Z</v>
       </c>
       <c r="S78" t="str">
         <v>[]</v>
@@ -27624,7 +28167,7 @@
         <v>2026-07-28T17:47:34.157Z</v>
       </c>
       <c r="R79" t="str">
-        <v>2026-08-04T08:17:43.802Z</v>
+        <v>2026-08-04T08:53:47.372Z</v>
       </c>
       <c r="S79" t="str">
         <v>[]</v>
@@ -27692,7 +28235,7 @@
         <v>2026-07-28T17:47:12.892Z</v>
       </c>
       <c r="R80" t="str">
-        <v>2026-08-04T08:17:43.802Z</v>
+        <v>2026-08-04T08:53:47.372Z</v>
       </c>
       <c r="S80" t="str">
         <v>[]</v>
@@ -27760,7 +28303,7 @@
         <v>2026-07-27T17:12:53.242Z</v>
       </c>
       <c r="R81" t="str">
-        <v>2026-08-04T08:17:43.803Z</v>
+        <v>2026-08-04T08:53:47.372Z</v>
       </c>
     </row>
     <row r="82">
@@ -27816,7 +28359,7 @@
         <v>2026-07-27T17:14:28.622Z</v>
       </c>
       <c r="R82" t="str">
-        <v>2026-08-04T08:17:43.803Z</v>
+        <v>2026-08-04T08:53:47.373Z</v>
       </c>
     </row>
     <row r="83">
@@ -27872,7 +28415,7 @@
         <v>2026-07-28T17:40:34.872Z</v>
       </c>
       <c r="R83" t="str">
-        <v>2026-08-04T08:17:43.803Z</v>
+        <v>2026-08-04T08:53:47.374Z</v>
       </c>
       <c r="S83" t="str">
         <v>[]</v>
@@ -27940,7 +28483,7 @@
         <v>2026-07-28T17:30:47.490Z</v>
       </c>
       <c r="R84" t="str">
-        <v>2026-08-04T08:17:43.803Z</v>
+        <v>2026-08-04T08:53:47.374Z</v>
       </c>
       <c r="S84" t="str">
         <v>[]</v>
@@ -28008,7 +28551,7 @@
         <v>2026-07-28T17:23:22.756Z</v>
       </c>
       <c r="R85" t="str">
-        <v>2026-08-04T08:17:43.804Z</v>
+        <v>2026-08-04T08:53:47.374Z</v>
       </c>
       <c r="S85" t="str">
         <v>[]</v>
@@ -28076,7 +28619,7 @@
         <v>2026-07-27T17:23:24.773Z</v>
       </c>
       <c r="R86" t="str">
-        <v>2026-08-04T08:17:43.805Z</v>
+        <v>2026-08-04T08:53:47.375Z</v>
       </c>
     </row>
     <row r="87">
@@ -28132,7 +28675,7 @@
         <v>2026-07-28T17:59:21.885Z</v>
       </c>
       <c r="R87" t="str">
-        <v>2026-08-04T08:17:43.806Z</v>
+        <v>2026-08-04T08:53:47.376Z</v>
       </c>
       <c r="S87" t="str">
         <v>[]</v>
@@ -28200,7 +28743,7 @@
         <v>2026-07-28T18:44:44.782Z</v>
       </c>
       <c r="R88" t="str">
-        <v>2026-08-04T08:17:43.806Z</v>
+        <v>2026-08-04T08:53:47.376Z</v>
       </c>
       <c r="S88" t="str">
         <v>[]</v>
@@ -28268,7 +28811,7 @@
         <v>2026-07-28T18:48:28.617Z</v>
       </c>
       <c r="R89" t="str">
-        <v>2026-08-04T08:17:43.806Z</v>
+        <v>2026-08-04T08:53:47.377Z</v>
       </c>
       <c r="S89" t="str">
         <v>[]</v>
@@ -28336,7 +28879,7 @@
         <v>2026-08-02T06:43:12.026Z</v>
       </c>
       <c r="R90" t="str">
-        <v>2026-08-04T08:17:43.806Z</v>
+        <v>2026-08-04T08:53:47.377Z</v>
       </c>
       <c r="S90" t="str">
         <v>[]</v>
@@ -28404,7 +28947,7 @@
         <v>2026-08-03T14:38:34.425Z</v>
       </c>
       <c r="R91" t="str">
-        <v>2026-08-04T08:17:43.807Z</v>
+        <v>2026-08-04T08:53:47.377Z</v>
       </c>
       <c r="S91" t="str">
         <v>[]</v>
@@ -28482,7 +29025,7 @@
         <v>2026-07-21T13:19:06.517Z</v>
       </c>
       <c r="G2" t="str">
-        <v>2026-08-04T08:17:43.947Z</v>
+        <v>2026-08-04T08:53:47.475Z</v>
       </c>
     </row>
     <row r="3">
@@ -28505,7 +29048,7 @@
         <v>2026-07-21T13:19:28.352Z</v>
       </c>
       <c r="G3" t="str">
-        <v>2026-08-04T08:17:43.947Z</v>
+        <v>2026-08-04T08:53:47.475Z</v>
       </c>
     </row>
     <row r="4">
@@ -28528,7 +29071,7 @@
         <v>2026-07-21T13:19:53.589Z</v>
       </c>
       <c r="G4" t="str">
-        <v>2026-08-04T08:17:43.947Z</v>
+        <v>2026-08-04T08:53:47.475Z</v>
       </c>
     </row>
     <row r="5">
@@ -28551,7 +29094,7 @@
         <v>2026-07-21T13:20:07.470Z</v>
       </c>
       <c r="G5" t="str">
-        <v>2026-08-04T08:17:43.947Z</v>
+        <v>2026-08-04T08:53:47.475Z</v>
       </c>
     </row>
     <row r="6">
@@ -28574,7 +29117,7 @@
         <v>2026-07-21T14:33:48.138Z</v>
       </c>
       <c r="G6" t="str">
-        <v>2026-08-04T08:17:43.947Z</v>
+        <v>2026-08-04T08:53:47.475Z</v>
       </c>
     </row>
     <row r="7">
@@ -28597,7 +29140,7 @@
         <v>2026-07-21T16:49:35.554Z</v>
       </c>
       <c r="G7" t="str">
-        <v>2026-08-04T08:17:43.947Z</v>
+        <v>2026-08-04T08:53:47.475Z</v>
       </c>
     </row>
     <row r="8">
@@ -28620,7 +29163,7 @@
         <v>2026-07-21T18:31:41.689Z</v>
       </c>
       <c r="G8" t="str">
-        <v>2026-08-04T08:17:43.947Z</v>
+        <v>2026-08-04T08:53:47.475Z</v>
       </c>
     </row>
     <row r="9">
@@ -28643,7 +29186,7 @@
         <v>2026-07-21T18:34:21.514Z</v>
       </c>
       <c r="G9" t="str">
-        <v>2026-08-04T08:17:43.947Z</v>
+        <v>2026-08-04T08:53:47.475Z</v>
       </c>
     </row>
   </sheetData>
@@ -28733,7 +29276,7 @@
         <v>2026-06-05T13:08:47.090Z</v>
       </c>
       <c r="I2" t="str">
-        <v>2026-08-04T08:17:44.232Z</v>
+        <v>2026-08-04T08:53:47.714Z</v>
       </c>
     </row>
     <row r="3">
@@ -28762,7 +29305,7 @@
         <v>2026-06-05T13:08:47.090Z</v>
       </c>
       <c r="I3" t="str">
-        <v>2026-08-04T08:17:44.232Z</v>
+        <v>2026-08-04T08:53:47.714Z</v>
       </c>
     </row>
     <row r="4">
@@ -28791,7 +29334,7 @@
         <v>2026-06-05T13:08:47.090Z</v>
       </c>
       <c r="I4" t="str">
-        <v>2026-08-04T08:17:44.232Z</v>
+        <v>2026-08-04T08:53:47.714Z</v>
       </c>
     </row>
     <row r="5">
@@ -28820,7 +29363,7 @@
         <v>2026-06-05T13:08:47.090Z</v>
       </c>
       <c r="I5" t="str">
-        <v>2026-08-04T08:17:44.232Z</v>
+        <v>2026-08-04T08:53:47.714Z</v>
       </c>
     </row>
     <row r="6">
@@ -28849,7 +29392,7 @@
         <v>2026-06-05T13:08:47.090Z</v>
       </c>
       <c r="I6" t="str">
-        <v>2026-08-04T08:17:44.232Z</v>
+        <v>2026-08-04T08:53:47.714Z</v>
       </c>
     </row>
     <row r="7">
@@ -28878,7 +29421,7 @@
         <v>2026-06-05T13:08:47.088Z</v>
       </c>
       <c r="I7" t="str">
-        <v>2026-08-04T08:17:44.232Z</v>
+        <v>2026-08-04T08:53:47.714Z</v>
       </c>
     </row>
     <row r="8">
@@ -28907,7 +29450,7 @@
         <v>2026-06-05T13:08:47.090Z</v>
       </c>
       <c r="I8" t="str">
-        <v>2026-08-04T08:17:44.232Z</v>
+        <v>2026-08-04T08:53:47.714Z</v>
       </c>
     </row>
     <row r="9">
@@ -28936,7 +29479,7 @@
         <v>2026-06-05T13:08:47.090Z</v>
       </c>
       <c r="I9" t="str">
-        <v>2026-08-04T08:17:44.232Z</v>
+        <v>2026-08-04T08:53:47.714Z</v>
       </c>
     </row>
     <row r="10">
@@ -28965,7 +29508,7 @@
         <v>2026-06-05T13:08:47.087Z</v>
       </c>
       <c r="I10" t="str">
-        <v>2026-08-04T08:17:44.232Z</v>
+        <v>2026-08-04T08:53:47.714Z</v>
       </c>
     </row>
     <row r="11">
@@ -28994,7 +29537,7 @@
         <v>2026-06-05T13:08:47.087Z</v>
       </c>
       <c r="I11" t="str">
-        <v>2026-08-04T08:17:44.232Z</v>
+        <v>2026-08-04T08:53:47.714Z</v>
       </c>
     </row>
     <row r="12">
@@ -29023,7 +29566,7 @@
         <v>2026-06-05T13:08:47.091Z</v>
       </c>
       <c r="I12" t="str">
-        <v>2026-08-04T08:17:44.232Z</v>
+        <v>2026-08-04T08:53:47.714Z</v>
       </c>
     </row>
     <row r="13">
@@ -29052,7 +29595,7 @@
         <v>2026-06-05T13:08:47.090Z</v>
       </c>
       <c r="I13" t="str">
-        <v>2026-08-04T08:17:44.232Z</v>
+        <v>2026-08-04T08:53:47.714Z</v>
       </c>
     </row>
     <row r="14">
@@ -29081,7 +29624,7 @@
         <v>2026-06-05T13:08:47.089Z</v>
       </c>
       <c r="I14" t="str">
-        <v>2026-08-04T08:17:44.232Z</v>
+        <v>2026-08-04T08:53:47.714Z</v>
       </c>
     </row>
     <row r="15">
@@ -29110,7 +29653,7 @@
         <v>2026-06-05T13:08:47.089Z</v>
       </c>
       <c r="I15" t="str">
-        <v>2026-08-04T08:17:44.232Z</v>
+        <v>2026-08-04T08:53:47.714Z</v>
       </c>
     </row>
     <row r="16">
@@ -29139,7 +29682,7 @@
         <v>2026-06-05T13:08:47.090Z</v>
       </c>
       <c r="I16" t="str">
-        <v>2026-08-04T08:17:44.232Z</v>
+        <v>2026-08-04T08:53:47.714Z</v>
       </c>
     </row>
     <row r="17">
@@ -29168,7 +29711,7 @@
         <v>2026-06-05T13:08:47.090Z</v>
       </c>
       <c r="I17" t="str">
-        <v>2026-08-04T08:17:44.232Z</v>
+        <v>2026-08-04T08:53:47.714Z</v>
       </c>
     </row>
     <row r="18">
@@ -29197,7 +29740,7 @@
         <v>2026-06-05T13:08:47.084Z</v>
       </c>
       <c r="I18" t="str">
-        <v>2026-08-04T08:17:44.232Z</v>
+        <v>2026-08-04T08:53:47.714Z</v>
       </c>
     </row>
     <row r="19">
@@ -29226,7 +29769,7 @@
         <v>2026-06-05T13:08:47.088Z</v>
       </c>
       <c r="I19" t="str">
-        <v>2026-08-04T08:17:44.232Z</v>
+        <v>2026-08-04T08:53:47.714Z</v>
       </c>
     </row>
     <row r="20">
@@ -29255,7 +29798,7 @@
         <v>2026-06-05T13:08:47.088Z</v>
       </c>
       <c r="I20" t="str">
-        <v>2026-08-04T08:17:44.232Z</v>
+        <v>2026-08-04T08:53:47.714Z</v>
       </c>
     </row>
     <row r="21">
@@ -29284,7 +29827,7 @@
         <v>2026-06-05T13:08:47.090Z</v>
       </c>
       <c r="I21" t="str">
-        <v>2026-08-04T08:17:44.232Z</v>
+        <v>2026-08-04T08:53:47.714Z</v>
       </c>
     </row>
     <row r="22">
@@ -29313,7 +29856,7 @@
         <v>2026-06-05T13:08:47.088Z</v>
       </c>
       <c r="I22" t="str">
-        <v>2026-08-04T08:17:44.232Z</v>
+        <v>2026-08-04T08:53:47.714Z</v>
       </c>
     </row>
     <row r="23">
@@ -29342,7 +29885,7 @@
         <v>2026-06-05T13:08:47.089Z</v>
       </c>
       <c r="I23" t="str">
-        <v>2026-08-04T08:17:44.232Z</v>
+        <v>2026-08-04T08:53:47.714Z</v>
       </c>
     </row>
     <row r="24">
@@ -29371,7 +29914,7 @@
         <v>2026-06-05T13:08:47.089Z</v>
       </c>
       <c r="I24" t="str">
-        <v>2026-08-04T08:17:44.232Z</v>
+        <v>2026-08-04T08:53:47.714Z</v>
       </c>
     </row>
     <row r="25">
@@ -29400,7 +29943,7 @@
         <v>2026-06-27T07:29:40.036Z</v>
       </c>
       <c r="I25" t="str">
-        <v>2026-08-04T08:17:44.232Z</v>
+        <v>2026-08-04T08:53:47.714Z</v>
       </c>
     </row>
     <row r="26">
@@ -29429,7 +29972,7 @@
         <v>2026-06-05T13:08:47.089Z</v>
       </c>
       <c r="I26" t="str">
-        <v>2026-08-04T08:17:44.232Z</v>
+        <v>2026-08-04T08:53:47.714Z</v>
       </c>
     </row>
     <row r="27">
@@ -29458,7 +30001,7 @@
         <v>2026-06-05T13:08:47.090Z</v>
       </c>
       <c r="I27" t="str">
-        <v>2026-08-04T08:17:44.232Z</v>
+        <v>2026-08-04T08:53:47.714Z</v>
       </c>
     </row>
     <row r="28">
@@ -29487,7 +30030,7 @@
         <v>2026-06-05T13:08:47.090Z</v>
       </c>
       <c r="I28" t="str">
-        <v>2026-08-04T08:17:44.232Z</v>
+        <v>2026-08-04T08:53:47.714Z</v>
       </c>
     </row>
     <row r="29">
@@ -29516,7 +30059,7 @@
         <v>2026-06-05T13:08:47.089Z</v>
       </c>
       <c r="I29" t="str">
-        <v>2026-08-04T08:17:44.232Z</v>
+        <v>2026-08-04T08:53:47.714Z</v>
       </c>
     </row>
     <row r="30">
@@ -29545,7 +30088,7 @@
         <v>2026-06-05T13:08:47.089Z</v>
       </c>
       <c r="I30" t="str">
-        <v>2026-08-04T08:17:44.232Z</v>
+        <v>2026-08-04T08:53:47.714Z</v>
       </c>
     </row>
     <row r="31">
@@ -29574,7 +30117,7 @@
         <v>2026-06-05T13:08:47.089Z</v>
       </c>
       <c r="I31" t="str">
-        <v>2026-08-04T08:17:44.232Z</v>
+        <v>2026-08-04T08:53:47.714Z</v>
       </c>
     </row>
     <row r="32">
@@ -29603,7 +30146,7 @@
         <v>2026-06-05T13:08:47.089Z</v>
       </c>
       <c r="I32" t="str">
-        <v>2026-08-04T08:17:44.233Z</v>
+        <v>2026-08-04T08:53:47.714Z</v>
       </c>
     </row>
     <row r="33">
@@ -29632,7 +30175,7 @@
         <v>2026-06-05T13:08:47.089Z</v>
       </c>
       <c r="I33" t="str">
-        <v>2026-08-04T08:17:44.233Z</v>
+        <v>2026-08-04T08:53:47.714Z</v>
       </c>
     </row>
     <row r="34">
@@ -29661,7 +30204,7 @@
         <v>2026-06-05T13:08:47.089Z</v>
       </c>
       <c r="I34" t="str">
-        <v>2026-08-04T08:17:44.233Z</v>
+        <v>2026-08-04T08:53:47.714Z</v>
       </c>
     </row>
     <row r="35">
@@ -29690,7 +30233,7 @@
         <v>2026-06-05T13:08:47.089Z</v>
       </c>
       <c r="I35" t="str">
-        <v>2026-08-04T08:17:44.233Z</v>
+        <v>2026-08-04T08:53:47.714Z</v>
       </c>
     </row>
     <row r="36">
@@ -29719,7 +30262,7 @@
         <v>2026-06-05T13:08:47.090Z</v>
       </c>
       <c r="I36" t="str">
-        <v>2026-08-04T08:17:44.233Z</v>
+        <v>2026-08-04T08:53:47.714Z</v>
       </c>
     </row>
     <row r="37">
@@ -29748,7 +30291,7 @@
         <v>2026-06-05T13:08:47.091Z</v>
       </c>
       <c r="I37" t="str">
-        <v>2026-08-04T08:17:44.233Z</v>
+        <v>2026-08-04T08:53:47.714Z</v>
       </c>
     </row>
     <row r="38">
@@ -29777,7 +30320,7 @@
         <v>2026-06-05T13:08:47.088Z</v>
       </c>
       <c r="I38" t="str">
-        <v>2026-08-04T08:17:44.233Z</v>
+        <v>2026-08-04T08:53:47.714Z</v>
       </c>
     </row>
   </sheetData>
@@ -29885,7 +30428,7 @@
         <v>ordinary</v>
       </c>
       <c r="M2" t="str">
-        <v>2026-08-04T08:17:44.357Z</v>
+        <v>2026-08-04T08:53:47.871Z</v>
       </c>
     </row>
     <row r="3">
@@ -29926,7 +30469,7 @@
         <v>custom</v>
       </c>
       <c r="M3" t="str">
-        <v>2026-08-04T08:17:44.357Z</v>
+        <v>2026-08-04T08:53:47.871Z</v>
       </c>
     </row>
     <row r="4">
@@ -29967,7 +30510,7 @@
         <v>ordinary</v>
       </c>
       <c r="M4" t="str">
-        <v>2026-08-04T08:17:44.357Z</v>
+        <v>2026-08-04T08:53:47.871Z</v>
       </c>
     </row>
     <row r="5">
@@ -30002,7 +30545,7 @@
         <v>ordinary</v>
       </c>
       <c r="M5" t="str">
-        <v>2026-08-04T08:17:44.357Z</v>
+        <v>2026-08-04T08:53:47.871Z</v>
       </c>
     </row>
     <row r="6">
@@ -30037,7 +30580,7 @@
         <v>ordinary</v>
       </c>
       <c r="M6" t="str">
-        <v>2026-08-04T08:17:44.357Z</v>
+        <v>2026-08-04T08:53:47.871Z</v>
       </c>
     </row>
     <row r="7">
@@ -30072,7 +30615,7 @@
         <v>ordinary</v>
       </c>
       <c r="M7" t="str">
-        <v>2026-08-04T08:17:44.357Z</v>
+        <v>2026-08-04T08:53:47.871Z</v>
       </c>
     </row>
     <row r="8">
@@ -30107,7 +30650,7 @@
         <v>custom</v>
       </c>
       <c r="M8" t="str">
-        <v>2026-08-04T08:17:44.357Z</v>
+        <v>2026-08-04T08:53:47.871Z</v>
       </c>
     </row>
     <row r="9">
@@ -30142,7 +30685,7 @@
         <v>ordinary</v>
       </c>
       <c r="M9" t="str">
-        <v>2026-08-04T08:17:44.357Z</v>
+        <v>2026-08-04T08:53:47.871Z</v>
       </c>
     </row>
   </sheetData>
@@ -30236,7 +30779,7 @@
         <v>2026-07-28T18:42:43.600Z</v>
       </c>
       <c r="K2" t="str">
-        <v>2026-08-04T08:17:44.467Z</v>
+        <v>2026-08-04T08:53:47.963Z</v>
       </c>
     </row>
     <row r="3">
@@ -30271,7 +30814,7 @@
         <v>2026-07-28T14:48:54.403Z</v>
       </c>
       <c r="K3" t="str">
-        <v>2026-08-04T08:17:44.467Z</v>
+        <v>2026-08-04T08:53:47.963Z</v>
       </c>
     </row>
     <row r="4">
@@ -30306,7 +30849,7 @@
         <v>2026-07-28T18:14:52.960Z</v>
       </c>
       <c r="K4" t="str">
-        <v>2026-08-04T08:17:44.467Z</v>
+        <v>2026-08-04T08:53:47.963Z</v>
       </c>
     </row>
   </sheetData>
